--- a/STX.xlsx
+++ b/STX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE130CE3-2162-A34B-95C2-02FFF4F75609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11CE31E-7B69-3146-9057-8C31C1AA9099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,28 +148,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -179,21 +158,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2430,9 +2400,7 @@
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2442,6 +2410,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2449,12 +2426,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2484,7 +2455,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12651,7 +12621,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12669,10 +12639,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1145</v>
-    <v>144.75</v>
-    <v>2.0870000000000002</v>
-    <v>-38.299999999999997</v>
-    <v>-4.4903000000000005E-2</v>
+    <v>175.815</v>
+    <v>2.0948000000000002</v>
+    <v>50.67</v>
+    <v>6.3448000000000004E-2</v>
+    <v>-0.15</v>
+    <v>-1.7659999999999998E-4</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12680,49 +12652,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>862.68</v>
+    <v>852.98</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46241.830135728909</v>
+    <v>46269.901031562498</v>
     <v>0</v>
-    <v>761.8</v>
-    <v>184635941925</v>
+    <v>805.01009999999997</v>
+    <v>192484640960</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>856.76</v>
-    <v>58.591500000000003</v>
-    <v>852.95</v>
-    <v>814.65</v>
+    <v>818.75</v>
+    <v>61.082099999999997</v>
+    <v>798.61</v>
+    <v>849.28</v>
+    <v>849.13</v>
     <v>226644500</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>5573053</v>
-    <v>5433694</v>
+    <v>2556498</v>
+    <v>4087698</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12734,30 +12692,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.47</v>
+    <v>48.06</v>
     <v>39.47</v>
-    <v>0.53</v>
-    <v>1.1479E-2</v>
+    <v>-0.34</v>
+    <v>-7.0889999999999998E-3</v>
     <v>US</v>
-    <v>46.76</v>
+    <v>47.68</v>
     <v>Index</v>
-    <v>6</v>
-    <v>46.35</v>
+    <v>3</v>
+    <v>47.32</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.43</v>
-    <v>46.17</v>
-    <v>46.7</v>
+    <v>47.66</v>
+    <v>47.96</v>
+    <v>47.62</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12779,6 +12737,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12799,6 +12759,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12808,11 +12769,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12848,7 +12804,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12859,13 +12815,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12959,13 +12918,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13037,6 +13002,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13044,6 +13012,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13560,7 +13531,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>193072.05</v>
+        <v>201279.35999999999</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13568,7 +13539,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>140.14474791151878</v>
+        <v>138.76356724687497</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13584,7 +13555,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>194933.05</v>
+        <v>203140.36</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13592,7 +13563,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>139.61067097160262</v>
+        <v>138.71605779137505</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13601,7 +13572,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13616,23 +13587,23 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>112.91154281588085</v>
+        <v>112.28454742641925</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>849.13</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>58.692363112391924</v>
+        <v>61.187319884726222</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13640,7 +13611,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>155.13973994429836</v>
+        <v>154.15567962861482</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13649,14 +13620,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-38.299999999999997</v>
+        <v>50.67</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>15.280950184501846</v>
+        <v>15.930528905289053</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13664,23 +13635,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>136.95167541082515</v>
+        <v>135.97996302332101</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.15</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>1.4978864107984559E-2</v>
+        <v>1.4368090200604772E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13688,7 +13659,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.83188893953130161</v>
+        <v>-0.83988794858783788</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13697,37 +13668,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-4.4903000000000005E-2</v>
+        <v>6.3448000000000004E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>1.7037991775609159E-2</v>
+        <v>1.6343255463451396E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-1.7659999999999998E-4</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>9.1157679218716546E-4</v>
+        <v>8.7440659588742739E-4</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>371</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>24.935538697508605</v>
+        <v>24.675516466206126</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13743,7 +13714,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>3.5843613821886699E-3</v>
+        <v>3.4382064807837228E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13752,7 +13723,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>144.75</v>
+        <v>175.815</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>101</v>
@@ -13768,7 +13739,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0870000000000002</v>
+        <v>2.0948000000000002</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>103</v>
@@ -13784,7 +13755,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5433694</v>
+        <v>4087698</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13800,7 +13771,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-9.6388886946608791E-3</v>
+        <v>-9.2458561076505814E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13905,12 +13876,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.7</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13925,7 +13896,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.6700000000000005E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13945,15 +13916,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="243" t="s">
+      <c r="B33" s="247" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
+      <c r="C33" s="247"/>
+      <c r="D33" s="247"/>
+      <c r="E33" s="247"/>
+      <c r="F33" s="247"/>
+      <c r="G33" s="247"/>
+      <c r="H33" s="247"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14039,24 +14010,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="243"/>
-      <c r="C49" s="243"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="243"/>
-      <c r="F49" s="243"/>
-      <c r="G49" s="243"/>
-      <c r="H49" s="243"/>
+      <c r="B49" s="247"/>
+      <c r="C49" s="247"/>
+      <c r="D49" s="247"/>
+      <c r="E49" s="247"/>
+      <c r="F49" s="247"/>
+      <c r="G49" s="247"/>
+      <c r="H49" s="247"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="243" t="s">
+      <c r="B52" s="247" t="s">
         <v>343</v>
       </c>
-      <c r="C52" s="243"/>
-      <c r="D52" s="243"/>
-      <c r="E52" s="243"/>
-      <c r="F52" s="243"/>
-      <c r="G52" s="243"/>
-      <c r="H52" s="243"/>
+      <c r="C52" s="247"/>
+      <c r="D52" s="247"/>
+      <c r="E52" s="247"/>
+      <c r="F52" s="247"/>
+      <c r="G52" s="247"/>
+      <c r="H52" s="247"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14139,24 +14110,24 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="243"/>
-      <c r="C65" s="243"/>
-      <c r="D65" s="243"/>
-      <c r="E65" s="243"/>
-      <c r="F65" s="243"/>
-      <c r="G65" s="243"/>
-      <c r="H65" s="243"/>
+      <c r="B65" s="247"/>
+      <c r="C65" s="247"/>
+      <c r="D65" s="247"/>
+      <c r="E65" s="247"/>
+      <c r="F65" s="247"/>
+      <c r="G65" s="247"/>
+      <c r="H65" s="247"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="243" t="s">
+      <c r="B68" s="247" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="243"/>
-      <c r="D68" s="243"/>
-      <c r="E68" s="243"/>
-      <c r="F68" s="243"/>
-      <c r="G68" s="243"/>
-      <c r="H68" s="243"/>
+      <c r="C68" s="247"/>
+      <c r="D68" s="247"/>
+      <c r="E68" s="247"/>
+      <c r="F68" s="247"/>
+      <c r="G68" s="247"/>
+      <c r="H68" s="247"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" s="41" t="s">
@@ -14171,28 +14142,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="243"/>
-      <c r="C75" s="243"/>
-      <c r="D75" s="243"/>
-      <c r="E75" s="243"/>
-      <c r="F75" s="243"/>
-      <c r="G75" s="243"/>
-      <c r="H75" s="243"/>
+      <c r="B75" s="247"/>
+      <c r="C75" s="247"/>
+      <c r="D75" s="247"/>
+      <c r="E75" s="247"/>
+      <c r="F75" s="247"/>
+      <c r="G75" s="247"/>
+      <c r="H75" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B65:H65"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B65:H65"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14262,36 +14233,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="247"/>
+      <c r="U2" s="247"/>
+      <c r="V2" s="247"/>
+      <c r="W2" s="247"/>
+      <c r="X2" s="247"/>
+      <c r="Y2" s="247"/>
+      <c r="Z2" s="247"/>
+      <c r="AA2" s="247" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="247"/>
+      <c r="AC2" s="247"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14302,32 +14273,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="253" t="s">
+      <c r="S4" s="254" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
-      <c r="AA4" s="254"/>
-      <c r="AB4" s="254"/>
-      <c r="AC4" s="254"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
+      <c r="AA4" s="255"/>
+      <c r="AB4" s="255"/>
+      <c r="AC4" s="255"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14718,33 +14689,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="252" t="s">
+      <c r="C10" s="253" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="252"/>
-      <c r="K10" s="252"/>
-      <c r="L10" s="252"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="253"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="253" t="s">
+      <c r="S10" s="254" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="254"/>
-      <c r="U10" s="254"/>
-      <c r="V10" s="254"/>
-      <c r="W10" s="254"/>
-      <c r="X10" s="254"/>
-      <c r="Y10" s="254"/>
-      <c r="Z10" s="254"/>
-      <c r="AA10" s="254"/>
-      <c r="AB10" s="254"/>
-      <c r="AC10" s="254"/>
+      <c r="T10" s="255"/>
+      <c r="U10" s="255"/>
+      <c r="V10" s="255"/>
+      <c r="W10" s="255"/>
+      <c r="X10" s="255"/>
+      <c r="Y10" s="255"/>
+      <c r="Z10" s="255"/>
+      <c r="AA10" s="255"/>
+      <c r="AB10" s="255"/>
+      <c r="AC10" s="255"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -15097,32 +15068,32 @@
     <row r="17" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="86"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="252" t="s">
+      <c r="C17" s="253" t="s">
         <v>404</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
-      <c r="J17" s="252"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="252"/>
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="253"/>
+      <c r="I17" s="253"/>
+      <c r="J17" s="253"/>
+      <c r="K17" s="253"/>
+      <c r="L17" s="253"/>
       <c r="O17" s="5"/>
-      <c r="S17" s="253" t="s">
+      <c r="S17" s="254" t="s">
         <v>115</v>
       </c>
-      <c r="T17" s="254"/>
-      <c r="U17" s="254"/>
-      <c r="V17" s="254"/>
-      <c r="W17" s="254"/>
-      <c r="X17" s="254"/>
-      <c r="Y17" s="254"/>
-      <c r="Z17" s="254"/>
-      <c r="AA17" s="254"/>
-      <c r="AB17" s="254"/>
-      <c r="AC17" s="254"/>
+      <c r="T17" s="255"/>
+      <c r="U17" s="255"/>
+      <c r="V17" s="255"/>
+      <c r="W17" s="255"/>
+      <c r="X17" s="255"/>
+      <c r="Y17" s="255"/>
+      <c r="Z17" s="255"/>
+      <c r="AA17" s="255"/>
+      <c r="AB17" s="255"/>
+      <c r="AC17" s="255"/>
       <c r="AE17" s="87"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -15614,35 +15585,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="P2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="247"/>
+      <c r="R2" s="247"/>
+      <c r="S2" s="247"/>
+      <c r="T2" s="247"/>
+      <c r="U2" s="247"/>
+      <c r="V2" s="247"/>
+      <c r="W2" s="247"/>
+      <c r="X2" s="247" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="247"/>
+      <c r="Z2" s="247"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15651,31 +15622,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="P4" s="254" t="s">
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
+      <c r="P4" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="254"/>
-      <c r="R4" s="254"/>
-      <c r="S4" s="254"/>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
+      <c r="Q4" s="255"/>
+      <c r="R4" s="255"/>
+      <c r="S4" s="255"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -15870,32 +15841,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="252" t="s">
+      <c r="C9" s="253" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="254" t="s">
+      <c r="P9" s="255" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="254"/>
-      <c r="R9" s="254"/>
-      <c r="S9" s="254"/>
-      <c r="T9" s="254"/>
-      <c r="U9" s="254"/>
-      <c r="V9" s="254"/>
-      <c r="W9" s="254"/>
-      <c r="X9" s="254"/>
-      <c r="Y9" s="254"/>
-      <c r="Z9" s="254"/>
+      <c r="Q9" s="255"/>
+      <c r="R9" s="255"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="255"/>
+      <c r="U9" s="255"/>
+      <c r="V9" s="255"/>
+      <c r="W9" s="255"/>
+      <c r="X9" s="255"/>
+      <c r="Y9" s="255"/>
+      <c r="Z9" s="255"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16372,31 +16343,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="252" t="s">
+      <c r="C17" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
-      <c r="J17" s="252"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="252"/>
-      <c r="P17" s="254" t="s">
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="253"/>
+      <c r="I17" s="253"/>
+      <c r="J17" s="253"/>
+      <c r="K17" s="253"/>
+      <c r="L17" s="253"/>
+      <c r="P17" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="254"/>
-      <c r="R17" s="254"/>
-      <c r="S17" s="254"/>
-      <c r="T17" s="254"/>
-      <c r="U17" s="254"/>
-      <c r="V17" s="254"/>
-      <c r="W17" s="254"/>
-      <c r="X17" s="254"/>
-      <c r="Y17" s="254"/>
-      <c r="Z17" s="254"/>
+      <c r="Q17" s="255"/>
+      <c r="R17" s="255"/>
+      <c r="S17" s="255"/>
+      <c r="T17" s="255"/>
+      <c r="U17" s="255"/>
+      <c r="V17" s="255"/>
+      <c r="W17" s="255"/>
+      <c r="X17" s="255"/>
+      <c r="Y17" s="255"/>
+      <c r="Z17" s="255"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16874,60 +16845,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17113,30 +17084,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="252" t="s">
+      <c r="C11" s="253" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="253"/>
+      <c r="I11" s="253"/>
+      <c r="J11" s="253"/>
+      <c r="K11" s="253"/>
+      <c r="L11" s="253"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="257"/>
-      <c r="Q11" s="257"/>
-      <c r="R11" s="257"/>
-      <c r="S11" s="257"/>
-      <c r="T11" s="257"/>
-      <c r="U11" s="257"/>
-      <c r="V11" s="257"/>
-      <c r="W11" s="257"/>
-      <c r="X11" s="257"/>
-      <c r="Y11" s="257"/>
-      <c r="Z11" s="257"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="258"/>
+      <c r="S11" s="258"/>
+      <c r="T11" s="258"/>
+      <c r="U11" s="258"/>
+      <c r="V11" s="258"/>
+      <c r="W11" s="258"/>
+      <c r="X11" s="258"/>
+      <c r="Y11" s="258"/>
+      <c r="Z11" s="258"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17378,18 +17349,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="253" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="252"/>
-      <c r="I18" s="252"/>
-      <c r="J18" s="252"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="252"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
+      <c r="F18" s="253"/>
+      <c r="G18" s="253"/>
+      <c r="H18" s="253"/>
+      <c r="I18" s="253"/>
+      <c r="J18" s="253"/>
+      <c r="K18" s="253"/>
+      <c r="L18" s="253"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17602,23 +17573,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="257"/>
-      <c r="C25" s="257"/>
+      <c r="B25" s="258"/>
+      <c r="C25" s="258"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="252" t="s">
+      <c r="C26" s="253" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="252"/>
-      <c r="E26" s="252"/>
-      <c r="F26" s="252"/>
-      <c r="G26" s="252"/>
-      <c r="H26" s="252"/>
-      <c r="I26" s="252"/>
-      <c r="J26" s="252"/>
-      <c r="K26" s="252"/>
-      <c r="L26" s="252"/>
+      <c r="D26" s="253"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="253"/>
+      <c r="G26" s="253"/>
+      <c r="H26" s="253"/>
+      <c r="I26" s="253"/>
+      <c r="J26" s="253"/>
+      <c r="K26" s="253"/>
+      <c r="L26" s="253"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17810,18 +17781,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="252" t="s">
+      <c r="C33" s="253" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
-      <c r="I33" s="252"/>
-      <c r="J33" s="252"/>
-      <c r="K33" s="252"/>
-      <c r="L33" s="252"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="253"/>
+      <c r="I33" s="253"/>
+      <c r="J33" s="253"/>
+      <c r="K33" s="253"/>
+      <c r="L33" s="253"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18005,18 +17976,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="252" t="s">
+      <c r="C40" s="253" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="252"/>
-      <c r="E40" s="252"/>
-      <c r="F40" s="252"/>
-      <c r="G40" s="252"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="252"/>
-      <c r="J40" s="252"/>
-      <c r="K40" s="252"/>
-      <c r="L40" s="252"/>
+      <c r="D40" s="253"/>
+      <c r="E40" s="253"/>
+      <c r="F40" s="253"/>
+      <c r="G40" s="253"/>
+      <c r="H40" s="253"/>
+      <c r="I40" s="253"/>
+      <c r="J40" s="253"/>
+      <c r="K40" s="253"/>
+      <c r="L40" s="253"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18280,6 +18251,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18287,12 +18264,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18330,60 +18301,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="S2" s="257"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="257"/>
-      <c r="V2" s="257"/>
-      <c r="W2" s="257"/>
-      <c r="X2" s="257"/>
-      <c r="Y2" s="257"/>
-      <c r="Z2" s="257"/>
-      <c r="AA2" s="257"/>
-      <c r="AB2" s="257"/>
-      <c r="AC2" s="257"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="S2" s="258"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
+      <c r="AA2" s="258"/>
+      <c r="AB2" s="258"/>
+      <c r="AC2" s="258"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="S4" s="257"/>
-      <c r="T4" s="257"/>
-      <c r="U4" s="257"/>
-      <c r="V4" s="257"/>
-      <c r="W4" s="257"/>
-      <c r="X4" s="257"/>
-      <c r="Y4" s="257"/>
-      <c r="Z4" s="257"/>
-      <c r="AA4" s="257"/>
-      <c r="AB4" s="257"/>
-      <c r="AC4" s="257"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
+      <c r="S4" s="258"/>
+      <c r="T4" s="258"/>
+      <c r="U4" s="258"/>
+      <c r="V4" s="258"/>
+      <c r="W4" s="258"/>
+      <c r="X4" s="258"/>
+      <c r="Y4" s="258"/>
+      <c r="Z4" s="258"/>
+      <c r="AA4" s="258"/>
+      <c r="AB4" s="258"/>
+      <c r="AC4" s="258"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18746,18 +18717,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="252" t="s">
+      <c r="C13" s="253" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="252"/>
-      <c r="G13" s="252"/>
-      <c r="H13" s="252"/>
-      <c r="I13" s="252"/>
-      <c r="J13" s="252"/>
-      <c r="K13" s="252"/>
-      <c r="L13" s="252"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="253"/>
+      <c r="I13" s="253"/>
+      <c r="J13" s="253"/>
+      <c r="K13" s="253"/>
+      <c r="L13" s="253"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18850,18 +18821,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="253" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="252"/>
-      <c r="I18" s="252"/>
-      <c r="J18" s="252"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="252"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
+      <c r="F18" s="253"/>
+      <c r="G18" s="253"/>
+      <c r="H18" s="253"/>
+      <c r="I18" s="253"/>
+      <c r="J18" s="253"/>
+      <c r="K18" s="253"/>
+      <c r="L18" s="253"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19053,18 +19024,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="252" t="s">
+      <c r="C25" s="253" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="252"/>
-      <c r="E25" s="252"/>
-      <c r="F25" s="252"/>
-      <c r="G25" s="252"/>
-      <c r="H25" s="252"/>
-      <c r="I25" s="252"/>
-      <c r="J25" s="252"/>
-      <c r="K25" s="252"/>
-      <c r="L25" s="252"/>
+      <c r="D25" s="253"/>
+      <c r="E25" s="253"/>
+      <c r="F25" s="253"/>
+      <c r="G25" s="253"/>
+      <c r="H25" s="253"/>
+      <c r="I25" s="253"/>
+      <c r="J25" s="253"/>
+      <c r="K25" s="253"/>
+      <c r="L25" s="253"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19202,18 +19173,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="252" t="s">
+      <c r="C31" s="253" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="252"/>
-      <c r="E31" s="252"/>
-      <c r="F31" s="252"/>
-      <c r="G31" s="252"/>
-      <c r="H31" s="252"/>
-      <c r="I31" s="252"/>
-      <c r="J31" s="252"/>
-      <c r="K31" s="252"/>
-      <c r="L31" s="252"/>
+      <c r="D31" s="253"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
+      <c r="I31" s="253"/>
+      <c r="J31" s="253"/>
+      <c r="K31" s="253"/>
+      <c r="L31" s="253"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19352,16 +19323,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19424,10 +19395,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="247" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="247"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19444,7 +19415,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19453,7 +19424,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>193072.05</v>
+        <v>201279.35999999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19471,7 +19442,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.6700000000000005E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19480,7 +19451,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0870000000000002</v>
+        <v>2.0948000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19512,10 +19483,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="247" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="247"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19523,7 +19494,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.8129848876394353E-2</v>
+        <v>1.7403456946532482E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19532,7 +19503,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98187015112360565</v>
+        <v>0.98259654305346755</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19550,7 +19521,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14061499999999999</v>
+        <v>0.14188600000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19559,7 +19530,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1389250261369869</v>
+        <v>0.14024161696694995</v>
       </c>
     </row>
   </sheetData>
@@ -19604,60 +19575,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="253" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19810,7 +19781,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>31776.184895503076</v>
+        <v>31442.140712285047</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19864,23 +19835,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3803.9055566908119</v>
+        <v>3799.5133409538471</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4680.9752450148244</v>
+        <v>4670.1716206796445</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4473.9509969804812</v>
+        <v>4458.4712143895977</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3510.3813066354719</v>
+        <v>3494.196185403066</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>2024.5059183399358</v>
+        <v>2012.8448035990855</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19899,14 +19870,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>16581.586231368427</v>
+        <v>16312.768272484131</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="247" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="247"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19922,14 +19893,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1389250261369869</v>
+        <v>0.14024161696694995</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="247" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="247"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19937,7 +19908,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18493.719023661524</v>
+        <v>18435.197165025238</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19946,7 +19917,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>16581.586231368427</v>
+        <v>16312.768272484131</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19955,7 +19926,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>35075.305255029947</v>
+        <v>34747.965437509367</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19982,7 +19953,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>33214.305255029947</v>
+        <v>32886.965437509367</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20000,7 +19971,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>140.14474791151878</v>
+        <v>138.76356724687497</v>
       </c>
     </row>
   </sheetData>
@@ -20043,37 +20014,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="253" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20262,18 +20233,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="252" t="s">
+      <c r="C10" s="253" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="252"/>
-      <c r="K10" s="252"/>
-      <c r="L10" s="252"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="253"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20467,18 +20438,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="252" t="s">
+      <c r="C16" s="253" t="s">
         <v>195</v>
       </c>
-      <c r="D16" s="252"/>
-      <c r="E16" s="252"/>
-      <c r="F16" s="252"/>
-      <c r="G16" s="252"/>
-      <c r="H16" s="252"/>
-      <c r="I16" s="252"/>
-      <c r="J16" s="252"/>
-      <c r="K16" s="252"/>
-      <c r="L16" s="252"/>
+      <c r="D16" s="253"/>
+      <c r="E16" s="253"/>
+      <c r="F16" s="253"/>
+      <c r="G16" s="253"/>
+      <c r="H16" s="253"/>
+      <c r="I16" s="253"/>
+      <c r="J16" s="253"/>
+      <c r="K16" s="253"/>
+      <c r="L16" s="253"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20612,18 +20583,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="252" t="s">
+      <c r="C21" s="253" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="252"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="252"/>
-      <c r="G21" s="252"/>
-      <c r="H21" s="252"/>
-      <c r="I21" s="252"/>
-      <c r="J21" s="252"/>
-      <c r="K21" s="252"/>
-      <c r="L21" s="252"/>
+      <c r="D21" s="253"/>
+      <c r="E21" s="253"/>
+      <c r="F21" s="253"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
+      <c r="I21" s="253"/>
+      <c r="J21" s="253"/>
+      <c r="K21" s="253"/>
+      <c r="L21" s="253"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20707,18 +20678,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="252" t="s">
+      <c r="C26" s="253" t="s">
         <v>199</v>
       </c>
-      <c r="D26" s="252"/>
-      <c r="E26" s="252"/>
-      <c r="F26" s="252"/>
-      <c r="G26" s="252"/>
-      <c r="H26" s="252"/>
-      <c r="I26" s="252"/>
-      <c r="J26" s="252"/>
-      <c r="K26" s="252"/>
-      <c r="L26" s="252"/>
+      <c r="D26" s="253"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="253"/>
+      <c r="G26" s="253"/>
+      <c r="H26" s="253"/>
+      <c r="I26" s="253"/>
+      <c r="J26" s="253"/>
+      <c r="K26" s="253"/>
+      <c r="L26" s="253"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -20988,10 +20959,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="247" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="243"/>
+      <c r="C37" s="247"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21009,7 +20980,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1389250261369869</v>
+        <v>0.14024161696694995</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21035,7 +21006,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>34948.72902026982</v>
+        <v>34736.705696555888</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21062,7 +21033,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>33087.72902026982</v>
+        <v>32875.705696555888</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21080,14 +21051,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>139.61067097160262</v>
+        <v>138.71605779137505</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="247" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="243"/>
+      <c r="C49" s="247"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21104,7 +21075,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14061499999999999</v>
+        <v>0.14188600000000001</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21139,14 +21110,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>112.91154281588085</v>
+        <v>112.28454742641925</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="243" t="s">
+      <c r="B57" s="247" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="243"/>
+      <c r="C57" s="247"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21163,7 +21134,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1389250261369869</v>
+        <v>0.14024161696694995</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21189,7 +21160,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>38629.118366798713</v>
+        <v>38395.896071981711</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21216,7 +21187,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>36768.118366798713</v>
+        <v>36534.896071981711</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21234,7 +21205,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>155.13973994429836</v>
+        <v>154.15567962861482</v>
       </c>
     </row>
   </sheetData>
@@ -21286,10 +21257,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="247" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="247"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21298,7 +21269,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>140.14474791151878</v>
+        <v>138.76356724687497</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21307,7 +21278,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>139.61067097160262</v>
+        <v>138.71605779137505</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21316,7 +21287,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>112.91154281588085</v>
+        <v>112.28454742641925</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21325,7 +21296,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>155.13973994429836</v>
+        <v>154.15567962861482</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21334,7 +21305,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>136.95167541082515</v>
+        <v>135.97996302332101</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21343,7 +21314,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21352,7 +21323,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.83188893953130161</v>
+        <v>-0.83988794858783788</v>
       </c>
     </row>
   </sheetData>
@@ -21408,37 +21379,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="253" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21551,18 +21522,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="252" t="s">
+      <c r="C9" s="253" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21683,18 +21654,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="252" t="s">
+      <c r="C14" s="253" t="s">
         <v>374</v>
       </c>
-      <c r="D14" s="252"/>
-      <c r="E14" s="252"/>
-      <c r="F14" s="252"/>
-      <c r="G14" s="252"/>
-      <c r="H14" s="252"/>
-      <c r="I14" s="252"/>
-      <c r="J14" s="252"/>
-      <c r="K14" s="252"/>
-      <c r="L14" s="252"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="253"/>
+      <c r="F14" s="253"/>
+      <c r="G14" s="253"/>
+      <c r="H14" s="253"/>
+      <c r="I14" s="253"/>
+      <c r="J14" s="253"/>
+      <c r="K14" s="253"/>
+      <c r="L14" s="253"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21784,10 +21755,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="247" t="s">
         <v>376</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="247"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21822,7 +21793,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14061499999999999</v>
+        <v>0.14188600000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21839,7 +21810,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>24.935538697508605</v>
+        <v>24.675516466206126</v>
       </c>
     </row>
   </sheetData>
@@ -21888,60 +21859,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="256" t="s">
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="257"/>
-      <c r="T3" s="257"/>
-      <c r="U3" s="257"/>
-      <c r="V3" s="257"/>
-      <c r="W3" s="257"/>
-      <c r="X3" s="257"/>
-      <c r="Y3" s="257"/>
-      <c r="Z3" s="257"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="252" t="s">
+      <c r="C5" s="253" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="P5" s="257"/>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22076,7 +22047,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1101685.5808022781</v>
+        <v>1090104.213774978</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22130,23 +22101,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7381.3453239353175</v>
+        <v>7372.8223833395041</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12961.951233912931</v>
+        <v>12932.035234692203</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>22761.72871163848</v>
+        <v>22682.973577287066</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>39970.547997951806</v>
+        <v>39786.257999640322</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>70189.95470408471</v>
+        <v>69785.661929218157</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22165,15 +22136,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>574886.33446721302</v>
+        <v>565566.3714150897</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="259" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="260"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22181,7 +22152,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22190,7 +22161,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>3199.5192177917897</v>
+        <v>3155.3529627280482</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22200,20 +22171,20 @@
       <c r="C17" s="158">
         <v>1</v>
       </c>
-      <c r="E17" s="260" t="s">
+      <c r="E17" s="261" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="259" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="260"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22229,7 +22200,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1389250261369869</v>
+        <v>0.14024161696694995</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22247,7 +22218,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>184925.55</v>
+        <v>192786.56</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22274,15 +22245,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>186786.55</v>
+        <v>194647.56</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="259" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="260"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22290,7 +22261,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>153265.52797152323</v>
+        <v>152559.75112417724</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22299,7 +22270,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>574886.33446721302</v>
+        <v>565566.3714150897</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22308,7 +22279,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>728151.86243873625</v>
+        <v>718126.12253926694</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22335,7 +22306,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>726290.86243873625</v>
+        <v>716265.12253926694</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22353,22 +22324,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>3199.5192177917897</v>
+        <v>3155.3529627280482</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="252" t="s">
+      <c r="C39" s="253" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="252"/>
-      <c r="E39" s="252"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="252"/>
-      <c r="H39" s="252"/>
-      <c r="I39" s="252"/>
-      <c r="J39" s="252"/>
-      <c r="K39" s="252"/>
-      <c r="L39" s="252"/>
+      <c r="D39" s="253"/>
+      <c r="E39" s="253"/>
+      <c r="F39" s="253"/>
+      <c r="G39" s="253"/>
+      <c r="H39" s="253"/>
+      <c r="I39" s="253"/>
+      <c r="J39" s="253"/>
+      <c r="K39" s="253"/>
+      <c r="L39" s="253"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22800,17 +22771,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23164,7 +23135,7 @@
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
       <c r="T7" s="22">
-        <f t="shared" ref="T7:Z7" si="3">T5-T6</f>
+        <f t="shared" ref="T7:Y7" si="3">T5-T6</f>
         <v>714</v>
       </c>
       <c r="U7" s="22">
@@ -24155,7 +24126,7 @@
         <v>229</v>
       </c>
       <c r="AA21" s="25">
-        <f t="shared" ref="T21:AA21" si="12">AA20*AA$84</f>
+        <f t="shared" ref="AA21" si="12">AA20*AA$84</f>
         <v>232</v>
       </c>
       <c r="AC21" s="25">
@@ -24237,59 +24208,59 @@
       <c r="J23" s="27"/>
       <c r="K23" s="27"/>
       <c r="L23" s="65">
-        <f>L22/L$84</f>
+        <f t="shared" ref="L23:Q23" si="13">L22/L$84</f>
         <v>5.43</v>
       </c>
       <c r="M23" s="65">
-        <f>M22/M$84</f>
+        <f t="shared" si="13"/>
         <v>7.5</v>
       </c>
       <c r="N23" s="65">
-        <f>N22/N$84</f>
+        <f t="shared" si="13"/>
         <v>-2.56</v>
       </c>
       <c r="O23" s="65">
-        <f>O22/O$84</f>
-        <v>1.6</v>
-      </c>
-      <c r="P23" s="65">
-        <f>P22/P$84</f>
-        <v>6.93</v>
-      </c>
-      <c r="Q23" s="65">
-        <f>Q22/Q$84</f>
-        <v>14.54</v>
-      </c>
-      <c r="T23" s="65">
-        <f t="shared" ref="T23:Z23" si="13">T22/T$84</f>
-        <v>1.45</v>
-      </c>
-      <c r="U23" s="65">
-        <f t="shared" si="13"/>
-        <v>1.58</v>
-      </c>
-      <c r="V23" s="65">
         <f t="shared" si="13"/>
         <v>1.6</v>
       </c>
+      <c r="P23" s="65">
+        <f t="shared" si="13"/>
+        <v>6.93</v>
+      </c>
+      <c r="Q23" s="65">
+        <f t="shared" si="13"/>
+        <v>14.54</v>
+      </c>
+      <c r="T23" s="65">
+        <f t="shared" ref="T23:Z23" si="14">T22/T$84</f>
+        <v>1.45</v>
+      </c>
+      <c r="U23" s="65">
+        <f t="shared" si="14"/>
+        <v>1.58</v>
+      </c>
+      <c r="V23" s="65">
+        <f t="shared" si="14"/>
+        <v>1.6</v>
+      </c>
       <c r="W23" s="65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="X23" s="65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.58</v>
       </c>
       <c r="Y23" s="65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.75</v>
       </c>
       <c r="Z23" s="65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.38</v>
       </c>
       <c r="AA23" s="65">
-        <f t="shared" ref="T23:AA23" si="14">AA22/AA$84</f>
+        <f t="shared" ref="AA23" si="15">AA22/AA$84</f>
         <v>5.75</v>
       </c>
       <c r="AC23" s="65">
@@ -24372,61 +24343,61 @@
       <c r="J25" s="29"/>
       <c r="K25" s="29"/>
       <c r="L25" s="66">
-        <f>L24/L$84</f>
+        <f t="shared" ref="L25:Q25" si="16">L24/L$84</f>
         <v>5.36</v>
       </c>
       <c r="M25" s="66">
-        <f>M24/M$84</f>
+        <f t="shared" si="16"/>
         <v>7.36</v>
       </c>
       <c r="N25" s="66">
-        <f>N24/N$84</f>
+        <f t="shared" si="16"/>
         <v>-2.56</v>
       </c>
       <c r="O25" s="66">
-        <f>O24/O$84</f>
+        <f t="shared" si="16"/>
         <v>1.58</v>
       </c>
       <c r="P25" s="66">
-        <f>P24/P$84</f>
+        <f t="shared" si="16"/>
         <v>6.77</v>
       </c>
       <c r="Q25" s="66">
-        <f>Q24/Q$84</f>
+        <f t="shared" si="16"/>
         <v>13.9</v>
       </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="66">
-        <f t="shared" ref="T25:Z25" si="15">T24/T$84</f>
+        <f t="shared" ref="T25:Z25" si="17">T24/T$84</f>
         <v>1.41</v>
       </c>
       <c r="U25" s="66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.55</v>
       </c>
       <c r="V25" s="66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.57</v>
       </c>
       <c r="W25" s="66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.2400000000000002</v>
       </c>
       <c r="X25" s="66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.4300000000000002</v>
       </c>
       <c r="Y25" s="66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.6</v>
       </c>
       <c r="Z25" s="66">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.27</v>
       </c>
       <c r="AA25" s="66">
-        <f t="shared" ref="T25:AA25" si="16">AA24/AA$84</f>
+        <f t="shared" ref="AA25" si="18">AA24/AA$84</f>
         <v>5.58</v>
       </c>
       <c r="AB25" s="1"/>
@@ -24579,7 +24550,7 @@
         <v>1534</v>
       </c>
       <c r="AC29" s="21">
-        <f t="shared" ref="AC29:AC49" si="17">AA29</f>
+        <f t="shared" ref="AC29:AC49" si="19">AA29</f>
         <v>1534</v>
       </c>
     </row>
@@ -24703,7 +24674,7 @@
       </c>
       <c r="AB31" s="1"/>
       <c r="AC31" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5221</v>
       </c>
       <c r="AD31" s="1"/>
@@ -24765,7 +24736,7 @@
         <v>2034</v>
       </c>
       <c r="AC32" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2034</v>
       </c>
     </row>
@@ -24825,7 +24796,7 @@
         <v>0</v>
       </c>
       <c r="AC33" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -24885,7 +24856,7 @@
         <v>1221</v>
       </c>
       <c r="AC34" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1221</v>
       </c>
     </row>
@@ -24904,15 +24875,15 @@
       <c r="J35" s="35"/>
       <c r="K35" s="35"/>
       <c r="L35" s="35">
-        <f t="shared" ref="L35:N35" si="18">L36-L31</f>
+        <f t="shared" ref="L35:N35" si="20">L36-L31</f>
         <v>4896</v>
       </c>
       <c r="M35" s="35">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4911</v>
       </c>
       <c r="N35" s="35">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4651</v>
       </c>
       <c r="O35" s="35">
@@ -24930,31 +24901,31 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="35">
-        <f t="shared" ref="T35:Z35" si="19">T36-T31</f>
+        <f t="shared" ref="T35:Y35" si="21">T36-T31</f>
         <v>4364</v>
       </c>
       <c r="U35" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>4297</v>
       </c>
       <c r="V35" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>4282</v>
       </c>
       <c r="W35" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>4370</v>
       </c>
       <c r="X35" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>4410</v>
       </c>
       <c r="Y35" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>4499</v>
       </c>
       <c r="Z35" s="35">
-        <f t="shared" ref="Z35:AA35" si="20">Z36-Z31</f>
+        <f t="shared" ref="Z35" si="22">Z36-Z31</f>
         <v>4593</v>
       </c>
       <c r="AA35" s="35">
@@ -24963,7 +24934,7 @@
       </c>
       <c r="AB35" s="1"/>
       <c r="AC35" s="35">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4751</v>
       </c>
       <c r="AD35" s="1"/>
@@ -25029,7 +25000,7 @@
       </c>
       <c r="AB36" s="1"/>
       <c r="AC36" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9972</v>
       </c>
       <c r="AD36" s="1"/>
@@ -25091,7 +25062,7 @@
         <v>1748</v>
       </c>
       <c r="AC37" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1748</v>
       </c>
     </row>
@@ -25151,7 +25122,7 @@
         <v>185</v>
       </c>
       <c r="AC38" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>185</v>
       </c>
     </row>
@@ -25215,7 +25186,7 @@
       </c>
       <c r="AB39" s="1"/>
       <c r="AC39" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3127</v>
       </c>
       <c r="AD39" s="1"/>
@@ -25277,7 +25248,7 @@
         <v>3380</v>
       </c>
       <c r="AC40" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3380</v>
       </c>
     </row>
@@ -25296,15 +25267,15 @@
       <c r="J41" s="35"/>
       <c r="K41" s="35"/>
       <c r="L41" s="35">
-        <f t="shared" ref="L41:N41" si="21">L42-L39</f>
+        <f t="shared" ref="L41:N41" si="23">L42-L39</f>
         <v>5123</v>
       </c>
       <c r="M41" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5280</v>
       </c>
       <c r="N41" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>6163</v>
       </c>
       <c r="O41" s="35">
@@ -25322,31 +25293,31 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="35">
-        <f t="shared" ref="T41:Z41" si="22">T42-T39</f>
+        <f t="shared" ref="T41:Y41" si="24">T42-T39</f>
         <v>6111</v>
       </c>
       <c r="U41" s="35">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>6069</v>
       </c>
       <c r="V41" s="35">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>5981</v>
       </c>
       <c r="W41" s="35">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>5828</v>
       </c>
       <c r="X41" s="35">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>4388</v>
       </c>
       <c r="Y41" s="35">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>4488</v>
       </c>
       <c r="Z41" s="35">
-        <f t="shared" ref="Z41:AA41" si="23">Z42-Z39</f>
+        <f t="shared" ref="Z41" si="25">Z42-Z39</f>
         <v>4556</v>
       </c>
       <c r="AA41" s="35">
@@ -25355,7 +25326,7 @@
       </c>
       <c r="AB41" s="1"/>
       <c r="AC41" s="35">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4678</v>
       </c>
       <c r="AD41" s="1"/>
@@ -25421,7 +25392,7 @@
       </c>
       <c r="AB42" s="1"/>
       <c r="AC42" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>7805</v>
       </c>
       <c r="AD42" s="1"/>
@@ -25483,7 +25454,7 @@
         <v>0</v>
       </c>
       <c r="AC43" s="62">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25543,7 +25514,7 @@
         <v>0</v>
       </c>
       <c r="AC44" s="62">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25603,7 +25574,7 @@
         <v>8078</v>
       </c>
       <c r="AC45" s="62">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8078</v>
       </c>
     </row>
@@ -25663,7 +25634,7 @@
         <v>-5911</v>
       </c>
       <c r="AC46" s="62">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-5911</v>
       </c>
     </row>
@@ -25723,7 +25694,7 @@
         <v>0</v>
       </c>
       <c r="AC47" s="62">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -25787,7 +25758,7 @@
       </c>
       <c r="AB48" s="1"/>
       <c r="AC48" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2167</v>
       </c>
       <c r="AD48" s="1"/>
@@ -25853,7 +25824,7 @@
       </c>
       <c r="AB49" s="1"/>
       <c r="AC49" s="37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9972</v>
       </c>
       <c r="AD49" s="1"/>
@@ -25997,7 +25968,7 @@
         <v>54</v>
       </c>
       <c r="AC53" s="62">
-        <f t="shared" ref="AC53:AC57" si="24">SUM(X53:AA53)</f>
+        <f t="shared" ref="AC53:AC57" si="26">SUM(X53:AA53)</f>
         <v>213</v>
       </c>
     </row>
@@ -26060,7 +26031,7 @@
         <v>-337</v>
       </c>
       <c r="AC54" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-575</v>
       </c>
     </row>
@@ -26186,7 +26157,7 @@
         <v>-23</v>
       </c>
       <c r="AC56" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>66</v>
       </c>
     </row>
@@ -26258,7 +26229,7 @@
         <v>280</v>
       </c>
       <c r="AC57" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>481</v>
       </c>
     </row>
@@ -26452,7 +26423,7 @@
         <v>0</v>
       </c>
       <c r="AC60" s="62">
-        <f t="shared" ref="AC60:AC65" si="25">SUM(X60:AA60)</f>
+        <f t="shared" ref="AC60:AC65" si="27">SUM(X60:AA60)</f>
         <v>0</v>
       </c>
     </row>
@@ -26520,7 +26491,7 @@
       </c>
       <c r="AB61" s="1"/>
       <c r="AC61" s="61">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-525</v>
       </c>
       <c r="AD61" s="1"/>
@@ -26583,7 +26554,7 @@
         <v>-117</v>
       </c>
       <c r="AC62" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-176</v>
       </c>
     </row>
@@ -26775,7 +26746,7 @@
       </c>
       <c r="AB65" s="1"/>
       <c r="AC65" s="71">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2337</v>
       </c>
       <c r="AD65" s="1"/>
@@ -26800,39 +26771,39 @@
         <v>64</v>
       </c>
       <c r="C68" s="64">
-        <f t="shared" ref="C68:L68" si="26">C5-C6-C10+C12+C13+C15-C16</f>
+        <f t="shared" ref="C68:K68" si="28">C5-C6-C10+C12+C13+C15-C16</f>
         <v>0</v>
       </c>
       <c r="D68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="G68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="I68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="J68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K68" s="64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L68" s="64">
@@ -26840,59 +26811,59 @@
         <v>1314</v>
       </c>
       <c r="M68" s="64">
-        <f t="shared" ref="M68:P68" si="27">M5-M6-M10+M12+M13+M15-M16</f>
+        <f t="shared" ref="M68:P68" si="29">M5-M6-M10+M12+M13+M15-M16</f>
         <v>1649</v>
       </c>
       <c r="N68" s="64">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-529</v>
       </c>
       <c r="O68" s="64">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>335</v>
       </c>
       <c r="P68" s="64">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1469</v>
       </c>
       <c r="Q68" s="64">
-        <f t="shared" ref="N68:Q68" si="28">Q5-Q6-Q10+Q12+Q13+Q15-Q16</f>
+        <f t="shared" ref="Q68" si="30">Q5-Q6-Q10+Q12+Q13+Q15-Q16</f>
         <v>3184</v>
       </c>
       <c r="T68" s="64">
-        <f t="shared" ref="T68:Z68" si="29">T5-T6-T10+T12+T13+T15-T16</f>
+        <f t="shared" ref="T68:Z68" si="31">T5-T6-T10+T12+T13+T15-T16</f>
         <v>305</v>
       </c>
       <c r="U68" s="64">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>336</v>
       </c>
       <c r="V68" s="64">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>340</v>
       </c>
       <c r="W68" s="64">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>488</v>
       </c>
       <c r="X68" s="64">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>549</v>
       </c>
       <c r="Y68" s="64">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>593</v>
       </c>
       <c r="Z68" s="64">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>748</v>
       </c>
       <c r="AA68" s="64">
-        <f t="shared" ref="T68:AC68" si="30">AA5-AA6-AA10+AA12+AA13+AA15-AA16</f>
+        <f t="shared" ref="AA68:AC68" si="32">AA5-AA6-AA10+AA12+AA13+AA15-AA16</f>
         <v>1294</v>
       </c>
       <c r="AC68" s="64">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3184</v>
       </c>
     </row>
@@ -26902,97 +26873,97 @@
         <v>65</v>
       </c>
       <c r="C69" s="40">
-        <f t="shared" ref="C69:Q69" si="31">C17-C68</f>
+        <f t="shared" ref="C69:Q69" si="33">C17-C68</f>
         <v>0</v>
       </c>
       <c r="D69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="E69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="F69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="G69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="H69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="I69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L69" s="40">
-        <f t="shared" ref="L69:P69" si="32">L17-L68</f>
+        <f t="shared" ref="L69:P69" si="34">L17-L68</f>
         <v>0</v>
       </c>
       <c r="M69" s="40">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N69" s="40">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O69" s="40">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="P69" s="40">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q69" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
       <c r="T69" s="40">
-        <f t="shared" ref="T69:Z69" si="33">T17-T68</f>
+        <f t="shared" ref="T69:Y69" si="35">T17-T68</f>
         <v>0</v>
       </c>
       <c r="U69" s="40">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="V69" s="40">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="W69" s="40">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="X69" s="40">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Y69" s="40">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z69" s="40">
-        <f t="shared" ref="Z69:AA69" si="34">Z17-Z68</f>
+        <f t="shared" ref="Z69:AA69" si="36">Z17-Z68</f>
         <v>0</v>
       </c>
       <c r="AA69" s="40">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AB69" s="16"/>
@@ -27009,97 +26980,97 @@
         <v>66</v>
       </c>
       <c r="C70" s="42">
-        <f t="shared" ref="C70:Q70" si="35">C36-(C42+C110)</f>
+        <f t="shared" ref="C70:Q70" si="37">C36-(C42+C110)</f>
         <v>0</v>
       </c>
       <c r="D70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="E70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="G70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="H70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="I70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="K70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L70" s="42">
-        <f t="shared" ref="L70:P70" si="36">L36-(L42+L110)</f>
+        <f t="shared" ref="L70:P70" si="38">L36-(L42+L110)</f>
         <v>0</v>
       </c>
       <c r="M70" s="42">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="N70" s="42">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="O70" s="42">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="P70" s="42">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="Q70" s="42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="42">
-        <f t="shared" ref="T70:Z70" si="37">T36-(T42+T110)</f>
+        <f t="shared" ref="T70:Z70" si="39">T36-(T42+T110)</f>
         <v>0</v>
       </c>
       <c r="U70" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V70" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="W70" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="X70" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Y70" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Z70" s="42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AA70" s="42">
-        <f t="shared" ref="T70:AA70" si="38">AA36-(AA42+AA110)</f>
+        <f t="shared" ref="AA70" si="40">AA36-(AA42+AA110)</f>
         <v>0</v>
       </c>
       <c r="AB70" s="16"/>
@@ -27204,59 +27175,59 @@
       <c r="J74" s="25"/>
       <c r="K74" s="25"/>
       <c r="L74" s="25">
-        <f t="shared" ref="L74:P74" si="39">L73*L84</f>
+        <f t="shared" ref="L74:P74" si="41">L73*L84</f>
         <v>227</v>
       </c>
       <c r="M74" s="25">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>209</v>
       </c>
       <c r="N74" s="25">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>207</v>
       </c>
       <c r="O74" s="25">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>210</v>
       </c>
       <c r="P74" s="25">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>213</v>
       </c>
       <c r="Q74" s="25">
-        <f t="shared" ref="M74:Q74" si="40">Q73*Q84</f>
+        <f t="shared" ref="Q74" si="42">Q73*Q84</f>
         <v>227</v>
       </c>
       <c r="T74" s="25">
-        <f t="shared" ref="T74:U74" si="41">T73*T84</f>
+        <f t="shared" ref="T74" si="43">T73*T84</f>
         <v>212</v>
       </c>
       <c r="U74" s="25">
-        <f t="shared" ref="U74:V74" si="42">U73*U84</f>
+        <f t="shared" ref="U74" si="44">U73*U84</f>
         <v>212</v>
       </c>
       <c r="V74" s="25">
-        <f t="shared" ref="V74:W74" si="43">V73*V84</f>
+        <f t="shared" ref="V74" si="45">V73*V84</f>
         <v>212</v>
       </c>
       <c r="W74" s="25">
-        <f t="shared" ref="W74:X74" si="44">W73*W84</f>
+        <f t="shared" ref="W74" si="46">W73*W84</f>
         <v>213</v>
       </c>
       <c r="X74" s="25">
-        <f t="shared" ref="X74:Z74" si="45">X73*X84</f>
+        <f t="shared" ref="X74:Z74" si="47">X73*X84</f>
         <v>214</v>
       </c>
       <c r="Y74" s="25">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>218</v>
       </c>
       <c r="Z74" s="25">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>224</v>
       </c>
       <c r="AA74" s="25">
-        <f t="shared" ref="Z74:AA74" si="46">AA73*AA84</f>
+        <f t="shared" ref="AA74" si="48">AA73*AA84</f>
         <v>227</v>
       </c>
       <c r="AC74" s="24">
@@ -27338,19 +27309,19 @@
       <c r="J76" s="25"/>
       <c r="K76" s="25"/>
       <c r="L76" s="25">
-        <f t="shared" ref="L76:O76" si="47">L75*L84</f>
+        <f t="shared" ref="L76:O76" si="49">L75*L84</f>
         <v>3</v>
       </c>
       <c r="M76" s="25">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>4</v>
       </c>
       <c r="N76" s="25">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="O76" s="25">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>3</v>
       </c>
       <c r="P76" s="25">
@@ -27362,35 +27333,35 @@
         <v>10</v>
       </c>
       <c r="T76" s="25">
-        <f t="shared" ref="T76:Z76" si="48">T75*T84</f>
+        <f t="shared" ref="T76:Y76" si="50">T75*T84</f>
         <v>5</v>
       </c>
       <c r="U76" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>5</v>
       </c>
       <c r="V76" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>4</v>
       </c>
       <c r="W76" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>5</v>
       </c>
       <c r="X76" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>13</v>
       </c>
       <c r="Y76" s="25">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>12</v>
       </c>
       <c r="Z76" s="25">
-        <f t="shared" ref="Z76:AA76" si="49">Z75*Z84</f>
+        <f t="shared" ref="Z76:AA76" si="51">Z75*Z84</f>
         <v>8</v>
       </c>
       <c r="AA76" s="25">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>10</v>
       </c>
       <c r="AC76" s="24">
@@ -27412,19 +27383,19 @@
       <c r="J77" s="25"/>
       <c r="K77" s="25"/>
       <c r="L77" s="25">
-        <f t="shared" ref="L77:O77" si="50">L74+L76</f>
+        <f t="shared" ref="L77:O77" si="52">L74+L76</f>
         <v>230</v>
       </c>
       <c r="M77" s="25">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>213</v>
       </c>
       <c r="N77" s="25">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>207</v>
       </c>
       <c r="O77" s="25">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>213</v>
       </c>
       <c r="P77" s="25">
@@ -27436,35 +27407,35 @@
         <v>237</v>
       </c>
       <c r="T77" s="25">
-        <f t="shared" ref="T77:Z77" si="51">T74+T76</f>
+        <f t="shared" ref="T77:Y77" si="53">T74+T76</f>
         <v>217</v>
       </c>
       <c r="U77" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>217</v>
       </c>
       <c r="V77" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>216</v>
       </c>
       <c r="W77" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>218</v>
       </c>
       <c r="X77" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>227</v>
       </c>
       <c r="Y77" s="25">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>230</v>
       </c>
       <c r="Z77" s="25">
-        <f t="shared" ref="Z77:AA77" si="52">Z74+Z76</f>
+        <f t="shared" ref="Z77:AA77" si="54">Z74+Z76</f>
         <v>232</v>
       </c>
       <c r="AA77" s="25">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>237</v>
       </c>
       <c r="AC77" s="24">
@@ -27500,7 +27471,7 @@
       <c r="P78" s="21">
         <v>2</v>
       </c>
-      <c r="Q78" s="261">
+      <c r="Q78" s="243">
         <v>2</v>
       </c>
       <c r="T78" s="68"/>
@@ -27530,19 +27501,19 @@
       <c r="J79" s="25"/>
       <c r="K79" s="25"/>
       <c r="L79" s="25">
-        <f t="shared" ref="L79:O79" si="53">L78*L84</f>
+        <f t="shared" ref="L79:O79" si="55">L78*L84</f>
         <v>2</v>
       </c>
       <c r="M79" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="N79" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="O79" s="25">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="P79" s="25">
@@ -27640,59 +27611,59 @@
       <c r="J81" s="45"/>
       <c r="K81" s="45"/>
       <c r="L81" s="45">
-        <f t="shared" ref="L81:P81" si="54">L80/L84</f>
+        <f t="shared" ref="L81:P81" si="56">L80/L84</f>
         <v>2.66</v>
       </c>
       <c r="M81" s="45">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2.77</v>
       </c>
       <c r="N81" s="45">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2.8</v>
       </c>
       <c r="O81" s="45">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2.8</v>
       </c>
       <c r="P81" s="45">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2.86</v>
       </c>
       <c r="Q81" s="45">
-        <f t="shared" ref="M81:Q81" si="55">Q80/Q84</f>
+        <f t="shared" ref="Q81" si="57">Q80/Q84</f>
         <v>2.92</v>
       </c>
       <c r="T81" s="45">
-        <f t="shared" ref="T81:U81" si="56">T80/T84</f>
+        <f t="shared" ref="T81" si="58">T80/T84</f>
         <v>0.7</v>
       </c>
       <c r="U81" s="45">
-        <f t="shared" ref="U81:V81" si="57">U80/U84</f>
+        <f t="shared" ref="U81" si="59">U80/U84</f>
         <v>0.72</v>
       </c>
       <c r="V81" s="45">
-        <f t="shared" ref="V81:W81" si="58">V80/V84</f>
+        <f t="shared" ref="V81" si="60">V80/V84</f>
         <v>0.72</v>
       </c>
       <c r="W81" s="45">
-        <f t="shared" ref="W81:X81" si="59">W80/W84</f>
+        <f t="shared" ref="W81" si="61">W80/W84</f>
         <v>0.72</v>
       </c>
       <c r="X81" s="45">
-        <f t="shared" ref="X81:Z81" si="60">X80/X84</f>
+        <f t="shared" ref="X81:Z81" si="62">X80/X84</f>
         <v>0.72</v>
       </c>
       <c r="Y81" s="45">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.72</v>
       </c>
       <c r="Z81" s="45">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
       <c r="AA81" s="45">
-        <f t="shared" ref="Z81:AA81" si="61">AA80/AA84</f>
+        <f t="shared" ref="AA81" si="63">AA80/AA84</f>
         <v>0.74</v>
       </c>
       <c r="AC81" s="72">
@@ -27705,95 +27676,95 @@
         <v>72</v>
       </c>
       <c r="C82" s="46">
-        <f t="shared" ref="C82:Q82" si="62">IF(AND(C14&gt;0,C15&lt;0),-(C15)/C14,0)</f>
+        <f t="shared" ref="C82:Q82" si="64">IF(AND(C14&gt;0,C15&lt;0),-(C15)/C14,0)</f>
         <v>0</v>
       </c>
       <c r="D82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="E82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="F82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="G82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="H82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="J82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="K82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="L82" s="46">
-        <f t="shared" ref="L82:P82" si="63">IF(AND(L14&gt;0,L15&lt;0),-(L15)/L14,0)</f>
+        <f t="shared" ref="L82:P82" si="65">IF(AND(L14&gt;0,L15&lt;0),-(L15)/L14,0)</f>
         <v>2.5222551928783383E-2</v>
       </c>
       <c r="M82" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>1.7867778439547351E-2</v>
       </c>
       <c r="N82" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="O82" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.24719101123595505</v>
       </c>
       <c r="P82" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>2.9081295439524125E-2</v>
       </c>
       <c r="Q82" s="46">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.13712737127371274</v>
       </c>
       <c r="T82" s="46">
-        <f t="shared" ref="T82:Z82" si="64">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
+        <f t="shared" ref="T82:Z82" si="66">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
         <v>3.4810126582278479E-2</v>
       </c>
       <c r="U82" s="46">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.04</v>
       </c>
       <c r="V82" s="46">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>4.2253521126760563E-2</v>
       </c>
       <c r="W82" s="46">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>8.130081300813009E-3</v>
       </c>
       <c r="X82" s="46">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.10586319218241043</v>
       </c>
       <c r="Y82" s="46">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.16124469589816123</v>
       </c>
       <c r="Z82" s="46">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.13425925925925927</v>
       </c>
       <c r="AA82" s="46">
-        <f t="shared" ref="T82:AA82" si="65">IF(AND(AA14&gt;0,AA15&lt;0),-(AA15)/AA14,0)</f>
+        <f t="shared" ref="AA82" si="67">IF(AND(AA14&gt;0,AA15&lt;0),-(AA15)/AA14,0)</f>
         <v>0.14019933554817277</v>
       </c>
       <c r="AC82" s="46">
@@ -27933,42 +27904,42 @@
       <c r="J88" s="48"/>
       <c r="K88" s="48"/>
       <c r="L88" s="48">
-        <f t="shared" ref="L88:L92" si="66">IF(K5=0,
+        <f t="shared" ref="L88:L92" si="68">IF(K5=0,
 IF(L5=0,0,IF(L5&gt;0,1,-1)),
 (L5-K5)/ABS(K5)
 )</f>
         <v>1</v>
       </c>
       <c r="M88" s="48">
-        <f t="shared" ref="M88:M93" si="67">IF(L5=0,
+        <f t="shared" ref="M88:M93" si="69">IF(L5=0,
 IF(M5=0,0,IF(M5&gt;0,1,-1)),
 (M5-L5)/ABS(L5)
 )</f>
         <v>9.1751708641512969E-2</v>
       </c>
       <c r="N88" s="48">
-        <f t="shared" ref="N88:N93" si="68">IF(M5=0,
+        <f t="shared" ref="N88:N93" si="70">IF(M5=0,
 IF(N5=0,0,IF(N5&gt;0,1,-1)),
 (N5-M5)/ABS(M5)
 )</f>
         <v>-0.36677814938684505</v>
       </c>
       <c r="O88" s="48">
-        <f t="shared" ref="O88:O93" si="69">IF(N5=0,
+        <f t="shared" ref="O88:O93" si="71">IF(N5=0,
 IF(O5=0,0,IF(O5&gt;0,1,-1)),
 (O5-N5)/ABS(N5)
 )</f>
         <v>-0.11281148429035753</v>
       </c>
       <c r="P88" s="48">
-        <f t="shared" ref="P88:P93" si="70">IF(O5=0,
+        <f t="shared" ref="P88:P93" si="72">IF(O5=0,
 IF(P5=0,0,IF(P5&gt;0,1,-1)),
 (P5-O5)/ABS(O5)
 )</f>
         <v>0.38864295527400394</v>
       </c>
       <c r="Q88" s="48">
-        <f t="shared" ref="M88:Q92" si="71">IF(P5=0,
+        <f t="shared" ref="Q88:Q92" si="73">IF(P5=0,
 IF(Q5=0,0,IF(Q5&gt;0,1,-1)),
 (Q5-P5)/ABS(P5)
 )</f>
@@ -27977,56 +27948,56 @@
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
       <c r="T88" s="48">
-        <f t="shared" ref="T88:T94" si="72">IF(S5=0,
+        <f t="shared" ref="T88:T94" si="74">IF(S5=0,
 IF(T5=0,0,IF(T5&gt;0,1,-1)),
 (T5-S5)/ABS(S5)
 )</f>
         <v>1</v>
       </c>
       <c r="U88" s="48">
-        <f t="shared" ref="U88:U94" si="73">IF(T5=0,
+        <f t="shared" ref="U88:U94" si="75">IF(T5=0,
 IF(U5=0,0,IF(U5&gt;0,1,-1)),
 (U5-T5)/ABS(T5)
 )</f>
         <v>7.2416974169741702E-2</v>
       </c>
       <c r="V88" s="48">
-        <f t="shared" ref="V88:V94" si="74">IF(U5=0,
+        <f t="shared" ref="V88:V94" si="76">IF(U5=0,
 IF(V5=0,0,IF(V5&gt;0,1,-1)),
 (V5-U5)/ABS(U5)
 )</f>
         <v>-7.0967741935483872E-2</v>
       </c>
       <c r="W88" s="48">
-        <f t="shared" ref="W88:W94" si="75">IF(V5=0,
+        <f t="shared" ref="W88:W94" si="77">IF(V5=0,
 IF(W5=0,0,IF(W5&gt;0,1,-1)),
 (W5-V5)/ABS(V5)
 )</f>
         <v>0.13148148148148148</v>
       </c>
       <c r="X88" s="48">
-        <f t="shared" ref="X88:X94" si="76">IF(W5=0,
+        <f t="shared" ref="X88:X94" si="78">IF(W5=0,
 IF(X5=0,0,IF(X5&gt;0,1,-1)),
 (X5-W5)/ABS(W5)
 )</f>
         <v>7.5695581014729951E-2</v>
       </c>
       <c r="Y88" s="48">
-        <f t="shared" ref="Y88:Y94" si="77">IF(X5=0,
+        <f t="shared" ref="Y88:Y94" si="79">IF(X5=0,
 IF(Y5=0,0,IF(Y5&gt;0,1,-1)),
 (Y5-X5)/ABS(X5)
 )</f>
         <v>7.4553062000760742E-2</v>
       </c>
       <c r="Z88" s="48">
-        <f t="shared" ref="Z88:Z94" si="78">IF(Y5=0,
+        <f t="shared" ref="Z88:Z94" si="80">IF(Y5=0,
 IF(Z5=0,0,IF(Z5&gt;0,1,-1)),
 (Z5-Y5)/ABS(Y5)
 )</f>
         <v>0.10159292035398231</v>
       </c>
       <c r="AA88" s="48">
-        <f t="shared" ref="T88:AA92" si="79">IF(Z5=0,
+        <f t="shared" ref="AA88:AA92" si="81">IF(Z5=0,
 IF(AA5=0,0,IF(AA5&gt;0,1,-1)),
 (AA5-Z5)/ABS(Z5)
 )</f>
@@ -28051,59 +28022,59 @@
       <c r="J89" s="50"/>
       <c r="K89" s="50"/>
       <c r="L89" s="50">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M89" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>5.5126223596084489E-2</v>
       </c>
       <c r="N89" s="50">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>-0.2635498046875</v>
       </c>
       <c r="O89" s="50">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-0.16873860434278137</v>
       </c>
       <c r="P89" s="50">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.17587238285144566</v>
       </c>
       <c r="Q89" s="50">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.12548753603527218</v>
       </c>
       <c r="T89" s="50">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="U89" s="50">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>4.05777166437414E-2</v>
       </c>
       <c r="V89" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-7.4686054196959686E-2</v>
       </c>
       <c r="W89" s="50">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>9.285714285714286E-2</v>
       </c>
       <c r="X89" s="50">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>4.0522875816993466E-2</v>
       </c>
       <c r="Y89" s="50">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>3.5804020100502515E-2</v>
       </c>
       <c r="Z89" s="50">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>9.7028502122498486E-3</v>
       </c>
       <c r="AA89" s="50">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>3.9639639639639637E-2</v>
       </c>
       <c r="AC89" s="68"/>
@@ -28123,61 +28094,61 @@
       <c r="J90" s="48"/>
       <c r="K90" s="48"/>
       <c r="L90" s="48">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M90" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.1892355159410353</v>
       </c>
       <c r="N90" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>-0.61055059094840014</v>
       </c>
       <c r="O90" s="48">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0.13693560325684678</v>
       </c>
       <c r="P90" s="48">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>1.0833333333333333</v>
       </c>
       <c r="Q90" s="48">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.73687499999999995</v>
       </c>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
       <c r="T90" s="48">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="U90" s="48">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.13725490196078433</v>
       </c>
       <c r="V90" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-6.4039408866995079E-2</v>
       </c>
       <c r="W90" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.20263157894736841</v>
       </c>
       <c r="X90" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.13457330415754923</v>
       </c>
       <c r="Y90" s="48">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.13404050144648022</v>
       </c>
       <c r="Z90" s="48">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0.23044217687074831</v>
       </c>
       <c r="AA90" s="48">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.31167933655839669</v>
       </c>
       <c r="AB90" s="1"/>
@@ -28199,59 +28170,59 @@
       <c r="J91" s="50"/>
       <c r="K91" s="50"/>
       <c r="L91" s="50">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M91" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>4.2081949058693245E-2</v>
       </c>
       <c r="N91" s="50">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>-0.153028692879915</v>
       </c>
       <c r="O91" s="50">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-0.1794228356336261</v>
       </c>
       <c r="P91" s="50">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.10703363914373089</v>
       </c>
       <c r="Q91" s="50">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>4.2817679558011051E-2</v>
       </c>
       <c r="T91" s="50">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="U91" s="50">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>1.6574585635359115E-2</v>
       </c>
       <c r="V91" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-2.1739130434782608E-2</v>
       </c>
       <c r="W91" s="50">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>-5.5555555555555558E-3</v>
       </c>
       <c r="X91" s="50">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>3.9106145251396648E-2</v>
       </c>
       <c r="Y91" s="50">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>5.3763440860215058E-3</v>
       </c>
       <c r="Z91" s="50">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>3.7433155080213901E-2</v>
       </c>
       <c r="AA91" s="50">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>-3.0927835051546393E-2</v>
       </c>
       <c r="AC91" s="68"/>
@@ -28270,59 +28241,59 @@
       <c r="J92" s="50"/>
       <c r="K92" s="50"/>
       <c r="L92" s="50">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M92" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>0.11354581673306773</v>
       </c>
       <c r="N92" s="50">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>-0.12164579606440072</v>
       </c>
       <c r="O92" s="50">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-6.313645621181263E-2</v>
       </c>
       <c r="P92" s="50">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.21956521739130436</v>
       </c>
       <c r="Q92" s="50">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>2.8520499108734401E-2</v>
       </c>
       <c r="T92" s="50">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="U92" s="50">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>7.7519379844961239E-2</v>
       </c>
       <c r="V92" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="W92" s="50">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.1079136690647482</v>
       </c>
       <c r="X92" s="50">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>-6.4935064935064929E-2</v>
       </c>
       <c r="Y92" s="50">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>-6.9444444444444441E-3</v>
       </c>
       <c r="Z92" s="50">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AA92" s="50">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.7972027972027972E-2</v>
       </c>
       <c r="AC92" s="68"/>
@@ -28348,58 +28319,58 @@
         <v>1</v>
       </c>
       <c r="M93" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>6.2456140350877196E-2</v>
       </c>
       <c r="N93" s="50">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.11822985468956407</v>
       </c>
       <c r="O93" s="50">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-0.35971647962197284</v>
       </c>
       <c r="P93" s="50">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.20848708487084872</v>
       </c>
       <c r="Q93" s="50">
-        <f t="shared" ref="N93:Q93" si="80">IF(P10=0,
+        <f t="shared" ref="Q93" si="82">IF(P10=0,
 IF(Q10=0,0,IF(Q10&gt;0,1,-1)),
 (Q10-P10)/ABS(P10)
 )</f>
         <v>0.11755725190839694</v>
       </c>
       <c r="T93" s="50">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="U93" s="50">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>4.1800643086816719E-2</v>
       </c>
       <c r="V93" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>1.5432098765432098E-2</v>
       </c>
       <c r="W93" s="50">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>5.1671732522796353E-2</v>
       </c>
       <c r="X93" s="50">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>-8.670520231213872E-3</v>
       </c>
       <c r="Y93" s="50">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>-2.9154518950437316E-2</v>
       </c>
       <c r="Z93" s="50">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0.34834834834834832</v>
       </c>
       <c r="AA93" s="50">
-        <f t="shared" ref="T93:AA93" si="81">IF(Z10=0,
+        <f t="shared" ref="AA93" si="83">IF(Z10=0,
 IF(AA10=0,0,IF(AA10&gt;0,1,-1)),
 (AA10-Z10)/ABS(Z10)
 )</f>
@@ -28466,35 +28437,35 @@
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
       <c r="T94" s="48">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="U94" s="48">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.21091811414392059</v>
       </c>
       <c r="V94" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-0.11680327868852459</v>
       </c>
       <c r="W94" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.31786542923433875</v>
       </c>
       <c r="X94" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.22183098591549297</v>
       </c>
       <c r="Y94" s="48">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.21469740634005763</v>
       </c>
       <c r="Z94" s="48">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0.18386714116251482</v>
       </c>
       <c r="AA94" s="48">
-        <f t="shared" ref="T94:AA94" si="82">IF(Z11=0,
+        <f t="shared" ref="AA94" si="84">IF(Z11=0,
 IF(AA11=0,0,IF(AA11&gt;0,1,-1)),
 (AA11-Z11)/ABS(Z11)
 )</f>
@@ -28520,100 +28491,85 @@
       <c r="J95" s="52"/>
       <c r="K95" s="52"/>
       <c r="L95" s="52">
-        <f>IF(K14=0,
+        <f t="shared" ref="L95:Q95" si="85">IF(K14=0,
 IF(L14=0,0,IF(L14&gt;0,1,-1)),
 (L14-K14)/ABS(K14)
 )</f>
         <v>1</v>
       </c>
       <c r="M95" s="52">
-        <f>IF(L14=0,
-IF(M14=0,0,IF(M14&gt;0,1,-1)),
-(M14-L14)/ABS(L14)
-)</f>
+        <f t="shared" si="85"/>
         <v>0.24554896142433236</v>
       </c>
       <c r="N95" s="52">
-        <f>IF(M14=0,
-IF(N14=0,0,IF(N14&gt;0,1,-1)),
-(N14-M14)/ABS(M14)
-)</f>
+        <f t="shared" si="85"/>
         <v>-1.2954139368671829</v>
       </c>
       <c r="O95" s="52">
-        <f>IF(N14=0,
-IF(O14=0,0,IF(O14&gt;0,1,-1)),
-(O14-N14)/ABS(N14)
-)</f>
+        <f t="shared" si="85"/>
         <v>1.8971774193548387</v>
       </c>
       <c r="P95" s="52">
-        <f>IF(O14=0,
-IF(P14=0,0,IF(P14&gt;0,1,-1)),
-(P14-O14)/ABS(O14)
-)</f>
+        <f t="shared" si="85"/>
         <v>2.4</v>
       </c>
       <c r="Q95" s="52">
-        <f>IF(P14=0,
-IF(Q14=0,0,IF(Q14&gt;0,1,-1)),
-(Q14-P14)/ABS(P14)
-)</f>
+        <f t="shared" si="85"/>
         <v>1.4388631857237277</v>
       </c>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
       <c r="T95" s="52">
-        <f t="shared" ref="T95" si="83">IF(S14=0,
+        <f t="shared" ref="T95" si="86">IF(S14=0,
 IF(T14=0,0,IF(T14&gt;0,1,-1)),
 (T14-S14)/ABS(S14)
 )</f>
         <v>1</v>
       </c>
       <c r="U95" s="52">
-        <f t="shared" ref="U95" si="84">IF(T14=0,
+        <f t="shared" ref="U95" si="87">IF(T14=0,
 IF(U14=0,0,IF(U14&gt;0,1,-1)),
 (U14-T14)/ABS(T14)
 )</f>
         <v>0.10759493670886076</v>
       </c>
       <c r="V95" s="52">
-        <f t="shared" ref="V95" si="85">IF(U14=0,
+        <f t="shared" ref="V95" si="88">IF(U14=0,
 IF(V14=0,0,IF(V14&gt;0,1,-1)),
 (V14-U14)/ABS(U14)
 )</f>
         <v>1.4285714285714285E-2</v>
       </c>
       <c r="W95" s="52">
-        <f t="shared" ref="W95" si="86">IF(V14=0,
+        <f t="shared" ref="W95" si="89">IF(V14=0,
 IF(W14=0,0,IF(W14&gt;0,1,-1)),
 (W14-V14)/ABS(V14)
 )</f>
         <v>0.38591549295774646</v>
       </c>
       <c r="X95" s="52">
-        <f t="shared" ref="X95" si="87">IF(W14=0,
+        <f t="shared" ref="X95" si="90">IF(W14=0,
 IF(X14=0,0,IF(X14&gt;0,1,-1)),
 (X14-W14)/ABS(W14)
 )</f>
         <v>0.24796747967479674</v>
       </c>
       <c r="Y95" s="52">
-        <f t="shared" ref="Y95" si="88">IF(X14=0,
+        <f t="shared" ref="Y95" si="91">IF(X14=0,
 IF(Y14=0,0,IF(Y14&gt;0,1,-1)),
 (Y14-X14)/ABS(X14)
 )</f>
         <v>0.15146579804560262</v>
       </c>
       <c r="Z95" s="52">
-        <f t="shared" ref="Z95" si="89">IF(Y14=0,
+        <f t="shared" ref="Z95" si="92">IF(Y14=0,
 IF(Z14=0,0,IF(Z14&gt;0,1,-1)),
 (Z14-Y14)/ABS(Y14)
 )</f>
         <v>0.22206506364922207</v>
       </c>
       <c r="AA95" s="52">
-        <f t="shared" ref="T95:AA95" si="90">IF(Z14=0,
+        <f t="shared" ref="AA95" si="93">IF(Z14=0,
 IF(AA14=0,0,IF(AA14&gt;0,1,-1)),
 (AA14-Z14)/ABS(Z14)
 )</f>
@@ -28639,100 +28595,85 @@
       <c r="J96" s="52"/>
       <c r="K96" s="52"/>
       <c r="L96" s="52">
-        <f>IF(K17=0,
+        <f t="shared" ref="L96:Q96" si="94">IF(K17=0,
 IF(L17=0,0,IF(L17&gt;0,1,-1)),
 (L17-K17)/ABS(K17)
 )</f>
         <v>1</v>
       </c>
       <c r="M96" s="52">
-        <f>IF(L17=0,
-IF(M17=0,0,IF(M17&gt;0,1,-1)),
-(M17-L17)/ABS(L17)
-)</f>
+        <f t="shared" si="94"/>
         <v>0.25494672754946729</v>
       </c>
       <c r="N96" s="52">
-        <f>IF(M17=0,
-IF(N17=0,0,IF(N17&gt;0,1,-1)),
-(N17-M17)/ABS(M17)
-)</f>
+        <f t="shared" si="94"/>
         <v>-1.3208004851425106</v>
       </c>
       <c r="O96" s="52">
-        <f>IF(N17=0,
-IF(O17=0,0,IF(O17&gt;0,1,-1)),
-(O17-N17)/ABS(N17)
-)</f>
+        <f t="shared" si="94"/>
         <v>1.6332703213610587</v>
       </c>
       <c r="P96" s="52">
-        <f>IF(O17=0,
-IF(P17=0,0,IF(P17&gt;0,1,-1)),
-(P17-O17)/ABS(O17)
-)</f>
+        <f t="shared" si="94"/>
         <v>3.3850746268656717</v>
       </c>
       <c r="Q96" s="52">
-        <f>IF(P17=0,
-IF(Q17=0,0,IF(Q17&gt;0,1,-1)),
-(Q17-P17)/ABS(P17)
-)</f>
+        <f t="shared" si="94"/>
         <v>1.1674608577263446</v>
       </c>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
       <c r="T96" s="52">
-        <f t="shared" ref="T96" si="91">IF(S17=0,
+        <f t="shared" ref="T96" si="95">IF(S17=0,
 IF(T17=0,0,IF(T17&gt;0,1,-1)),
 (T17-S17)/ABS(S17)
 )</f>
         <v>1</v>
       </c>
       <c r="U96" s="52">
-        <f t="shared" ref="U96" si="92">IF(T17=0,
+        <f t="shared" ref="U96" si="96">IF(T17=0,
 IF(U17=0,0,IF(U17&gt;0,1,-1)),
 (U17-T17)/ABS(T17)
 )</f>
         <v>0.10163934426229508</v>
       </c>
       <c r="V96" s="52">
-        <f t="shared" ref="V96" si="93">IF(U17=0,
+        <f t="shared" ref="V96" si="97">IF(U17=0,
 IF(V17=0,0,IF(V17&gt;0,1,-1)),
 (V17-U17)/ABS(U17)
 )</f>
         <v>1.1904761904761904E-2</v>
       </c>
       <c r="W96" s="52">
-        <f t="shared" ref="W96" si="94">IF(V17=0,
+        <f t="shared" ref="W96" si="98">IF(V17=0,
 IF(W17=0,0,IF(W17&gt;0,1,-1)),
 (W17-V17)/ABS(V17)
 )</f>
         <v>0.43529411764705883</v>
       </c>
       <c r="X96" s="52">
-        <f t="shared" ref="X96" si="95">IF(W17=0,
+        <f t="shared" ref="X96" si="99">IF(W17=0,
 IF(X17=0,0,IF(X17&gt;0,1,-1)),
 (X17-W17)/ABS(W17)
 )</f>
         <v>0.125</v>
       </c>
       <c r="Y96" s="52">
-        <f t="shared" ref="Y96" si="96">IF(X17=0,
+        <f t="shared" ref="Y96" si="100">IF(X17=0,
 IF(Y17=0,0,IF(Y17&gt;0,1,-1)),
 (Y17-X17)/ABS(X17)
 )</f>
         <v>8.0145719489981782E-2</v>
       </c>
       <c r="Z96" s="52">
-        <f t="shared" ref="Z96" si="97">IF(Y17=0,
+        <f t="shared" ref="Z96" si="101">IF(Y17=0,
 IF(Z17=0,0,IF(Z17&gt;0,1,-1)),
 (Z17-Y17)/ABS(Y17)
 )</f>
         <v>0.26138279932546377</v>
       </c>
       <c r="AA96" s="52">
-        <f t="shared" ref="T96:AA96" si="98">IF(Z17=0,
+        <f t="shared" ref="AA96" si="102">IF(Z17=0,
 IF(AA17=0,0,IF(AA17&gt;0,1,-1)),
 (AA17-Z17)/ABS(Z17)
 )</f>
@@ -28771,59 +28712,59 @@
       <c r="J99" s="50"/>
       <c r="K99" s="50"/>
       <c r="L99" s="50">
-        <f>L7/L5</f>
+        <f t="shared" ref="L99:Q99" si="103">L7/L5</f>
         <v>0.27310176949723808</v>
       </c>
       <c r="M99" s="50">
-        <f>M7/M5</f>
+        <f t="shared" si="103"/>
         <v>0.29748735099905671</v>
       </c>
       <c r="N99" s="50">
-        <f>N7/N5</f>
+        <f t="shared" si="103"/>
         <v>0.1829631635969664</v>
       </c>
       <c r="O99" s="50">
-        <f>O7/O5</f>
+        <f t="shared" si="103"/>
         <v>0.23446802014959547</v>
       </c>
       <c r="P99" s="50">
-        <f>P7/P5</f>
+        <f t="shared" si="103"/>
         <v>0.3517643179070023</v>
       </c>
       <c r="Q99" s="50">
-        <f>Q7/Q5</f>
+        <f t="shared" si="103"/>
         <v>0.45576055760557604</v>
       </c>
       <c r="T99" s="50">
-        <f t="shared" ref="T99:Z99" si="99">T7/T5</f>
+        <f t="shared" ref="T99:Z99" si="104">T7/T5</f>
         <v>0.32933579335793356</v>
       </c>
       <c r="U99" s="50">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>0.34924731182795699</v>
       </c>
       <c r="V99" s="50">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>0.35185185185185186</v>
       </c>
       <c r="W99" s="50">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>0.3739770867430442</v>
       </c>
       <c r="X99" s="50">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>0.39444655762647396</v>
       </c>
       <c r="Y99" s="50">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>0.41628318584070795</v>
       </c>
       <c r="Z99" s="50">
-        <f t="shared" si="99"/>
+        <f t="shared" si="104"/>
         <v>0.46497429305912596</v>
       </c>
       <c r="AA99" s="50">
-        <f t="shared" ref="T99:AA99" si="100">AA7/AA5</f>
+        <f t="shared" ref="AA99" si="105">AA7/AA5</f>
         <v>0.52300909341416368</v>
       </c>
       <c r="AC99" s="50">
@@ -28845,59 +28786,59 @@
       <c r="J100" s="50"/>
       <c r="K100" s="50"/>
       <c r="L100" s="50">
-        <f>L11/L5</f>
+        <f t="shared" ref="L100:Q100" si="106">L11/L5</f>
         <v>0.13968729519707893</v>
       </c>
       <c r="M100" s="50">
-        <f>M11/M5</f>
+        <f t="shared" si="106"/>
         <v>0.16765285996055226</v>
       </c>
       <c r="N100" s="50">
-        <f>N11/N5</f>
+        <f t="shared" si="106"/>
         <v>-4.6316359696641385E-2</v>
       </c>
       <c r="O100" s="50">
-        <f>O11/O5</f>
+        <f t="shared" si="106"/>
         <v>6.8997099679438248E-2</v>
       </c>
       <c r="P100" s="50">
-        <f>P11/P5</f>
+        <f t="shared" si="106"/>
         <v>0.20776080026382324</v>
       </c>
       <c r="Q100" s="50">
-        <f>Q11/Q5</f>
+        <f t="shared" si="106"/>
         <v>0.33571135711357114</v>
       </c>
       <c r="T100" s="50">
-        <f t="shared" ref="T100:Z100" si="101">T11/T5</f>
+        <f t="shared" ref="T100:Z100" si="107">T11/T5</f>
         <v>0.18588560885608857</v>
       </c>
       <c r="U100" s="50">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>0.20989247311827958</v>
       </c>
       <c r="V100" s="50">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>0.19953703703703704</v>
       </c>
       <c r="W100" s="50">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>0.23240589198036007</v>
       </c>
       <c r="X100" s="50">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>0.26397869912514266</v>
       </c>
       <c r="Y100" s="50">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>0.2984070796460177</v>
       </c>
       <c r="Z100" s="50">
-        <f t="shared" si="101"/>
+        <f t="shared" si="107"/>
         <v>0.32069408740359895</v>
       </c>
       <c r="AA100" s="50">
-        <f t="shared" ref="T100:AA100" si="102">AA11/AA5</f>
+        <f t="shared" ref="AA100" si="108">AA11/AA5</f>
         <v>0.42959492973270874</v>
       </c>
       <c r="AC100" s="50">
@@ -28920,61 +28861,61 @@
       <c r="J101" s="55"/>
       <c r="K101" s="55"/>
       <c r="L101" s="55">
-        <f>L109/L5</f>
+        <f t="shared" ref="L101:Q101" si="109">L109/L5</f>
         <v>0.12302218893362045</v>
       </c>
       <c r="M101" s="55">
-        <f>M109/M5</f>
+        <f t="shared" si="109"/>
         <v>0.1414115427493354</v>
       </c>
       <c r="N101" s="55">
-        <f>N109/N5</f>
+        <f t="shared" si="109"/>
         <v>-7.164138678223185E-2</v>
       </c>
       <c r="O101" s="55">
-        <f>O109/O5</f>
+        <f t="shared" si="109"/>
         <v>5.1137230957105782E-2</v>
       </c>
       <c r="P101" s="55">
-        <f>P109/P5</f>
+        <f t="shared" si="109"/>
         <v>0.16148180718918326</v>
       </c>
       <c r="Q101" s="55">
-        <f>Q109/Q5</f>
+        <f t="shared" si="109"/>
         <v>0.26109061090610908</v>
       </c>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
       <c r="T101" s="55">
-        <f t="shared" ref="T101:Z101" si="103">T109/T5</f>
+        <f t="shared" ref="T101:Z101" si="110">T109/T5</f>
         <v>0.14068265682656828</v>
       </c>
       <c r="U101" s="55">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>0.14451612903225808</v>
       </c>
       <c r="V101" s="55">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>0.15740740740740741</v>
       </c>
       <c r="W101" s="55">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>0.19967266775777415</v>
       </c>
       <c r="X101" s="55">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>0.20882464815519208</v>
       </c>
       <c r="Y101" s="55">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>0.20991150442477877</v>
       </c>
       <c r="Z101" s="55">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>0.24035989717223649</v>
       </c>
       <c r="AA101" s="55">
-        <f t="shared" ref="T101:AA101" si="104">AA109/AA5</f>
+        <f t="shared" ref="AA101" si="111">AA109/AA5</f>
         <v>0.35657205841829703</v>
       </c>
       <c r="AB101" s="1"/>
@@ -29004,95 +28945,95 @@
         <v>72</v>
       </c>
       <c r="C104" s="81">
-        <f t="shared" ref="C104:Q104" si="105">IF(AND(C82&gt;=0,C11&gt;=0),C82,0)</f>
+        <f t="shared" ref="C104:Q104" si="112">IF(AND(C82&gt;=0,C11&gt;=0),C82,0)</f>
         <v>0</v>
       </c>
       <c r="D104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="E104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="F104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="G104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="H104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="I104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="J104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="K104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="L104" s="81">
-        <f t="shared" ref="L104:P104" si="106">IF(AND(L82&gt;=0,L11&gt;=0),L82,0)</f>
+        <f t="shared" ref="L104:P104" si="113">IF(AND(L82&gt;=0,L11&gt;=0),L82,0)</f>
         <v>2.5222551928783383E-2</v>
       </c>
       <c r="M104" s="81">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>1.7867778439547351E-2</v>
       </c>
       <c r="N104" s="81">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="O104" s="81">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>0.24719101123595505</v>
       </c>
       <c r="P104" s="81">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>2.9081295439524125E-2</v>
       </c>
       <c r="Q104" s="81">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0.13712737127371274</v>
       </c>
       <c r="T104" s="81">
-        <f t="shared" ref="T104:Z104" si="107">IF(AND(T82&gt;=0,T11&gt;=0),T82,0)</f>
+        <f t="shared" ref="T104:Z104" si="114">IF(AND(T82&gt;=0,T11&gt;=0),T82,0)</f>
         <v>3.4810126582278479E-2</v>
       </c>
       <c r="U104" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>0.04</v>
       </c>
       <c r="V104" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>4.2253521126760563E-2</v>
       </c>
       <c r="W104" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>8.130081300813009E-3</v>
       </c>
       <c r="X104" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>0.10586319218241043</v>
       </c>
       <c r="Y104" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>0.16124469589816123</v>
       </c>
       <c r="Z104" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>0.13425925925925927</v>
       </c>
       <c r="AA104" s="81">
-        <f t="shared" ref="T104:AA104" si="108">IF(AND(AA82&gt;=0,AA11&gt;=0),AA82,0)</f>
+        <f t="shared" ref="AA104" si="115">IF(AND(AA82&gt;=0,AA11&gt;=0),AA82,0)</f>
         <v>0.14019933554817277</v>
       </c>
       <c r="AC104" s="81">
@@ -29114,59 +29055,59 @@
       <c r="J105" s="25"/>
       <c r="K105" s="25"/>
       <c r="L105" s="25">
-        <f>L28+L33</f>
+        <f t="shared" ref="L105:Q105" si="116">L28+L33</f>
         <v>1209</v>
       </c>
       <c r="M105" s="25">
-        <f>M28+M33</f>
+        <f t="shared" si="116"/>
         <v>615</v>
       </c>
       <c r="N105" s="25">
-        <f>N28+N33</f>
+        <f t="shared" si="116"/>
         <v>786</v>
       </c>
       <c r="O105" s="25">
-        <f>O28+O33</f>
+        <f t="shared" si="116"/>
         <v>1358</v>
       </c>
       <c r="P105" s="25">
-        <f>P28+P33</f>
+        <f t="shared" si="116"/>
         <v>891</v>
       </c>
       <c r="Q105" s="25">
-        <f>Q28+Q33</f>
+        <f t="shared" si="116"/>
         <v>1704</v>
       </c>
       <c r="T105" s="25">
-        <f t="shared" ref="T105:Z105" si="109">T28+T33</f>
+        <f t="shared" ref="T105:Z105" si="117">T28+T33</f>
         <v>1239</v>
       </c>
       <c r="U105" s="25">
-        <f t="shared" si="109"/>
+        <f t="shared" si="117"/>
         <v>1238</v>
       </c>
       <c r="V105" s="25">
-        <f t="shared" si="109"/>
+        <f t="shared" si="117"/>
         <v>814</v>
       </c>
       <c r="W105" s="25">
-        <f t="shared" si="109"/>
+        <f t="shared" si="117"/>
         <v>891</v>
       </c>
       <c r="X105" s="25">
-        <f t="shared" si="109"/>
+        <f t="shared" si="117"/>
         <v>1112</v>
       </c>
       <c r="Y105" s="25">
-        <f t="shared" si="109"/>
+        <f t="shared" si="117"/>
         <v>1046</v>
       </c>
       <c r="Z105" s="25">
-        <f t="shared" si="109"/>
+        <f t="shared" si="117"/>
         <v>1146</v>
       </c>
       <c r="AA105" s="25">
-        <f t="shared" ref="T105:AA105" si="110">AA28+AA33</f>
+        <f t="shared" ref="AA105" si="118">AA28+AA33</f>
         <v>1704</v>
       </c>
       <c r="AC105" s="25">
@@ -29206,59 +29147,59 @@
         <v>0</v>
       </c>
       <c r="L106" s="25">
-        <f>L38+L40</f>
+        <f t="shared" ref="L106:Q106" si="119">L38+L40</f>
         <v>5139</v>
       </c>
       <c r="M106" s="25">
-        <f>M38+M40</f>
+        <f t="shared" si="119"/>
         <v>5646</v>
       </c>
       <c r="N106" s="25">
-        <f>N38+N40</f>
+        <f t="shared" si="119"/>
         <v>5451</v>
       </c>
       <c r="O106" s="25">
-        <f>O38+O40</f>
+        <f t="shared" si="119"/>
         <v>5674</v>
       </c>
       <c r="P106" s="25">
-        <f>P38+P40</f>
+        <f t="shared" si="119"/>
         <v>4995</v>
       </c>
       <c r="Q106" s="25">
-        <f>Q38+Q40</f>
+        <f t="shared" si="119"/>
         <v>3565</v>
       </c>
       <c r="T106" s="25">
-        <f t="shared" ref="T106:Z106" si="111">T38+T40</f>
+        <f t="shared" ref="T106:Z106" si="120">T38+T40</f>
         <v>5676</v>
       </c>
       <c r="U106" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="120"/>
         <v>5679</v>
       </c>
       <c r="V106" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="120"/>
         <v>5146</v>
       </c>
       <c r="W106" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="120"/>
         <v>4995</v>
       </c>
       <c r="X106" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="120"/>
         <v>4994</v>
       </c>
       <c r="Y106" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="120"/>
         <v>4499</v>
       </c>
       <c r="Z106" s="25">
-        <f t="shared" si="111"/>
+        <f t="shared" si="120"/>
         <v>3863</v>
       </c>
       <c r="AA106" s="25">
-        <f t="shared" ref="T106:AA106" si="112">AA38+AA40</f>
+        <f t="shared" ref="AA106" si="121">AA38+AA40</f>
         <v>3565</v>
       </c>
       <c r="AC106" s="25">
@@ -29280,27 +29221,27 @@
       <c r="J107" s="25"/>
       <c r="K107" s="25"/>
       <c r="L107" s="126">
-        <f>L11*(1-L104)</f>
+        <f t="shared" ref="L107:Q107" si="122">L11*(1-L104)</f>
         <v>1454.3679525222551</v>
       </c>
       <c r="M107" s="126">
-        <f>M11*(1-M104)</f>
+        <f t="shared" si="122"/>
         <v>1920.0684931506848</v>
       </c>
       <c r="N107" s="126">
-        <f>N11*(1-N104)</f>
+        <f t="shared" si="122"/>
         <v>-342</v>
       </c>
       <c r="O107" s="126">
-        <f>O11*(1-O104)</f>
+        <f t="shared" si="122"/>
         <v>340.26966292134836</v>
       </c>
       <c r="P107" s="25">
-        <f>P11*(1-P104)</f>
+        <f t="shared" si="122"/>
         <v>1835.0363516192995</v>
       </c>
       <c r="Q107" s="25">
-        <f>Q11*(1-Q104)</f>
+        <f t="shared" si="122"/>
         <v>3532.6005420054198</v>
       </c>
       <c r="T107" s="67"/>
@@ -29330,59 +29271,59 @@
       <c r="J108" s="25"/>
       <c r="K108" s="25"/>
       <c r="L108" s="126">
-        <f>L59+L60</f>
+        <f t="shared" ref="L108:Q108" si="123">L59+L60</f>
         <v>-498</v>
       </c>
       <c r="M108" s="126">
-        <f>M59+M60</f>
+        <f t="shared" si="123"/>
         <v>-381</v>
       </c>
       <c r="N108" s="126">
-        <f>N59+N60</f>
+        <f t="shared" si="123"/>
         <v>-316</v>
       </c>
       <c r="O108" s="126">
-        <f>O59+O60</f>
+        <f t="shared" si="123"/>
         <v>-254</v>
       </c>
       <c r="P108" s="126">
-        <f>P59+P60</f>
+        <f t="shared" si="123"/>
         <v>-265</v>
       </c>
       <c r="Q108" s="126">
-        <f>Q59+Q60</f>
+        <f t="shared" si="123"/>
         <v>-569</v>
       </c>
       <c r="T108" s="126">
-        <f t="shared" ref="T108:Z108" si="113">T59+T60</f>
+        <f t="shared" ref="T108:Z108" si="124">T59+T60</f>
         <v>-68</v>
       </c>
       <c r="U108" s="126">
-        <f t="shared" si="113"/>
+        <f t="shared" si="124"/>
         <v>-71</v>
       </c>
       <c r="V108" s="126">
-        <f t="shared" si="113"/>
+        <f t="shared" si="124"/>
         <v>-43</v>
       </c>
       <c r="W108" s="126">
-        <f t="shared" si="113"/>
+        <f t="shared" si="124"/>
         <v>-83</v>
       </c>
       <c r="X108" s="126">
-        <f t="shared" si="113"/>
+        <f t="shared" si="124"/>
         <v>-105</v>
       </c>
       <c r="Y108" s="126">
-        <f t="shared" si="113"/>
+        <f t="shared" si="124"/>
         <v>-116</v>
       </c>
       <c r="Z108" s="126">
-        <f t="shared" si="113"/>
+        <f t="shared" si="124"/>
         <v>-161</v>
       </c>
       <c r="AA108" s="126">
-        <f t="shared" ref="T108:AA108" si="114">AA59+AA60</f>
+        <f t="shared" ref="AA108" si="125">AA59+AA60</f>
         <v>-187</v>
       </c>
       <c r="AC108" s="126">
@@ -29404,59 +29345,59 @@
       <c r="J109" s="25"/>
       <c r="K109" s="25"/>
       <c r="L109" s="126">
-        <f>L16+L17</f>
+        <f t="shared" ref="L109:Q109" si="126">L16+L17</f>
         <v>1314</v>
       </c>
       <c r="M109" s="126">
-        <f>M16+M17</f>
+        <f t="shared" si="126"/>
         <v>1649</v>
       </c>
       <c r="N109" s="126">
-        <f>N16+N17</f>
+        <f t="shared" si="126"/>
         <v>-529</v>
       </c>
       <c r="O109" s="126">
-        <f>O16+O17</f>
+        <f t="shared" si="126"/>
         <v>335</v>
       </c>
       <c r="P109" s="126">
-        <f>P16+P17</f>
+        <f t="shared" si="126"/>
         <v>1469</v>
       </c>
       <c r="Q109" s="126">
-        <f>Q16+Q17</f>
+        <f t="shared" si="126"/>
         <v>3184</v>
       </c>
       <c r="T109" s="126">
-        <f t="shared" ref="T109:Z109" si="115">T16+T17</f>
+        <f t="shared" ref="T109:Z109" si="127">T16+T17</f>
         <v>305</v>
       </c>
       <c r="U109" s="126">
-        <f t="shared" si="115"/>
+        <f t="shared" si="127"/>
         <v>336</v>
       </c>
       <c r="V109" s="126">
-        <f t="shared" si="115"/>
+        <f t="shared" si="127"/>
         <v>340</v>
       </c>
       <c r="W109" s="126">
-        <f t="shared" si="115"/>
+        <f t="shared" si="127"/>
         <v>488</v>
       </c>
       <c r="X109" s="126">
-        <f t="shared" si="115"/>
+        <f t="shared" si="127"/>
         <v>549</v>
       </c>
       <c r="Y109" s="126">
-        <f t="shared" si="115"/>
+        <f t="shared" si="127"/>
         <v>593</v>
       </c>
       <c r="Z109" s="126">
-        <f t="shared" si="115"/>
+        <f t="shared" si="127"/>
         <v>748</v>
       </c>
       <c r="AA109" s="126">
-        <f t="shared" ref="T109:AA109" si="116">AA16+AA17</f>
+        <f t="shared" ref="AA109" si="128">AA16+AA17</f>
         <v>1294</v>
       </c>
       <c r="AC109" s="126">
@@ -29478,59 +29419,59 @@
       <c r="J110" s="25"/>
       <c r="K110" s="25"/>
       <c r="L110" s="126">
-        <f>L48+L47</f>
+        <f t="shared" ref="L110:Q110" si="129">L48+L47</f>
         <v>631</v>
       </c>
       <c r="M110" s="126">
-        <f>M48+M47</f>
+        <f t="shared" si="129"/>
         <v>109</v>
       </c>
       <c r="N110" s="126">
-        <f>N48+N47</f>
+        <f t="shared" si="129"/>
         <v>-1199</v>
       </c>
       <c r="O110" s="126">
-        <f>O48+O47</f>
+        <f t="shared" si="129"/>
         <v>-1491</v>
       </c>
       <c r="P110" s="126">
-        <f>P48+P47</f>
+        <f t="shared" si="129"/>
         <v>-453</v>
       </c>
       <c r="Q110" s="126">
-        <f>Q48+Q47</f>
+        <f t="shared" si="129"/>
         <v>2167</v>
       </c>
       <c r="T110" s="126">
-        <f t="shared" ref="T110:Z110" si="117">T48+T47</f>
+        <f t="shared" ref="T110:Z110" si="130">T48+T47</f>
         <v>-1300</v>
       </c>
       <c r="U110" s="126">
-        <f t="shared" si="117"/>
+        <f t="shared" si="130"/>
         <v>-1079</v>
       </c>
       <c r="V110" s="126">
-        <f t="shared" si="117"/>
+        <f t="shared" si="130"/>
         <v>-829</v>
       </c>
       <c r="W110" s="126">
-        <f t="shared" si="117"/>
+        <f t="shared" si="130"/>
         <v>-453</v>
       </c>
       <c r="X110" s="126">
-        <f t="shared" si="117"/>
+        <f t="shared" si="130"/>
         <v>-63</v>
       </c>
       <c r="Y110" s="126">
-        <f t="shared" si="117"/>
+        <f t="shared" si="130"/>
         <v>459</v>
       </c>
       <c r="Z110" s="126">
-        <f t="shared" si="117"/>
+        <f t="shared" si="130"/>
         <v>1095</v>
       </c>
       <c r="AA110" s="126">
-        <f t="shared" ref="T110:AA110" si="118">AA48+AA47</f>
+        <f t="shared" ref="AA110" si="131">AA48+AA47</f>
         <v>2167</v>
       </c>
       <c r="AC110" s="126">
@@ -29620,7 +29561,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29637,64 +29578,64 @@
       <c r="J115" s="26"/>
       <c r="K115" s="26"/>
       <c r="L115" s="65">
-        <f>L114/L84</f>
+        <f t="shared" ref="L115:Q115" si="132">L114/L84</f>
         <v>87.03</v>
       </c>
       <c r="M115" s="65">
-        <f>M114/M84</f>
+        <f t="shared" si="132"/>
         <v>69.09</v>
       </c>
       <c r="N115" s="65">
-        <f>N114/N84</f>
+        <f t="shared" si="132"/>
         <v>61.87</v>
       </c>
       <c r="O115" s="65">
-        <f>O114/O84</f>
+        <f t="shared" si="132"/>
         <v>103.27</v>
       </c>
       <c r="P115" s="65">
-        <f>P114/P84</f>
+        <f t="shared" si="132"/>
         <v>141.44</v>
       </c>
       <c r="Q115" s="65">
-        <f>Q114/Q84</f>
+        <f t="shared" si="132"/>
         <v>820.16</v>
       </c>
       <c r="T115" s="65">
-        <f t="shared" ref="T115:Z115" si="119">T114/T84</f>
+        <f t="shared" ref="T115:Z115" si="133">T114/T84</f>
         <v>108.74</v>
       </c>
       <c r="U115" s="65">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
         <v>87.39</v>
       </c>
       <c r="V115" s="65">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
         <v>84.92</v>
       </c>
       <c r="W115" s="65">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
         <v>141.44</v>
       </c>
       <c r="X115" s="65">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
         <v>252.79</v>
       </c>
       <c r="Y115" s="65">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
         <v>286.83999999999997</v>
       </c>
       <c r="Z115" s="65">
-        <f t="shared" si="119"/>
+        <f t="shared" si="133"/>
         <v>375.01</v>
       </c>
       <c r="AA115" s="65">
-        <f t="shared" ref="T115:AA115" si="120">AA114/AA84</f>
+        <f t="shared" ref="AA115" si="134">AA114/AA84</f>
         <v>820.16</v>
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29734,27 +29675,27 @@
         <v>99</v>
       </c>
       <c r="L119" s="74">
-        <f>L109/L5</f>
+        <f t="shared" ref="L119:Q119" si="135">L109/L5</f>
         <v>0.12302218893362045</v>
       </c>
       <c r="M119" s="74">
-        <f>M109/M5</f>
+        <f t="shared" si="135"/>
         <v>0.1414115427493354</v>
       </c>
       <c r="N119" s="74">
-        <f>N109/N5</f>
+        <f t="shared" si="135"/>
         <v>-7.164138678223185E-2</v>
       </c>
       <c r="O119" s="74">
-        <f>O109/O5</f>
+        <f t="shared" si="135"/>
         <v>5.1137230957105782E-2</v>
       </c>
       <c r="P119" s="74">
-        <f>P109/P5</f>
+        <f t="shared" si="135"/>
         <v>0.16148180718918326</v>
       </c>
       <c r="Q119" s="74">
-        <f>Q109/Q5</f>
+        <f t="shared" si="135"/>
         <v>0.26109061090610908</v>
       </c>
       <c r="T119" s="77"/>
@@ -29775,27 +29716,27 @@
         <v>100</v>
       </c>
       <c r="L120" s="75">
-        <f>L5/L36</f>
+        <f t="shared" ref="L120:Q120" si="136">L5/L36</f>
         <v>1.2312391930835735</v>
       </c>
       <c r="M120" s="75">
-        <f>M5/M36</f>
+        <f t="shared" si="136"/>
         <v>1.3037790697674418</v>
       </c>
       <c r="N120" s="75">
-        <f>N5/N36</f>
+        <f t="shared" si="136"/>
         <v>0.97723663313922715</v>
       </c>
       <c r="O120" s="75">
-        <f>O5/O36</f>
+        <f t="shared" si="136"/>
         <v>0.84649179480553038</v>
       </c>
       <c r="P120" s="75">
-        <f>P5/P36</f>
+        <f t="shared" si="136"/>
         <v>1.133865137729029</v>
       </c>
       <c r="Q120" s="75">
-        <f>Q5/Q36</f>
+        <f t="shared" si="136"/>
         <v>1.2229241877256318</v>
       </c>
       <c r="T120" s="78"/>
@@ -29816,19 +29757,19 @@
         <v>101</v>
       </c>
       <c r="L121" s="76">
-        <f t="shared" ref="L121:O121" si="121">L119*L120</f>
+        <f t="shared" ref="L121:O121" si="137">L119*L120</f>
         <v>0.15146974063400578</v>
       </c>
       <c r="M121" s="76">
-        <f t="shared" si="121"/>
+        <f t="shared" si="137"/>
         <v>0.18436940966010734</v>
       </c>
       <c r="N121" s="76">
-        <f t="shared" si="121"/>
+        <f t="shared" si="137"/>
         <v>-7.0010587612493388E-2</v>
       </c>
       <c r="O121" s="76">
-        <f t="shared" si="121"/>
+        <f t="shared" si="137"/>
         <v>4.3287246414265401E-2</v>
       </c>
       <c r="P121" s="76">
@@ -29857,27 +29798,27 @@
         <v>102</v>
       </c>
       <c r="L122" s="75">
-        <f>L36/L48</f>
+        <f t="shared" ref="L122:Q122" si="138">L36/L48</f>
         <v>13.748019017432647</v>
       </c>
       <c r="M122" s="75">
-        <f>M36/M48</f>
+        <f t="shared" si="138"/>
         <v>82.055045871559628</v>
       </c>
       <c r="N122" s="75">
-        <f>N36/N48</f>
+        <f t="shared" si="138"/>
         <v>-6.3019182652210173</v>
       </c>
       <c r="O122" s="75">
-        <f>O36/O48</f>
+        <f t="shared" si="138"/>
         <v>-5.1904761904761907</v>
       </c>
       <c r="P122" s="75">
-        <f>P36/P48</f>
+        <f t="shared" si="138"/>
         <v>-17.710816777041941</v>
       </c>
       <c r="Q122" s="75">
-        <f>Q36/Q48</f>
+        <f t="shared" si="138"/>
         <v>4.6017535763728654</v>
       </c>
       <c r="T122" s="80"/>
@@ -29898,19 +29839,19 @@
         <v>103</v>
       </c>
       <c r="L123" s="76">
-        <f t="shared" ref="L123:O123" si="122">L121*L122</f>
+        <f t="shared" ref="L123:O123" si="139">L121*L122</f>
         <v>2.0824088748019021</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>15.128440366972477</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>0.44120100083402836</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>-0.22468142186452042</v>
       </c>
       <c r="P123" s="76">
@@ -30076,35 +30017,35 @@
       <c r="P129" s="49"/>
       <c r="Q129" s="49"/>
       <c r="T129" s="25">
-        <f t="shared" ref="T129" si="123">U5</f>
+        <f t="shared" ref="T129" si="140">U5</f>
         <v>2325</v>
       </c>
       <c r="U129" s="25">
-        <f t="shared" ref="U129" si="124">V5</f>
+        <f t="shared" ref="U129" si="141">V5</f>
         <v>2160</v>
       </c>
       <c r="V129" s="25">
-        <f t="shared" ref="V129" si="125">W5</f>
+        <f t="shared" ref="V129" si="142">W5</f>
         <v>2444</v>
       </c>
       <c r="W129" s="25">
-        <f t="shared" ref="W129" si="126">X5</f>
+        <f t="shared" ref="W129" si="143">X5</f>
         <v>2629</v>
       </c>
       <c r="X129" s="25">
-        <f t="shared" ref="X129" si="127">Y5</f>
+        <f t="shared" ref="X129" si="144">Y5</f>
         <v>2825</v>
       </c>
       <c r="Y129" s="25">
-        <f t="shared" ref="Y129" si="128">Z5</f>
+        <f t="shared" ref="Y129" si="145">Z5</f>
         <v>3112</v>
       </c>
       <c r="Z129" s="25">
-        <f t="shared" ref="Z129" si="129">AA5</f>
+        <f t="shared" ref="Z129" si="146">AA5</f>
         <v>3629</v>
       </c>
       <c r="AA129" s="25">
-        <f t="shared" ref="T129:AA129" si="130">AB5</f>
+        <f t="shared" ref="AA129" si="147">AB5</f>
         <v>0</v>
       </c>
       <c r="AC129" s="49"/>
@@ -30129,27 +30070,27 @@
       <c r="P130" s="49"/>
       <c r="Q130" s="49"/>
       <c r="T130" s="225" t="str">
-        <f t="shared" ref="T130:Z130" si="131">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
+        <f t="shared" ref="T130:Y130" si="148">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U130" s="225" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="148"/>
         <v>MET</v>
       </c>
       <c r="V130" s="225" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="148"/>
         <v>MET</v>
       </c>
       <c r="W130" s="225" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="148"/>
         <v>MET</v>
       </c>
       <c r="X130" s="225" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="148"/>
         <v>BEAT</v>
       </c>
       <c r="Y130" s="225" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="148"/>
         <v>BEAT</v>
       </c>
       <c r="Z130" s="225" t="str">
@@ -30272,35 +30213,35 @@
       <c r="P133" s="49"/>
       <c r="Q133" s="49"/>
       <c r="T133" s="229">
-        <f t="shared" ref="T133" si="132">U24</f>
+        <f t="shared" ref="T133" si="149">U24</f>
         <v>1.55</v>
       </c>
       <c r="U133" s="229">
-        <f t="shared" ref="U133" si="133">V24</f>
+        <f t="shared" ref="U133" si="150">V24</f>
         <v>1.57</v>
       </c>
       <c r="V133" s="229">
-        <f t="shared" ref="V133" si="134">W24</f>
+        <f t="shared" ref="V133" si="151">W24</f>
         <v>2.2400000000000002</v>
       </c>
       <c r="W133" s="229">
-        <f t="shared" ref="W133" si="135">X24</f>
+        <f t="shared" ref="W133" si="152">X24</f>
         <v>2.4300000000000002</v>
       </c>
       <c r="X133" s="229">
-        <f t="shared" ref="X133" si="136">Y24</f>
+        <f t="shared" ref="X133" si="153">Y24</f>
         <v>2.6</v>
       </c>
       <c r="Y133" s="229">
-        <f t="shared" ref="Y133" si="137">Z24</f>
+        <f t="shared" ref="Y133" si="154">Z24</f>
         <v>3.27</v>
       </c>
       <c r="Z133" s="229">
-        <f t="shared" ref="Z133" si="138">AA24</f>
+        <f t="shared" ref="Z133" si="155">AA24</f>
         <v>5.58</v>
       </c>
       <c r="AA133" s="229">
-        <f t="shared" ref="T133:AA133" si="139">AB24</f>
+        <f t="shared" ref="AA133" si="156">AB24</f>
         <v>0</v>
       </c>
       <c r="AC133" s="49"/>
@@ -30325,27 +30266,27 @@
       <c r="P134" s="49"/>
       <c r="Q134" s="49"/>
       <c r="T134" s="225" t="str">
-        <f t="shared" ref="T134:Z134" si="140">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
+        <f t="shared" ref="T134:Y134" si="157">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U134" s="225" t="str">
-        <f t="shared" si="140"/>
+        <f t="shared" si="157"/>
         <v>MET</v>
       </c>
       <c r="V134" s="225" t="str">
-        <f t="shared" si="140"/>
+        <f t="shared" si="157"/>
         <v>MET</v>
       </c>
       <c r="W134" s="225" t="str">
-        <f t="shared" si="140"/>
+        <f t="shared" si="157"/>
         <v>BEAT</v>
       </c>
       <c r="X134" s="225" t="str">
-        <f t="shared" si="140"/>
+        <f t="shared" si="157"/>
         <v>MET</v>
       </c>
       <c r="Y134" s="225" t="str">
-        <f t="shared" si="140"/>
+        <f t="shared" si="157"/>
         <v>MET</v>
       </c>
       <c r="Z134" s="225" t="str">
@@ -30404,27 +30345,27 @@
       <c r="J138" s="81"/>
       <c r="K138" s="81"/>
       <c r="L138" s="81">
-        <f>L107/(L106+L110-L105)</f>
+        <f t="shared" ref="L138:Q138" si="158">L107/(L106+L110-L105)</f>
         <v>0.31887041274331401</v>
       </c>
       <c r="M138" s="81">
-        <f>M107/(M106+M110-M105)</f>
+        <f t="shared" si="158"/>
         <v>0.37355418154682585</v>
       </c>
       <c r="N138" s="81">
-        <f>N107/(N106+N110-N105)</f>
+        <f t="shared" si="158"/>
         <v>-9.867282169648009E-2</v>
       </c>
       <c r="O138" s="81">
-        <f>O107/(O106+O110-O105)</f>
+        <f t="shared" si="158"/>
         <v>0.12044943820224721</v>
       </c>
       <c r="P138" s="81">
-        <f>P107/(P106+P110-P105)</f>
+        <f t="shared" si="158"/>
         <v>0.5026119834618733</v>
       </c>
       <c r="Q138" s="81">
-        <f>Q107/(Q106+Q110-Q105)</f>
+        <f t="shared" si="158"/>
         <v>0.87701105809469215</v>
       </c>
       <c r="T138" s="49"/>
@@ -30445,59 +30386,59 @@
         <v>138</v>
       </c>
       <c r="L139" s="118">
-        <f t="shared" ref="L139:P139" si="141">L29/L5*365</f>
+        <f t="shared" ref="L139:P139" si="159">L29/L5*365</f>
         <v>39.572137440314577</v>
       </c>
       <c r="M139" s="118">
-        <f t="shared" si="141"/>
+        <f t="shared" si="159"/>
         <v>47.953005745647879</v>
       </c>
       <c r="N139" s="118">
-        <f t="shared" si="141"/>
+        <f t="shared" si="159"/>
         <v>30.696776814734559</v>
       </c>
       <c r="O139" s="118">
-        <f t="shared" si="141"/>
+        <f t="shared" si="159"/>
         <v>23.902457640054951</v>
       </c>
       <c r="P139" s="118">
-        <f t="shared" si="141"/>
+        <f t="shared" si="159"/>
         <v>38.478069693305486</v>
       </c>
       <c r="Q139" s="118">
-        <f t="shared" ref="M139:Q140" si="142">Q29/Q5*365</f>
+        <f t="shared" ref="Q139:Q140" si="160">Q29/Q5*365</f>
         <v>45.913079130791303</v>
       </c>
       <c r="T139" s="118">
-        <f t="shared" ref="T139:Z139" si="143">T29/T5*90</f>
+        <f t="shared" ref="T139:Z139" si="161">T29/T5*90</f>
         <v>26.070110701107012</v>
       </c>
       <c r="U139" s="118">
-        <f t="shared" si="143"/>
+        <f t="shared" si="161"/>
         <v>22.722580645161294</v>
       </c>
       <c r="V139" s="118">
-        <f t="shared" si="143"/>
+        <f t="shared" si="161"/>
         <v>25.916666666666668</v>
       </c>
       <c r="W139" s="118">
-        <f t="shared" si="143"/>
+        <f t="shared" si="161"/>
         <v>35.315057283142387</v>
       </c>
       <c r="X139" s="118">
-        <f t="shared" si="143"/>
+        <f t="shared" si="161"/>
         <v>36.732597945987067</v>
       </c>
       <c r="Y139" s="118">
-        <f t="shared" si="143"/>
+        <f t="shared" si="161"/>
         <v>39.69557522123894</v>
       </c>
       <c r="Z139" s="118">
-        <f t="shared" si="143"/>
+        <f t="shared" si="161"/>
         <v>34.617609254498717</v>
       </c>
       <c r="AA139" s="118">
-        <f t="shared" ref="T139:AA139" si="144">AA29/AA5*90</f>
+        <f t="shared" ref="AA139" si="162">AA29/AA5*90</f>
         <v>38.043538164783691</v>
       </c>
       <c r="AC139" s="118">
@@ -30510,59 +30451,59 @@
         <v>139</v>
       </c>
       <c r="L140" s="118">
-        <f t="shared" ref="L140:P140" si="145">L30/L6*365</f>
+        <f t="shared" ref="L140:P140" si="163">L30/L6*365</f>
         <v>56.602266872746</v>
       </c>
       <c r="M140" s="118">
-        <f t="shared" si="145"/>
+        <f t="shared" si="163"/>
         <v>69.7296142578125</v>
       </c>
       <c r="N140" s="118">
-        <f t="shared" si="145"/>
+        <f t="shared" si="163"/>
         <v>68.97066136250622</v>
       </c>
       <c r="O140" s="118">
-        <f t="shared" si="145"/>
+        <f t="shared" si="163"/>
         <v>90.176470588235304</v>
       </c>
       <c r="P140" s="118">
-        <f t="shared" si="145"/>
+        <f t="shared" si="163"/>
         <v>89.130066135323048</v>
       </c>
       <c r="Q140" s="118">
-        <f t="shared" si="142"/>
+        <f t="shared" si="160"/>
         <v>86.396715383456382</v>
       </c>
       <c r="T140" s="118">
-        <f t="shared" ref="T140:Z140" si="146">T30/T6*365</f>
+        <f t="shared" ref="T140:Z140" si="164">T30/T6*365</f>
         <v>347.17675378266847</v>
       </c>
       <c r="U140" s="118">
-        <f t="shared" si="146"/>
+        <f t="shared" si="164"/>
         <v>355.35029742233974</v>
       </c>
       <c r="V140" s="118">
-        <f t="shared" si="146"/>
+        <f t="shared" si="164"/>
         <v>383.77142857142854</v>
       </c>
       <c r="W140" s="118">
-        <f t="shared" si="146"/>
+        <f t="shared" si="164"/>
         <v>343.52941176470586</v>
       </c>
       <c r="X140" s="118">
-        <f t="shared" si="146"/>
+        <f t="shared" si="164"/>
         <v>342.9899497487437</v>
       </c>
       <c r="Y140" s="118">
-        <f t="shared" si="146"/>
+        <f t="shared" si="164"/>
         <v>331.57671315949062</v>
       </c>
       <c r="Z140" s="118">
-        <f t="shared" si="146"/>
+        <f t="shared" si="164"/>
         <v>335.40540540540542</v>
       </c>
       <c r="AA140" s="118">
-        <f t="shared" ref="T140:AA140" si="147">AA30/AA6*365</f>
+        <f t="shared" ref="AA140" si="165">AA30/AA6*365</f>
         <v>331.26227614095899</v>
       </c>
       <c r="AC140" s="118">
@@ -30575,59 +30516,59 @@
         <v>140</v>
       </c>
       <c r="L141" s="118">
-        <f>L37/L6*365</f>
+        <f t="shared" ref="L141:Q141" si="166">L37/L6*365</f>
         <v>81.09544049459042</v>
       </c>
       <c r="M141" s="118">
-        <f>M37/M6*365</f>
+        <f t="shared" si="166"/>
         <v>91.695556640625</v>
       </c>
       <c r="N141" s="118">
-        <f>N37/N6*365</f>
+        <f t="shared" si="166"/>
         <v>96.982429968506537</v>
       </c>
       <c r="O141" s="118">
-        <f>O37/O6*365</f>
+        <f t="shared" si="166"/>
         <v>129.98803589232301</v>
       </c>
       <c r="P141" s="118">
-        <f>P37/P6*365</f>
+        <f t="shared" si="166"/>
         <v>99.280990334068164</v>
       </c>
       <c r="Q141" s="118">
-        <f>Q37/Q6*365</f>
+        <f t="shared" si="166"/>
         <v>96.130781979810152</v>
       </c>
       <c r="T141" s="118">
-        <f t="shared" ref="T141:Z141" si="148">T37/T6*90</f>
+        <f t="shared" ref="T141:Z141" si="167">T37/T6*90</f>
         <v>110.05502063273727</v>
       </c>
       <c r="U141" s="118">
-        <f t="shared" si="148"/>
+        <f t="shared" si="167"/>
         <v>93.212161269001996</v>
       </c>
       <c r="V141" s="118">
-        <f t="shared" si="148"/>
+        <f t="shared" si="167"/>
         <v>94.30714285714285</v>
       </c>
       <c r="W141" s="118">
-        <f t="shared" si="148"/>
+        <f t="shared" si="167"/>
         <v>94.352941176470594</v>
       </c>
       <c r="X141" s="118">
-        <f t="shared" si="148"/>
+        <f t="shared" si="167"/>
         <v>94.579145728643212</v>
       </c>
       <c r="Y141" s="118">
-        <f t="shared" si="148"/>
+        <f t="shared" si="167"/>
         <v>96.658580958156449</v>
       </c>
       <c r="Z141" s="118">
-        <f t="shared" si="148"/>
+        <f t="shared" si="167"/>
         <v>91.567567567567565</v>
       </c>
       <c r="AA141" s="118">
-        <f t="shared" ref="T141:AA141" si="149">AA37/AA6*90</f>
+        <f t="shared" ref="AA141" si="168">AA37/AA6*90</f>
         <v>90.883882149046798</v>
       </c>
       <c r="AC141" s="118">
@@ -30644,59 +30585,59 @@
         <v>15.078963818470157</v>
       </c>
       <c r="M142" s="118">
-        <f t="shared" ref="M142:P142" si="150">M139+M140-M141</f>
+        <f t="shared" ref="M142:P142" si="169">M139+M140-M141</f>
         <v>25.987063362835386</v>
       </c>
       <c r="N142" s="118">
-        <f t="shared" si="150"/>
+        <f t="shared" si="169"/>
         <v>2.6850082087342457</v>
       </c>
       <c r="O142" s="118">
-        <f t="shared" si="150"/>
+        <f t="shared" si="169"/>
         <v>-15.90910766403276</v>
       </c>
       <c r="P142" s="118">
-        <f t="shared" si="150"/>
+        <f t="shared" si="169"/>
         <v>28.327145494560369</v>
       </c>
       <c r="Q142" s="118">
-        <f t="shared" ref="N142:Q142" si="151">Q139+Q140-Q141</f>
+        <f t="shared" ref="Q142" si="170">Q139+Q140-Q141</f>
         <v>36.179012534437547</v>
       </c>
       <c r="T142" s="118">
-        <f t="shared" ref="T142:U142" si="152">T139+T140-T141</f>
+        <f t="shared" ref="T142" si="171">T139+T140-T141</f>
         <v>263.19184385103824</v>
       </c>
       <c r="U142" s="118">
-        <f t="shared" ref="U142:V142" si="153">U139+U140-U141</f>
+        <f t="shared" ref="U142" si="172">U139+U140-U141</f>
         <v>284.86071679849908</v>
       </c>
       <c r="V142" s="118">
-        <f t="shared" ref="V142:W142" si="154">V139+V140-V141</f>
+        <f t="shared" ref="V142" si="173">V139+V140-V141</f>
         <v>315.38095238095241</v>
       </c>
       <c r="W142" s="118">
-        <f t="shared" ref="W142:X142" si="155">W139+W140-W141</f>
+        <f t="shared" ref="W142" si="174">W139+W140-W141</f>
         <v>284.49152787137763</v>
       </c>
       <c r="X142" s="118">
-        <f t="shared" ref="X142:Z142" si="156">X139+X140-X141</f>
+        <f t="shared" ref="X142:Z142" si="175">X139+X140-X141</f>
         <v>285.14340196608759</v>
       </c>
       <c r="Y142" s="118">
-        <f t="shared" si="156"/>
+        <f t="shared" si="175"/>
         <v>274.6137074225731</v>
       </c>
       <c r="Z142" s="118">
-        <f t="shared" si="156"/>
+        <f t="shared" si="175"/>
         <v>278.45544709233656</v>
       </c>
       <c r="AA142" s="118">
-        <f t="shared" ref="Z142:AA142" si="157">AA139+AA140-AA141</f>
+        <f t="shared" ref="AA142" si="176">AA139+AA140-AA141</f>
         <v>278.4219321566959</v>
       </c>
       <c r="AC142" s="118">
-        <f t="shared" ref="AC142" si="158">AC139+AC140-AC141</f>
+        <f t="shared" ref="AC142" si="177">AC139+AC140-AC141</f>
         <v>36.179012534437547</v>
       </c>
     </row>
@@ -30705,59 +30646,59 @@
         <v>255</v>
       </c>
       <c r="L143" s="118">
-        <f>L106/L48</f>
+        <f t="shared" ref="L143:Q143" si="178">L106/L48</f>
         <v>8.1442155309033275</v>
       </c>
       <c r="M143" s="118">
-        <f>M106/M48</f>
+        <f t="shared" si="178"/>
         <v>51.798165137614681</v>
       </c>
       <c r="N143" s="118">
-        <f>N106/N48</f>
+        <f t="shared" si="178"/>
         <v>-4.54628857381151</v>
       </c>
       <c r="O143" s="118">
-        <f>O106/O48</f>
+        <f t="shared" si="178"/>
         <v>-3.8054996646545942</v>
       </c>
       <c r="P143" s="118">
-        <f>P106/P48</f>
+        <f t="shared" si="178"/>
         <v>-11.026490066225165</v>
       </c>
       <c r="Q143" s="118">
-        <f>Q106/Q48</f>
+        <f t="shared" si="178"/>
         <v>1.6451315182279649</v>
       </c>
       <c r="T143" s="118">
-        <f t="shared" ref="T143:Z143" si="159">T106/T48</f>
+        <f t="shared" ref="T143:Z143" si="179">T106/T48</f>
         <v>-4.3661538461538463</v>
       </c>
       <c r="U143" s="118">
-        <f t="shared" si="159"/>
+        <f t="shared" si="179"/>
         <v>-5.2632066728452269</v>
       </c>
       <c r="V143" s="118">
-        <f t="shared" si="159"/>
+        <f t="shared" si="179"/>
         <v>-6.2074788902291917</v>
       </c>
       <c r="W143" s="118">
-        <f t="shared" si="159"/>
+        <f t="shared" si="179"/>
         <v>-11.026490066225165</v>
       </c>
       <c r="X143" s="118">
-        <f t="shared" si="159"/>
+        <f t="shared" si="179"/>
         <v>-79.269841269841265</v>
       </c>
       <c r="Y143" s="118">
-        <f t="shared" si="159"/>
+        <f t="shared" si="179"/>
         <v>9.8017429193899783</v>
       </c>
       <c r="Z143" s="118">
-        <f t="shared" si="159"/>
+        <f t="shared" si="179"/>
         <v>3.5278538812785389</v>
       </c>
       <c r="AA143" s="118">
-        <f t="shared" ref="T143:AA143" si="160">AA106/AA48</f>
+        <f t="shared" ref="AA143" si="180">AA106/AA48</f>
         <v>1.6451315182279649</v>
       </c>
       <c r="AC143" s="118">
@@ -30770,59 +30711,59 @@
         <v>259</v>
       </c>
       <c r="L144" s="179">
-        <f>(L106-L105)/L48</f>
+        <f t="shared" ref="L144:Q144" si="181">(L106-L105)/L48</f>
         <v>6.2282091917591123</v>
       </c>
       <c r="M144" s="179">
-        <f>(M106-M105)/M48</f>
+        <f t="shared" si="181"/>
         <v>46.155963302752291</v>
       </c>
       <c r="N144" s="179">
-        <f>(N106-N105)/N48</f>
+        <f t="shared" si="181"/>
         <v>-3.8907422852376983</v>
       </c>
       <c r="O144" s="179">
-        <f>(O106-O105)/O48</f>
+        <f t="shared" si="181"/>
         <v>-2.8947015425888667</v>
       </c>
       <c r="P144" s="179">
-        <f>(P106-P105)/P48</f>
+        <f t="shared" si="181"/>
         <v>-9.0596026490066226</v>
       </c>
       <c r="Q144" s="179">
-        <f>(Q106-Q105)/Q48</f>
+        <f t="shared" si="181"/>
         <v>0.8587909552376557</v>
       </c>
       <c r="T144" s="179">
-        <f t="shared" ref="T144:Z144" si="161">(T106-T105)/T48</f>
+        <f t="shared" ref="T144:Z144" si="182">(T106-T105)/T48</f>
         <v>-3.4130769230769231</v>
       </c>
       <c r="U144" s="179">
-        <f t="shared" si="161"/>
+        <f t="shared" si="182"/>
         <v>-4.1158480074142725</v>
       </c>
       <c r="V144" s="179">
-        <f t="shared" si="161"/>
+        <f t="shared" si="182"/>
         <v>-5.2255729794933652</v>
       </c>
       <c r="W144" s="179">
-        <f t="shared" si="161"/>
+        <f t="shared" si="182"/>
         <v>-9.0596026490066226</v>
       </c>
       <c r="X144" s="179">
-        <f t="shared" si="161"/>
+        <f t="shared" si="182"/>
         <v>-61.61904761904762</v>
       </c>
       <c r="Y144" s="179">
-        <f t="shared" si="161"/>
+        <f t="shared" si="182"/>
         <v>7.522875816993464</v>
       </c>
       <c r="Z144" s="179">
-        <f t="shared" si="161"/>
+        <f t="shared" si="182"/>
         <v>2.4812785388127856</v>
       </c>
       <c r="AA144" s="179">
-        <f t="shared" ref="T144:AA144" si="162">(AA106-AA105)/AA48</f>
+        <f t="shared" ref="AA144" si="183">(AA106-AA105)/AA48</f>
         <v>0.8587909552376557</v>
       </c>
       <c r="AC144" s="179">
@@ -30835,59 +30776,59 @@
         <v>256</v>
       </c>
       <c r="L145" s="118">
-        <f>(L105+L29)/L39</f>
+        <f t="shared" ref="L145:Q145" si="184">(L105+L29)/L39</f>
         <v>0.81033892502567617</v>
       </c>
       <c r="M145" s="118">
-        <f>(M105+M29)/M39</f>
+        <f t="shared" si="184"/>
         <v>0.60393811533052044</v>
       </c>
       <c r="N145" s="118">
-        <f>(N105+N29)/N39</f>
+        <f t="shared" si="184"/>
         <v>0.54282407407407407</v>
       </c>
       <c r="O145" s="118">
-        <f>(O105+O29)/O39</f>
+        <f t="shared" si="184"/>
         <v>0.57663762504033556</v>
       </c>
       <c r="P145" s="118">
-        <f>(P105+P29)/P39</f>
+        <f t="shared" si="184"/>
         <v>0.69864048338368578</v>
       </c>
       <c r="Q145" s="118">
-        <f>(Q105+Q29)/Q39</f>
+        <f t="shared" si="184"/>
         <v>1.0354972817396866</v>
       </c>
       <c r="T145" s="118">
-        <f t="shared" ref="T145:Z145" si="163">(T105+T29)/T39</f>
+        <f t="shared" ref="T145:Z145" si="185">(T105+T29)/T39</f>
         <v>0.5906358747231889</v>
       </c>
       <c r="U145" s="118">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.61468507915122939</v>
       </c>
       <c r="V145" s="118">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.59535655058043113</v>
       </c>
       <c r="W145" s="118">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.69864048338368578</v>
       </c>
       <c r="X145" s="118">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.53072625698324027</v>
       </c>
       <c r="Y145" s="118">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.6094123903217229</v>
       </c>
       <c r="Z145" s="118">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.72292502314100582</v>
       </c>
       <c r="AA145" s="118">
-        <f t="shared" ref="T145:AA145" si="164">(AA105+AA29)/AA39</f>
+        <f t="shared" ref="AA145" si="186">(AA105+AA29)/AA39</f>
         <v>1.0354972817396866</v>
       </c>
       <c r="AC145" s="118">
@@ -30900,59 +30841,59 @@
         <v>257</v>
       </c>
       <c r="L146" s="118">
-        <f>L31/L39</f>
+        <f t="shared" ref="L146:Q146" si="187">L31/L39</f>
         <v>1.2937350222526531</v>
       </c>
       <c r="M146" s="118">
-        <f>M31/M39</f>
+        <f t="shared" si="187"/>
         <v>1.1344585091420534</v>
       </c>
       <c r="N146" s="118">
-        <f>N31/N39</f>
+        <f t="shared" si="187"/>
         <v>1.1207561728395061</v>
       </c>
       <c r="O146" s="118">
-        <f>O31/O39</f>
+        <f t="shared" si="187"/>
         <v>1.0751855437237818</v>
       </c>
       <c r="P146" s="118">
-        <f>P31/P39</f>
+        <f t="shared" si="187"/>
         <v>1.3795317220543806</v>
       </c>
       <c r="Q146" s="118">
-        <f>Q31/Q39</f>
+        <f t="shared" si="187"/>
         <v>1.669651423089223</v>
       </c>
       <c r="T146" s="118">
-        <f t="shared" ref="T146:Z146" si="165">T31/T39</f>
+        <f t="shared" ref="T146:Z146" si="188">T31/T39</f>
         <v>1.1414109459031951</v>
       </c>
       <c r="U146" s="118">
-        <f t="shared" si="165"/>
+        <f t="shared" si="188"/>
         <v>1.2334119232064669</v>
       </c>
       <c r="V146" s="118">
-        <f t="shared" si="165"/>
+        <f t="shared" si="188"/>
         <v>1.3606965174129353</v>
       </c>
       <c r="W146" s="118">
-        <f t="shared" si="165"/>
+        <f t="shared" si="188"/>
         <v>1.3795317220543806</v>
       </c>
       <c r="X146" s="118">
-        <f t="shared" si="165"/>
+        <f t="shared" si="188"/>
         <v>0.97935389846975951</v>
       </c>
       <c r="Y146" s="118">
-        <f t="shared" si="165"/>
+        <f t="shared" si="188"/>
         <v>1.1191172560489231</v>
       </c>
       <c r="Z146" s="118">
-        <f t="shared" si="165"/>
+        <f t="shared" si="188"/>
         <v>1.3264424560320889</v>
       </c>
       <c r="AA146" s="118">
-        <f t="shared" ref="T146:AA146" si="166">AA31/AA39</f>
+        <f t="shared" ref="AA146" si="189">AA31/AA39</f>
         <v>1.669651423089223</v>
       </c>
       <c r="AC146" s="118">
@@ -30965,59 +30906,59 @@
         <v>263</v>
       </c>
       <c r="L147" s="181">
-        <f>IF(L12&gt;=0,"N/A",IF(L11&lt;=0,"N/A",L11/-L12))</f>
+        <f t="shared" ref="L147:Q147" si="190">IF(L12&gt;=0,"N/A",IF(L11&lt;=0,"N/A",L11/-L12))</f>
         <v>6.8440366972477067</v>
       </c>
       <c r="M147" s="181">
-        <f>IF(M12&gt;=0,"N/A",IF(M11&lt;=0,"N/A",M11/-M12))</f>
+        <f t="shared" si="190"/>
         <v>7.9149797570850202</v>
       </c>
       <c r="N147" s="181" t="str">
-        <f>IF(N12&gt;=0,"N/A",IF(N11&lt;=0,"N/A",N11/-N12))</f>
+        <f t="shared" si="190"/>
         <v>N/A</v>
       </c>
       <c r="O147" s="181">
-        <f>IF(O12&gt;=0,"N/A",IF(O11&lt;=0,"N/A",O11/-O12))</f>
+        <f t="shared" si="190"/>
         <v>1.4258675078864353</v>
       </c>
       <c r="P147" s="181">
-        <f>IF(P12&gt;=0,"N/A",IF(P11&lt;=0,"N/A",P11/-P12))</f>
+        <f t="shared" si="190"/>
         <v>6.3851351351351351</v>
       </c>
       <c r="Q147" s="181">
-        <f>IF(Q12&gt;=0,"N/A",IF(Q11&lt;=0,"N/A",Q11/-Q12))</f>
+        <f t="shared" si="190"/>
         <v>16.118110236220474</v>
       </c>
       <c r="T147" s="181">
-        <f t="shared" ref="T147:Z147" si="167">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
+        <f t="shared" ref="T147:Z147" si="191">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>5.166666666666667</v>
       </c>
       <c r="U147" s="181">
-        <f t="shared" si="167"/>
+        <f t="shared" si="191"/>
         <v>6.4210526315789478</v>
       </c>
       <c r="V147" s="181">
-        <f t="shared" si="167"/>
+        <f t="shared" si="191"/>
         <v>5.904109589041096</v>
       </c>
       <c r="W147" s="181">
-        <f t="shared" si="167"/>
+        <f t="shared" si="191"/>
         <v>8.2318840579710137</v>
       </c>
       <c r="X147" s="181">
-        <f t="shared" si="167"/>
+        <f t="shared" si="191"/>
         <v>9.506849315068493</v>
       </c>
       <c r="Y147" s="181">
-        <f t="shared" si="167"/>
+        <f t="shared" si="191"/>
         <v>12.969230769230769</v>
       </c>
       <c r="Z147" s="181">
-        <f t="shared" si="167"/>
+        <f t="shared" si="191"/>
         <v>16.096774193548388</v>
       </c>
       <c r="AA147" s="181">
-        <f t="shared" ref="T147:AA147" si="168">IF(AA12&gt;=0,"N/A",IF(AA11&lt;=0,"N/A",AA11/-AA12))</f>
+        <f t="shared" ref="AA147" si="192">IF(AA12&gt;=0,"N/A",IF(AA11&lt;=0,"N/A",AA11/-AA12))</f>
         <v>28.87037037037037</v>
       </c>
       <c r="AC147" s="181">
@@ -31063,7 +31004,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>58.692363112391924</v>
+        <v>61.187319884726222</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31104,7 +31045,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>15.280950184501846</v>
+        <v>15.930528905289053</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31169,7 +31110,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>85.337125057683437</v>
+        <v>88.964725426857399</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31234,7 +31175,7 @@
       </c>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>193072.05</v>
+        <v>201279.35999999999</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31242,64 +31183,64 @@
         <v>187</v>
       </c>
       <c r="L152" s="143">
-        <f>L151+L106-L105+L47+L44</f>
+        <f t="shared" ref="L152:Q152" si="193">L151+L106-L105+L47+L44</f>
         <v>23946.9</v>
       </c>
       <c r="M152" s="143">
-        <f>M151+M106-M105+M47+M44</f>
+        <f t="shared" si="193"/>
         <v>19747.169999999998</v>
       </c>
       <c r="N152" s="143">
-        <f>N151+N106-N105+N47+N44</f>
+        <f t="shared" si="193"/>
         <v>17472.09</v>
       </c>
       <c r="O152" s="143">
-        <f>O151+O106-O105+O47+O44</f>
+        <f t="shared" si="193"/>
         <v>26312.51</v>
       </c>
       <c r="P152" s="143">
-        <f>P151+P106-P105+P47+P44</f>
+        <f t="shared" si="193"/>
         <v>34937.919999999998</v>
       </c>
       <c r="Q152" s="143">
-        <f>Q151+Q106-Q105+Q47+Q44</f>
+        <f t="shared" si="193"/>
         <v>196238.91999999998</v>
       </c>
       <c r="T152" s="143">
-        <f t="shared" ref="T152:Z152" si="169">T151+T106-T105+T47+T44</f>
+        <f t="shared" ref="T152:Z152" si="194">T151+T106-T105+T47+T44</f>
         <v>28033.579999999998</v>
       </c>
       <c r="U152" s="143">
-        <f t="shared" si="169"/>
+        <f t="shared" si="194"/>
         <v>23404.63</v>
       </c>
       <c r="V152" s="143">
-        <f t="shared" si="169"/>
+        <f t="shared" si="194"/>
         <v>22674.720000000001</v>
       </c>
       <c r="W152" s="143">
-        <f t="shared" si="169"/>
+        <f t="shared" si="194"/>
         <v>34937.919999999998</v>
       </c>
       <c r="X152" s="143">
-        <f t="shared" si="169"/>
+        <f t="shared" si="194"/>
         <v>61265.33</v>
       </c>
       <c r="Y152" s="143">
-        <f t="shared" si="169"/>
+        <f t="shared" si="194"/>
         <v>69426.2</v>
       </c>
       <c r="Z152" s="143">
-        <f t="shared" si="169"/>
+        <f t="shared" si="194"/>
         <v>89719.319999999992</v>
       </c>
       <c r="AA152" s="143">
-        <f t="shared" ref="T152:AA152" si="170">AA151+AA106-AA105+AA47+AA44</f>
+        <f t="shared" ref="AA152" si="195">AA151+AA106-AA105+AA47+AA44</f>
         <v>196238.91999999998</v>
       </c>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>194933.05</v>
+        <v>203140.36</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31307,27 +31248,27 @@
         <v>264</v>
       </c>
       <c r="L153" s="183">
-        <f>L152/L5</f>
+        <f t="shared" ref="L153:Q153" si="196">L152/L5</f>
         <v>2.2420091751708644</v>
       </c>
       <c r="M153" s="183">
-        <f>M152/M5</f>
+        <f t="shared" si="196"/>
         <v>1.6934370980190376</v>
       </c>
       <c r="N153" s="183">
-        <f>N152/N5</f>
+        <f t="shared" si="196"/>
         <v>2.3662093716143011</v>
       </c>
       <c r="O153" s="183">
-        <f>O152/O5</f>
+        <f t="shared" si="196"/>
         <v>4.0165638833765831</v>
       </c>
       <c r="P153" s="183">
-        <f>P152/P5</f>
+        <f t="shared" si="196"/>
         <v>3.8405979993404418</v>
       </c>
       <c r="Q153" s="183">
-        <f>Q152/Q5</f>
+        <f t="shared" si="196"/>
         <v>16.091752357523575</v>
       </c>
       <c r="T153" s="49"/>
@@ -31340,7 +31281,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>15.984669946699466</v>
+        <v>16.657676096760966</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31348,27 +31289,27 @@
         <v>203</v>
       </c>
       <c r="L154" s="183">
-        <f>L152/L11</f>
+        <f t="shared" ref="L154:Q154" si="197">L152/L11</f>
         <v>16.050201072386059</v>
       </c>
       <c r="M154" s="183">
-        <f>M152/M11</f>
+        <f t="shared" si="197"/>
         <v>10.100854219948848</v>
       </c>
       <c r="N154" s="183">
-        <f>N152/N11</f>
+        <f t="shared" si="197"/>
         <v>-51.087982456140352</v>
       </c>
       <c r="O154" s="183">
-        <f>O152/O11</f>
+        <f t="shared" si="197"/>
         <v>58.213517699115037</v>
       </c>
       <c r="P154" s="183">
-        <f>P152/P11</f>
+        <f t="shared" si="197"/>
         <v>18.485671957671958</v>
       </c>
       <c r="Q154" s="183">
-        <f>Q152/Q11</f>
+        <f t="shared" si="197"/>
         <v>47.933297508549096</v>
       </c>
       <c r="T154" s="49"/>
@@ -31381,7 +31322,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>47.61432584269663</v>
+        <v>49.619042501221294</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31389,59 +31330,59 @@
         <v>265</v>
       </c>
       <c r="L155" s="64">
-        <f>L58-L53+L108+L64</f>
+        <f t="shared" ref="L155:Q155" si="198">L58-L53+L108+L64</f>
         <v>1016</v>
       </c>
       <c r="M155" s="64">
-        <f>M58-M53+M108+M64</f>
+        <f t="shared" si="198"/>
         <v>1131</v>
       </c>
       <c r="N155" s="64">
-        <f>N58-N53+N108+N64</f>
+        <f t="shared" si="198"/>
         <v>511</v>
       </c>
       <c r="O155" s="64">
-        <f>O58-O53+O108+O64</f>
+        <f t="shared" si="198"/>
         <v>537</v>
       </c>
       <c r="P155" s="64">
-        <f>P58-P53+P108+P64</f>
+        <f t="shared" si="198"/>
         <v>618</v>
       </c>
       <c r="Q155" s="64">
-        <f>Q58-Q53+Q108+Q64</f>
+        <f t="shared" si="198"/>
         <v>2892</v>
       </c>
       <c r="T155" s="64">
-        <f t="shared" ref="T155:Z155" si="171">T58-T53+T108+T64</f>
+        <f t="shared" ref="T155:Z155" si="199">T58-T53+T108+T64</f>
         <v>-11</v>
       </c>
       <c r="U155" s="64">
-        <f t="shared" si="171"/>
+        <f t="shared" si="199"/>
         <v>101</v>
       </c>
       <c r="V155" s="64">
-        <f t="shared" si="171"/>
+        <f t="shared" si="199"/>
         <v>162</v>
       </c>
       <c r="W155" s="64">
-        <f t="shared" si="171"/>
+        <f t="shared" si="199"/>
         <v>366</v>
       </c>
       <c r="X155" s="64">
-        <f t="shared" si="171"/>
+        <f t="shared" si="199"/>
         <v>375</v>
       </c>
       <c r="Y155" s="64">
-        <f t="shared" si="171"/>
+        <f t="shared" si="199"/>
         <v>554</v>
       </c>
       <c r="Z155" s="64">
-        <f t="shared" si="171"/>
+        <f t="shared" si="199"/>
         <v>899</v>
       </c>
       <c r="AA155" s="64">
-        <f t="shared" ref="T155:AA155" si="172">AA58-AA53+AA108+AA64</f>
+        <f t="shared" ref="AA155" si="200">AA58-AA53+AA108+AA64</f>
         <v>1064</v>
       </c>
       <c r="AC155" s="64">
@@ -31454,27 +31395,27 @@
         <v>266</v>
       </c>
       <c r="L156" s="64">
-        <f>L107+L52+L108+L54+L56+L57+L55</f>
+        <f t="shared" ref="L156:Q156" si="201">L107+L52+L108+L54+L56+L57+L55</f>
         <v>1209.3679525222551</v>
       </c>
       <c r="M156" s="64">
-        <f>M107+M52+M108+M54+M56+M57+M55</f>
+        <f t="shared" si="201"/>
         <v>1347.0684931506848</v>
       </c>
       <c r="N156" s="64">
-        <f>N107+N52+N108+N54+N56+N57+N55</f>
+        <f t="shared" si="201"/>
         <v>1017</v>
       </c>
       <c r="O156" s="64">
-        <f>O107+O52+O108+O54+O56+O57+O55</f>
+        <f t="shared" si="201"/>
         <v>736.2696629213483</v>
       </c>
       <c r="P156" s="64">
-        <f>P107+P52+P108+P54+P56+P57+P55</f>
+        <f t="shared" si="201"/>
         <v>856.03635161929924</v>
       </c>
       <c r="Q156" s="64">
-        <f>Q107+Q52+Q108+Q54+Q56+Q57+Q55</f>
+        <f t="shared" si="201"/>
         <v>3080.6005420054198</v>
       </c>
       <c r="T156" s="49"/>
@@ -31499,23 +31440,23 @@
         <v>19.701673228346458</v>
       </c>
       <c r="M157" s="72">
-        <f t="shared" ref="M157:P157" si="173">M151/M155</f>
+        <f t="shared" ref="M157:P157" si="202">M151/M155</f>
         <v>13.011644562334217</v>
       </c>
       <c r="N157" s="72">
-        <f t="shared" si="173"/>
+        <f t="shared" si="202"/>
         <v>25.062798434442271</v>
       </c>
       <c r="O157" s="72">
-        <f t="shared" si="173"/>
+        <f t="shared" si="202"/>
         <v>40.961843575418989</v>
       </c>
       <c r="P157" s="72">
-        <f t="shared" si="173"/>
+        <f t="shared" si="202"/>
         <v>49.893074433656956</v>
       </c>
       <c r="Q157" s="72">
-        <f t="shared" ref="N157:Q157" si="174">Q151/Q155</f>
+        <f t="shared" ref="Q157" si="203">Q151/Q155</f>
         <v>67.212282157676341</v>
       </c>
       <c r="T157" s="49"/>
@@ -31527,8 +31468,8 @@
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
-        <f t="shared" ref="AC157:AC158" ca="1" si="175">AC151/AC155</f>
-        <v>66.760736514522819</v>
+        <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
+        <v>69.598672199170124</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31540,23 +31481,23 @@
         <v>19.801169652343109</v>
       </c>
       <c r="M158" s="72">
-        <f t="shared" ref="M158:P158" si="176">M152/M156</f>
+        <f t="shared" ref="M158:P158" si="205">M152/M156</f>
         <v>14.659365949397982</v>
       </c>
       <c r="N158" s="72">
-        <f t="shared" si="176"/>
+        <f t="shared" si="205"/>
         <v>17.180029498525073</v>
       </c>
       <c r="O158" s="72">
-        <f t="shared" si="176"/>
+        <f t="shared" si="205"/>
         <v>35.737599041631057</v>
       </c>
       <c r="P158" s="72">
-        <f t="shared" si="176"/>
+        <f t="shared" si="205"/>
         <v>40.813593878239608</v>
       </c>
       <c r="Q158" s="72">
-        <f t="shared" ref="N158:Q158" si="177">Q152/Q156</f>
+        <f t="shared" ref="Q158" si="206">Q152/Q156</f>
         <v>63.70151446907547</v>
       </c>
       <c r="T158" s="49"/>
@@ -31568,8 +31509,8 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
-        <f t="shared" ca="1" si="175"/>
-        <v>60.696542876492956</v>
+        <f t="shared" ca="1" si="204"/>
+        <v>63.252063057989474</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31581,23 +31522,23 @@
         <v>5.0757110241845635E-2</v>
       </c>
       <c r="M159" s="74">
-        <f t="shared" ref="M159:P159" si="178">M155/M151</f>
+        <f t="shared" ref="M159:P159" si="207">M155/M151</f>
         <v>7.685423585076824E-2</v>
       </c>
       <c r="N159" s="74">
-        <f t="shared" si="178"/>
+        <f t="shared" si="207"/>
         <v>3.9899774265660659E-2</v>
       </c>
       <c r="O159" s="74">
-        <f t="shared" si="178"/>
+        <f t="shared" si="207"/>
         <v>2.4412963692876734E-2</v>
       </c>
       <c r="P159" s="74">
-        <f t="shared" si="178"/>
+        <f t="shared" si="207"/>
         <v>2.0042861887168417E-2</v>
       </c>
       <c r="Q159" s="74">
-        <f t="shared" ref="N159:Q159" si="179">Q155/Q151</f>
+        <f t="shared" ref="Q159" si="208">Q155/Q151</f>
         <v>1.4878233083263779E-2</v>
       </c>
       <c r="T159" s="49"/>
@@ -31609,8 +31550,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
-        <f t="shared" ref="AC159" ca="1" si="180">AC155/AC151</f>
-        <v>1.4978864107984559E-2</v>
+        <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
+        <v>1.4368090200604772E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31618,27 +31559,27 @@
         <v>270</v>
       </c>
       <c r="L160" s="74">
-        <f>L25/L115</f>
+        <f t="shared" ref="L160:Q160" si="210">L25/L115</f>
         <v>6.1587958175341836E-2</v>
       </c>
       <c r="M160" s="74">
-        <f>M25/M115</f>
+        <f t="shared" si="210"/>
         <v>0.10652771746996671</v>
       </c>
       <c r="N160" s="74">
-        <f>N25/N115</f>
+        <f t="shared" si="210"/>
         <v>-4.1377080976240509E-2</v>
       </c>
       <c r="O160" s="74">
-        <f>O25/O115</f>
+        <f t="shared" si="210"/>
         <v>1.529969981601627E-2</v>
       </c>
       <c r="P160" s="74">
-        <f>P25/P115</f>
+        <f t="shared" si="210"/>
         <v>4.7864819004524883E-2</v>
       </c>
       <c r="Q160" s="74">
-        <f>Q25/Q115</f>
+        <f t="shared" si="210"/>
         <v>1.6947912602419041E-2</v>
       </c>
       <c r="T160" s="49"/>
@@ -31651,7 +31592,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.7037991775609159E-2</v>
+        <v>1.6343255463451396E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31659,27 +31600,27 @@
         <v>271</v>
       </c>
       <c r="L161" s="154">
-        <f>L81/L115</f>
+        <f t="shared" ref="L161:Q161" si="211">L81/L115</f>
         <v>3.0564173273583822E-2</v>
       </c>
       <c r="M161" s="154">
-        <f>M81/M115</f>
+        <f t="shared" si="211"/>
         <v>4.0092632797799968E-2</v>
       </c>
       <c r="N161" s="154">
-        <f>N81/N115</f>
+        <f t="shared" si="211"/>
         <v>4.5256182317763051E-2</v>
       </c>
       <c r="O161" s="154">
-        <f>O81/O115</f>
+        <f t="shared" si="211"/>
         <v>2.7113392079016172E-2</v>
       </c>
       <c r="P161" s="154">
-        <f>P81/P115</f>
+        <f t="shared" si="211"/>
         <v>2.0220588235294119E-2</v>
       </c>
       <c r="Q161" s="154">
-        <f>Q81/Q115</f>
+        <f t="shared" si="211"/>
         <v>3.5602809207959424E-3</v>
       </c>
       <c r="T161" s="49"/>
@@ -31692,7 +31633,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>3.5843613821886699E-3</v>
+        <v>3.4382064807837228E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31700,27 +31641,27 @@
         <v>296</v>
       </c>
       <c r="L162" s="154">
-        <f>-L62/L151</f>
+        <f t="shared" ref="L162:Q162" si="212">-L62/L151</f>
         <v>0.10226358726875789</v>
       </c>
       <c r="M162" s="154">
-        <f>-M62/M151</f>
+        <f t="shared" si="212"/>
         <v>0.12224648125157565</v>
       </c>
       <c r="N162" s="154">
-        <f>-N62/N151</f>
+        <f t="shared" si="212"/>
         <v>3.1857354012504009E-2</v>
       </c>
       <c r="O162" s="154">
-        <f>-O62/O151</f>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="P162" s="154">
-        <f>-P62/P151</f>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="Q162" s="154">
-        <f>-Q62/Q151</f>
+        <f t="shared" si="212"/>
         <v>9.0545263577262276E-4</v>
       </c>
       <c r="T162" s="49"/>
@@ -31733,7 +31674,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>9.1157679218716546E-4</v>
+        <v>8.7440659588742739E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31741,27 +31682,27 @@
         <v>298</v>
       </c>
       <c r="L163" s="154">
-        <f>-(L62+L63)/L151</f>
+        <f t="shared" ref="L163:Q163" si="213">-(L62+L63)/L151</f>
         <v>0.13468619016930691</v>
       </c>
       <c r="M163" s="154">
-        <f>-(M62+M63)/M151</f>
+        <f t="shared" si="213"/>
         <v>0.16369748378824109</v>
       </c>
       <c r="N163" s="154">
-        <f>-(N62+N63)/N151</f>
+        <f t="shared" si="213"/>
         <v>7.7300932530340621E-2</v>
       </c>
       <c r="O163" s="154">
-        <f>-(O62+O63)/O151</f>
+        <f t="shared" si="213"/>
         <v>2.6595128045312645E-2</v>
       </c>
       <c r="P163" s="154">
-        <f>-(P62+P63)/P151</f>
+        <f t="shared" si="213"/>
         <v>1.9459089210843123E-2</v>
       </c>
       <c r="Q163" s="154">
-        <f>-(Q62+Q63)/Q151</f>
+        <f t="shared" si="213"/>
         <v>4.1671399714535481E-3</v>
       </c>
       <c r="T163" s="49"/>
@@ -31774,7 +31715,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>4.1953250094977496E-3</v>
+        <v>4.0242576288000917E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31782,27 +31723,27 @@
         <v>348</v>
       </c>
       <c r="L164" s="154">
-        <f>L156/L5</f>
+        <f t="shared" ref="L164:Q164" si="214">L156/L5</f>
         <v>0.11322609797980106</v>
       </c>
       <c r="M164" s="154">
-        <f>M156/M5</f>
+        <f t="shared" si="214"/>
         <v>0.11551912298693807</v>
       </c>
       <c r="N164" s="154">
-        <f>N156/N5</f>
+        <f t="shared" si="214"/>
         <v>0.13773022751895991</v>
       </c>
       <c r="O164" s="154">
-        <f>O156/O5</f>
+        <f t="shared" si="214"/>
         <v>0.1123904232821475</v>
       </c>
       <c r="P164" s="154">
-        <f>P156/P5</f>
+        <f t="shared" si="214"/>
         <v>9.4100951040925501E-2</v>
       </c>
       <c r="Q164" s="154">
-        <f>Q156/Q5</f>
+        <f t="shared" si="214"/>
         <v>0.25261177056215006</v>
       </c>
       <c r="T164" s="49"/>
@@ -31823,27 +31764,27 @@
         <v>349</v>
       </c>
       <c r="L165" s="154">
-        <f>L155/L5</f>
+        <f t="shared" ref="L165:Q165" si="215">L155/L5</f>
         <v>9.5122179571201199E-2</v>
       </c>
       <c r="M165" s="154">
-        <f>M155/M5</f>
+        <f t="shared" si="215"/>
         <v>9.6989966555183951E-2</v>
       </c>
       <c r="N165" s="154">
-        <f>N155/N5</f>
+        <f t="shared" si="215"/>
         <v>6.9203683640303354E-2</v>
       </c>
       <c r="O165" s="154">
-        <f>O155/O5</f>
+        <f t="shared" si="215"/>
         <v>8.1972217981987477E-2</v>
       </c>
       <c r="P165" s="154">
-        <f>P155/P5</f>
+        <f t="shared" si="215"/>
         <v>6.7934483895789821E-2</v>
       </c>
       <c r="Q165" s="154">
-        <f>Q155/Q5</f>
+        <f t="shared" si="215"/>
         <v>0.23714637146371464</v>
       </c>
       <c r="T165" s="49"/>
@@ -31864,27 +31805,27 @@
         <v>274</v>
       </c>
       <c r="L166" s="154">
-        <f>-L63/L155</f>
+        <f t="shared" ref="L166:Q166" si="216">-L63/L155</f>
         <v>0.63877952755905509</v>
       </c>
       <c r="M166" s="154">
-        <f>-M63/M155</f>
+        <f t="shared" si="216"/>
         <v>0.53934571175950485</v>
       </c>
       <c r="N166" s="154">
-        <f>-N63/N155</f>
+        <f t="shared" si="216"/>
         <v>1.1389432485322897</v>
       </c>
       <c r="O166" s="154">
-        <f>-O63/O155</f>
+        <f t="shared" si="216"/>
         <v>1.0893854748603351</v>
       </c>
       <c r="P166" s="154">
-        <f>-P63/P155</f>
+        <f t="shared" si="216"/>
         <v>0.970873786407767</v>
       </c>
       <c r="Q166" s="154">
-        <f>-Q63/Q155</f>
+        <f t="shared" si="216"/>
         <v>0.21922544951590595</v>
       </c>
       <c r="T166" s="49"/>
@@ -31905,27 +31846,27 @@
         <v>276</v>
       </c>
       <c r="L167" s="154">
-        <f>-L62/L155</f>
+        <f t="shared" ref="L167:Q167" si="217">-L62/L155</f>
         <v>2.0147637795275593</v>
       </c>
       <c r="M167" s="154">
-        <f>-M62/M155</f>
+        <f t="shared" si="217"/>
         <v>1.5906277630415562</v>
       </c>
       <c r="N167" s="154">
-        <f>-N62/N155</f>
+        <f t="shared" si="217"/>
         <v>0.79843444227005866</v>
       </c>
       <c r="O167" s="154">
-        <f>-O62/O155</f>
+        <f t="shared" si="217"/>
         <v>0</v>
       </c>
       <c r="P167" s="154">
-        <f>-P62/P155</f>
+        <f t="shared" si="217"/>
         <v>0</v>
       </c>
       <c r="Q167" s="154">
-        <f>-Q62/Q155</f>
+        <f t="shared" si="217"/>
         <v>6.0857538035961271E-2</v>
       </c>
       <c r="T167" s="49"/>
@@ -31946,27 +31887,27 @@
         <v>287</v>
       </c>
       <c r="L168" s="154">
-        <f>(-L63-L62)/L155</f>
+        <f t="shared" ref="L168:Q168" si="218">(-L63-L62)/L155</f>
         <v>2.6535433070866143</v>
       </c>
       <c r="M168" s="154">
-        <f>(-M63-M62)/M155</f>
+        <f t="shared" si="218"/>
         <v>2.1299734748010608</v>
       </c>
       <c r="N168" s="154">
-        <f>(-N63-N62)/N155</f>
+        <f t="shared" si="218"/>
         <v>1.9373776908023483</v>
       </c>
       <c r="O168" s="154">
-        <f>(-O63-O62)/O155</f>
+        <f t="shared" si="218"/>
         <v>1.0893854748603351</v>
       </c>
       <c r="P168" s="154">
-        <f>(-P63-P62)/P155</f>
+        <f t="shared" si="218"/>
         <v>0.970873786407767</v>
       </c>
       <c r="Q168" s="154">
-        <f>(-Q63-Q62)/Q155</f>
+        <f t="shared" si="218"/>
         <v>0.28008298755186722</v>
       </c>
       <c r="T168" s="49"/>
@@ -31987,27 +31928,27 @@
         <v>281</v>
       </c>
       <c r="L169" s="154">
-        <f>L79/L77</f>
+        <f t="shared" ref="L169:Q169" si="219">L79/L77</f>
         <v>8.6956521739130436E-3</v>
       </c>
       <c r="M169" s="154">
-        <f>M79/M77</f>
+        <f t="shared" si="219"/>
         <v>9.3896713615023476E-3</v>
       </c>
       <c r="N169" s="154">
-        <f>N79/N77</f>
+        <f t="shared" si="219"/>
         <v>9.6618357487922701E-3</v>
       </c>
       <c r="O169" s="154">
-        <f>O79/O77</f>
+        <f t="shared" si="219"/>
         <v>9.3896713615023476E-3</v>
       </c>
       <c r="P169" s="154">
-        <f>P79/P77</f>
+        <f t="shared" si="219"/>
         <v>9.1743119266055051E-3</v>
       </c>
       <c r="Q169" s="154">
-        <f>Q79/Q77</f>
+        <f t="shared" si="219"/>
         <v>8.4388185654008432E-3</v>
       </c>
       <c r="T169" s="49"/>
@@ -32028,59 +31969,59 @@
         <v>282</v>
       </c>
       <c r="L170" s="72">
-        <f>L105/L74</f>
+        <f t="shared" ref="L170:Q170" si="220">L105/L74</f>
         <v>5.3259911894273131</v>
       </c>
       <c r="M170" s="72">
-        <f>M105/M74</f>
+        <f t="shared" si="220"/>
         <v>2.9425837320574164</v>
       </c>
       <c r="N170" s="72">
-        <f>N105/N74</f>
+        <f t="shared" si="220"/>
         <v>3.7971014492753623</v>
       </c>
       <c r="O170" s="72">
-        <f>O105/O74</f>
+        <f t="shared" si="220"/>
         <v>6.4666666666666668</v>
       </c>
       <c r="P170" s="72">
-        <f>P105/P74</f>
+        <f t="shared" si="220"/>
         <v>4.183098591549296</v>
       </c>
       <c r="Q170" s="72">
-        <f>Q105/Q74</f>
+        <f t="shared" si="220"/>
         <v>7.5066079295154182</v>
       </c>
       <c r="T170" s="72">
-        <f t="shared" ref="T170:Z170" si="181">T105/T74</f>
+        <f t="shared" ref="T170:Z170" si="221">T105/T74</f>
         <v>5.8443396226415096</v>
       </c>
       <c r="U170" s="72">
-        <f t="shared" si="181"/>
+        <f t="shared" si="221"/>
         <v>5.8396226415094343</v>
       </c>
       <c r="V170" s="72">
-        <f t="shared" si="181"/>
+        <f t="shared" si="221"/>
         <v>3.8396226415094339</v>
       </c>
       <c r="W170" s="72">
-        <f t="shared" si="181"/>
+        <f t="shared" si="221"/>
         <v>4.183098591549296</v>
       </c>
       <c r="X170" s="72">
-        <f t="shared" si="181"/>
+        <f t="shared" si="221"/>
         <v>5.1962616822429908</v>
       </c>
       <c r="Y170" s="72">
-        <f t="shared" si="181"/>
+        <f t="shared" si="221"/>
         <v>4.7981651376146788</v>
       </c>
       <c r="Z170" s="72">
-        <f t="shared" si="181"/>
+        <f t="shared" si="221"/>
         <v>5.1160714285714288</v>
       </c>
       <c r="AA170" s="72">
-        <f t="shared" ref="T170:AA170" si="182">AA105/AA74</f>
+        <f t="shared" ref="AA170" si="222">AA105/AA74</f>
         <v>7.5066079295154182</v>
       </c>
       <c r="AC170" s="72">
@@ -32093,59 +32034,59 @@
         <v>284</v>
       </c>
       <c r="L171" s="154">
-        <f>L53/L58</f>
+        <f t="shared" ref="L171:Q171" si="223">L53/L58</f>
         <v>6.8880688806888066E-2</v>
       </c>
       <c r="M171" s="154">
-        <f>M53/M58</f>
+        <f t="shared" si="223"/>
         <v>8.7507543753771871E-2</v>
       </c>
       <c r="N171" s="154">
-        <f>N53/N58</f>
+        <f t="shared" si="223"/>
         <v>0.12208067940552017</v>
       </c>
       <c r="O171" s="154">
-        <f>O53/O58</f>
+        <f t="shared" si="223"/>
         <v>0.1383442265795207</v>
       </c>
       <c r="P171" s="154">
-        <f>P53/P58</f>
+        <f t="shared" si="223"/>
         <v>0.18467220683287167</v>
       </c>
       <c r="Q171" s="154">
-        <f>Q53/Q58</f>
+        <f t="shared" si="223"/>
         <v>5.7974959172563963E-2</v>
       </c>
       <c r="T171" s="154">
-        <f t="shared" ref="T171:Z171" si="183">T53/T58</f>
+        <f t="shared" ref="T171:Z171" si="224">T53/T58</f>
         <v>0.4</v>
       </c>
       <c r="U171" s="154">
-        <f t="shared" si="183"/>
+        <f t="shared" si="224"/>
         <v>0.22171945701357465</v>
       </c>
       <c r="V171" s="154">
-        <f t="shared" si="183"/>
+        <f t="shared" si="224"/>
         <v>0.20849420849420849</v>
       </c>
       <c r="W171" s="154">
-        <f t="shared" si="183"/>
+        <f t="shared" si="224"/>
         <v>0.11614173228346457</v>
       </c>
       <c r="X171" s="154">
-        <f t="shared" si="183"/>
+        <f t="shared" si="224"/>
         <v>9.7744360902255634E-2</v>
       </c>
       <c r="Y171" s="154">
-        <f t="shared" si="183"/>
+        <f t="shared" si="224"/>
         <v>7.3305670816044263E-2</v>
       </c>
       <c r="Z171" s="154">
-        <f t="shared" si="183"/>
+        <f t="shared" si="224"/>
         <v>4.8473967684021541E-2</v>
       </c>
       <c r="AA171" s="154">
-        <f t="shared" ref="T171:AA171" si="184">AA53/AA58</f>
+        <f t="shared" ref="AA171" si="225">AA53/AA58</f>
         <v>4.1379310344827586E-2</v>
       </c>
       <c r="AC171" s="154">
@@ -32158,59 +32099,59 @@
         <v>285</v>
       </c>
       <c r="L172" s="154">
-        <f>L53/L5</f>
+        <f t="shared" ref="L172:Q172" si="226">L53/L5</f>
         <v>1.0485909559030053E-2</v>
       </c>
       <c r="M172" s="154">
-        <f>M53/M5</f>
+        <f t="shared" si="226"/>
         <v>1.2434611096818454E-2</v>
       </c>
       <c r="N172" s="154">
-        <f>N53/N5</f>
+        <f t="shared" si="226"/>
         <v>1.5574214517876489E-2</v>
       </c>
       <c r="O172" s="154">
-        <f>O53/O5</f>
+        <f t="shared" si="226"/>
         <v>1.938635322851473E-2</v>
       </c>
       <c r="P172" s="154">
-        <f>P53/P5</f>
+        <f t="shared" si="226"/>
         <v>2.1985269869187644E-2</v>
       </c>
       <c r="Q172" s="154">
-        <f>Q53/Q5</f>
+        <f t="shared" si="226"/>
         <v>1.7466174661746617E-2</v>
       </c>
       <c r="T172" s="154">
-        <f t="shared" ref="T172:Z172" si="185">T53/T5</f>
+        <f t="shared" ref="T172:Z172" si="227">T53/T5</f>
         <v>1.7527675276752766E-2</v>
       </c>
       <c r="U172" s="154">
-        <f t="shared" si="185"/>
+        <f t="shared" si="227"/>
         <v>2.1075268817204302E-2</v>
       </c>
       <c r="V172" s="154">
-        <f t="shared" si="185"/>
+        <f t="shared" si="227"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="W172" s="154">
-        <f t="shared" si="185"/>
+        <f t="shared" si="227"/>
         <v>2.4140752864157119E-2</v>
       </c>
       <c r="X172" s="154">
-        <f t="shared" si="185"/>
+        <f t="shared" si="227"/>
         <v>1.9779383796120199E-2</v>
       </c>
       <c r="Y172" s="154">
-        <f t="shared" si="185"/>
+        <f t="shared" si="227"/>
         <v>1.8761061946902656E-2</v>
       </c>
       <c r="Z172" s="154">
-        <f t="shared" si="185"/>
+        <f t="shared" si="227"/>
         <v>1.7352185089974295E-2</v>
       </c>
       <c r="AA172" s="154">
-        <f t="shared" ref="T172:AA172" si="186">AA53/AA5</f>
+        <f t="shared" ref="AA172" si="228">AA53/AA5</f>
         <v>1.4880132267842381E-2</v>
       </c>
       <c r="AC172" s="154">
@@ -32223,59 +32164,59 @@
         <v>290</v>
       </c>
       <c r="L173" s="72">
-        <f>(L105-L106)/L74</f>
+        <f t="shared" ref="L173:Q173" si="229">(L105-L106)/L74</f>
         <v>-17.312775330396477</v>
       </c>
       <c r="M173" s="72">
-        <f>(M105-M106)/M74</f>
+        <f t="shared" si="229"/>
         <v>-24.071770334928228</v>
       </c>
       <c r="N173" s="72">
-        <f>(N105-N106)/N74</f>
+        <f t="shared" si="229"/>
         <v>-22.536231884057973</v>
       </c>
       <c r="O173" s="72">
-        <f>(O105-O106)/O74</f>
+        <f t="shared" si="229"/>
         <v>-20.552380952380954</v>
       </c>
       <c r="P173" s="72">
-        <f>(P105-P106)/P74</f>
+        <f t="shared" si="229"/>
         <v>-19.267605633802816</v>
       </c>
       <c r="Q173" s="72">
-        <f>(Q105-Q106)/Q74</f>
+        <f t="shared" si="229"/>
         <v>-8.1982378854625555</v>
       </c>
       <c r="T173" s="72">
-        <f t="shared" ref="T173:Z173" si="187">(T105-T106)/T74</f>
+        <f t="shared" ref="T173:Z173" si="230">(T105-T106)/T74</f>
         <v>-20.929245283018869</v>
       </c>
       <c r="U173" s="72">
-        <f t="shared" si="187"/>
+        <f t="shared" si="230"/>
         <v>-20.94811320754717</v>
       </c>
       <c r="V173" s="72">
-        <f t="shared" si="187"/>
+        <f t="shared" si="230"/>
         <v>-20.433962264150942</v>
       </c>
       <c r="W173" s="72">
-        <f t="shared" si="187"/>
+        <f t="shared" si="230"/>
         <v>-19.267605633802816</v>
       </c>
       <c r="X173" s="72">
-        <f t="shared" si="187"/>
+        <f t="shared" si="230"/>
         <v>-18.140186915887849</v>
       </c>
       <c r="Y173" s="72">
-        <f t="shared" si="187"/>
+        <f t="shared" si="230"/>
         <v>-15.839449541284404</v>
       </c>
       <c r="Z173" s="72">
-        <f t="shared" si="187"/>
+        <f t="shared" si="230"/>
         <v>-12.129464285714286</v>
       </c>
       <c r="AA173" s="72">
-        <f t="shared" ref="T173:AA173" si="188">(AA105-AA106)/AA74</f>
+        <f t="shared" ref="AA173" si="231">(AA105-AA106)/AA74</f>
         <v>-8.1982378854625555</v>
       </c>
       <c r="AC173" s="72">
@@ -32288,27 +32229,27 @@
         <v>295</v>
       </c>
       <c r="L174" s="154">
-        <f>(L105-L106)/L151</f>
+        <f t="shared" ref="L174:Q174" si="232">(L105-L106)/L151</f>
         <v>-0.19633409768745408</v>
       </c>
       <c r="M174" s="154">
-        <f>(M105-M106)/M151</f>
+        <f t="shared" si="232"/>
         <v>-0.34186884223272768</v>
       </c>
       <c r="N174" s="154">
-        <f>(N105-N106)/N151</f>
+        <f t="shared" si="232"/>
         <v>-0.36425136389296864</v>
       </c>
       <c r="O174" s="154">
-        <f>(O105-O106)/O151</f>
+        <f t="shared" si="232"/>
         <v>-0.19621294468986217</v>
       </c>
       <c r="P174" s="154">
-        <f>(P105-P106)/P151</f>
+        <f t="shared" si="232"/>
         <v>-0.13310017020216697</v>
       </c>
       <c r="Q174" s="154">
-        <f>(Q105-Q106)/Q151</f>
+        <f t="shared" si="232"/>
         <v>-9.5741326998457447E-3</v>
       </c>
       <c r="T174" s="49"/>
@@ -32321,7 +32262,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-9.6388886946608791E-3</v>
+        <v>-9.2458561076505814E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -32329,59 +32270,59 @@
         <v>304</v>
       </c>
       <c r="L175" s="154">
-        <f>-L108/L5</f>
+        <f t="shared" ref="L175:Q175" si="233">-L108/L5</f>
         <v>4.6624847860687199E-2</v>
       </c>
       <c r="M175" s="154">
-        <f>-M108/M5</f>
+        <f t="shared" si="233"/>
         <v>3.2673012606122973E-2</v>
       </c>
       <c r="N175" s="154">
-        <f>-N108/N5</f>
+        <f t="shared" si="233"/>
         <v>4.2795232936078009E-2</v>
       </c>
       <c r="O175" s="154">
-        <f>-O108/O5</f>
+        <f t="shared" si="233"/>
         <v>3.877270645702946E-2</v>
       </c>
       <c r="P175" s="154">
-        <f>-P108/P5</f>
+        <f t="shared" si="233"/>
         <v>2.9130482576673628E-2</v>
       </c>
       <c r="Q175" s="154">
-        <f>-Q108/Q5</f>
+        <f t="shared" si="233"/>
         <v>4.6658466584665846E-2</v>
       </c>
       <c r="T175" s="154">
-        <f t="shared" ref="T175:Z175" si="189">-T108/T5</f>
+        <f t="shared" ref="T175:Z175" si="234">-T108/T5</f>
         <v>3.136531365313653E-2</v>
       </c>
       <c r="U175" s="154">
-        <f t="shared" si="189"/>
+        <f t="shared" si="234"/>
         <v>3.053763440860215E-2</v>
       </c>
       <c r="V175" s="154">
-        <f t="shared" si="189"/>
+        <f t="shared" si="234"/>
         <v>1.9907407407407408E-2</v>
       </c>
       <c r="W175" s="154">
-        <f t="shared" si="189"/>
+        <f t="shared" si="234"/>
         <v>3.3960720130932896E-2</v>
       </c>
       <c r="X175" s="154">
-        <f t="shared" si="189"/>
+        <f t="shared" si="234"/>
         <v>3.9939140357550397E-2</v>
       </c>
       <c r="Y175" s="154">
-        <f t="shared" si="189"/>
+        <f t="shared" si="234"/>
         <v>4.1061946902654869E-2</v>
       </c>
       <c r="Z175" s="154">
-        <f t="shared" si="189"/>
+        <f t="shared" si="234"/>
         <v>5.1735218508997427E-2</v>
       </c>
       <c r="AA175" s="154">
-        <f t="shared" ref="T175:AA175" si="190">-AA108/AA5</f>
+        <f t="shared" ref="AA175" si="235">-AA108/AA5</f>
         <v>5.1529346927528245E-2</v>
       </c>
       <c r="AC175" s="154">
@@ -32394,59 +32335,59 @@
         <v>305</v>
       </c>
       <c r="L176" s="154">
-        <f>-(L108/L58)</f>
+        <f t="shared" ref="L176:Q176" si="236">-(L108/L58)</f>
         <v>0.30627306273062732</v>
       </c>
       <c r="M176" s="154">
-        <f>-(M108/M58)</f>
+        <f t="shared" si="236"/>
         <v>0.22993361496680748</v>
       </c>
       <c r="N176" s="154">
-        <f>-(N108/N58)</f>
+        <f t="shared" si="236"/>
         <v>0.3354564755838641</v>
       </c>
       <c r="O176" s="154">
-        <f>-(O108/O58)</f>
+        <f t="shared" si="236"/>
         <v>0.27668845315904139</v>
       </c>
       <c r="P176" s="154">
-        <f>-(P108/P58)</f>
+        <f t="shared" si="236"/>
         <v>0.24469067405355494</v>
       </c>
       <c r="Q176" s="154">
-        <f>-(Q108/Q58)</f>
+        <f t="shared" si="236"/>
         <v>0.15487207403375067</v>
       </c>
       <c r="T176" s="154">
-        <f t="shared" ref="T176:Z176" si="191">-(T108/T58)</f>
+        <f t="shared" ref="T176:Z176" si="237">-(T108/T58)</f>
         <v>0.71578947368421053</v>
       </c>
       <c r="U176" s="154">
-        <f t="shared" si="191"/>
+        <f t="shared" si="237"/>
         <v>0.32126696832579188</v>
       </c>
       <c r="V176" s="154">
-        <f t="shared" si="191"/>
+        <f t="shared" si="237"/>
         <v>0.16602316602316602</v>
       </c>
       <c r="W176" s="154">
-        <f t="shared" si="191"/>
+        <f t="shared" si="237"/>
         <v>0.16338582677165353</v>
       </c>
       <c r="X176" s="154">
-        <f t="shared" si="191"/>
+        <f t="shared" si="237"/>
         <v>0.19736842105263158</v>
       </c>
       <c r="Y176" s="154">
-        <f t="shared" si="191"/>
+        <f t="shared" si="237"/>
         <v>0.16044260027662519</v>
       </c>
       <c r="Z176" s="154">
-        <f t="shared" si="191"/>
+        <f t="shared" si="237"/>
         <v>0.14452423698384201</v>
       </c>
       <c r="AA176" s="154">
-        <f t="shared" ref="T176:AA176" si="192">-(AA108/AA58)</f>
+        <f t="shared" ref="AA176" si="238">-(AA108/AA58)</f>
         <v>0.14329501915708812</v>
       </c>
       <c r="AC176" s="154">
@@ -32459,59 +32400,59 @@
         <v>306</v>
       </c>
       <c r="L177" s="154">
-        <f>-L108/L52</f>
+        <f t="shared" ref="L177:Q177" si="239">-L108/L52</f>
         <v>1.2544080604534005</v>
       </c>
       <c r="M177" s="154">
-        <f>-M108/M52</f>
+        <f t="shared" si="239"/>
         <v>0.84478935698447899</v>
       </c>
       <c r="N177" s="154">
-        <f>-N108/N52</f>
+        <f t="shared" si="239"/>
         <v>0.61598440545808963</v>
       </c>
       <c r="O177" s="154">
-        <f>-O108/O52</f>
+        <f t="shared" si="239"/>
         <v>0.96212121212121215</v>
       </c>
       <c r="P177" s="154">
-        <f>-P108/P52</f>
+        <f t="shared" si="239"/>
         <v>1.0557768924302788</v>
       </c>
       <c r="Q177" s="154">
-        <f>-Q108/Q52</f>
+        <f t="shared" si="239"/>
         <v>2.0615942028985508</v>
       </c>
       <c r="T177" s="154">
-        <f t="shared" ref="T177:Z177" si="193">-T108/T52</f>
+        <f t="shared" ref="T177:Z177" si="240">-T108/T52</f>
         <v>1.0625</v>
       </c>
       <c r="U177" s="154">
-        <f t="shared" si="193"/>
+        <f t="shared" si="240"/>
         <v>1.126984126984127</v>
       </c>
       <c r="V177" s="154">
-        <f t="shared" si="193"/>
+        <f t="shared" si="240"/>
         <v>0.68253968253968256</v>
       </c>
       <c r="W177" s="154">
-        <f t="shared" si="193"/>
+        <f t="shared" si="240"/>
         <v>1.360655737704918</v>
       </c>
       <c r="X177" s="154">
-        <f t="shared" si="193"/>
+        <f t="shared" si="240"/>
         <v>1.4583333333333333</v>
       </c>
       <c r="Y177" s="154">
-        <f t="shared" si="193"/>
+        <f t="shared" si="240"/>
         <v>1.7058823529411764</v>
       </c>
       <c r="Z177" s="154">
-        <f t="shared" si="193"/>
+        <f t="shared" si="240"/>
         <v>2.4393939393939394</v>
       </c>
       <c r="AA177" s="154">
-        <f t="shared" ref="T177:AA177" si="194">-AA108/AA52</f>
+        <f t="shared" ref="AA177" si="241">-AA108/AA52</f>
         <v>2.6714285714285713</v>
       </c>
       <c r="AC177" s="154">
@@ -32524,27 +32465,27 @@
         <v>362</v>
       </c>
       <c r="L178" s="224">
-        <f>L5/L36</f>
+        <f t="shared" ref="L178:Q178" si="242">L5/L36</f>
         <v>1.2312391930835735</v>
       </c>
       <c r="M178" s="224">
-        <f>M5/M36</f>
+        <f t="shared" si="242"/>
         <v>1.3037790697674418</v>
       </c>
       <c r="N178" s="224">
-        <f>N5/N36</f>
+        <f t="shared" si="242"/>
         <v>0.97723663313922715</v>
       </c>
       <c r="O178" s="224">
-        <f>O5/O36</f>
+        <f t="shared" si="242"/>
         <v>0.84649179480553038</v>
       </c>
       <c r="P178" s="224">
-        <f>P5/P36</f>
+        <f t="shared" si="242"/>
         <v>1.133865137729029</v>
       </c>
       <c r="Q178" s="224">
-        <f>Q5/Q36</f>
+        <f t="shared" si="242"/>
         <v>1.2229241877256318</v>
       </c>
       <c r="T178" s="49"/>
@@ -32565,27 +32506,27 @@
         <v>359</v>
       </c>
       <c r="L179" s="226">
-        <f>IF(AND(L11&gt;0,L106&gt;0),L106/L11,"N/A")</f>
+        <f t="shared" ref="L179:Q179" si="243">IF(AND(L11&gt;0,L106&gt;0),L106/L11,"N/A")</f>
         <v>3.4443699731903483</v>
       </c>
       <c r="M179" s="226">
-        <f>IF(AND(M11&gt;0,M106&gt;0),M106/M11,"N/A")</f>
+        <f t="shared" si="243"/>
         <v>2.8879795396419436</v>
       </c>
       <c r="N179" s="226" t="str">
-        <f>IF(AND(N11&gt;0,N106&gt;0),N106/N11,"N/A")</f>
+        <f t="shared" si="243"/>
         <v>N/A</v>
       </c>
       <c r="O179" s="226">
-        <f>IF(AND(O11&gt;0,O106&gt;0),O106/O11,"N/A")</f>
+        <f t="shared" si="243"/>
         <v>12.553097345132743</v>
       </c>
       <c r="P179" s="226">
-        <f>IF(AND(P11&gt;0,P106&gt;0),P106/P11,"N/A")</f>
+        <f t="shared" si="243"/>
         <v>2.6428571428571428</v>
       </c>
       <c r="Q179" s="226">
-        <f>IF(AND(Q11&gt;0,Q106&gt;0),Q106/Q11,"N/A")</f>
+        <f t="shared" si="243"/>
         <v>0.8707865168539326</v>
       </c>
       <c r="T179" s="49"/>
@@ -32606,27 +32547,27 @@
         <v>360</v>
       </c>
       <c r="L180" s="226">
-        <f>IF(AND(L11&gt;0,L106&gt;0),(L106-L105)/L11,"N/A")</f>
+        <f t="shared" ref="L180:Q180" si="244">IF(AND(L11&gt;0,L106&gt;0),(L106-L105)/L11,"N/A")</f>
         <v>2.6340482573726542</v>
       </c>
       <c r="M180" s="226">
-        <f>IF(AND(M11&gt;0,M106&gt;0),(M106-M105)/M11,"N/A")</f>
+        <f t="shared" si="244"/>
         <v>2.5734015345268544</v>
       </c>
       <c r="N180" s="226" t="str">
-        <f>IF(AND(N11&gt;0,N106&gt;0),(N106-N105)/N11,"N/A")</f>
+        <f t="shared" si="244"/>
         <v>N/A</v>
       </c>
       <c r="O180" s="226">
-        <f>IF(AND(O11&gt;0,O106&gt;0),(O106-O105)/O11,"N/A")</f>
+        <f t="shared" si="244"/>
         <v>9.5486725663716818</v>
       </c>
       <c r="P180" s="226">
-        <f>IF(AND(P11&gt;0,P106&gt;0),(P106-P105)/P11,"N/A")</f>
+        <f t="shared" si="244"/>
         <v>2.1714285714285713</v>
       </c>
       <c r="Q180" s="226">
-        <f>IF(AND(Q11&gt;0,Q106&gt;0),(Q106-Q105)/Q11,"N/A")</f>
+        <f t="shared" si="244"/>
         <v>0.45456765999022958</v>
       </c>
       <c r="T180" s="49"/>
@@ -32647,27 +32588,27 @@
         <v>361</v>
       </c>
       <c r="L181" s="226">
-        <f>L5/(L106+L110-L105)</f>
+        <f t="shared" ref="L181:Q181" si="245">L5/(L106+L110-L105)</f>
         <v>2.3418110063582547</v>
       </c>
       <c r="M181" s="226">
-        <f>M5/(M106+M110-M105)</f>
+        <f t="shared" si="245"/>
         <v>2.2686770428015564</v>
       </c>
       <c r="N181" s="226">
-        <f>N5/(N106+N110-N105)</f>
+        <f t="shared" si="245"/>
         <v>2.1304096941719561</v>
       </c>
       <c r="O181" s="226">
-        <f>O5/(O106+O110-O105)</f>
+        <f t="shared" si="245"/>
         <v>2.3189380530973454</v>
       </c>
       <c r="P181" s="226">
-        <f>P5/(P106+P110-P105)</f>
+        <f t="shared" si="245"/>
         <v>2.4916461243494932</v>
       </c>
       <c r="Q181" s="226">
-        <f>Q5/(Q106+Q110-Q105)</f>
+        <f t="shared" si="245"/>
         <v>3.0275571002979147</v>
       </c>
       <c r="T181" s="49"/>
@@ -32813,7 +32754,7 @@
         <v>697</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" ref="AC186" si="195">SUM(X186:AA186)</f>
+        <f t="shared" ref="AC186" si="246">SUM(X186:AA186)</f>
         <v>2425</v>
       </c>
     </row>
@@ -32877,98 +32818,98 @@
       <c r="J190" s="81"/>
       <c r="K190" s="81"/>
       <c r="L190" s="81">
-        <f t="shared" ref="L190:L191" si="196">IF(K185=0,
+        <f t="shared" ref="L190:L191" si="247">IF(K185=0,
 IF(L185=0,0,IF(L185&gt;0,1,-1)),
 (L185-K185)/ABS(K185)
 )</f>
         <v>0</v>
       </c>
       <c r="M190" s="81">
-        <f t="shared" ref="M190:M191" si="197">IF(L185=0,
+        <f t="shared" ref="M190:M191" si="248">IF(L185=0,
 IF(M185=0,0,IF(M185&gt;0,1,-1)),
 (M185-L185)/ABS(L185)
 )</f>
         <v>0</v>
       </c>
       <c r="N190" s="81">
-        <f t="shared" ref="N190:N191" si="198">IF(M185=0,
+        <f t="shared" ref="N190:N191" si="249">IF(M185=0,
 IF(N185=0,0,IF(N185&gt;0,1,-1)),
 (N185-M185)/ABS(M185)
 )</f>
         <v>0</v>
       </c>
       <c r="O190" s="81">
-        <f t="shared" ref="O190:O191" si="199">IF(N185=0,
+        <f t="shared" ref="O190:O191" si="250">IF(N185=0,
 IF(O185=0,0,IF(O185&gt;0,1,-1)),
 (O185-N185)/ABS(N185)
 )</f>
         <v>0</v>
       </c>
       <c r="P190" s="81">
-        <f t="shared" ref="P190:P191" si="200">IF(O185=0,
+        <f t="shared" ref="P190:P191" si="251">IF(O185=0,
 IF(P185=0,0,IF(P185&gt;0,1,-1)),
 (P185-O185)/ABS(O185)
 )</f>
         <v>1</v>
       </c>
       <c r="Q190" s="81">
-        <f t="shared" ref="M190:Q191" si="201">IF(P185=0,
+        <f t="shared" ref="Q190:Q191" si="252">IF(P185=0,
 IF(Q185=0,0,IF(Q185&gt;0,1,-1)),
 (Q185-P185)/ABS(P185)
 )</f>
         <v>0.4377575044143614</v>
       </c>
       <c r="T190" s="81">
-        <f t="shared" ref="T190:T191" si="202">IF(S185=0,
+        <f t="shared" ref="T190:T191" si="253">IF(S185=0,
 IF(T185=0,0,IF(T185&gt;0,1,-1)),
 (T185-S185)/ABS(S185)
 )</f>
         <v>1</v>
       </c>
       <c r="U190" s="81">
-        <f t="shared" ref="U190:U191" si="203">IF(T185=0,
+        <f t="shared" ref="U190:U191" si="254">IF(T185=0,
 IF(U185=0,0,IF(U185&gt;0,1,-1)),
 (U185-T185)/ABS(T185)
 )</f>
         <v>9.7345132743362831E-2</v>
       </c>
       <c r="V190" s="81">
-        <f t="shared" ref="V190:V191" si="204">IF(U185=0,
+        <f t="shared" ref="V190:V191" si="255">IF(U185=0,
 IF(V185=0,0,IF(V185&gt;0,1,-1)),
 (V185-U185)/ABS(U185)
 )</f>
         <v>-6.9700460829493091E-2</v>
       </c>
       <c r="W190" s="81">
-        <f t="shared" ref="W190:W191" si="205">IF(V185=0,
+        <f t="shared" ref="W190:W191" si="256">IF(V185=0,
 IF(W185=0,0,IF(W185&gt;0,1,-1)),
 (W185-V185)/ABS(V185)
 )</f>
         <v>0.15356037151702787</v>
       </c>
       <c r="X190" s="81">
-        <f t="shared" ref="X190:X191" si="206">IF(W185=0,
+        <f t="shared" ref="X190:X191" si="257">IF(W185=0,
 IF(X185=0,0,IF(X185&gt;0,1,-1)),
 (X185-W185)/ABS(W185)
 )</f>
         <v>0.13472893183038109</v>
       </c>
       <c r="Y190" s="81">
-        <f t="shared" ref="Y190:Y191" si="207">IF(X185=0,
+        <f t="shared" ref="Y190:Y191" si="258">IF(X185=0,
 IF(Y185=0,0,IF(Y185&gt;0,1,-1)),
 (Y185-X185)/ABS(X185)
 )</f>
         <v>5.2034058656575212E-2</v>
       </c>
       <c r="Z190" s="81">
-        <f t="shared" ref="Z190:Z191" si="208">IF(Y185=0,
+        <f t="shared" ref="Z190:Z191" si="259">IF(Y185=0,
 IF(Z185=0,0,IF(Z185&gt;0,1,-1)),
 (Z185-Y185)/ABS(Y185)
 )</f>
         <v>0.12410071942446044</v>
       </c>
       <c r="AA190" s="81">
-        <f t="shared" ref="T190:AA191" si="209">IF(Z185=0,
+        <f t="shared" ref="AA190:AA191" si="260">IF(Z185=0,
 IF(AA185=0,0,IF(AA185&gt;0,1,-1)),
 (AA185-Z185)/ABS(Z185)
 )</f>
@@ -32982,59 +32923,59 @@
         <v>Edge &amp; IoT</v>
       </c>
       <c r="L191" s="81">
-        <f t="shared" si="196"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="M191" s="81">
-        <f t="shared" si="197"/>
+        <f t="shared" si="248"/>
         <v>0</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" si="198"/>
+        <f t="shared" si="249"/>
         <v>0</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" si="199"/>
+        <f t="shared" si="250"/>
         <v>0</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" si="200"/>
+        <f t="shared" si="251"/>
         <v>1</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" si="201"/>
+        <f t="shared" si="252"/>
         <v>5.434782608695652E-2</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" si="202"/>
+        <f t="shared" si="253"/>
         <v>1</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" si="203"/>
+        <f t="shared" si="254"/>
         <v>6.8376068376068376E-3</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" si="204"/>
+        <f t="shared" si="255"/>
         <v>-7.4702886247877756E-2</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" si="205"/>
+        <f t="shared" si="256"/>
         <v>6.6055045871559637E-2</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" si="206"/>
+        <f t="shared" si="257"/>
         <v>-0.11359724612736662</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" si="207"/>
+        <f t="shared" si="258"/>
         <v>0.16699029126213591</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" si="208"/>
+        <f t="shared" si="259"/>
         <v>1.8302828618968387E-2</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" si="209"/>
+        <f t="shared" si="260"/>
         <v>0.1388888888888889</v>
       </c>
       <c r="AC191" s="49"/>
@@ -33085,45 +33026,30 @@
       <c r="J195" s="81"/>
       <c r="K195" s="81"/>
       <c r="L195" s="81">
-        <f>IF(K63=0,
+        <f t="shared" ref="L195:Q195" si="261">IF(K63=0,
 IF(L63=0,0,IF(L63&gt;0,1,-1)),
 (L63-K63)/K63
 )</f>
         <v>-1</v>
       </c>
       <c r="M195" s="81">
-        <f>IF(L63=0,
-IF(M63=0,0,IF(M63&gt;0,1,-1)),
-(M63-L63)/L63
-)</f>
+        <f t="shared" si="261"/>
         <v>-6.0092449922958396E-2</v>
       </c>
       <c r="N195" s="81">
-        <f>IF(M63=0,
-IF(N63=0,0,IF(N63&gt;0,1,-1)),
-(N63-M63)/M63
-)</f>
+        <f t="shared" si="261"/>
         <v>-4.5901639344262293E-2</v>
       </c>
       <c r="O195" s="81">
-        <f>IF(N63=0,
-IF(O63=0,0,IF(O63&gt;0,1,-1)),
-(O63-N63)/N63
-)</f>
+        <f t="shared" si="261"/>
         <v>5.1546391752577319E-3</v>
       </c>
       <c r="P195" s="81">
-        <f>IF(O63=0,
-IF(P63=0,0,IF(P63&gt;0,1,-1)),
-(P63-O63)/O63
-)</f>
+        <f t="shared" si="261"/>
         <v>2.564102564102564E-2</v>
       </c>
       <c r="Q195" s="81">
-        <f>IF(P63=0,
-IF(Q63=0,0,IF(Q63&gt;0,1,-1)),
-(Q63-P63)/P63
-)</f>
+        <f t="shared" si="261"/>
         <v>5.6666666666666664E-2</v>
       </c>
       <c r="T195" s="49"/>
@@ -33409,7 +33335,7 @@
         <v>195</v>
       </c>
       <c r="AC206" s="62">
-        <f t="shared" ref="AC206:AC207" si="210">SUM(X206:AA206)</f>
+        <f t="shared" ref="AC206:AC207" si="262">SUM(X206:AA206)</f>
         <v>694.4</v>
       </c>
     </row>
@@ -33469,7 +33395,7 @@
         <v>23</v>
       </c>
       <c r="AC207" s="62">
-        <f t="shared" si="210"/>
+        <f t="shared" si="262"/>
         <v>94</v>
       </c>
     </row>
@@ -33514,19 +33440,19 @@
       <c r="J209" s="62"/>
       <c r="K209" s="62"/>
       <c r="L209" s="63" t="e">
-        <f t="shared" ref="L209:O209" si="211">L185/L206</f>
+        <f t="shared" ref="L209:O209" si="263">L185/L206</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M209" s="63" t="e">
-        <f t="shared" si="211"/>
+        <f t="shared" si="263"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N209" s="63" t="e">
-        <f t="shared" si="211"/>
+        <f t="shared" si="263"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O209" s="63" t="e">
-        <f t="shared" si="211"/>
+        <f t="shared" si="263"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P209" s="63">
@@ -33538,39 +33464,39 @@
         <v>14.058992805755397</v>
       </c>
       <c r="T209" s="63">
-        <f t="shared" ref="T209:Z209" si="212">T185/T206</f>
+        <f t="shared" ref="T209:Z209" si="264">T185/T206</f>
         <v>13.87719298245614</v>
       </c>
       <c r="U209" s="63">
-        <f t="shared" si="212"/>
+        <f t="shared" si="264"/>
         <v>13.777777777777779</v>
       </c>
       <c r="V209" s="63">
-        <f t="shared" si="212"/>
+        <f t="shared" si="264"/>
         <v>13.503344481605351</v>
       </c>
       <c r="W209" s="63">
-        <f t="shared" si="212"/>
+        <f t="shared" si="264"/>
         <v>13.598540145985401</v>
       </c>
       <c r="X209" s="63">
-        <f t="shared" si="212"/>
+        <f t="shared" si="264"/>
         <v>13.29559748427673</v>
       </c>
       <c r="Y209" s="63">
-        <f t="shared" si="212"/>
+        <f t="shared" si="264"/>
         <v>13.478787878787879</v>
       </c>
       <c r="Z209" s="63">
-        <f t="shared" si="212"/>
+        <f t="shared" si="264"/>
         <v>14.253135689851767</v>
       </c>
       <c r="AA209" s="63">
-        <f t="shared" ref="T209:AC209" si="213">AA185/AA206</f>
+        <f t="shared" ref="AA209:AC209" si="265">AA185/AA206</f>
         <v>15.041025641025641</v>
       </c>
       <c r="AC209" s="63">
-        <f t="shared" si="213"/>
+        <f t="shared" si="265"/>
         <v>14.071140552995391</v>
       </c>
     </row>
@@ -33655,15 +33581,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="247" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="247"/>
+      <c r="E4" s="247" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33671,7 +33597,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33687,7 +33613,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>193072.05</v>
+        <v>201279.35999999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33707,7 +33633,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>194933.05</v>
+        <v>203140.36</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33727,7 +33653,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>58.692363112391924</v>
+        <v>61.187319884726222</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -33747,7 +33673,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>15.280950184501846</v>
+        <v>15.930528905289053</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -33767,7 +33693,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>85.337125057683437</v>
+        <v>88.964725426857399</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33787,7 +33713,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>15.984669946699466</v>
+        <v>16.657676096760966</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33796,18 +33722,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>47.61432584269663</v>
+        <v>49.619042501221294</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="247" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="247"/>
+      <c r="E15" s="247" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33858,14 +33784,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="247" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="247"/>
+      <c r="E21" s="247" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="247"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33934,14 +33860,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="247" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="247"/>
+      <c r="E29" s="247" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="247"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34017,14 +33943,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="247" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="247"/>
+      <c r="E37" s="247" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="247"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34032,7 +33958,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.7037991775609159E-2</v>
+        <v>1.6343255463451396E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -34048,7 +33974,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>1.4978864107984559E-2</v>
+        <v>1.4368090200604772E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -34064,7 +33990,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.5843613821886699E-3</v>
+        <v>3.4382064807837228E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -34080,7 +34006,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>9.1157679218716546E-4</v>
+        <v>8.7440659588742739E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34089,18 +34015,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.1953250094977496E-3</v>
+        <v>4.0242576288000917E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="247" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="247"/>
+      <c r="E45" s="247" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="247"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34133,18 +34059,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>-9.6388886946608791E-3</v>
+        <v>-9.2458561076505814E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="247" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="247"/>
+      <c r="E51" s="247" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="247"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34312,7 +34238,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>814.65</v>
+        <v>849.28</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34341,7 +34267,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>193072.05</v>
+        <v>201279.35999999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34370,7 +34296,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>194933.05</v>
+        <v>203140.36</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34399,7 +34325,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>58.692363112391924</v>
+        <v>61.187319884726222</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34428,7 +34354,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>15.280950184501846</v>
+        <v>15.930528905289053</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34457,7 +34383,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>85.337125057683437</v>
+        <v>88.964725426857399</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34486,7 +34412,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>15.984669946699466</v>
+        <v>16.657676096760966</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34515,7 +34441,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>47.61432584269663</v>
+        <v>49.619042501221294</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35288,7 +35214,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.7037991775609159E-2</v>
+        <v>1.6343255463451396E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35317,7 +35243,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>1.4978864107984559E-2</v>
+        <v>1.4368090200604772E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35346,7 +35272,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.5843613821886699E-3</v>
+        <v>3.4382064807837228E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35375,7 +35301,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>9.1157679218716546E-4</v>
+        <v>8.7440659588742739E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35404,7 +35330,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.1953250094977496E-3</v>
+        <v>4.0242576288000917E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35640,7 +35566,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>-9.6388886946608791E-3</v>
+        <v>-9.2458561076505814E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36102,14 +36028,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="250" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="F3" s="249" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="248"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36176,19 +36102,19 @@
       <c r="B7" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="248">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="249"/>
+      <c r="F7" s="248">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="249"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36215,19 +36141,19 @@
       <c r="B9" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="248">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="249"/>
+      <c r="F9" s="248">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="249"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36254,19 +36180,19 @@
       <c r="B11" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="248">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="249"/>
+      <c r="F11" s="248">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="249"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36293,19 +36219,19 @@
       <c r="B13" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="248">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="249"/>
+      <c r="F13" s="248">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="249"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36332,19 +36258,19 @@
       <c r="B15" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="248">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="249"/>
+      <c r="F15" s="248">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36371,19 +36297,19 @@
       <c r="B17" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="248">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="249"/>
+      <c r="F17" s="248">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="249"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36410,22 +36336,22 @@
       <c r="B19" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="248">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="249"/>
+      <c r="F19" s="248">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="249"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36452,22 +36378,22 @@
       <c r="B21" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="248">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="249"/>
+      <c r="F21" s="248">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="249"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36516,22 +36442,22 @@
       <c r="B25" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="248">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="249"/>
+      <c r="F25" s="248">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="249"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36559,25 +36485,37 @@
       <c r="B27" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="248">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="249"/>
+      <c r="F27" s="248">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36588,18 +36526,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11CE31E-7B69-3146-9057-8C31C1AA9099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0EF1ED-0992-4043-BCF2-A2CA18338B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2401,6 +2431,9 @@
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2410,15 +2443,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2426,6 +2450,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12413,7 +12443,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -12621,7 +12651,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12639,12 +12669,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1145</v>
-    <v>175.815</v>
-    <v>2.0948000000000002</v>
-    <v>50.67</v>
-    <v>6.3448000000000004E-2</v>
-    <v>-0.15</v>
-    <v>-1.7659999999999998E-4</v>
+    <v>209</v>
+    <v>2.0929000000000002</v>
+    <v>35.909999999999997</v>
+    <v>4.0930999999999995E-2</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12652,35 +12680,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>852.98</v>
+    <v>936.94</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46269.901031562498</v>
+    <v>46287.765208066405</v>
     <v>0</v>
-    <v>805.01009999999997</v>
-    <v>192484640960</v>
+    <v>856.39</v>
+    <v>209168166311</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>818.75</v>
-    <v>61.082099999999997</v>
-    <v>798.61</v>
-    <v>849.28</v>
-    <v>849.13</v>
-    <v>226644500</v>
+    <v>857.69</v>
+    <v>65.681899999999999</v>
+    <v>877.32500000000005</v>
+    <v>913.23500000000001</v>
+    <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>2556498</v>
-    <v>4087698</v>
+    <v>3506640</v>
+    <v>3782309</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12692,30 +12734,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>3</v>
-    <v>47.32</v>
+    <v>6</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
-    <v>47.62</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12737,8 +12779,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12759,7 +12799,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12769,6 +12808,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12804,7 +12848,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12815,16 +12859,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12918,19 +12959,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13002,9 +13037,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13012,9 +13044,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13505,18 +13534,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="245"/>
-      <c r="E2" s="244" t="s">
+      <c r="C2" s="246"/>
+      <c r="E2" s="245" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="245"/>
-      <c r="H2" s="244" t="s">
+      <c r="F2" s="246"/>
+      <c r="H2" s="245" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="245"/>
+      <c r="I2" s="246"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13531,7 +13560,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>201279.35999999999</v>
+        <v>216436.69500000001</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13539,7 +13568,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>138.76356724687497</v>
+        <v>138.81798383520456</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13555,7 +13584,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>203140.36</v>
+        <v>218297.69500000001</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13563,7 +13592,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>138.71605779137505</v>
+        <v>138.75153062794726</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13572,7 +13601,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13587,23 +13616,23 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>112.28454742641925</v>
+        <v>112.36738006633963</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>849.13</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>61.187319884726222</v>
+        <v>65.795028818443797</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13611,7 +13640,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>154.15567962861482</v>
+        <v>154.19469918648292</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13620,14 +13649,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>50.67</v>
+        <v>35.909999999999997</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>15.930528905289053</v>
+        <v>17.130176814268143</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13635,23 +13664,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>135.97996302332101</v>
+        <v>136.03289842899358</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.15</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>1.4368090200604772E-2</v>
+        <v>1.336187470428709E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13659,7 +13688,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.83988794858783788</v>
+        <v>-0.85104283297399508</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13668,37 +13697,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.3448000000000004E-2</v>
+        <v>4.0930999999999995E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>1.6343255463451396E-2</v>
+        <v>1.5198716650150291E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.7659999999999998E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>8.7440659588742739E-4</v>
+        <v>8.1317079804790033E-4</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>371</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>24.675516466206126</v>
+        <v>24.70965579341032</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13714,7 +13743,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>3.4382064807837228E-3</v>
+        <v>3.1974245402333463E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13723,7 +13752,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>175.815</v>
+        <v>209</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>101</v>
@@ -13739,7 +13768,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0948000000000002</v>
+        <v>2.0929000000000002</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>103</v>
@@ -13755,7 +13784,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4087698</v>
+        <v>3782309</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13771,7 +13800,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-9.2458561076505814E-3</v>
+        <v>-8.5983571316314913E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13784,10 +13813,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="246" t="s">
+      <c r="B17" s="247" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="246"/>
+      <c r="C17" s="247"/>
       <c r="E17" s="184" t="s">
         <v>300</v>
       </c>
@@ -13860,14 +13889,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="246" t="s">
+      <c r="B25" s="247" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="246"/>
-      <c r="E25" s="244" t="s">
+      <c r="C25" s="247"/>
+      <c r="E25" s="245" t="s">
         <v>345</v>
       </c>
-      <c r="F25" s="245"/>
+      <c r="F25" s="246"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13876,12 +13905,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13896,7 +13925,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13916,15 +13945,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="247" t="s">
+      <c r="B33" s="244" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="247"/>
-      <c r="D33" s="247"/>
-      <c r="E33" s="247"/>
-      <c r="F33" s="247"/>
-      <c r="G33" s="247"/>
-      <c r="H33" s="247"/>
+      <c r="C33" s="244"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14010,24 +14039,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="247"/>
-      <c r="C49" s="247"/>
-      <c r="D49" s="247"/>
-      <c r="E49" s="247"/>
-      <c r="F49" s="247"/>
-      <c r="G49" s="247"/>
-      <c r="H49" s="247"/>
+      <c r="B49" s="244"/>
+      <c r="C49" s="244"/>
+      <c r="D49" s="244"/>
+      <c r="E49" s="244"/>
+      <c r="F49" s="244"/>
+      <c r="G49" s="244"/>
+      <c r="H49" s="244"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="247" t="s">
+      <c r="B52" s="244" t="s">
         <v>343</v>
       </c>
-      <c r="C52" s="247"/>
-      <c r="D52" s="247"/>
-      <c r="E52" s="247"/>
-      <c r="F52" s="247"/>
-      <c r="G52" s="247"/>
-      <c r="H52" s="247"/>
+      <c r="C52" s="244"/>
+      <c r="D52" s="244"/>
+      <c r="E52" s="244"/>
+      <c r="F52" s="244"/>
+      <c r="G52" s="244"/>
+      <c r="H52" s="244"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14110,24 +14139,24 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="247"/>
-      <c r="C65" s="247"/>
-      <c r="D65" s="247"/>
-      <c r="E65" s="247"/>
-      <c r="F65" s="247"/>
-      <c r="G65" s="247"/>
-      <c r="H65" s="247"/>
+      <c r="B65" s="244"/>
+      <c r="C65" s="244"/>
+      <c r="D65" s="244"/>
+      <c r="E65" s="244"/>
+      <c r="F65" s="244"/>
+      <c r="G65" s="244"/>
+      <c r="H65" s="244"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="247" t="s">
+      <c r="B68" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="247"/>
-      <c r="D68" s="247"/>
-      <c r="E68" s="247"/>
-      <c r="F68" s="247"/>
-      <c r="G68" s="247"/>
-      <c r="H68" s="247"/>
+      <c r="C68" s="244"/>
+      <c r="D68" s="244"/>
+      <c r="E68" s="244"/>
+      <c r="F68" s="244"/>
+      <c r="G68" s="244"/>
+      <c r="H68" s="244"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" s="41" t="s">
@@ -14142,28 +14171,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="247"/>
-      <c r="C75" s="247"/>
-      <c r="D75" s="247"/>
-      <c r="E75" s="247"/>
-      <c r="F75" s="247"/>
-      <c r="G75" s="247"/>
-      <c r="H75" s="247"/>
+      <c r="B75" s="244"/>
+      <c r="C75" s="244"/>
+      <c r="D75" s="244"/>
+      <c r="E75" s="244"/>
+      <c r="F75" s="244"/>
+      <c r="G75" s="244"/>
+      <c r="H75" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B68:H68"/>
     <mergeCell ref="B75:H75"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14233,36 +14262,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
       <c r="G2" s="256"/>
       <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="247" t="s">
+      <c r="S2" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="247"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="247"/>
-      <c r="W2" s="247"/>
-      <c r="X2" s="247"/>
-      <c r="Y2" s="247"/>
-      <c r="Z2" s="247"/>
-      <c r="AA2" s="247" t="s">
+      <c r="T2" s="244"/>
+      <c r="U2" s="244"/>
+      <c r="V2" s="244"/>
+      <c r="W2" s="244"/>
+      <c r="X2" s="244"/>
+      <c r="Y2" s="244"/>
+      <c r="Z2" s="244"/>
+      <c r="AA2" s="244" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="247"/>
-      <c r="AC2" s="247"/>
+      <c r="AB2" s="244"/>
+      <c r="AC2" s="244"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15585,35 +15614,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
       <c r="G2" s="256"/>
       <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
-      <c r="P2" s="247" t="s">
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
+      <c r="P2" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="247"/>
-      <c r="R2" s="247"/>
-      <c r="S2" s="247"/>
-      <c r="T2" s="247"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="247"/>
-      <c r="W2" s="247"/>
-      <c r="X2" s="247" t="s">
+      <c r="Q2" s="244"/>
+      <c r="R2" s="244"/>
+      <c r="S2" s="244"/>
+      <c r="T2" s="244"/>
+      <c r="U2" s="244"/>
+      <c r="V2" s="244"/>
+      <c r="W2" s="244"/>
+      <c r="X2" s="244" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="247"/>
-      <c r="Z2" s="247"/>
+      <c r="Y2" s="244"/>
+      <c r="Z2" s="244"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16845,20 +16874,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
+      <c r="D3" s="244"/>
+      <c r="E3" s="244"/>
+      <c r="F3" s="244"/>
       <c r="G3" s="256"/>
       <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="247"/>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
+      <c r="I3" s="244"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="244"/>
       <c r="P3" s="258"/>
       <c r="Q3" s="258"/>
       <c r="R3" s="258"/>
@@ -18251,12 +18280,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18264,6 +18287,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18301,20 +18330,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
       <c r="G2" s="256"/>
       <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
       <c r="S2" s="258"/>
       <c r="T2" s="258"/>
       <c r="U2" s="258"/>
@@ -18777,24 +18806,24 @@
         <v>72</v>
       </c>
       <c r="C15" s="129">
-        <f>-Statement!M82</f>
-        <v>-1.7867778439547351E-2</v>
+        <f>Statement!M82</f>
+        <v>1.7867778439547351E-2</v>
       </c>
       <c r="D15" s="129">
-        <f>-Statement!N82</f>
+        <f>Statement!N82</f>
         <v>0</v>
       </c>
       <c r="E15" s="129">
-        <f>-Statement!O82</f>
-        <v>-0.24719101123595505</v>
+        <f>Statement!O82</f>
+        <v>0.24719101123595505</v>
       </c>
       <c r="F15" s="129">
-        <f>-Statement!P82</f>
-        <v>-2.9081295439524125E-2</v>
+        <f>Statement!P82</f>
+        <v>2.9081295439524125E-2</v>
       </c>
       <c r="G15" s="130">
-        <f>-Statement!Q82</f>
-        <v>-0.13712737127371274</v>
+        <f>Statement!Q82</f>
+        <v>0.13712737127371274</v>
       </c>
       <c r="H15" s="129">
         <f>Overview!$C$26</f>
@@ -19088,7 +19117,7 @@
       </c>
       <c r="C27" s="126">
         <f>C10*(1-C15)</f>
-        <v>1989.9315068493152</v>
+        <v>1920.0684931506848</v>
       </c>
       <c r="D27" s="126">
         <f t="shared" ref="D27:L27" si="6">D10*(1-D15)</f>
@@ -19096,15 +19125,15 @@
       </c>
       <c r="E27" s="126">
         <f t="shared" si="6"/>
-        <v>563.7303370786517</v>
+        <v>340.26966292134836</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="6"/>
-        <v>1944.9636483807005</v>
+        <v>1835.0363516192995</v>
       </c>
       <c r="G27" s="131">
         <f t="shared" si="6"/>
-        <v>4655.3994579945793</v>
+        <v>3532.6005420054198</v>
       </c>
       <c r="H27" s="126">
         <f t="shared" si="6"/>
@@ -19133,7 +19162,7 @@
       </c>
       <c r="C28" s="94">
         <f>C27+C20-C21+C22</f>
-        <v>1416.9315068493152</v>
+        <v>1347.0684931506848</v>
       </c>
       <c r="D28" s="94">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
@@ -19141,15 +19170,15 @@
       </c>
       <c r="E28" s="94">
         <f t="shared" si="7"/>
-        <v>959.7303370786517</v>
+        <v>736.2696629213483</v>
       </c>
       <c r="F28" s="94">
         <f t="shared" si="7"/>
-        <v>965.96364838070076</v>
+        <v>856.03635161929924</v>
       </c>
       <c r="G28" s="127">
         <f t="shared" si="7"/>
-        <v>4203.3994579945793</v>
+        <v>3080.6005420054198</v>
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
@@ -19323,16 +19352,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19395,10 +19424,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="244" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="247"/>
+      <c r="C4" s="244"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19415,7 +19444,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19424,7 +19453,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>201279.35999999999</v>
+        <v>216436.69500000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19442,7 +19471,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19451,7 +19480,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0948000000000002</v>
+        <v>2.0929000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19460,7 +19489,7 @@
       </c>
       <c r="C11" s="135">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19483,10 +19512,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="247" t="s">
+      <c r="B15" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="247"/>
+      <c r="C15" s="244"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19494,7 +19523,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.7403456946532482E-2</v>
+        <v>1.6204420606850324E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19503,7 +19532,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98259654305346755</v>
+        <v>0.98379557939314966</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19521,7 +19550,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14188600000000001</v>
+        <v>0.1417176</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19530,7 +19559,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14024161696694995</v>
+        <v>0.14018923793897134</v>
       </c>
     </row>
   </sheetData>
@@ -19575,20 +19604,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
+      <c r="D3" s="244"/>
+      <c r="E3" s="244"/>
+      <c r="F3" s="244"/>
       <c r="G3" s="256"/>
       <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="247"/>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
+      <c r="I3" s="244"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="244"/>
       <c r="P3" s="258"/>
       <c r="Q3" s="258"/>
       <c r="R3" s="258"/>
@@ -19695,7 +19724,7 @@
       </c>
       <c r="C7" s="112">
         <f>'FCF &amp; Other'!C28</f>
-        <v>1416.9315068493152</v>
+        <v>1347.0684931506848</v>
       </c>
       <c r="D7" s="112">
         <f>'FCF &amp; Other'!D28</f>
@@ -19703,15 +19732,15 @@
       </c>
       <c r="E7" s="112">
         <f>'FCF &amp; Other'!E28</f>
-        <v>959.7303370786517</v>
+        <v>736.2696629213483</v>
       </c>
       <c r="F7" s="112">
         <f>'FCF &amp; Other'!F28</f>
-        <v>965.96364838070076</v>
+        <v>856.03635161929924</v>
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>4203.3994579945793</v>
+        <v>3080.6005420054198</v>
       </c>
       <c r="H7" s="112">
         <f>'FCF &amp; Other'!H28</f>
@@ -19781,7 +19810,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>31442.140712285047</v>
+        <v>31455.296066492723</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19835,23 +19864,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3799.5133409538471</v>
+        <v>3799.6878863792635</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4670.1716206796445</v>
+        <v>4670.6007155361985</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4458.4712143895977</v>
+        <v>4459.0856942732898</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3494.196185403066</v>
+        <v>3494.8383076257178</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>2012.8448035990855</v>
+        <v>2013.3071853598226</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19870,14 +19899,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>16312.768272484131</v>
+        <v>16323.342379769188</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="247" t="s">
+      <c r="B13" s="244" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="247"/>
+      <c r="C13" s="244"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19893,14 +19922,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14024161696694995</v>
+        <v>0.14018923793897134</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="247" t="s">
+      <c r="B18" s="244" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="247"/>
+      <c r="C18" s="244"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19908,7 +19937,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18435.197165025238</v>
+        <v>18437.519789174294</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19917,7 +19946,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>16312.768272484131</v>
+        <v>16323.342379769188</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19926,7 +19955,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>34747.965437509367</v>
+        <v>34760.86216894348</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19953,7 +19982,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>32886.965437509367</v>
+        <v>32899.86216894348</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19971,7 +20000,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>138.76356724687497</v>
+        <v>138.81798383520456</v>
       </c>
     </row>
   </sheetData>
@@ -20014,20 +20043,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
       <c r="G2" s="256"/>
       <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20189,7 +20218,7 @@
       </c>
       <c r="C8" s="92">
         <f>'FCF &amp; Other'!C28</f>
-        <v>1416.9315068493152</v>
+        <v>1347.0684931506848</v>
       </c>
       <c r="D8" s="92">
         <f>'FCF &amp; Other'!D28</f>
@@ -20197,15 +20226,15 @@
       </c>
       <c r="E8" s="92">
         <f>'FCF &amp; Other'!E28</f>
-        <v>959.7303370786517</v>
+        <v>736.2696629213483</v>
       </c>
       <c r="F8" s="92">
         <f>'FCF &amp; Other'!F28</f>
-        <v>965.96364838070076</v>
+        <v>856.03635161929924</v>
       </c>
       <c r="G8" s="93">
         <f>'FCF &amp; Other'!G28</f>
-        <v>4203.3994579945793</v>
+        <v>3080.6005420054198</v>
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
@@ -20395,26 +20424,26 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>-0.28225182721682979</v>
+        <v>-0.24502725349821017</v>
       </c>
       <c r="E14" s="95">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
 IF(E8=0,0,IF(E8&gt;0,1,-1)),
 (E8-D8)/ABS(D8)
 )</f>
-        <v>-5.6312352921679742E-2</v>
+        <v>-0.27603769624252872</v>
       </c>
       <c r="F14" s="95">
         <f t="shared" si="3"/>
-        <v>6.4948570043360304E-3</v>
+        <v>0.16266687971733662</v>
       </c>
       <c r="G14" s="96">
         <f t="shared" si="3"/>
-        <v>3.351508946574723</v>
+        <v>2.5986795843168116</v>
       </c>
       <c r="H14" s="95">
         <f t="shared" si="3"/>
-        <v>3.068082842729913E-2</v>
+        <v>0.40633723084279422</v>
       </c>
       <c r="I14" s="95">
         <f t="shared" si="3"/>
@@ -20927,7 +20956,7 @@
       </c>
       <c r="C34" s="149">
         <f>C32/C8</f>
-        <v>14.472936695154491</v>
+        <v>15.223546615684999</v>
       </c>
       <c r="D34" s="149">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
@@ -20935,15 +20964,15 @@
       </c>
       <c r="E34" s="149">
         <f t="shared" si="13"/>
-        <v>27.308962723611497</v>
+        <v>35.597337931876446</v>
       </c>
       <c r="F34" s="149">
         <f t="shared" si="13"/>
-        <v>36.022556395710431</v>
+        <v>40.648367250033395</v>
       </c>
       <c r="G34" s="150">
         <f t="shared" si="13"/>
-        <v>45.124819065017967</v>
+        <v>61.57164403941934</v>
       </c>
       <c r="H34" s="137"/>
       <c r="I34" s="137"/>
@@ -20959,10 +20988,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="247" t="s">
+      <c r="B37" s="244" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="247"/>
+      <c r="C37" s="244"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20980,7 +21009,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14024161696694995</v>
+        <v>0.14018923793897134</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21006,7 +21035,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>34736.705696555888</v>
+        <v>34745.112758823503</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21033,7 +21062,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>32875.705696555888</v>
+        <v>32884.112758823503</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21051,14 +21080,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>138.71605779137505</v>
+        <v>138.75153062794726</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="247" t="s">
+      <c r="B49" s="244" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="247"/>
+      <c r="C49" s="244"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21075,7 +21104,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14188600000000001</v>
+        <v>0.1417176</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21110,14 +21139,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>112.28454742641925</v>
+        <v>112.36738006633963</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="247" t="s">
+      <c r="B57" s="244" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="247"/>
+      <c r="C57" s="244"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21134,7 +21163,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14024161696694995</v>
+        <v>0.14018923793897134</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21160,7 +21189,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>38395.896071981711</v>
+        <v>38405.143707196454</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21187,7 +21216,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>36534.896071981711</v>
+        <v>36544.143707196454</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21205,7 +21234,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>154.15567962861482</v>
+        <v>154.19469918648292</v>
       </c>
     </row>
   </sheetData>
@@ -21257,10 +21286,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="244" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="247"/>
+      <c r="C4" s="244"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21269,7 +21298,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>138.76356724687497</v>
+        <v>138.81798383520456</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21278,7 +21307,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>138.71605779137505</v>
+        <v>138.75153062794726</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21287,7 +21316,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>112.28454742641925</v>
+        <v>112.36738006633963</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21296,7 +21325,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>154.15567962861482</v>
+        <v>154.19469918648292</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21305,7 +21334,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>135.97996302332101</v>
+        <v>136.03289842899358</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21314,7 +21343,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21323,7 +21352,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.83988794858783788</v>
+        <v>-0.85104283297399508</v>
       </c>
     </row>
   </sheetData>
@@ -21379,20 +21408,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
       <c r="G2" s="256"/>
       <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21755,10 +21784,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="244" t="s">
         <v>376</v>
       </c>
-      <c r="C20" s="247"/>
+      <c r="C20" s="244"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21793,7 +21822,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14188600000000001</v>
+        <v>0.1417176</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21810,7 +21839,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>24.675516466206126</v>
+        <v>24.70965579341032</v>
       </c>
     </row>
   </sheetData>
@@ -21859,20 +21888,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
+      <c r="D3" s="244"/>
+      <c r="E3" s="244"/>
+      <c r="F3" s="244"/>
       <c r="G3" s="256"/>
       <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="247"/>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
+      <c r="I3" s="244"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="244"/>
       <c r="P3" s="258"/>
       <c r="Q3" s="258"/>
       <c r="R3" s="258"/>
@@ -21979,7 +22008,7 @@
       </c>
       <c r="C7" s="112">
         <f>'FCF &amp; Other'!C28</f>
-        <v>1416.9315068493152</v>
+        <v>1347.0684931506848</v>
       </c>
       <c r="D7" s="112">
         <f>'FCF &amp; Other'!D28</f>
@@ -21987,35 +22016,35 @@
       </c>
       <c r="E7" s="112">
         <f>'FCF &amp; Other'!E28</f>
-        <v>959.7303370786517</v>
+        <v>736.2696629213483</v>
       </c>
       <c r="F7" s="112">
         <f>'FCF &amp; Other'!F28</f>
-        <v>965.96364838070076</v>
+        <v>856.03635161929924</v>
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>4203.3994579945793</v>
+        <v>3080.6005420054198</v>
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>8406.7989159891586</v>
+        <v>6161.2010840108396</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>16813.597831978317</v>
+        <v>12322.402168021679</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>33627.195663956634</v>
+        <v>24644.804336043358</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>67254.391327913268</v>
+        <v>49289.608672086717</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>134508.78265582654</v>
+        <v>98579.217344173434</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22047,7 +22076,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>1090104.213774978</v>
+        <v>799253.2525288905</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22101,23 +22130,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7372.8223833395041</v>
+        <v>5403.6653557158188</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12932.035234692203</v>
+        <v>9478.5412384414212</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>22682.973577287066</v>
+        <v>16626.259787498118</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>39786.257999640322</v>
+        <v>29164.035642981638</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>69785.661929218157</v>
+        <v>51156.482928569167</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22136,7 +22165,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>565566.3714150897</v>
+        <v>414762.730625536</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22152,7 +22181,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22161,7 +22190,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>3155.3529627280482</v>
+        <v>2311.5890554129614</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22200,7 +22229,7 @@
       </c>
       <c r="C21" s="222">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14024161696694995</v>
+        <v>0.14018923793897134</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22218,7 +22247,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>192786.56</v>
+        <v>207304.345</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22245,7 +22274,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>194647.56</v>
+        <v>209165.345</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22261,7 +22290,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>152559.75112417724</v>
+        <v>111828.98495320616</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22270,7 +22299,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>565566.3714150897</v>
+        <v>414762.730625536</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22279,7 +22308,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>718126.12253926694</v>
+        <v>526591.71557874221</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22306,7 +22335,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>716265.12253926694</v>
+        <v>524730.71557874221</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22324,7 +22353,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>3155.3529627280482</v>
+        <v>2311.5890554129614</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22389,7 +22418,7 @@
       </c>
       <c r="C41" s="112">
         <f>C7</f>
-        <v>1416.9315068493152</v>
+        <v>1347.0684931506848</v>
       </c>
       <c r="D41" s="112">
         <f t="shared" si="2"/>
@@ -22397,35 +22426,35 @@
       </c>
       <c r="E41" s="112">
         <f t="shared" si="2"/>
-        <v>959.7303370786517</v>
+        <v>736.2696629213483</v>
       </c>
       <c r="F41" s="112">
         <f t="shared" si="2"/>
-        <v>965.96364838070076</v>
+        <v>856.03635161929924</v>
       </c>
       <c r="G41" s="113">
         <f t="shared" si="2"/>
-        <v>4203.3994579945793</v>
+        <v>3080.6005420054198</v>
       </c>
       <c r="H41" s="143">
         <f t="shared" si="2"/>
-        <v>8406.7989159891586</v>
+        <v>6161.2010840108396</v>
       </c>
       <c r="I41" s="143">
         <f t="shared" si="2"/>
-        <v>16813.597831978317</v>
+        <v>12322.402168021679</v>
       </c>
       <c r="J41" s="143">
         <f t="shared" si="2"/>
-        <v>33627.195663956634</v>
+        <v>24644.804336043358</v>
       </c>
       <c r="K41" s="143">
         <f t="shared" si="2"/>
-        <v>67254.391327913268</v>
+        <v>49289.608672086717</v>
       </c>
       <c r="L41" s="143">
         <f t="shared" si="2"/>
-        <v>134508.78265582654</v>
+        <v>98579.217344173434</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -22454,23 +22483,23 @@
       </c>
       <c r="H42" s="143">
         <f>H41/H43</f>
-        <v>7642.5444690810527</v>
+        <v>5601.0918945553085</v>
       </c>
       <c r="I42" s="143">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>15285.088938162105</v>
+        <v>11202.183789110617</v>
       </c>
       <c r="J42" s="143">
         <f t="shared" si="3"/>
-        <v>30570.177876324211</v>
+        <v>22404.367578221234</v>
       </c>
       <c r="K42" s="143">
         <f t="shared" si="3"/>
-        <v>61140.355752648422</v>
+        <v>44808.735156442468</v>
       </c>
       <c r="L42" s="143">
         <f t="shared" si="3"/>
-        <v>122280.71150529684</v>
+        <v>89617.470312884936</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -22479,7 +22508,7 @@
       </c>
       <c r="C43" s="95">
         <f>C41/C42</f>
-        <v>0.7247731492835372</v>
+        <v>0.6890375924044424</v>
       </c>
       <c r="D43" s="95">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
@@ -22487,15 +22516,15 @@
       </c>
       <c r="E43" s="95">
         <f t="shared" si="4"/>
-        <v>2.1232972059262205</v>
+        <v>1.6289151834543103</v>
       </c>
       <c r="F43" s="95">
         <f t="shared" si="4"/>
-        <v>0.5110918774501062</v>
+        <v>0.4529292865710578</v>
       </c>
       <c r="G43" s="96">
         <f t="shared" si="4"/>
-        <v>1.0267218998521199</v>
+        <v>0.7524671573046946</v>
       </c>
       <c r="H43" s="168">
         <v>1.1000000000000001</v>
@@ -22539,23 +22568,23 @@
       </c>
       <c r="H44" s="143">
         <f>H41/H45</f>
-        <v>840679.8915989158</v>
+        <v>616120.10840108397</v>
       </c>
       <c r="I44" s="143">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>840679.8915989158</v>
+        <v>616120.10840108397</v>
       </c>
       <c r="J44" s="143">
         <f t="shared" si="5"/>
-        <v>800647.51580849127</v>
+        <v>586781.05562007998</v>
       </c>
       <c r="K44" s="143">
         <f t="shared" si="5"/>
-        <v>960777.0189701895</v>
+        <v>704137.26674409583</v>
       </c>
       <c r="L44" s="143">
         <f t="shared" si="5"/>
-        <v>896725.21770551032</v>
+        <v>657194.78229448956</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -22564,7 +22593,7 @@
       </c>
       <c r="C45" s="95">
         <f>C41/C44</f>
-        <v>0.12151029130000129</v>
+        <v>0.11551912298693807</v>
       </c>
       <c r="D45" s="95">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
@@ -22572,15 +22601,15 @@
       </c>
       <c r="E45" s="95">
         <f t="shared" si="6"/>
-        <v>0.14650134896636419</v>
+        <v>0.1123904232821475</v>
       </c>
       <c r="F45" s="95">
         <f t="shared" si="6"/>
-        <v>0.10618485746737394</v>
+        <v>9.4100951040925501E-2</v>
       </c>
       <c r="G45" s="96">
         <f t="shared" si="6"/>
-        <v>0.34468220237757929</v>
+        <v>0.25261177056215006</v>
       </c>
       <c r="H45" s="168">
         <v>0.01</v>
@@ -22605,19 +22634,19 @@
       <c r="C46" s="137"/>
       <c r="D46" s="95">
         <f>D41/C41-1</f>
-        <v>-0.28225182721682973</v>
+        <v>-0.2450272534982102</v>
       </c>
       <c r="E46" s="95">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
-        <v>-5.6312352921679798E-2</v>
+        <v>-0.27603769624252872</v>
       </c>
       <c r="F46" s="95">
         <f t="shared" si="7"/>
-        <v>6.494857004335941E-3</v>
+        <v>0.16266687971733651</v>
       </c>
       <c r="G46" s="96">
         <f t="shared" si="7"/>
-        <v>3.3515089465747225</v>
+        <v>2.5986795843168116</v>
       </c>
       <c r="H46" s="169">
         <f t="shared" si="7"/>
@@ -22663,7 +22692,7 @@
       </c>
       <c r="H47" s="169">
         <f t="shared" si="7"/>
-        <v>0.86676709064021806</v>
+        <v>0.36812210419035374</v>
       </c>
       <c r="I47" s="169">
         <f t="shared" si="7"/>
@@ -22705,7 +22734,7 @@
       </c>
       <c r="H48" s="169">
         <f t="shared" si="8"/>
-        <v>67.936440475515852</v>
+        <v>49.522354112430008</v>
       </c>
       <c r="I48" s="169">
         <f t="shared" si="8"/>
@@ -22717,7 +22746,7 @@
       </c>
       <c r="K48" s="169">
         <f t="shared" si="8"/>
-        <v>0.19999999999999996</v>
+        <v>0.19999999999999973</v>
       </c>
       <c r="L48" s="169">
         <f t="shared" si="8"/>
@@ -22762,7 +22791,7 @@
       </c>
       <c r="K49" s="169">
         <f t="shared" si="9"/>
-        <v>6.363636363636363E-2</v>
+        <v>6.3636363636363644E-2</v>
       </c>
       <c r="L49" s="169">
         <f t="shared" si="9"/>
@@ -22771,17 +22800,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29561,7 +29590,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29635,7 +29664,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31004,7 +31033,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>61.187319884726222</v>
+        <v>65.795028818443797</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31045,7 +31074,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>15.930528905289053</v>
+        <v>17.130176814268143</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31110,7 +31139,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>88.964725426857399</v>
+        <v>95.664210890632219</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31175,7 +31204,7 @@
       </c>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>201279.35999999999</v>
+        <v>216436.69500000001</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31240,7 +31269,7 @@
       </c>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>203140.36</v>
+        <v>218297.69500000001</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31281,7 +31310,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>16.657676096760966</v>
+        <v>17.90058999589996</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31322,7 +31351,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>49.619042501221294</v>
+        <v>53.321371519296534</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31469,7 +31498,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>69.598672199170124</v>
+        <v>74.83979771784233</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31510,7 +31539,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="204"/>
-        <v>63.252063057989474</v>
+        <v>67.971621048391142</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31551,7 +31580,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>1.4368090200604772E-2</v>
+        <v>1.336187470428709E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31592,7 +31621,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.6343255463451396E-2</v>
+        <v>1.5198716650150291E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31633,7 +31662,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>3.4382064807837228E-3</v>
+        <v>3.1974245402333463E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31674,7 +31703,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>8.7440659588742739E-4</v>
+        <v>8.1317079804790033E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31715,7 +31744,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>4.0242576288000917E-3</v>
+        <v>3.7424337864704503E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32262,7 +32291,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-9.2458561076505814E-3</v>
+        <v>-8.5983571316314913E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33581,15 +33610,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="244" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="247"/>
-      <c r="E4" s="247" t="s">
+      <c r="C4" s="244"/>
+      <c r="E4" s="244" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33597,7 +33626,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33613,7 +33642,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>201279.35999999999</v>
+        <v>216436.69500000001</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33633,7 +33662,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>203140.36</v>
+        <v>218297.69500000001</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33653,7 +33682,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>61.187319884726222</v>
+        <v>65.795028818443797</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -33673,7 +33702,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>15.930528905289053</v>
+        <v>17.130176814268143</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -33693,7 +33722,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>88.964725426857399</v>
+        <v>95.664210890632219</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33713,7 +33742,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>16.657676096760966</v>
+        <v>17.90058999589996</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33722,18 +33751,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>49.619042501221294</v>
+        <v>53.321371519296534</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="247" t="s">
+      <c r="B15" s="244" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="247"/>
-      <c r="E15" s="247" t="s">
+      <c r="C15" s="244"/>
+      <c r="E15" s="244" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="247"/>
+      <c r="F15" s="244"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33784,14 +33813,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="247" t="s">
+      <c r="B21" s="244" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="247"/>
-      <c r="E21" s="247" t="s">
+      <c r="C21" s="244"/>
+      <c r="E21" s="244" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="247"/>
+      <c r="F21" s="244"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33860,14 +33889,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="247" t="s">
+      <c r="B29" s="244" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="247"/>
-      <c r="E29" s="247" t="s">
+      <c r="C29" s="244"/>
+      <c r="E29" s="244" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="247"/>
+      <c r="F29" s="244"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33943,14 +33972,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="247" t="s">
+      <c r="B37" s="244" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="247"/>
-      <c r="E37" s="247" t="s">
+      <c r="C37" s="244"/>
+      <c r="E37" s="244" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="247"/>
+      <c r="F37" s="244"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33958,7 +33987,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.6343255463451396E-2</v>
+        <v>1.5198716650150291E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -33974,7 +34003,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>1.4368090200604772E-2</v>
+        <v>1.336187470428709E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -33990,7 +34019,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.4382064807837228E-3</v>
+        <v>3.1974245402333463E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -34006,7 +34035,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.7440659588742739E-4</v>
+        <v>8.1317079804790033E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34015,18 +34044,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.0242576288000917E-3</v>
+        <v>3.7424337864704503E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="247" t="s">
+      <c r="B45" s="244" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="247"/>
-      <c r="E45" s="247" t="s">
+      <c r="C45" s="244"/>
+      <c r="E45" s="244" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="247"/>
+      <c r="F45" s="244"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34059,18 +34088,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>-9.2458561076505814E-3</v>
+        <v>-8.5983571316314913E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="247" t="s">
+      <c r="B51" s="244" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="247"/>
-      <c r="E51" s="247" t="s">
+      <c r="C51" s="244"/>
+      <c r="E51" s="244" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="247"/>
+      <c r="F51" s="244"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34238,7 +34267,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>849.28</v>
+        <v>913.23500000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34267,7 +34296,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>201279.35999999999</v>
+        <v>216436.69500000001</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34296,7 +34325,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>203140.36</v>
+        <v>218297.69500000001</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34325,7 +34354,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>61.187319884726222</v>
+        <v>65.795028818443797</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34354,7 +34383,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>15.930528905289053</v>
+        <v>17.130176814268143</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34383,7 +34412,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>88.964725426857399</v>
+        <v>95.664210890632219</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34412,7 +34441,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>16.657676096760966</v>
+        <v>17.90058999589996</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34441,7 +34470,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>49.619042501221294</v>
+        <v>53.321371519296534</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35214,7 +35243,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>1.6343255463451396E-2</v>
+        <v>1.5198716650150291E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35243,7 +35272,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>1.4368090200604772E-2</v>
+        <v>1.336187470428709E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35272,7 +35301,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>3.4382064807837228E-3</v>
+        <v>3.1974245402333463E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35301,7 +35330,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>8.7440659588742739E-4</v>
+        <v>8.1317079804790033E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35330,7 +35359,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>4.0242576288000917E-3</v>
+        <v>3.7424337864704503E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35566,7 +35595,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>-9.2458561076505814E-3</v>
+        <v>-8.5983571316314913E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36028,14 +36057,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="250" t="s">
+      <c r="C3" s="248" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="F3" s="252" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="251"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36102,19 +36131,19 @@
       <c r="B7" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="248">
+      <c r="C7" s="251">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="249"/>
-      <c r="F7" s="248">
+      <c r="D7" s="252"/>
+      <c r="F7" s="251">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="249"/>
+      <c r="G7" s="252"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36141,19 +36170,19 @@
       <c r="B9" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="248">
+      <c r="C9" s="251">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="249"/>
-      <c r="F9" s="248">
+      <c r="D9" s="252"/>
+      <c r="F9" s="251">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="249"/>
+      <c r="G9" s="252"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36180,19 +36209,19 @@
       <c r="B11" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="248">
+      <c r="C11" s="251">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="249"/>
-      <c r="F11" s="248">
+      <c r="D11" s="252"/>
+      <c r="F11" s="251">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="249"/>
+      <c r="G11" s="252"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36219,19 +36248,19 @@
       <c r="B13" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="248">
+      <c r="C13" s="251">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="249"/>
-      <c r="F13" s="248">
+      <c r="D13" s="252"/>
+      <c r="F13" s="251">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="249"/>
+      <c r="G13" s="252"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36258,19 +36287,19 @@
       <c r="B15" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="248">
+      <c r="C15" s="251">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="249"/>
-      <c r="F15" s="248">
+      <c r="D15" s="252"/>
+      <c r="F15" s="251">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="249"/>
+      <c r="G15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36297,19 +36326,19 @@
       <c r="B17" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="248">
+      <c r="C17" s="251">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="249"/>
-      <c r="F17" s="248">
+      <c r="D17" s="252"/>
+      <c r="F17" s="251">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="249"/>
+      <c r="G17" s="252"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36336,22 +36365,22 @@
       <c r="B19" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="248">
+      <c r="C19" s="251">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="249"/>
-      <c r="F19" s="248">
+      <c r="D19" s="252"/>
+      <c r="F19" s="251">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="249"/>
+      <c r="G19" s="252"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36378,22 +36407,22 @@
       <c r="B21" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="248">
+      <c r="C21" s="251">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="249"/>
-      <c r="F21" s="248">
+      <c r="D21" s="252"/>
+      <c r="F21" s="251">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="249"/>
+      <c r="G21" s="252"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36442,22 +36471,22 @@
       <c r="B25" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="248">
+      <c r="C25" s="251">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="249"/>
-      <c r="F25" s="248">
+      <c r="D25" s="252"/>
+      <c r="F25" s="251">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="249"/>
+      <c r="G25" s="252"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36485,37 +36514,25 @@
       <c r="B27" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="248">
+      <c r="C27" s="251">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="249"/>
-      <c r="F27" s="248">
+      <c r="D27" s="252"/>
+      <c r="F27" s="251">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="249"/>
+      <c r="G27" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36526,6 +36543,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BADA801-8934-2545-8BD7-65F919324840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBE7F9F-71B0-8244-9BBF-F6038BA7C16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,28 +148,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -179,21 +158,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2414,7 +2384,16 @@
     <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2426,12 +2405,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2441,19 +2414,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12634,7 +12604,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12654,8 +12624,10 @@
     <v>1145</v>
     <v>209</v>
     <v>2.0886999999999998</v>
-    <v>10.8476</v>
-    <v>1.1974E-2</v>
+    <v>10.91</v>
+    <v>1.2043E-2</v>
+    <v>7.0000000000000007E-2</v>
+    <v>7.6349999999999999E-5</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12666,46 +12638,32 @@
     <v>924.36</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46290.718975497657</v>
+    <v>46290.838552303125</v>
     <v>0</v>
     <v>903.54</v>
-    <v>209977276194</v>
+    <v>209991568347</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>924.36</v>
-    <v>65.936000000000007</v>
+    <v>65.9405</v>
     <v>905.92</v>
-    <v>916.76760000000002</v>
+    <v>916.83</v>
+    <v>916.9</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>1596176</v>
+    <v>2761831</v>
     <v>3649657</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12724,7 +12682,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -12734,13 +12692,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12762,6 +12720,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12782,6 +12742,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12791,11 +12752,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12831,7 +12787,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12842,13 +12798,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12942,13 +12901,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13020,6 +12985,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13027,6 +12995,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13517,18 +13488,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="E2" s="243" t="s">
+      <c r="C2" s="247"/>
+      <c r="E2" s="246" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="247"/>
+      <c r="H2" s="246" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="244"/>
+      <c r="I2" s="247"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
@@ -13543,7 +13514,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>217273.92120000001</v>
+        <v>217288.71000000002</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13551,7 +13522,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>134.9439995770777</v>
+        <v>134.94389543944112</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13567,7 +13538,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>219134.92120000001</v>
+        <v>219149.71000000002</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13575,7 +13546,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>204.90801137992779</v>
+        <v>212.7602458808405</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13584,7 +13555,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13606,16 +13577,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="204" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>916.9</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>66.049538904899137</v>
+        <v>66.054034582132559</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13623,7 +13594,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>220.09394464758526</v>
+        <v>227.94617210237942</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13632,14 +13603,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>10.8476</v>
+        <v>10.91</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>17.196440221402217</v>
+        <v>17.197610701107013</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13647,23 +13618,23 @@
       </c>
       <c r="I7" s="208">
         <f ca="1">'AVG target price'!C9</f>
-        <v>167.60415155661354</v>
+        <v>171.53024101113112</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.3310387109633478E-2</v>
+        <v>1.3309481196699082E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B11</f>
@@ -13671,7 +13642,7 @@
       </c>
       <c r="I8" s="209">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.81717923762073008</v>
+        <v>-0.81290943685183614</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13680,30 +13651,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.1974E-2</v>
+        <v>1.2043E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>1.5140151113542845E-2</v>
+        <v>1.513912066577228E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>7.6349999999999999E-5</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>8.1003738979788797E-4</v>
+        <v>8.0998225816702573E-4</v>
       </c>
       <c r="H10" s="180" t="s">
         <v>362</v>
@@ -13726,7 +13697,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>3.18510383656665E-3</v>
+        <v>3.1848870564881162E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13783,7 +13754,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-8.5652249000788046E-3</v>
+        <v>-8.5646419457320166E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13796,10 +13767,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="245" t="s">
+      <c r="B17" s="248" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="245"/>
+      <c r="C17" s="248"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -13872,14 +13843,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="E25" s="243" t="s">
+      <c r="C25" s="248"/>
+      <c r="E25" s="246" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="244"/>
+      <c r="F25" s="247"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -13888,7 +13859,7 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="5">
+      <c r="E26" s="181" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
@@ -13928,15 +13899,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="242" t="s">
+      <c r="B33" s="243" t="s">
         <v>332</v>
       </c>
-      <c r="C33" s="242"/>
-      <c r="D33" s="242"/>
-      <c r="E33" s="242"/>
-      <c r="F33" s="242"/>
-      <c r="G33" s="242"/>
-      <c r="H33" s="242"/>
+      <c r="C33" s="243"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14022,24 +13993,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="242"/>
-      <c r="C49" s="242"/>
-      <c r="D49" s="242"/>
-      <c r="E49" s="242"/>
-      <c r="F49" s="242"/>
-      <c r="G49" s="242"/>
-      <c r="H49" s="242"/>
+      <c r="B49" s="243"/>
+      <c r="C49" s="243"/>
+      <c r="D49" s="243"/>
+      <c r="E49" s="243"/>
+      <c r="F49" s="243"/>
+      <c r="G49" s="243"/>
+      <c r="H49" s="243"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="243" t="s">
         <v>335</v>
       </c>
-      <c r="C52" s="242"/>
-      <c r="D52" s="242"/>
-      <c r="E52" s="242"/>
-      <c r="F52" s="242"/>
-      <c r="G52" s="242"/>
-      <c r="H52" s="242"/>
+      <c r="C52" s="243"/>
+      <c r="D52" s="243"/>
+      <c r="E52" s="243"/>
+      <c r="F52" s="243"/>
+      <c r="G52" s="243"/>
+      <c r="H52" s="243"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14122,24 +14093,24 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="242"/>
-      <c r="C65" s="242"/>
-      <c r="D65" s="242"/>
-      <c r="E65" s="242"/>
-      <c r="F65" s="242"/>
-      <c r="G65" s="242"/>
-      <c r="H65" s="242"/>
+      <c r="B65" s="243"/>
+      <c r="C65" s="243"/>
+      <c r="D65" s="243"/>
+      <c r="E65" s="243"/>
+      <c r="F65" s="243"/>
+      <c r="G65" s="243"/>
+      <c r="H65" s="243"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="242" t="s">
+      <c r="B68" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="242"/>
-      <c r="D68" s="242"/>
-      <c r="E68" s="242"/>
-      <c r="F68" s="242"/>
-      <c r="G68" s="242"/>
-      <c r="H68" s="242"/>
+      <c r="C68" s="243"/>
+      <c r="D68" s="243"/>
+      <c r="E68" s="243"/>
+      <c r="F68" s="243"/>
+      <c r="G68" s="243"/>
+      <c r="H68" s="243"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" s="41" t="s">
@@ -14154,28 +14125,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="242"/>
-      <c r="C75" s="242"/>
-      <c r="D75" s="242"/>
-      <c r="E75" s="242"/>
-      <c r="F75" s="242"/>
-      <c r="G75" s="242"/>
-      <c r="H75" s="242"/>
+      <c r="B75" s="243"/>
+      <c r="C75" s="243"/>
+      <c r="D75" s="243"/>
+      <c r="E75" s="243"/>
+      <c r="F75" s="243"/>
+      <c r="G75" s="243"/>
+      <c r="H75" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B68:H68"/>
     <mergeCell ref="B75:H75"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14245,36 +14216,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14285,32 +14256,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="242" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="252" t="s">
+      <c r="S4" s="254" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
+      <c r="AA4" s="255"/>
+      <c r="AB4" s="255"/>
+      <c r="AC4" s="255"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14701,33 +14672,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="251" t="s">
+      <c r="C10" s="242" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="251"/>
-      <c r="L10" s="251"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="242"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="242"/>
+      <c r="J10" s="242"/>
+      <c r="K10" s="242"/>
+      <c r="L10" s="242"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="252" t="s">
+      <c r="S10" s="254" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="253"/>
-      <c r="U10" s="253"/>
-      <c r="V10" s="253"/>
-      <c r="W10" s="253"/>
-      <c r="X10" s="253"/>
-      <c r="Y10" s="253"/>
-      <c r="Z10" s="253"/>
-      <c r="AA10" s="253"/>
-      <c r="AB10" s="253"/>
-      <c r="AC10" s="253"/>
+      <c r="T10" s="255"/>
+      <c r="U10" s="255"/>
+      <c r="V10" s="255"/>
+      <c r="W10" s="255"/>
+      <c r="X10" s="255"/>
+      <c r="Y10" s="255"/>
+      <c r="Z10" s="255"/>
+      <c r="AA10" s="255"/>
+      <c r="AB10" s="255"/>
+      <c r="AC10" s="255"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -15080,32 +15051,32 @@
     <row r="17" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="86"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="251" t="s">
+      <c r="C17" s="242" t="s">
         <v>395</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="242"/>
+      <c r="F17" s="242"/>
+      <c r="G17" s="242"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="242"/>
+      <c r="J17" s="242"/>
+      <c r="K17" s="242"/>
+      <c r="L17" s="242"/>
       <c r="O17" s="5"/>
-      <c r="S17" s="252" t="s">
+      <c r="S17" s="254" t="s">
         <v>115</v>
       </c>
-      <c r="T17" s="253"/>
-      <c r="U17" s="253"/>
-      <c r="V17" s="253"/>
-      <c r="W17" s="253"/>
-      <c r="X17" s="253"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
-      <c r="AA17" s="253"/>
-      <c r="AB17" s="253"/>
-      <c r="AC17" s="253"/>
+      <c r="T17" s="255"/>
+      <c r="U17" s="255"/>
+      <c r="V17" s="255"/>
+      <c r="W17" s="255"/>
+      <c r="X17" s="255"/>
+      <c r="Y17" s="255"/>
+      <c r="Z17" s="255"/>
+      <c r="AA17" s="255"/>
+      <c r="AB17" s="255"/>
+      <c r="AC17" s="255"/>
       <c r="AE17" s="87"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -15597,35 +15568,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="P2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15634,31 +15605,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="242" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="P4" s="253" t="s">
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="P4" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="253"/>
-      <c r="R4" s="253"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
+      <c r="Q4" s="255"/>
+      <c r="R4" s="255"/>
+      <c r="S4" s="255"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -15853,32 +15824,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="251" t="s">
+      <c r="C9" s="242" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="242"/>
+      <c r="K9" s="242"/>
+      <c r="L9" s="242"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="253" t="s">
+      <c r="P9" s="255" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="253"/>
-      <c r="R9" s="253"/>
-      <c r="S9" s="253"/>
-      <c r="T9" s="253"/>
-      <c r="U9" s="253"/>
-      <c r="V9" s="253"/>
-      <c r="W9" s="253"/>
-      <c r="X9" s="253"/>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
+      <c r="Q9" s="255"/>
+      <c r="R9" s="255"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="255"/>
+      <c r="U9" s="255"/>
+      <c r="V9" s="255"/>
+      <c r="W9" s="255"/>
+      <c r="X9" s="255"/>
+      <c r="Y9" s="255"/>
+      <c r="Z9" s="255"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16355,31 +16326,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="251" t="s">
+      <c r="C17" s="242" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
-      <c r="P17" s="253" t="s">
+      <c r="D17" s="242"/>
+      <c r="E17" s="242"/>
+      <c r="F17" s="242"/>
+      <c r="G17" s="242"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="242"/>
+      <c r="J17" s="242"/>
+      <c r="K17" s="242"/>
+      <c r="L17" s="242"/>
+      <c r="P17" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="253"/>
-      <c r="R17" s="253"/>
-      <c r="S17" s="253"/>
-      <c r="T17" s="253"/>
-      <c r="U17" s="253"/>
-      <c r="V17" s="253"/>
-      <c r="W17" s="253"/>
-      <c r="X17" s="253"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
+      <c r="Q17" s="255"/>
+      <c r="R17" s="255"/>
+      <c r="S17" s="255"/>
+      <c r="T17" s="255"/>
+      <c r="U17" s="255"/>
+      <c r="V17" s="255"/>
+      <c r="W17" s="255"/>
+      <c r="X17" s="255"/>
+      <c r="Y17" s="255"/>
+      <c r="Z17" s="255"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16857,20 +16828,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -16888,18 +16859,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="242" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -17096,18 +17067,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="242" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="242"/>
+      <c r="K11" s="242"/>
+      <c r="L11" s="242"/>
       <c r="N11" s="91"/>
       <c r="P11" s="256"/>
       <c r="Q11" s="256"/>
@@ -17361,18 +17332,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="251" t="s">
+      <c r="C18" s="242" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="242"/>
+      <c r="G18" s="242"/>
+      <c r="H18" s="242"/>
+      <c r="I18" s="242"/>
+      <c r="J18" s="242"/>
+      <c r="K18" s="242"/>
+      <c r="L18" s="242"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17590,18 +17561,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="251" t="s">
+      <c r="C26" s="242" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="251"/>
-      <c r="E26" s="251"/>
-      <c r="F26" s="251"/>
-      <c r="G26" s="251"/>
-      <c r="H26" s="251"/>
-      <c r="I26" s="251"/>
-      <c r="J26" s="251"/>
-      <c r="K26" s="251"/>
-      <c r="L26" s="251"/>
+      <c r="D26" s="242"/>
+      <c r="E26" s="242"/>
+      <c r="F26" s="242"/>
+      <c r="G26" s="242"/>
+      <c r="H26" s="242"/>
+      <c r="I26" s="242"/>
+      <c r="J26" s="242"/>
+      <c r="K26" s="242"/>
+      <c r="L26" s="242"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17793,18 +17764,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="251" t="s">
+      <c r="C33" s="242" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="251"/>
-      <c r="E33" s="251"/>
-      <c r="F33" s="251"/>
-      <c r="G33" s="251"/>
-      <c r="H33" s="251"/>
-      <c r="I33" s="251"/>
-      <c r="J33" s="251"/>
-      <c r="K33" s="251"/>
-      <c r="L33" s="251"/>
+      <c r="D33" s="242"/>
+      <c r="E33" s="242"/>
+      <c r="F33" s="242"/>
+      <c r="G33" s="242"/>
+      <c r="H33" s="242"/>
+      <c r="I33" s="242"/>
+      <c r="J33" s="242"/>
+      <c r="K33" s="242"/>
+      <c r="L33" s="242"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17988,18 +17959,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="251" t="s">
+      <c r="C40" s="242" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="251"/>
-      <c r="E40" s="251"/>
-      <c r="F40" s="251"/>
-      <c r="G40" s="251"/>
-      <c r="H40" s="251"/>
-      <c r="I40" s="251"/>
-      <c r="J40" s="251"/>
-      <c r="K40" s="251"/>
-      <c r="L40" s="251"/>
+      <c r="D40" s="242"/>
+      <c r="E40" s="242"/>
+      <c r="F40" s="242"/>
+      <c r="G40" s="242"/>
+      <c r="H40" s="242"/>
+      <c r="I40" s="242"/>
+      <c r="J40" s="242"/>
+      <c r="K40" s="242"/>
+      <c r="L40" s="242"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18263,12 +18234,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18276,6 +18241,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18313,20 +18284,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="S2" s="256"/>
       <c r="T2" s="256"/>
       <c r="U2" s="256"/>
@@ -18344,18 +18315,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="242" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
       <c r="S4" s="256"/>
       <c r="T4" s="256"/>
       <c r="U4" s="256"/>
@@ -18729,18 +18700,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="251" t="s">
+      <c r="C13" s="242" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="E13" s="251"/>
-      <c r="F13" s="251"/>
-      <c r="G13" s="251"/>
-      <c r="H13" s="251"/>
-      <c r="I13" s="251"/>
-      <c r="J13" s="251"/>
-      <c r="K13" s="251"/>
-      <c r="L13" s="251"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="242"/>
+      <c r="G13" s="242"/>
+      <c r="H13" s="242"/>
+      <c r="I13" s="242"/>
+      <c r="J13" s="242"/>
+      <c r="K13" s="242"/>
+      <c r="L13" s="242"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18833,18 +18804,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="251" t="s">
+      <c r="C18" s="242" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="242"/>
+      <c r="G18" s="242"/>
+      <c r="H18" s="242"/>
+      <c r="I18" s="242"/>
+      <c r="J18" s="242"/>
+      <c r="K18" s="242"/>
+      <c r="L18" s="242"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19036,18 +19007,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="251" t="s">
+      <c r="C25" s="242" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="251"/>
-      <c r="G25" s="251"/>
-      <c r="H25" s="251"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="251"/>
-      <c r="K25" s="251"/>
-      <c r="L25" s="251"/>
+      <c r="D25" s="242"/>
+      <c r="E25" s="242"/>
+      <c r="F25" s="242"/>
+      <c r="G25" s="242"/>
+      <c r="H25" s="242"/>
+      <c r="I25" s="242"/>
+      <c r="J25" s="242"/>
+      <c r="K25" s="242"/>
+      <c r="L25" s="242"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19185,18 +19156,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="251" t="s">
+      <c r="C31" s="242" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="251"/>
-      <c r="E31" s="251"/>
-      <c r="F31" s="251"/>
-      <c r="G31" s="251"/>
-      <c r="H31" s="251"/>
-      <c r="I31" s="251"/>
-      <c r="J31" s="251"/>
-      <c r="K31" s="251"/>
-      <c r="L31" s="251"/>
+      <c r="D31" s="242"/>
+      <c r="E31" s="242"/>
+      <c r="F31" s="242"/>
+      <c r="G31" s="242"/>
+      <c r="H31" s="242"/>
+      <c r="I31" s="242"/>
+      <c r="J31" s="242"/>
+      <c r="K31" s="242"/>
+      <c r="L31" s="242"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19335,16 +19306,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19407,10 +19378,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="243" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="243"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19427,7 +19398,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19436,7 +19407,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>217273.92120000001</v>
+        <v>217288.71000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19495,10 +19466,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="243" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="243"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19506,7 +19477,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.6142987751563059E-2</v>
+        <v>1.6141906785265232E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19515,7 +19486,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98385701224843691</v>
+        <v>0.98385809321473472</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19542,7 +19513,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14402607295843739</v>
+        <v>0.14402617912175891</v>
       </c>
     </row>
   </sheetData>
@@ -19587,20 +19558,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -19618,18 +19589,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="242" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -19793,7 +19764,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30519.913172723118</v>
+        <v>30519.888060801051</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19847,23 +19818,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3786.9444918971781</v>
+        <v>3786.9441404763684</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4639.3247259144964</v>
+        <v>4639.3238648745837</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4414.3713439356234</v>
+        <v>4414.3701150014704</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3448.1896804174553</v>
+        <v>3448.188400477447</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1979.7717319656476</v>
+        <v>1979.7708133717026</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19882,14 +19853,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15574.12592563701</v>
+        <v>15574.10588494597</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="243" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="243"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19905,14 +19876,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402607295843739</v>
+        <v>0.14402617912175891</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="243" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="243"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19920,7 +19891,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18268.601974130401</v>
+        <v>18268.597334201571</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19929,7 +19900,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15574.12592563701</v>
+        <v>15574.10588494597</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19938,7 +19909,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33842.727899767415</v>
+        <v>33842.703219147545</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19965,7 +19936,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31981.727899767415</v>
+        <v>31981.703219147545</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19983,7 +19954,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>134.9439995770777</v>
+        <v>134.94389543944112</v>
       </c>
     </row>
   </sheetData>
@@ -20026,37 +19997,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="242" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20252,23 +20223,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3786.9444918971781</v>
+        <v>3786.9441404763684</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4639.3247259144964</v>
+        <v>4639.3238648745837</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4414.3713439356234</v>
+        <v>4414.3701150014704</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3448.1896804174553</v>
+        <v>3448.188400477447</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1979.7717319656476</v>
+        <v>1979.7708133717026</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20276,18 +20247,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="242" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="242"/>
+      <c r="K11" s="242"/>
+      <c r="L11" s="242"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20481,18 +20452,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="251" t="s">
+      <c r="C17" s="242" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="242"/>
+      <c r="F17" s="242"/>
+      <c r="G17" s="242"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="242"/>
+      <c r="J17" s="242"/>
+      <c r="K17" s="242"/>
+      <c r="L17" s="242"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20626,18 +20597,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="251" t="s">
+      <c r="C22" s="242" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="251"/>
-      <c r="E22" s="251"/>
-      <c r="F22" s="251"/>
-      <c r="G22" s="251"/>
-      <c r="H22" s="251"/>
-      <c r="I22" s="251"/>
-      <c r="J22" s="251"/>
-      <c r="K22" s="251"/>
-      <c r="L22" s="251"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="242"/>
+      <c r="F22" s="242"/>
+      <c r="G22" s="242"/>
+      <c r="H22" s="242"/>
+      <c r="I22" s="242"/>
+      <c r="J22" s="242"/>
+      <c r="K22" s="242"/>
+      <c r="L22" s="242"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20721,18 +20692,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="251" t="s">
+      <c r="C27" s="242" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="251"/>
-      <c r="G27" s="251"/>
-      <c r="H27" s="251"/>
-      <c r="I27" s="251"/>
-      <c r="J27" s="251"/>
-      <c r="K27" s="251"/>
-      <c r="L27" s="251"/>
+      <c r="D27" s="242"/>
+      <c r="E27" s="242"/>
+      <c r="F27" s="242"/>
+      <c r="G27" s="242"/>
+      <c r="H27" s="242"/>
+      <c r="I27" s="242"/>
+      <c r="J27" s="242"/>
+      <c r="K27" s="242"/>
+      <c r="L27" s="242"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21002,10 +20973,10 @@
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="242" t="s">
+      <c r="B38" s="243" t="s">
         <v>204</v>
       </c>
-      <c r="C38" s="242"/>
+      <c r="C38" s="243"/>
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -21023,7 +20994,7 @@
       </c>
       <c r="C40" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402607295843739</v>
+        <v>0.14402617912175891</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -21048,8 +21019,8 @@
         <v>424</v>
       </c>
       <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5-G31+G32</f>
-        <v>34135.368454878131</v>
+        <f ca="1">C42/(1+C40)^5</f>
+        <v>35996.351752929331</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21058,7 +21029,7 @@
       </c>
       <c r="C44" s="108">
         <f ca="1">SUM(H9:K9)+C43</f>
-        <v>50424.198697042884</v>
+        <v>52285.1782737592</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21085,7 +21056,7 @@
       </c>
       <c r="C47" s="108">
         <f ca="1">C44+C45-C46</f>
-        <v>48563.198697042884</v>
+        <v>50424.1782737592</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -21103,14 +21074,14 @@
       </c>
       <c r="C49" s="241">
         <f ca="1">C47/C48</f>
-        <v>204.90801137992779</v>
+        <v>212.7602458808405</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="243" t="s">
         <v>209</v>
       </c>
-      <c r="C51" s="242"/>
+      <c r="C51" s="243"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -21166,10 +21137,10 @@
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="242" t="s">
+      <c r="B59" s="243" t="s">
         <v>321</v>
       </c>
-      <c r="C59" s="242"/>
+      <c r="C59" s="243"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -21186,7 +21157,7 @@
       </c>
       <c r="C61" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402607295843739</v>
+        <v>0.14402617912175891</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -21211,8 +21182,8 @@
         <v>424</v>
       </c>
       <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5-G31+G32</f>
-        <v>37734.434639312953</v>
+        <f ca="1">C63/(1+C61)^5</f>
+        <v>39595.416267434055</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -21221,7 +21192,7 @@
       </c>
       <c r="C65" s="108">
         <f ca="1">SUM(H9:K9)+C64</f>
-        <v>54023.264881477706</v>
+        <v>55884.242788263924</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21248,7 +21219,7 @@
       </c>
       <c r="C68" s="108">
         <f ca="1">C65+C66-C67</f>
-        <v>52162.264881477706</v>
+        <v>54023.242788263924</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -21266,7 +21237,7 @@
       </c>
       <c r="C70" s="241">
         <f ca="1">C68/C69</f>
-        <v>220.09394464758526</v>
+        <v>227.94617210237942</v>
       </c>
     </row>
   </sheetData>
@@ -21318,10 +21289,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="243" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="243"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21330,7 +21301,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>134.9439995770777</v>
+        <v>134.94389543944112</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21339,7 +21310,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C49</f>
-        <v>204.90801137992779</v>
+        <v>212.7602458808405</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21357,7 +21328,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C70</f>
-        <v>220.09394464758526</v>
+        <v>227.94617210237942</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21366,7 +21337,7 @@
       </c>
       <c r="C9" s="241">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>167.60415155661354</v>
+        <v>171.53024101113112</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21375,7 +21346,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21384,7 +21355,7 @@
       </c>
       <c r="C11" s="152">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.81717923762073008</v>
+        <v>-0.81290943685183614</v>
       </c>
     </row>
   </sheetData>
@@ -21440,37 +21411,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="242" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21583,18 +21554,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="251" t="s">
+      <c r="C9" s="242" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="242"/>
+      <c r="K9" s="242"/>
+      <c r="L9" s="242"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21715,18 +21686,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="251" t="s">
+      <c r="C14" s="242" t="s">
         <v>365</v>
       </c>
-      <c r="D14" s="251"/>
-      <c r="E14" s="251"/>
-      <c r="F14" s="251"/>
-      <c r="G14" s="251"/>
-      <c r="H14" s="251"/>
-      <c r="I14" s="251"/>
-      <c r="J14" s="251"/>
-      <c r="K14" s="251"/>
-      <c r="L14" s="251"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="242"/>
+      <c r="F14" s="242"/>
+      <c r="G14" s="242"/>
+      <c r="H14" s="242"/>
+      <c r="I14" s="242"/>
+      <c r="J14" s="242"/>
+      <c r="K14" s="242"/>
+      <c r="L14" s="242"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21816,10 +21787,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="242" t="s">
+      <c r="B20" s="243" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="242"/>
+      <c r="C20" s="243"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21920,20 +21891,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -21951,18 +21922,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="242" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -22108,7 +22079,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>305467.06397543184</v>
+        <v>305466.81263575528</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22162,23 +22133,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4470.0003090880455</v>
+        <v>4469.9998942810334</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6486.0414360116893</v>
+        <v>6486.0402322286218</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9411.3491276789864</v>
+        <v>9411.3465076165867</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13656.017044739767</v>
+        <v>13656.011975737134</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>19815.0976014439</v>
+        <v>19815.088407440177</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22197,7 +22168,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>155877.98345179623</v>
+        <v>155877.78286894993</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22213,7 +22184,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22222,7 +22193,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>915.66294700774722</v>
+        <v>915.66198187776865</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22261,7 +22232,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402607295843739</v>
+        <v>0.14402617912175891</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22279,7 +22250,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>208106.2452</v>
+        <v>208120.41</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22306,7 +22277,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>209967.2452</v>
+        <v>209981.41</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22322,7 +22293,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>53838.505518962389</v>
+        <v>53838.487017303552</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22331,7 +22302,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>155877.98345179623</v>
+        <v>155877.78286894993</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22340,7 +22311,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>209716.48897075863</v>
+        <v>209716.26988625349</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22367,7 +22338,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>207855.48897075863</v>
+        <v>207855.26988625349</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22385,21 +22356,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>915.66294700774722</v>
+        <v>915.66198187776865</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29179,7 +29150,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29253,7 +29224,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30622,7 +30593,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>66.049538904899137</v>
+        <v>66.054034582132559</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30663,7 +30634,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.196440221402217</v>
+        <v>17.197610701107013</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30728,7 +30699,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>96.03426174434702</v>
+        <v>96.040798338717124</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30793,7 +30764,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>217273.92120000001</v>
+        <v>217288.71000000002</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30858,7 +30829,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>219134.92120000001</v>
+        <v>219149.71000000002</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30899,7 +30870,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>17.969243230832308</v>
+        <v>17.970455924559246</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30940,7 +30911,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>53.525872300928192</v>
+        <v>53.529484611626778</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31087,7 +31058,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>75.129295020746895</v>
+        <v>75.134408713692949</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31128,7 +31099,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="204"/>
-        <v>68.232309197197225</v>
+        <v>68.236914003992652</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31169,7 +31140,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>1.3310387109633478E-2</v>
+        <v>1.3309481196699082E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31210,7 +31181,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.5140151113542845E-2</v>
+        <v>1.513912066577228E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31251,7 +31222,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>3.18510383656665E-3</v>
+        <v>3.1848870564881162E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31292,7 +31263,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>8.1003738979788797E-4</v>
+        <v>8.0998225816702573E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31333,7 +31304,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>3.7280129871380069E-3</v>
+        <v>3.7277592563368799E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31880,7 +31851,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-8.5652249000788046E-3</v>
+        <v>-8.5646419457320166E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33199,15 +33170,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="243" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="242"/>
-      <c r="E4" s="242" t="s">
+      <c r="C4" s="243"/>
+      <c r="E4" s="243" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33215,7 +33186,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33231,7 +33202,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>217273.92120000001</v>
+        <v>217288.71000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33251,7 +33222,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>219134.92120000001</v>
+        <v>219149.71000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33271,7 +33242,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>66.049538904899137</v>
+        <v>66.054034582132559</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33291,7 +33262,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>17.196440221402217</v>
+        <v>17.197610701107013</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33311,7 +33282,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>96.03426174434702</v>
+        <v>96.040798338717124</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33331,7 +33302,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>17.969243230832308</v>
+        <v>17.970455924559246</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33340,18 +33311,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>53.525872300928192</v>
+        <v>53.529484611626778</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="243" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="242"/>
-      <c r="E15" s="242" t="s">
+      <c r="C15" s="243"/>
+      <c r="E15" s="243" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="242"/>
+      <c r="F15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33402,14 +33373,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="242" t="s">
+      <c r="B21" s="243" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="242"/>
-      <c r="E21" s="242" t="s">
+      <c r="C21" s="243"/>
+      <c r="E21" s="243" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="242"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33478,14 +33449,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="242" t="s">
+      <c r="B29" s="243" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="242"/>
-      <c r="E29" s="242" t="s">
+      <c r="C29" s="243"/>
+      <c r="E29" s="243" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="242"/>
+      <c r="F29" s="243"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33561,14 +33532,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="243" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="242"/>
-      <c r="E37" s="242" t="s">
+      <c r="C37" s="243"/>
+      <c r="E37" s="243" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="242"/>
+      <c r="F37" s="243"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33576,7 +33547,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.5140151113542845E-2</v>
+        <v>1.513912066577228E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -33592,7 +33563,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.3310387109633478E-2</v>
+        <v>1.3309481196699082E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -33608,7 +33579,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.18510383656665E-3</v>
+        <v>3.1848870564881162E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -33624,7 +33595,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>8.1003738979788797E-4</v>
+        <v>8.0998225816702573E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33633,18 +33604,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.7280129871380069E-3</v>
+        <v>3.7277592563368799E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="242" t="s">
+      <c r="B45" s="243" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="242"/>
-      <c r="E45" s="242" t="s">
+      <c r="C45" s="243"/>
+      <c r="E45" s="243" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="242"/>
+      <c r="F45" s="243"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33677,18 +33648,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-8.5652249000788046E-3</v>
+        <v>-8.5646419457320166E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="243" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="242"/>
-      <c r="E51" s="242" t="s">
+      <c r="C51" s="243"/>
+      <c r="E51" s="243" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="242"/>
+      <c r="F51" s="243"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33856,7 +33827,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>916.76760000000002</v>
+        <v>916.83</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33885,7 +33856,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>217273.92120000001</v>
+        <v>217288.71000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33914,7 +33885,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>219134.92120000001</v>
+        <v>219149.71000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33943,7 +33914,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>66.049538904899137</v>
+        <v>66.054034582132559</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33972,7 +33943,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>17.196440221402217</v>
+        <v>17.197610701107013</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34001,7 +33972,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>96.03426174434702</v>
+        <v>96.040798338717124</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34030,7 +34001,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>17.969243230832308</v>
+        <v>17.970455924559246</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34059,7 +34030,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>53.525872300928192</v>
+        <v>53.529484611626778</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34832,7 +34803,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.5140151113542845E-2</v>
+        <v>1.513912066577228E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34861,7 +34832,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.3310387109633478E-2</v>
+        <v>1.3309481196699082E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34890,7 +34861,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.18510383656665E-3</v>
+        <v>3.1848870564881162E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -34919,7 +34890,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>8.1003738979788797E-4</v>
+        <v>8.0998225816702573E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34948,7 +34919,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.7280129871380069E-3</v>
+        <v>3.7277592563368799E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35184,7 +35155,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-8.5652249000788046E-3</v>
+        <v>-8.5646419457320166E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35646,14 +35617,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="249" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="F3" s="250" t="s">
+      <c r="D3" s="250"/>
+      <c r="F3" s="251" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="249"/>
+      <c r="G3" s="250"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35720,19 +35691,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="252">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="253"/>
+      <c r="F7" s="252">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="253"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -35759,19 +35730,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="252">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="253"/>
+      <c r="F9" s="252">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="253"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -35798,19 +35769,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="252">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="253"/>
+      <c r="F11" s="252">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="253"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -35837,19 +35808,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="252">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="253"/>
+      <c r="F13" s="252">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="253"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -35876,19 +35847,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="252">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="253"/>
+      <c r="F15" s="252">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="253"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -35915,19 +35886,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="252">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="253"/>
+      <c r="F17" s="252">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="253"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -35954,22 +35925,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="252">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="253"/>
+      <c r="F19" s="252">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="253"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -35996,22 +35967,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="252">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="253"/>
+      <c r="F21" s="252">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="253"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36060,22 +36031,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="252">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="253"/>
+      <c r="F25" s="252">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="253"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36103,37 +36074,25 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="252">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="253"/>
+      <c r="F27" s="252">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36144,6 +36103,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBE7F9F-71B0-8244-9BBF-F6038BA7C16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE518C2D-5F0D-F846-9CFE-596B1822559E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="431">
   <si>
     <t>Ticker</t>
   </si>
@@ -1451,6 +1451,18 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
   </si>
 </sst>
 </file>
@@ -2405,6 +2417,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2412,12 +2430,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2429,14 +2441,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12623,11 +12635,11 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>209</v>
-    <v>2.0886999999999998</v>
+    <v>2.0912000000000002</v>
     <v>10.91</v>
     <v>1.2043E-2</v>
-    <v>7.0000000000000007E-2</v>
-    <v>7.6349999999999999E-5</v>
+    <v>-0.83</v>
+    <v>-9.0529999999999994E-4</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12638,21 +12650,21 @@
     <v>924.36</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46290.838552303125</v>
+    <v>46290.999916990622</v>
     <v>0</v>
-    <v>903.54</v>
+    <v>903.53</v>
     <v>209991568347</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>924.36</v>
-    <v>65.9405</v>
+    <v>65.155699999999996</v>
     <v>905.92</v>
     <v>916.83</v>
-    <v>916.9</v>
+    <v>916</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>2761831</v>
+    <v>2798981</v>
     <v>3649657</v>
     <v>2017</v>
   </rv>
@@ -12675,19 +12687,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12909,9 +12921,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13522,7 +13534,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>134.94389543944112</v>
+        <v>134.62378151387438</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13546,7 +13558,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>212.7602458808405</v>
+        <v>212.49492114379254</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13570,7 +13582,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>110.4706506218634</v>
+        <v>147.08063494255472</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13579,7 +13591,7 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>916.9</v>
+        <v>916</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
@@ -13594,7 +13606,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>227.94617210237942</v>
+        <v>227.65915399799462</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13613,12 +13625,12 @@
         <v>17.197610701107013</v>
       </c>
       <c r="H7" s="180" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="208">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>171.53024101113112</v>
+        <f ca="1">'AVG target price'!C10</f>
+        <v>188.13456898723263</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13627,7 +13639,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>7.0000000000000007E-2</v>
+        <v>-0.83</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
@@ -13637,12 +13649,12 @@
         <v>1.3309481196699082E-2</v>
       </c>
       <c r="H8" s="180" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="209">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>-0.81290943685183614</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.79479885149129859</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13667,7 +13679,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>7.6349999999999999E-5</v>
+        <v>-9.0529999999999994E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
@@ -13681,7 +13693,7 @@
       </c>
       <c r="I10" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.943667578207407</v>
+        <v>23.880454805310293</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13722,7 +13734,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0886999999999998</v>
+        <v>2.0912000000000002</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13864,7 +13876,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13879,7 +13891,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14135,18 +14147,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B65:H65"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B65:H65"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -18234,6 +18246,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18241,12 +18259,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19306,16 +19318,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19425,7 +19437,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19434,7 +19446,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0886999999999998</v>
+        <v>2.0912000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19504,7 +19516,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1456115</v>
+        <v>0.14594400000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19513,7 +19525,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14402617912175891</v>
+        <v>0.14435331193775283</v>
       </c>
     </row>
   </sheetData>
@@ -19764,7 +19776,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30519.888060801051</v>
+        <v>30442.703667331833</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19818,23 +19830,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3786.9441404763684</v>
+        <v>3785.8615782224188</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4639.3238648745837</v>
+        <v>4636.67178507055</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4414.3701150014704</v>
+        <v>4410.5854292723234</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3448.188400477447</v>
+        <v>3444.2471981639987</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1979.7708133717026</v>
+        <v>1976.9426753397718</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19853,7 +19865,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15574.10588494597</v>
+        <v>15512.527552719166</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -19876,7 +19888,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402617912175891</v>
+        <v>0.14435331193775283</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -19891,7 +19903,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18268.597334201571</v>
+        <v>18254.308666069064</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19900,7 +19912,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15574.10588494597</v>
+        <v>15512.527552719166</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19909,7 +19921,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33842.703219147545</v>
+        <v>33766.83621878823</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19936,7 +19948,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31981.703219147545</v>
+        <v>31905.83621878823</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19954,7 +19966,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>134.94389543944112</v>
+        <v>134.62378151387438</v>
       </c>
     </row>
   </sheetData>
@@ -19975,7 +19987,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -20223,23 +20235,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3786.9441404763684</v>
+        <v>3785.8615782224188</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4639.3238648745837</v>
+        <v>4636.67178507055</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4414.3701150014704</v>
+        <v>4410.5854292723234</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3448.188400477447</v>
+        <v>3444.2471981639987</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1979.7708133717026</v>
+        <v>1976.9426753397718</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20944,7 +20956,7 @@
         <v>15.223546615684999</v>
       </c>
       <c r="D35" s="147">
-        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
         <v>17.180029498525073</v>
       </c>
       <c r="E35" s="147">
@@ -20967,285 +20979,421 @@
       <c r="N35" s="91"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C36" s="147">
+        <f>C33/C6</f>
+        <v>1.7586107537947002</v>
+      </c>
+      <c r="D36" s="147">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>2.3662093716143011</v>
+      </c>
+      <c r="E36" s="147">
+        <f t="shared" si="14"/>
+        <v>4.0007998778812395</v>
+      </c>
+      <c r="F36" s="147">
+        <f t="shared" si="14"/>
+        <v>3.825050016488952</v>
+      </c>
+      <c r="G36" s="148">
+        <f t="shared" si="14"/>
+        <v>15.553722017220171</v>
+      </c>
+      <c r="H36" s="137"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="137"/>
+      <c r="K36" s="137"/>
+      <c r="L36" s="137"/>
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="243" t="s">
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="243" t="s">
         <v>204</v>
       </c>
-      <c r="C38" s="243"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="243"/>
+      <c r="N39" s="91"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>4408.7788819651487</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="135">
+      <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402617912175891</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+        <v>0.14435331193775283</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C42" s="105">
         <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>70540.462111442379</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>70540.462111442379</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5</f>
-        <v>35996.351752929331</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="24">
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>35944.930320349544</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="C44" s="108">
-        <f ca="1">SUM(H9:K9)+C43</f>
-        <v>52285.1782737592</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="108">
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>52222.296311078833</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C45" s="88">
+      <c r="C46" s="88">
         <f>Statement!AC105</f>
         <v>1704</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C46" s="88">
+      <c r="C47" s="88">
         <f>Statement!AC106</f>
         <v>3565</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="108">
-        <f ca="1">C44+C45-C46</f>
-        <v>50424.1782737592</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="108">
+        <f ca="1">C45+C46-C47</f>
+        <v>50361.296311078833</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C49" s="88">
         <f>Statement!AC77</f>
         <v>237</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="240" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="240" t="s">
         <v>208</v>
       </c>
-      <c r="C49" s="241">
-        <f ca="1">C47/C48</f>
-        <v>212.7602458808405</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="C50" s="241">
+        <f ca="1">C48/C49</f>
+        <v>212.49492114379254</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="243" t="s">
         <v>209</v>
       </c>
-      <c r="C51" s="243"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="243"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>18369.912008188126</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C53" s="135">
+      <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1456115</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+        <v>0.14594400000000002</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="C54" s="105">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>252.81020226960001</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
-        <v>217.98857613267782</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="240" t="s">
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
+        <v>290.65143484357043</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="240" t="s">
         <v>208</v>
       </c>
-      <c r="C57" s="241">
-        <f ca="1">C56/(1+C53)^5</f>
-        <v>110.4706506218634</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="243" t="s">
+      <c r="C58" s="241">
+        <f ca="1">C57/(1+C54)^5</f>
+        <v>147.08063494255472</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="243" t="s">
         <v>321</v>
       </c>
-      <c r="C59" s="243"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="243"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>3879.6695011910815</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C61" s="135">
+      <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402617912175891</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+        <v>0.14435331193775283</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="C62" s="105">
+      <c r="C63" s="105">
         <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>77593.39002382163</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>77593.39002382163</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5</f>
-        <v>39595.416267434055</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="24">
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>39538.853506795436</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="C65" s="108">
-        <f ca="1">SUM(H9:K9)+C64</f>
-        <v>55884.242788263924</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="108">
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>55816.219497524726</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C66" s="88">
+      <c r="C67" s="88">
         <f>Statement!AC105</f>
         <v>1704</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C67" s="88">
+      <c r="C68" s="88">
         <f>Statement!AC106</f>
         <v>3565</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C68" s="108">
-        <f ca="1">C65+C66-C67</f>
-        <v>54023.242788263924</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="108">
+        <f ca="1">C66+C67-C68</f>
+        <v>53955.219497524726</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="88">
+      <c r="C70" s="88">
         <f>Statement!AC77</f>
         <v>237</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="240" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="240" t="s">
         <v>208</v>
       </c>
-      <c r="C70" s="241">
-        <f ca="1">C68/C69</f>
-        <v>227.94617210237942</v>
+      <c r="C71" s="241">
+        <f ca="1">C69/C70</f>
+        <v>227.65915399799462</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="243" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="243"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>18369.912008188126</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="135">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.14435331193775283</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>430</v>
+      </c>
+      <c r="C76" s="105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>73479.648032752506</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C78" s="24">
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>37442.635750364127</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="C79" s="108">
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>53720.001741093416</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C80" s="88">
+        <f>Statement!AC105</f>
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C81" s="88">
+        <f>Statement!AC106</f>
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C82" s="108">
+        <f ca="1">C79+C80-C81</f>
+        <v>51859.001741093416</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" s="88">
+        <f>Statement!AC77</f>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="240" t="s">
+        <v>208</v>
+      </c>
+      <c r="C84" s="241">
+        <f ca="1">C82/C83</f>
+        <v>218.8143533379469</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -21262,7 +21410,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -21301,7 +21449,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>134.94389543944112</v>
+        <v>134.62378151387438</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21309,8 +21457,8 @@
         <v>215</v>
       </c>
       <c r="C6" s="133">
-        <f ca="1">Multiples!C49</f>
-        <v>212.7602458808405</v>
+        <f ca="1">Multiples!C50</f>
+        <v>212.49492114379254</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21318,8 +21466,8 @@
         <v>216</v>
       </c>
       <c r="C7" s="133">
-        <f ca="1">Multiples!C57</f>
-        <v>110.4706506218634</v>
+        <f ca="1">Multiples!C58</f>
+        <v>147.08063494255472</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21327,35 +21475,44 @@
         <v>322</v>
       </c>
       <c r="C8" s="133">
-        <f ca="1">Multiples!C70</f>
-        <v>227.94617210237942</v>
+        <f ca="1">Multiples!C71</f>
+        <v>227.65915399799462</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="240" t="s">
+      <c r="B9" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C9" s="133">
+        <f ca="1">Multiples!C84</f>
+        <v>218.8143533379469</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="240" t="s">
         <v>217</v>
       </c>
-      <c r="C9" s="241">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>171.53024101113112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="241">
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>188.13456898723263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="133">
+      <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
         <v>916.83</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="152">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>-0.81290943685183614</v>
+      <c r="C12" s="152">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>-0.79479885149129859</v>
       </c>
     </row>
   </sheetData>
@@ -21825,7 +21982,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1456115</v>
+        <v>0.14594400000000002</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -21842,7 +21999,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.943667578207407</v>
+        <v>23.880454805310293</v>
       </c>
     </row>
   </sheetData>
@@ -22079,7 +22236,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>305466.81263575528</v>
+        <v>304694.2911045067</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22133,23 +22290,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4469.9998942810334</v>
+        <v>4468.7220689471487</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6486.0402322286218</v>
+        <v>6482.3324729065625</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9411.3465076165867</v>
+        <v>9403.2776352992478</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13656.011975737134</v>
+        <v>13640.403459107414</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>19815.088407440177</v>
+        <v>19786.782199088859</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22168,15 +22325,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>155877.78286894993</v>
+        <v>155261.45895467891</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="257" t="s">
+      <c r="B14" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="258"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22193,7 +22350,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>915.66198187776865</v>
+        <v>912.69593299571875</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22203,20 +22360,20 @@
       <c r="C17" s="156">
         <v>0.66</v>
       </c>
-      <c r="E17" s="259" t="s">
+      <c r="E17" s="257" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="257" t="s">
+      <c r="B19" s="258" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="258"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22232,7 +22389,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14402617912175891</v>
+        <v>0.14435331193775283</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22282,10 +22439,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="257" t="s">
+      <c r="B28" s="258" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="258"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22293,7 +22450,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>53838.487017303552</v>
+        <v>53781.517835349237</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22302,7 +22459,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>155877.78286894993</v>
+        <v>155261.45895467891</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22311,7 +22468,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>209716.26988625349</v>
+        <v>209042.97679002816</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22338,7 +22495,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>207855.26988625349</v>
+        <v>207181.97679002816</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22356,21 +22513,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>915.66198187776865</v>
+        <v>912.69593299571875</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -35617,14 +35774,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="251" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="252"/>
+      <c r="F3" s="253" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="252"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35691,19 +35848,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="252">
+      <c r="C7" s="249">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="253"/>
-      <c r="F7" s="252">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="253"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -35730,19 +35887,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="252">
+      <c r="C9" s="249">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="253"/>
-      <c r="F9" s="252">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="253"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -35769,19 +35926,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="252">
+      <c r="C11" s="249">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="253"/>
-      <c r="F11" s="252">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="253"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -35808,19 +35965,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="252">
+      <c r="C13" s="249">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="253"/>
-      <c r="F13" s="252">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="253"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -35847,19 +36004,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="252">
+      <c r="C15" s="249">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="253"/>
-      <c r="F15" s="252">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="253"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -35886,19 +36043,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="252">
+      <c r="C17" s="249">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="253"/>
-      <c r="F17" s="252">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="253"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -35925,22 +36082,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="252">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="253"/>
-      <c r="F19" s="252">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="253"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -35967,22 +36124,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="252">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="253"/>
-      <c r="F21" s="252">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="253"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36031,22 +36188,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="252">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="253"/>
-      <c r="F25" s="252">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="253"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36074,25 +36231,37 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="252">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="253"/>
-      <c r="F27" s="252">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="253"/>
+      <c r="G27" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36103,18 +36272,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE518C2D-5F0D-F846-9CFE-596B1822559E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324AB072-A71C-714B-A8AC-ED55471AE71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="432">
   <si>
     <t>Ticker</t>
   </si>
@@ -1463,6 +1463,9 @@
   </si>
   <si>
     <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2396,16 +2399,7 @@
     <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2417,12 +2411,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2432,23 +2420,38 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13500,18 +13503,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="246" t="s">
+      <c r="B2" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="247"/>
-      <c r="E2" s="246" t="s">
+      <c r="C2" s="244"/>
+      <c r="E2" s="243" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="247"/>
-      <c r="H2" s="246" t="s">
+      <c r="F2" s="244"/>
+      <c r="H2" s="243" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="247"/>
+      <c r="I2" s="244"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
@@ -13624,13 +13627,13 @@
         <f ca="1">Statement!AC149</f>
         <v>17.197610701107013</v>
       </c>
-      <c r="H7" s="180" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="208">
-        <f ca="1">'AVG target price'!C10</f>
-        <v>188.13456898723263</v>
+      <c r="H7" s="181" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales</v>
+      </c>
+      <c r="I7" s="207">
+        <f ca="1">'AVG target price'!C9</f>
+        <v>218.8143533379469</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13649,12 +13652,12 @@
         <v>1.3309481196699082E-2</v>
       </c>
       <c r="H8" s="180" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="209">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>-0.79479885149129859</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="208">
+        <f ca="1">'AVG target price'!C10</f>
+        <v>188.13456898723263</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13672,6 +13675,14 @@
         <f ca="1">Statement!AC160</f>
         <v>1.513912066577228E-2</v>
       </c>
+      <c r="H9" s="180" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="209">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.79479885149129859</v>
+      </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
@@ -13688,13 +13699,6 @@
         <f ca="1">Statement!AC162</f>
         <v>8.0998225816702573E-4</v>
       </c>
-      <c r="H10" s="180" t="s">
-        <v>362</v>
-      </c>
-      <c r="I10" s="208">
-        <f ca="1">DDM!C26</f>
-        <v>23.880454805310293</v>
-      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="181" t="s">
@@ -13711,6 +13715,13 @@
         <f ca="1">Statement!AC161</f>
         <v>3.1848870564881162E-3</v>
       </c>
+      <c r="H11" s="180" t="s">
+        <v>362</v>
+      </c>
+      <c r="I11" s="208">
+        <f ca="1">DDM!C26</f>
+        <v>23.880454805310293</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="181" t="s">
@@ -13743,6 +13754,13 @@
         <f>Statement!AC123</f>
         <v>1.4693124134748501</v>
       </c>
+      <c r="H13" s="180" t="s">
+        <v>431</v>
+      </c>
+      <c r="I13" s="209">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.66</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="182" t="s">
@@ -13779,10 +13797,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="248" t="s">
+      <c r="B17" s="245" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="248"/>
+      <c r="C17" s="245"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -13855,14 +13873,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="248" t="s">
+      <c r="B25" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="248"/>
-      <c r="E25" s="246" t="s">
+      <c r="C25" s="245"/>
+      <c r="E25" s="243" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="247"/>
+      <c r="F25" s="244"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -13911,15 +13929,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="243" t="s">
+      <c r="B33" s="132" t="s">
         <v>332</v>
       </c>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
+      <c r="C33" s="132"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14005,24 +14023,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="243"/>
-      <c r="C49" s="243"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="243"/>
-      <c r="F49" s="243"/>
-      <c r="G49" s="243"/>
-      <c r="H49" s="243"/>
+      <c r="B49" s="132"/>
+      <c r="C49" s="132"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="132"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="243" t="s">
+      <c r="B52" s="132" t="s">
         <v>335</v>
       </c>
-      <c r="C52" s="243"/>
-      <c r="D52" s="243"/>
-      <c r="E52" s="243"/>
-      <c r="F52" s="243"/>
-      <c r="G52" s="243"/>
-      <c r="H52" s="243"/>
+      <c r="C52" s="132"/>
+      <c r="D52" s="132"/>
+      <c r="E52" s="132"/>
+      <c r="F52" s="132"/>
+      <c r="G52" s="132"/>
+      <c r="H52" s="132"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14105,24 +14123,24 @@
       </c>
     </row>
     <row r="65" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="243"/>
-      <c r="C65" s="243"/>
-      <c r="D65" s="243"/>
-      <c r="E65" s="243"/>
-      <c r="F65" s="243"/>
-      <c r="G65" s="243"/>
-      <c r="H65" s="243"/>
+      <c r="B65" s="132"/>
+      <c r="C65" s="132"/>
+      <c r="D65" s="132"/>
+      <c r="E65" s="132"/>
+      <c r="F65" s="132"/>
+      <c r="G65" s="132"/>
+      <c r="H65" s="132"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="243" t="s">
+      <c r="B68" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="C68" s="243"/>
-      <c r="D68" s="243"/>
-      <c r="E68" s="243"/>
-      <c r="F68" s="243"/>
-      <c r="G68" s="243"/>
-      <c r="H68" s="243"/>
+      <c r="C68" s="132"/>
+      <c r="D68" s="132"/>
+      <c r="E68" s="132"/>
+      <c r="F68" s="132"/>
+      <c r="G68" s="132"/>
+      <c r="H68" s="132"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" s="41" t="s">
@@ -14137,22 +14155,16 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="243"/>
-      <c r="C75" s="243"/>
-      <c r="D75" s="243"/>
-      <c r="E75" s="243"/>
-      <c r="F75" s="243"/>
-      <c r="G75" s="243"/>
-      <c r="H75" s="243"/>
+      <c r="B75" s="132"/>
+      <c r="C75" s="132"/>
+      <c r="D75" s="132"/>
+      <c r="E75" s="132"/>
+      <c r="F75" s="132"/>
+      <c r="G75" s="132"/>
+      <c r="H75" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B65:H65"/>
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -14228,36 +14240,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14268,32 +14280,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="254" t="s">
+      <c r="S4" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="255"/>
-      <c r="U4" s="255"/>
-      <c r="V4" s="255"/>
-      <c r="W4" s="255"/>
-      <c r="X4" s="255"/>
-      <c r="Y4" s="255"/>
-      <c r="Z4" s="255"/>
-      <c r="AA4" s="255"/>
-      <c r="AB4" s="255"/>
-      <c r="AC4" s="255"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14684,33 +14696,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="242" t="s">
+      <c r="C10" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="242"/>
-      <c r="E10" s="242"/>
-      <c r="F10" s="242"/>
-      <c r="G10" s="242"/>
-      <c r="H10" s="242"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="242"/>
-      <c r="K10" s="242"/>
-      <c r="L10" s="242"/>
+      <c r="D10" s="251"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="251"/>
+      <c r="H10" s="251"/>
+      <c r="I10" s="251"/>
+      <c r="J10" s="251"/>
+      <c r="K10" s="251"/>
+      <c r="L10" s="251"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="254" t="s">
+      <c r="S10" s="252" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="255"/>
-      <c r="U10" s="255"/>
-      <c r="V10" s="255"/>
-      <c r="W10" s="255"/>
-      <c r="X10" s="255"/>
-      <c r="Y10" s="255"/>
-      <c r="Z10" s="255"/>
-      <c r="AA10" s="255"/>
-      <c r="AB10" s="255"/>
-      <c r="AC10" s="255"/>
+      <c r="T10" s="253"/>
+      <c r="U10" s="253"/>
+      <c r="V10" s="253"/>
+      <c r="W10" s="253"/>
+      <c r="X10" s="253"/>
+      <c r="Y10" s="253"/>
+      <c r="Z10" s="253"/>
+      <c r="AA10" s="253"/>
+      <c r="AB10" s="253"/>
+      <c r="AC10" s="253"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -15063,32 +15075,32 @@
     <row r="17" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="86"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="251" t="s">
         <v>395</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
       <c r="O17" s="5"/>
-      <c r="S17" s="254" t="s">
+      <c r="S17" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="T17" s="255"/>
-      <c r="U17" s="255"/>
-      <c r="V17" s="255"/>
-      <c r="W17" s="255"/>
-      <c r="X17" s="255"/>
-      <c r="Y17" s="255"/>
-      <c r="Z17" s="255"/>
-      <c r="AA17" s="255"/>
-      <c r="AB17" s="255"/>
-      <c r="AC17" s="255"/>
+      <c r="T17" s="253"/>
+      <c r="U17" s="253"/>
+      <c r="V17" s="253"/>
+      <c r="W17" s="253"/>
+      <c r="X17" s="253"/>
+      <c r="Y17" s="253"/>
+      <c r="Z17" s="253"/>
+      <c r="AA17" s="253"/>
+      <c r="AB17" s="253"/>
+      <c r="AC17" s="253"/>
       <c r="AE17" s="87"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -15580,35 +15592,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15617,31 +15629,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="P4" s="255" t="s">
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="P4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="255"/>
-      <c r="R4" s="255"/>
-      <c r="S4" s="255"/>
-      <c r="T4" s="255"/>
-      <c r="U4" s="255"/>
-      <c r="V4" s="255"/>
-      <c r="W4" s="255"/>
-      <c r="X4" s="255"/>
-      <c r="Y4" s="255"/>
-      <c r="Z4" s="255"/>
+      <c r="Q4" s="253"/>
+      <c r="R4" s="253"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -15836,32 +15848,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="251" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="255" t="s">
+      <c r="P9" s="253" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="255"/>
-      <c r="R9" s="255"/>
-      <c r="S9" s="255"/>
-      <c r="T9" s="255"/>
-      <c r="U9" s="255"/>
-      <c r="V9" s="255"/>
-      <c r="W9" s="255"/>
-      <c r="X9" s="255"/>
-      <c r="Y9" s="255"/>
-      <c r="Z9" s="255"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
+      <c r="T9" s="253"/>
+      <c r="U9" s="253"/>
+      <c r="V9" s="253"/>
+      <c r="W9" s="253"/>
+      <c r="X9" s="253"/>
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16338,31 +16350,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="251" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
-      <c r="P17" s="255" t="s">
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
+      <c r="P17" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="255"/>
-      <c r="R17" s="255"/>
-      <c r="S17" s="255"/>
-      <c r="T17" s="255"/>
-      <c r="U17" s="255"/>
-      <c r="V17" s="255"/>
-      <c r="W17" s="255"/>
-      <c r="X17" s="255"/>
-      <c r="Y17" s="255"/>
-      <c r="Z17" s="255"/>
+      <c r="Q17" s="253"/>
+      <c r="R17" s="253"/>
+      <c r="S17" s="253"/>
+      <c r="T17" s="253"/>
+      <c r="U17" s="253"/>
+      <c r="V17" s="253"/>
+      <c r="W17" s="253"/>
+      <c r="X17" s="253"/>
+      <c r="Y17" s="253"/>
+      <c r="Z17" s="253"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16840,20 +16852,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -16871,18 +16883,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -17079,18 +17091,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="251" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
       <c r="P11" s="256"/>
       <c r="Q11" s="256"/>
@@ -17344,18 +17356,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="251" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17573,18 +17585,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="242" t="s">
+      <c r="C26" s="251" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
-      <c r="F26" s="242"/>
-      <c r="G26" s="242"/>
-      <c r="H26" s="242"/>
-      <c r="I26" s="242"/>
-      <c r="J26" s="242"/>
-      <c r="K26" s="242"/>
-      <c r="L26" s="242"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17776,18 +17788,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="242" t="s">
+      <c r="C33" s="251" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="242"/>
-      <c r="E33" s="242"/>
-      <c r="F33" s="242"/>
-      <c r="G33" s="242"/>
-      <c r="H33" s="242"/>
-      <c r="I33" s="242"/>
-      <c r="J33" s="242"/>
-      <c r="K33" s="242"/>
-      <c r="L33" s="242"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17971,18 +17983,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="242" t="s">
+      <c r="C40" s="251" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="242"/>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
-      <c r="G40" s="242"/>
-      <c r="H40" s="242"/>
-      <c r="I40" s="242"/>
-      <c r="J40" s="242"/>
-      <c r="K40" s="242"/>
-      <c r="L40" s="242"/>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="251"/>
+      <c r="G40" s="251"/>
+      <c r="H40" s="251"/>
+      <c r="I40" s="251"/>
+      <c r="J40" s="251"/>
+      <c r="K40" s="251"/>
+      <c r="L40" s="251"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18246,12 +18258,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18259,6 +18265,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18296,20 +18308,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="S2" s="256"/>
       <c r="T2" s="256"/>
       <c r="U2" s="256"/>
@@ -18327,18 +18339,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="S4" s="256"/>
       <c r="T4" s="256"/>
       <c r="U4" s="256"/>
@@ -18712,18 +18724,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="242" t="s">
+      <c r="C13" s="251" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="242"/>
-      <c r="G13" s="242"/>
-      <c r="H13" s="242"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="251"/>
+      <c r="L13" s="251"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18816,18 +18828,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="251" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19019,18 +19031,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="242" t="s">
+      <c r="C25" s="251" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
-      <c r="F25" s="242"/>
-      <c r="G25" s="242"/>
-      <c r="H25" s="242"/>
-      <c r="I25" s="242"/>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242"/>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="251"/>
+      <c r="G25" s="251"/>
+      <c r="H25" s="251"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="251"/>
+      <c r="K25" s="251"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19168,18 +19180,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="242" t="s">
+      <c r="C31" s="251" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="242"/>
-      <c r="G31" s="242"/>
-      <c r="H31" s="242"/>
-      <c r="I31" s="242"/>
-      <c r="J31" s="242"/>
-      <c r="K31" s="242"/>
-      <c r="L31" s="242"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19318,16 +19330,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19390,10 +19402,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="242" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19478,10 +19490,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="242" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19570,20 +19582,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -19601,18 +19613,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -19869,10 +19881,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="242" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19892,10 +19904,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="242" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20009,37 +20021,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20259,18 +20271,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20464,18 +20476,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="251" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20609,18 +20621,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="242" t="s">
+      <c r="C22" s="251" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="242"/>
-      <c r="E22" s="242"/>
-      <c r="F22" s="242"/>
-      <c r="G22" s="242"/>
-      <c r="H22" s="242"/>
-      <c r="I22" s="242"/>
-      <c r="J22" s="242"/>
-      <c r="K22" s="242"/>
-      <c r="L22" s="242"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="251"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
+      <c r="K22" s="251"/>
+      <c r="L22" s="251"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20704,18 +20716,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="242" t="s">
+      <c r="C27" s="251" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="E27" s="242"/>
-      <c r="F27" s="242"/>
-      <c r="G27" s="242"/>
-      <c r="H27" s="242"/>
-      <c r="I27" s="242"/>
-      <c r="J27" s="242"/>
-      <c r="K27" s="242"/>
-      <c r="L27" s="242"/>
+      <c r="D27" s="251"/>
+      <c r="E27" s="251"/>
+      <c r="F27" s="251"/>
+      <c r="G27" s="251"/>
+      <c r="H27" s="251"/>
+      <c r="I27" s="251"/>
+      <c r="J27" s="251"/>
+      <c r="K27" s="251"/>
+      <c r="L27" s="251"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -20956,7 +20968,7 @@
         <v>15.223546615684999</v>
       </c>
       <c r="D35" s="147">
-        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
         <v>17.180029498525073</v>
       </c>
       <c r="E35" s="147">
@@ -21016,10 +21028,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="243" t="s">
+      <c r="B39" s="242" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="243"/>
+      <c r="C39" s="242"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21121,10 +21133,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="243" t="s">
+      <c r="B52" s="242" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="243"/>
+      <c r="C52" s="242"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21180,10 +21192,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="243" t="s">
+      <c r="B60" s="242" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="243"/>
+      <c r="C60" s="242"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21284,10 +21296,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="243" t="s">
+      <c r="B73" s="242" t="s">
         <v>428</v>
       </c>
-      <c r="C73" s="243"/>
+      <c r="C73" s="242"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21389,17 +21401,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="C17:L17"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21437,10 +21449,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="242" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21568,37 +21580,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21711,18 +21723,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21843,18 +21855,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="242" t="s">
+      <c r="C14" s="251" t="s">
         <v>365</v>
       </c>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+      <c r="K14" s="251"/>
+      <c r="L14" s="251"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21944,10 +21956,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="242" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22048,20 +22060,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -22079,18 +22091,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -22330,10 +22342,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="257" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="258"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22360,20 +22372,20 @@
       <c r="C17" s="156">
         <v>0.66</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="259" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="257" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="258"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22439,10 +22451,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="257" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="258"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22518,16 +22530,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33327,15 +33339,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="242" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33472,14 +33484,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="242" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33530,14 +33542,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="242" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33606,14 +33618,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="242" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33689,14 +33701,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="242" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33765,14 +33777,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="242" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33809,14 +33821,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="242" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35774,14 +35786,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="246" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="F3" s="253" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="252"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36250,18 +36262,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36272,6 +36272,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324AB072-A71C-714B-A8AC-ED55471AE71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C34A69-959C-BE46-9A07-DE601F7E0470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2399,9 +2399,6 @@
     <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2411,6 +2408,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2418,12 +2424,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2444,14 +2444,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12638,11 +12638,11 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>209</v>
-    <v>2.0912000000000002</v>
-    <v>10.91</v>
-    <v>1.2043E-2</v>
-    <v>-0.83</v>
-    <v>-9.0529999999999994E-4</v>
+    <v>2.1294</v>
+    <v>38.1</v>
+    <v>4.4877E-2</v>
+    <v>-1.08</v>
+    <v>-1.217E-3</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12650,25 +12650,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>924.36</v>
+    <v>903</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46290.999916990622</v>
+    <v>46300.894407117972</v>
     <v>0</v>
-    <v>903.53</v>
-    <v>209991568347</v>
+    <v>875</v>
+    <v>203179891981</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>924.36</v>
-    <v>65.155699999999996</v>
-    <v>905.92</v>
-    <v>916.83</v>
-    <v>916</v>
+    <v>876</v>
+    <v>63.801499999999997</v>
+    <v>848.99</v>
+    <v>887.09</v>
+    <v>886.01</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>2798981</v>
-    <v>3649657</v>
+    <v>5585185</v>
+    <v>4012182</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -12690,19 +12690,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12924,9 +12924,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13503,18 +13503,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="E2" s="243" t="s">
+      <c r="C2" s="243"/>
+      <c r="E2" s="242" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="H2" s="243" t="s">
+      <c r="F2" s="243"/>
+      <c r="H2" s="242" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="244"/>
+      <c r="I2" s="243"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>217288.71000000002</v>
+        <v>210240.33000000002</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>134.62378151387438</v>
+        <v>132.17834199816471</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>219149.71000000002</v>
+        <v>212101.33000000002</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>212.49492114379254</v>
+        <v>210.43934123311055</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>147.08063494255472</v>
+        <v>145.39237984946135</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13594,14 +13594,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>916</v>
+        <v>886.01</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>66.054034582132559</v>
+        <v>63.911383285302591</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>227.65915399799462</v>
+        <v>225.43558658156454</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13618,14 +13618,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>10.91</v>
+        <v>38.1</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>17.197610701107013</v>
+        <v>16.639757072570728</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>218.8143533379469</v>
+        <v>216.68876753496247</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13642,14 +13642,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.83</v>
+        <v>-1.08</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.3309481196699082E-2</v>
+        <v>1.3755686171154696E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>188.13456898723263</v>
+        <v>186.02688343945272</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13666,14 +13666,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.2043E-2</v>
+        <v>4.4877E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>1.513912066577228E-2</v>
+        <v>1.564666493816862E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.79479885149129859</v>
+        <v>-0.79029536637832387</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13690,14 +13690,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-9.0529999999999994E-4</v>
+        <v>-1.217E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>8.0998225816702573E-4</v>
+        <v>8.3713719437179335E-4</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13713,14 +13713,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>3.1848870564881162E-3</v>
+        <v>3.2916614999605452E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.880454805310293</v>
+        <v>23.388520370471173</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.0912000000000002</v>
+        <v>2.1294</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>3649657</v>
+        <v>4012182</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-8.5646419457320166E-3</v>
+        <v>-8.8517745382153835E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13797,10 +13797,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="245" t="s">
+      <c r="B17" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="245"/>
+      <c r="C17" s="244"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -13873,14 +13873,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="245"/>
-      <c r="E25" s="243" t="s">
+      <c r="C25" s="244"/>
+      <c r="E25" s="242" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="244"/>
+      <c r="F25" s="243"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14240,36 +14240,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
+      <c r="AA2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="245"/>
+      <c r="AC2" s="245"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15592,35 +15592,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="P2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="245"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16852,20 +16852,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
       <c r="G3" s="254"/>
       <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -18258,6 +18258,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18265,12 +18271,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18308,20 +18308,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
       <c r="S2" s="256"/>
       <c r="T2" s="256"/>
       <c r="U2" s="256"/>
@@ -19330,16 +19330,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19402,10 +19402,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>217288.71000000002</v>
+        <v>210240.33000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.0912000000000002</v>
+        <v>2.1294</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19490,10 +19490,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="245"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.6141906785265232E-2</v>
+        <v>1.6674046432799405E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98385809321473472</v>
+        <v>0.98332595356720054</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14594400000000002</v>
+        <v>0.148593</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14435331193775283</v>
+        <v>0.14690570321932572</v>
       </c>
     </row>
   </sheetData>
@@ -19582,20 +19582,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
       <c r="G3" s="254"/>
       <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30442.703667331833</v>
+        <v>29853.633676182126</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19842,23 +19842,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3785.8615782224188</v>
+        <v>3777.4362996154919</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4636.67178507055</v>
+        <v>4616.0573057824331</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4410.5854292723234</v>
+        <v>4381.2041859152223</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3444.2471981639987</v>
+        <v>3413.6892760007327</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1976.9426753397718</v>
+        <v>1955.0423476258457</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19877,14 +19877,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15512.527552719166</v>
+        <v>15043.837638625319</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="245" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="245"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19900,14 +19900,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14435331193775283</v>
+        <v>0.14690570321932572</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="245" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="245"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19915,7 +19915,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18254.308666069064</v>
+        <v>18143.429414939725</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15512.527552719166</v>
+        <v>15043.837638625319</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33766.83621878823</v>
+        <v>33187.26705356504</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31905.83621878823</v>
+        <v>31326.26705356504</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>134.62378151387438</v>
+        <v>132.17834199816471</v>
       </c>
     </row>
   </sheetData>
@@ -20021,20 +20021,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20247,23 +20247,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3785.8615782224188</v>
+        <v>3777.4362996154919</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4636.67178507055</v>
+        <v>4616.0573057824331</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4410.5854292723234</v>
+        <v>4381.2041859152223</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3444.2471981639987</v>
+        <v>3413.6892760007327</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1976.9426753397718</v>
+        <v>1955.0423476258457</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21028,10 +21028,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="242" t="s">
+      <c r="B39" s="245" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="242"/>
+      <c r="C39" s="245"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14435331193775283</v>
+        <v>0.14690570321932572</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35944.930320349544</v>
+        <v>35546.736804933324</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>52222.296311078833</v>
+        <v>51735.123872247204</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50361.296311078833</v>
+        <v>49874.123872247204</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21129,14 +21129,14 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>212.49492114379254</v>
+        <v>210.43934123311055</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="245" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="242"/>
+      <c r="C52" s="245"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14594400000000002</v>
+        <v>0.148593</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21188,14 +21188,14 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>147.08063494255472</v>
+        <v>145.39237984946135</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="242" t="s">
+      <c r="B60" s="245" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="242"/>
+      <c r="C60" s="245"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14435331193775283</v>
+        <v>0.14690570321932572</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39538.853506795436</v>
+        <v>39100.846952516913</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21247,7 +21247,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55816.219497524726</v>
+        <v>55289.234019830794</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53955.219497524726</v>
+        <v>53428.234019830794</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21292,14 +21292,14 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>227.65915399799462</v>
+        <v>225.43558658156454</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="242" t="s">
+      <c r="B73" s="245" t="s">
         <v>428</v>
       </c>
-      <c r="C73" s="242"/>
+      <c r="C73" s="245"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14435331193775283</v>
+        <v>0.14690570321932572</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37442.635750364127</v>
+        <v>37027.850838472223</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53720.001741093416</v>
+        <v>53216.237905786104</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51859.001741093416</v>
+        <v>51355.237905786104</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21396,22 +21396,22 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>218.8143533379469</v>
+        <v>216.68876753496247</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21449,10 +21449,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>134.62378151387438</v>
+        <v>132.17834199816471</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>212.49492114379254</v>
+        <v>210.43934123311055</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>147.08063494255472</v>
+        <v>145.39237984946135</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>227.65915399799462</v>
+        <v>225.43558658156454</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21497,7 +21497,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>218.8143533379469</v>
+        <v>216.68876753496247</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>188.13456898723263</v>
+        <v>186.02688343945272</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.79479885149129859</v>
+        <v>-0.79029536637832387</v>
       </c>
     </row>
   </sheetData>
@@ -21580,20 +21580,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21956,10 +21956,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="242" t="s">
+      <c r="B20" s="245" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="242"/>
+      <c r="C20" s="245"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14594400000000002</v>
+        <v>0.148593</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.880454805310293</v>
+        <v>23.388520370471173</v>
       </c>
     </row>
   </sheetData>
@@ -22060,20 +22060,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
       <c r="G3" s="254"/>
       <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -22248,7 +22248,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>304694.2911045067</v>
+        <v>298798.41978750192</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22302,23 +22302,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4468.7220689471487</v>
+        <v>4458.7771125165227</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6482.3324729065625</v>
+        <v>6453.5122512700664</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9403.2776352992478</v>
+        <v>9340.6374273296897</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13640.403459107414</v>
+        <v>13519.383577781491</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>19786.782199088859</v>
+        <v>19567.586660457651</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22337,15 +22337,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>155261.45895467891</v>
+        <v>150570.44521676627</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="257" t="s">
+      <c r="B14" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="258"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>912.69593299571875</v>
+        <v>890.08520813269467</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22372,20 +22372,20 @@
       <c r="C17" s="156">
         <v>0.66</v>
       </c>
-      <c r="E17" s="259" t="s">
+      <c r="E17" s="257" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="257" t="s">
+      <c r="B19" s="258" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="258"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14435331193775283</v>
+        <v>0.14690570321932572</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>208120.41</v>
+        <v>201369.43</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22446,15 +22446,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>209981.41</v>
+        <v>203230.43</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="257" t="s">
+      <c r="B28" s="258" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="258"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22462,7 +22462,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>53781.517835349237</v>
+        <v>53339.897029355423</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>155261.45895467891</v>
+        <v>150570.44521676627</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>209042.97679002816</v>
+        <v>203910.3422461217</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>207181.97679002816</v>
+        <v>202049.3422461217</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22525,21 +22525,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>912.69593299571875</v>
+        <v>890.08520813269467</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29319,7 +29319,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30762,7 +30762,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>66.054034582132559</v>
+        <v>63.911383285302591</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30803,7 +30803,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>17.197610701107013</v>
+        <v>16.639757072570728</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30868,7 +30868,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>96.040798338717124</v>
+        <v>92.92544070143056</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30933,7 +30933,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>217288.71000000002</v>
+        <v>210240.33000000002</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>219149.71000000002</v>
+        <v>212101.33000000002</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31039,7 +31039,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>17.970455924559246</v>
+        <v>17.392482984829851</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31080,7 +31080,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>53.529484611626778</v>
+        <v>51.80784807034685</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31185,8 +31185,8 @@
       <c r="Z156" s="49"/>
       <c r="AA156" s="49"/>
       <c r="AC156" s="64">
-        <f>AC107+AC52+AC108+AC54+AC56+AC57</f>
-        <v>3211.6005420054198</v>
+        <f t="shared" ref="AC156" si="202">AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
+        <v>3080.6005420054198</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31198,23 +31198,23 @@
         <v>19.701673228346458</v>
       </c>
       <c r="M157" s="72">
-        <f t="shared" ref="M157:P157" si="202">M151/M155</f>
+        <f t="shared" ref="M157:P157" si="203">M151/M155</f>
         <v>13.011644562334217</v>
       </c>
       <c r="N157" s="72">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>25.062798434442271</v>
       </c>
       <c r="O157" s="72">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>40.961843575418989</v>
       </c>
       <c r="P157" s="72">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>49.893074433656956</v>
       </c>
       <c r="Q157" s="72">
-        <f t="shared" ref="Q157" si="203">Q151/Q155</f>
+        <f t="shared" ref="Q157" si="204">Q151/Q155</f>
         <v>67.212282157676341</v>
       </c>
       <c r="T157" s="49"/>
@@ -31226,8 +31226,8 @@
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
-        <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>75.134408713692949</v>
+        <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
+        <v>72.697209543568476</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31239,23 +31239,23 @@
         <v>19.801169652343109</v>
       </c>
       <c r="M158" s="72">
-        <f t="shared" ref="M158:P158" si="205">M152/M156</f>
+        <f t="shared" ref="M158:P158" si="206">M152/M156</f>
         <v>14.659365949397982</v>
       </c>
       <c r="N158" s="72">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>17.180029498525073</v>
       </c>
       <c r="O158" s="72">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>35.737599041631057</v>
       </c>
       <c r="P158" s="72">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>40.813593878239608</v>
       </c>
       <c r="Q158" s="72">
-        <f t="shared" ref="Q158" si="206">Q152/Q156</f>
+        <f t="shared" ref="Q158" si="207">Q152/Q156</f>
         <v>63.70151446907547</v>
       </c>
       <c r="T158" s="49"/>
@@ -31267,8 +31267,8 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
-        <f t="shared" ca="1" si="204"/>
-        <v>68.236914003992652</v>
+        <f t="shared" ca="1" si="205"/>
+        <v>68.850643602732589</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31280,23 +31280,23 @@
         <v>5.0757110241845635E-2</v>
       </c>
       <c r="M159" s="74">
-        <f t="shared" ref="M159:P159" si="207">M155/M151</f>
+        <f t="shared" ref="M159:P159" si="208">M155/M151</f>
         <v>7.685423585076824E-2</v>
       </c>
       <c r="N159" s="74">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>3.9899774265660659E-2</v>
       </c>
       <c r="O159" s="74">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>2.4412963692876734E-2</v>
       </c>
       <c r="P159" s="74">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>2.0042861887168417E-2</v>
       </c>
       <c r="Q159" s="74">
-        <f t="shared" ref="Q159" si="208">Q155/Q151</f>
+        <f t="shared" ref="Q159" si="209">Q155/Q151</f>
         <v>1.4878233083263779E-2</v>
       </c>
       <c r="T159" s="49"/>
@@ -31308,8 +31308,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
-        <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>1.3309481196699082E-2</v>
+        <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
+        <v>1.3755686171154696E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31317,27 +31317,27 @@
         <v>265</v>
       </c>
       <c r="L160" s="74">
-        <f t="shared" ref="L160:Q160" si="210">L25/L115</f>
+        <f t="shared" ref="L160:Q160" si="211">L25/L115</f>
         <v>6.1587958175341836E-2</v>
       </c>
       <c r="M160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.10652771746996671</v>
       </c>
       <c r="N160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>-4.1377080976240509E-2</v>
       </c>
       <c r="O160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>1.529969981601627E-2</v>
       </c>
       <c r="P160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>4.7864819004524883E-2</v>
       </c>
       <c r="Q160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>1.6947912602419041E-2</v>
       </c>
       <c r="T160" s="49"/>
@@ -31350,7 +31350,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.513912066577228E-2</v>
+        <v>1.564666493816862E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31358,27 +31358,27 @@
         <v>266</v>
       </c>
       <c r="L161" s="152">
-        <f t="shared" ref="L161:Q161" si="211">L81/L115</f>
+        <f t="shared" ref="L161:Q161" si="212">L81/L115</f>
         <v>3.0564173273583822E-2</v>
       </c>
       <c r="M161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>4.0092632797799968E-2</v>
       </c>
       <c r="N161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>4.5256182317763051E-2</v>
       </c>
       <c r="O161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>2.7113392079016172E-2</v>
       </c>
       <c r="P161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>2.0220588235294119E-2</v>
       </c>
       <c r="Q161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>3.5602809207959424E-3</v>
       </c>
       <c r="T161" s="49"/>
@@ -31391,7 +31391,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>3.1848870564881162E-3</v>
+        <v>3.2916614999605452E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31399,27 +31399,27 @@
         <v>291</v>
       </c>
       <c r="L162" s="152">
-        <f t="shared" ref="L162:Q162" si="212">-L62/L151</f>
+        <f t="shared" ref="L162:Q162" si="213">-L62/L151</f>
         <v>0.10226358726875789</v>
       </c>
       <c r="M162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>0.12224648125157565</v>
       </c>
       <c r="N162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>3.1857354012504009E-2</v>
       </c>
       <c r="O162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>0</v>
       </c>
       <c r="P162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>0</v>
       </c>
       <c r="Q162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>9.0545263577262276E-4</v>
       </c>
       <c r="T162" s="49"/>
@@ -31432,7 +31432,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>8.0998225816702573E-4</v>
+        <v>8.3713719437179335E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31440,27 +31440,27 @@
         <v>293</v>
       </c>
       <c r="L163" s="152">
-        <f t="shared" ref="L163:Q163" si="213">-(L62+L63)/L151</f>
+        <f t="shared" ref="L163:Q163" si="214">-(L62+L63)/L151</f>
         <v>0.13468619016930691</v>
       </c>
       <c r="M163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.16369748378824109</v>
       </c>
       <c r="N163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>7.7300932530340621E-2</v>
       </c>
       <c r="O163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>2.6595128045312645E-2</v>
       </c>
       <c r="P163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>1.9459089210843123E-2</v>
       </c>
       <c r="Q163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>4.1671399714535481E-3</v>
       </c>
       <c r="T163" s="49"/>
@@ -31473,7 +31473,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>3.7277592563368799E-3</v>
+        <v>3.8527336786429128E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31481,27 +31481,27 @@
         <v>340</v>
       </c>
       <c r="L164" s="152">
-        <f t="shared" ref="L164:Q164" si="214">L156/L5</f>
+        <f t="shared" ref="L164:Q164" si="215">L156/L5</f>
         <v>0.11322609797980106</v>
       </c>
       <c r="M164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.11551912298693807</v>
       </c>
       <c r="N164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.13773022751895991</v>
       </c>
       <c r="O164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.1123904232821475</v>
       </c>
       <c r="P164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>9.4100951040925501E-2</v>
       </c>
       <c r="Q164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.25261177056215006</v>
       </c>
       <c r="T164" s="49"/>
@@ -31514,7 +31514,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="152">
         <f>AC156/AC5</f>
-        <v>0.26335387798322424</v>
+        <v>0.25261177056215006</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31522,27 +31522,27 @@
         <v>341</v>
       </c>
       <c r="L165" s="152">
-        <f t="shared" ref="L165:Q165" si="215">L155/L5</f>
+        <f t="shared" ref="L165:Q165" si="216">L155/L5</f>
         <v>9.5122179571201199E-2</v>
       </c>
       <c r="M165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>9.6989966555183951E-2</v>
       </c>
       <c r="N165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>6.9203683640303354E-2</v>
       </c>
       <c r="O165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>8.1972217981987477E-2</v>
       </c>
       <c r="P165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>6.7934483895789821E-2</v>
       </c>
       <c r="Q165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>0.23714637146371464</v>
       </c>
       <c r="T165" s="49"/>
@@ -31563,27 +31563,27 @@
         <v>269</v>
       </c>
       <c r="L166" s="152">
-        <f t="shared" ref="L166:Q166" si="216">-L63/L155</f>
+        <f t="shared" ref="L166:Q166" si="217">-L63/L155</f>
         <v>0.63877952755905509</v>
       </c>
       <c r="M166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0.53934571175950485</v>
       </c>
       <c r="N166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>1.1389432485322897</v>
       </c>
       <c r="O166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>1.0893854748603351</v>
       </c>
       <c r="P166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0.970873786407767</v>
       </c>
       <c r="Q166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0.21922544951590595</v>
       </c>
       <c r="T166" s="49"/>
@@ -31604,27 +31604,27 @@
         <v>271</v>
       </c>
       <c r="L167" s="152">
-        <f t="shared" ref="L167:Q167" si="217">-L62/L155</f>
+        <f t="shared" ref="L167:Q167" si="218">-L62/L155</f>
         <v>2.0147637795275593</v>
       </c>
       <c r="M167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>1.5906277630415562</v>
       </c>
       <c r="N167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0.79843444227005866</v>
       </c>
       <c r="O167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0</v>
       </c>
       <c r="P167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0</v>
       </c>
       <c r="Q167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>6.0857538035961271E-2</v>
       </c>
       <c r="T167" s="49"/>
@@ -31645,27 +31645,27 @@
         <v>282</v>
       </c>
       <c r="L168" s="152">
-        <f t="shared" ref="L168:Q168" si="218">(-L63-L62)/L155</f>
+        <f t="shared" ref="L168:Q168" si="219">(-L63-L62)/L155</f>
         <v>2.6535433070866143</v>
       </c>
       <c r="M168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>2.1299734748010608</v>
       </c>
       <c r="N168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>1.9373776908023483</v>
       </c>
       <c r="O168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>1.0893854748603351</v>
       </c>
       <c r="P168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0.970873786407767</v>
       </c>
       <c r="Q168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0.28008298755186722</v>
       </c>
       <c r="T168" s="49"/>
@@ -31686,27 +31686,27 @@
         <v>276</v>
       </c>
       <c r="L169" s="152">
-        <f t="shared" ref="L169:Q169" si="219">L79/L77</f>
+        <f t="shared" ref="L169:Q169" si="220">L79/L77</f>
         <v>8.6956521739130436E-3</v>
       </c>
       <c r="M169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>9.3896713615023476E-3</v>
       </c>
       <c r="N169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>9.6618357487922701E-3</v>
       </c>
       <c r="O169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>9.3896713615023476E-3</v>
       </c>
       <c r="P169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>9.1743119266055051E-3</v>
       </c>
       <c r="Q169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>8.4388185654008432E-3</v>
       </c>
       <c r="T169" s="49"/>
@@ -31727,59 +31727,59 @@
         <v>277</v>
       </c>
       <c r="L170" s="72">
-        <f t="shared" ref="L170:Q170" si="220">L105/L74</f>
+        <f t="shared" ref="L170:Q170" si="221">L105/L74</f>
         <v>5.3259911894273131</v>
       </c>
       <c r="M170" s="72">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>2.9425837320574164</v>
       </c>
       <c r="N170" s="72">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>3.7971014492753623</v>
       </c>
       <c r="O170" s="72">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>6.4666666666666668</v>
       </c>
       <c r="P170" s="72">
-        <f t="shared" si="220"/>
-        <v>4.183098591549296</v>
-      </c>
-      <c r="Q170" s="72">
-        <f t="shared" si="220"/>
-        <v>7.5066079295154182</v>
-      </c>
-      <c r="T170" s="72">
-        <f t="shared" ref="T170:Z170" si="221">T105/T74</f>
-        <v>5.8443396226415096</v>
-      </c>
-      <c r="U170" s="72">
-        <f t="shared" si="221"/>
-        <v>5.8396226415094343</v>
-      </c>
-      <c r="V170" s="72">
-        <f t="shared" si="221"/>
-        <v>3.8396226415094339</v>
-      </c>
-      <c r="W170" s="72">
         <f t="shared" si="221"/>
         <v>4.183098591549296</v>
       </c>
+      <c r="Q170" s="72">
+        <f t="shared" si="221"/>
+        <v>7.5066079295154182</v>
+      </c>
+      <c r="T170" s="72">
+        <f t="shared" ref="T170:Z170" si="222">T105/T74</f>
+        <v>5.8443396226415096</v>
+      </c>
+      <c r="U170" s="72">
+        <f t="shared" si="222"/>
+        <v>5.8396226415094343</v>
+      </c>
+      <c r="V170" s="72">
+        <f t="shared" si="222"/>
+        <v>3.8396226415094339</v>
+      </c>
+      <c r="W170" s="72">
+        <f t="shared" si="222"/>
+        <v>4.183098591549296</v>
+      </c>
       <c r="X170" s="72">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>5.1962616822429908</v>
       </c>
       <c r="Y170" s="72">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>4.7981651376146788</v>
       </c>
       <c r="Z170" s="72">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>5.1160714285714288</v>
       </c>
       <c r="AA170" s="72">
-        <f t="shared" ref="AA170" si="222">AA105/AA74</f>
+        <f t="shared" ref="AA170" si="223">AA105/AA74</f>
         <v>7.5066079295154182</v>
       </c>
       <c r="AC170" s="72">
@@ -31792,59 +31792,59 @@
         <v>279</v>
       </c>
       <c r="L171" s="152">
-        <f t="shared" ref="L171:Q171" si="223">L53/L58</f>
+        <f t="shared" ref="L171:Q171" si="224">L53/L58</f>
         <v>6.8880688806888066E-2</v>
       </c>
       <c r="M171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>8.7507543753771871E-2</v>
       </c>
       <c r="N171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.12208067940552017</v>
       </c>
       <c r="O171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.1383442265795207</v>
       </c>
       <c r="P171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.18467220683287167</v>
       </c>
       <c r="Q171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>5.7974959172563963E-2</v>
       </c>
       <c r="T171" s="152">
-        <f t="shared" ref="T171:Z171" si="224">T53/T58</f>
+        <f t="shared" ref="T171:Z171" si="225">T53/T58</f>
         <v>0.4</v>
       </c>
       <c r="U171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0.22171945701357465</v>
       </c>
       <c r="V171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0.20849420849420849</v>
       </c>
       <c r="W171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0.11614173228346457</v>
       </c>
       <c r="X171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>9.7744360902255634E-2</v>
       </c>
       <c r="Y171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>7.3305670816044263E-2</v>
       </c>
       <c r="Z171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>4.8473967684021541E-2</v>
       </c>
       <c r="AA171" s="152">
-        <f t="shared" ref="AA171" si="225">AA53/AA58</f>
+        <f t="shared" ref="AA171" si="226">AA53/AA58</f>
         <v>4.1379310344827586E-2</v>
       </c>
       <c r="AC171" s="152">
@@ -31857,59 +31857,59 @@
         <v>280</v>
       </c>
       <c r="L172" s="152">
-        <f t="shared" ref="L172:Q172" si="226">L53/L5</f>
+        <f t="shared" ref="L172:Q172" si="227">L53/L5</f>
         <v>1.0485909559030053E-2</v>
       </c>
       <c r="M172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>1.2434611096818454E-2</v>
       </c>
       <c r="N172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>1.5574214517876489E-2</v>
       </c>
       <c r="O172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>1.938635322851473E-2</v>
       </c>
       <c r="P172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>2.1985269869187644E-2</v>
       </c>
       <c r="Q172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>1.7466174661746617E-2</v>
       </c>
       <c r="T172" s="152">
-        <f t="shared" ref="T172:Z172" si="227">T53/T5</f>
+        <f t="shared" ref="T172:Z172" si="228">T53/T5</f>
         <v>1.7527675276752766E-2</v>
       </c>
       <c r="U172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>2.1075268817204302E-2</v>
       </c>
       <c r="V172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="W172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>2.4140752864157119E-2</v>
       </c>
       <c r="X172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>1.9779383796120199E-2</v>
       </c>
       <c r="Y172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>1.8761061946902656E-2</v>
       </c>
       <c r="Z172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>1.7352185089974295E-2</v>
       </c>
       <c r="AA172" s="152">
-        <f t="shared" ref="AA172" si="228">AA53/AA5</f>
+        <f t="shared" ref="AA172" si="229">AA53/AA5</f>
         <v>1.4880132267842381E-2</v>
       </c>
       <c r="AC172" s="152">
@@ -31922,59 +31922,59 @@
         <v>285</v>
       </c>
       <c r="L173" s="72">
-        <f t="shared" ref="L173:Q173" si="229">(L105-L106)/L74</f>
+        <f t="shared" ref="L173:Q173" si="230">(L105-L106)/L74</f>
         <v>-17.312775330396477</v>
       </c>
       <c r="M173" s="72">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-24.071770334928228</v>
       </c>
       <c r="N173" s="72">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-22.536231884057973</v>
       </c>
       <c r="O173" s="72">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-20.552380952380954</v>
       </c>
       <c r="P173" s="72">
-        <f t="shared" si="229"/>
-        <v>-19.267605633802816</v>
-      </c>
-      <c r="Q173" s="72">
-        <f t="shared" si="229"/>
-        <v>-8.1982378854625555</v>
-      </c>
-      <c r="T173" s="72">
-        <f t="shared" ref="T173:Z173" si="230">(T105-T106)/T74</f>
-        <v>-20.929245283018869</v>
-      </c>
-      <c r="U173" s="72">
-        <f t="shared" si="230"/>
-        <v>-20.94811320754717</v>
-      </c>
-      <c r="V173" s="72">
-        <f t="shared" si="230"/>
-        <v>-20.433962264150942</v>
-      </c>
-      <c r="W173" s="72">
         <f t="shared" si="230"/>
         <v>-19.267605633802816</v>
       </c>
+      <c r="Q173" s="72">
+        <f t="shared" si="230"/>
+        <v>-8.1982378854625555</v>
+      </c>
+      <c r="T173" s="72">
+        <f t="shared" ref="T173:Z173" si="231">(T105-T106)/T74</f>
+        <v>-20.929245283018869</v>
+      </c>
+      <c r="U173" s="72">
+        <f t="shared" si="231"/>
+        <v>-20.94811320754717</v>
+      </c>
+      <c r="V173" s="72">
+        <f t="shared" si="231"/>
+        <v>-20.433962264150942</v>
+      </c>
+      <c r="W173" s="72">
+        <f t="shared" si="231"/>
+        <v>-19.267605633802816</v>
+      </c>
       <c r="X173" s="72">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>-18.140186915887849</v>
       </c>
       <c r="Y173" s="72">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>-15.839449541284404</v>
       </c>
       <c r="Z173" s="72">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>-12.129464285714286</v>
       </c>
       <c r="AA173" s="72">
-        <f t="shared" ref="AA173" si="231">(AA105-AA106)/AA74</f>
+        <f t="shared" ref="AA173" si="232">(AA105-AA106)/AA74</f>
         <v>-8.1982378854625555</v>
       </c>
       <c r="AC173" s="72">
@@ -31987,27 +31987,27 @@
         <v>290</v>
       </c>
       <c r="L174" s="152">
-        <f t="shared" ref="L174:Q174" si="232">(L105-L106)/L151</f>
+        <f t="shared" ref="L174:Q174" si="233">(L105-L106)/L151</f>
         <v>-0.19633409768745408</v>
       </c>
       <c r="M174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.34186884223272768</v>
       </c>
       <c r="N174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.36425136389296864</v>
       </c>
       <c r="O174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.19621294468986217</v>
       </c>
       <c r="P174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.13310017020216697</v>
       </c>
       <c r="Q174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-9.5741326998457447E-3</v>
       </c>
       <c r="T174" s="49"/>
@@ -32020,7 +32020,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-8.5646419457320166E-3</v>
+        <v>-8.8517745382153835E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -32028,59 +32028,59 @@
         <v>299</v>
       </c>
       <c r="L175" s="152">
-        <f t="shared" ref="L175:Q175" si="233">-L108/L5</f>
+        <f t="shared" ref="L175:Q175" si="234">-L108/L5</f>
         <v>4.6624847860687199E-2</v>
       </c>
       <c r="M175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>3.2673012606122973E-2</v>
       </c>
       <c r="N175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>4.2795232936078009E-2</v>
       </c>
       <c r="O175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>3.877270645702946E-2</v>
       </c>
       <c r="P175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>2.9130482576673628E-2</v>
       </c>
       <c r="Q175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>4.6658466584665846E-2</v>
       </c>
       <c r="T175" s="152">
-        <f t="shared" ref="T175:Z175" si="234">-T108/T5</f>
+        <f t="shared" ref="T175:Z175" si="235">-T108/T5</f>
         <v>3.136531365313653E-2</v>
       </c>
       <c r="U175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>3.053763440860215E-2</v>
       </c>
       <c r="V175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>1.9907407407407408E-2</v>
       </c>
       <c r="W175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>3.3960720130932896E-2</v>
       </c>
       <c r="X175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>3.9939140357550397E-2</v>
       </c>
       <c r="Y175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>4.1061946902654869E-2</v>
       </c>
       <c r="Z175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>5.1735218508997427E-2</v>
       </c>
       <c r="AA175" s="152">
-        <f t="shared" ref="AA175" si="235">-AA108/AA5</f>
+        <f t="shared" ref="AA175" si="236">-AA108/AA5</f>
         <v>5.1529346927528245E-2</v>
       </c>
       <c r="AC175" s="152">
@@ -32093,59 +32093,59 @@
         <v>300</v>
       </c>
       <c r="L176" s="152">
-        <f t="shared" ref="L176:Q176" si="236">-(L108/L58)</f>
+        <f t="shared" ref="L176:Q176" si="237">-(L108/L58)</f>
         <v>0.30627306273062732</v>
       </c>
       <c r="M176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.22993361496680748</v>
       </c>
       <c r="N176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.3354564755838641</v>
       </c>
       <c r="O176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.27668845315904139</v>
       </c>
       <c r="P176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.24469067405355494</v>
       </c>
       <c r="Q176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.15487207403375067</v>
       </c>
       <c r="T176" s="152">
-        <f t="shared" ref="T176:Z176" si="237">-(T108/T58)</f>
+        <f t="shared" ref="T176:Z176" si="238">-(T108/T58)</f>
         <v>0.71578947368421053</v>
       </c>
       <c r="U176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.32126696832579188</v>
       </c>
       <c r="V176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.16602316602316602</v>
       </c>
       <c r="W176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.16338582677165353</v>
       </c>
       <c r="X176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.19736842105263158</v>
       </c>
       <c r="Y176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.16044260027662519</v>
       </c>
       <c r="Z176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.14452423698384201</v>
       </c>
       <c r="AA176" s="152">
-        <f t="shared" ref="AA176" si="238">-(AA108/AA58)</f>
+        <f t="shared" ref="AA176" si="239">-(AA108/AA58)</f>
         <v>0.14329501915708812</v>
       </c>
       <c r="AC176" s="152">
@@ -32158,59 +32158,59 @@
         <v>301</v>
       </c>
       <c r="L177" s="152">
-        <f t="shared" ref="L177:Q177" si="239">-L108/L52</f>
+        <f t="shared" ref="L177:Q177" si="240">-L108/L52</f>
         <v>1.2544080604534005</v>
       </c>
       <c r="M177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0.84478935698447899</v>
       </c>
       <c r="N177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0.61598440545808963</v>
       </c>
       <c r="O177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0.96212121212121215</v>
       </c>
       <c r="P177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>1.0557768924302788</v>
       </c>
       <c r="Q177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>2.0615942028985508</v>
       </c>
       <c r="T177" s="152">
-        <f t="shared" ref="T177:Z177" si="240">-T108/T52</f>
+        <f t="shared" ref="T177:Z177" si="241">-T108/T52</f>
         <v>1.0625</v>
       </c>
       <c r="U177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>1.126984126984127</v>
       </c>
       <c r="V177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>0.68253968253968256</v>
       </c>
       <c r="W177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>1.360655737704918</v>
       </c>
       <c r="X177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>1.4583333333333333</v>
       </c>
       <c r="Y177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>1.7058823529411764</v>
       </c>
       <c r="Z177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>2.4393939393939394</v>
       </c>
       <c r="AA177" s="152">
-        <f t="shared" ref="AA177" si="241">-AA108/AA52</f>
+        <f t="shared" ref="AA177" si="242">-AA108/AA52</f>
         <v>2.6714285714285713</v>
       </c>
       <c r="AC177" s="152">
@@ -32223,27 +32223,27 @@
         <v>353</v>
       </c>
       <c r="L178" s="220">
-        <f t="shared" ref="L178:Q178" si="242">L5/L36</f>
+        <f t="shared" ref="L178:Q178" si="243">L5/L36</f>
         <v>1.2312391930835735</v>
       </c>
       <c r="M178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>1.3037790697674418</v>
       </c>
       <c r="N178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.97723663313922715</v>
       </c>
       <c r="O178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.84649179480553038</v>
       </c>
       <c r="P178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>1.133865137729029</v>
       </c>
       <c r="Q178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>1.2229241877256318</v>
       </c>
       <c r="T178" s="49"/>
@@ -32264,27 +32264,27 @@
         <v>350</v>
       </c>
       <c r="L179" s="222">
-        <f t="shared" ref="L179:Q179" si="243">IF(AND(L11&gt;0,L106&gt;0),L106/L11,"N/A")</f>
+        <f t="shared" ref="L179:Q179" si="244">IF(AND(L11&gt;0,L106&gt;0),L106/L11,"N/A")</f>
         <v>3.4443699731903483</v>
       </c>
       <c r="M179" s="222">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>2.8879795396419436</v>
       </c>
       <c r="N179" s="222" t="str">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>N/A</v>
       </c>
       <c r="O179" s="222">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>12.553097345132743</v>
       </c>
       <c r="P179" s="222">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>2.6428571428571428</v>
       </c>
       <c r="Q179" s="222">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>0.8707865168539326</v>
       </c>
       <c r="T179" s="49"/>
@@ -32305,27 +32305,27 @@
         <v>351</v>
       </c>
       <c r="L180" s="222">
-        <f t="shared" ref="L180:Q180" si="244">IF(AND(L11&gt;0,L106&gt;0),(L106-L105)/L11,"N/A")</f>
+        <f t="shared" ref="L180:Q180" si="245">IF(AND(L11&gt;0,L106&gt;0),(L106-L105)/L11,"N/A")</f>
         <v>2.6340482573726542</v>
       </c>
       <c r="M180" s="222">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>2.5734015345268544</v>
       </c>
       <c r="N180" s="222" t="str">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>N/A</v>
       </c>
       <c r="O180" s="222">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>9.5486725663716818</v>
       </c>
       <c r="P180" s="222">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>2.1714285714285713</v>
       </c>
       <c r="Q180" s="222">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>0.45456765999022958</v>
       </c>
       <c r="T180" s="49"/>
@@ -32346,27 +32346,27 @@
         <v>352</v>
       </c>
       <c r="L181" s="222">
-        <f t="shared" ref="L181:Q181" si="245">L5/(L106+L110-L105)</f>
+        <f t="shared" ref="L181:Q181" si="246">L5/(L106+L110-L105)</f>
         <v>2.3418110063582547</v>
       </c>
       <c r="M181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>2.2686770428015564</v>
       </c>
       <c r="N181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>2.1304096941719561</v>
       </c>
       <c r="O181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>2.3189380530973454</v>
       </c>
       <c r="P181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>2.4916461243494932</v>
       </c>
       <c r="Q181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>3.0275571002979147</v>
       </c>
       <c r="T181" s="49"/>
@@ -32512,7 +32512,7 @@
         <v>697</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" ref="AC186" si="246">SUM(X186:AA186)</f>
+        <f t="shared" ref="AC186" si="247">SUM(X186:AA186)</f>
         <v>2425</v>
       </c>
     </row>
@@ -32576,98 +32576,98 @@
       <c r="J190" s="81"/>
       <c r="K190" s="81"/>
       <c r="L190" s="81">
-        <f t="shared" ref="L190:L191" si="247">IF(K185=0,
+        <f t="shared" ref="L190:L191" si="248">IF(K185=0,
 IF(L185=0,0,IF(L185&gt;0,1,-1)),
 (L185-K185)/ABS(K185)
 )</f>
         <v>0</v>
       </c>
       <c r="M190" s="81">
-        <f t="shared" ref="M190:M191" si="248">IF(L185=0,
+        <f t="shared" ref="M190:M191" si="249">IF(L185=0,
 IF(M185=0,0,IF(M185&gt;0,1,-1)),
 (M185-L185)/ABS(L185)
 )</f>
         <v>0</v>
       </c>
       <c r="N190" s="81">
-        <f t="shared" ref="N190:N191" si="249">IF(M185=0,
+        <f t="shared" ref="N190:N191" si="250">IF(M185=0,
 IF(N185=0,0,IF(N185&gt;0,1,-1)),
 (N185-M185)/ABS(M185)
 )</f>
         <v>0</v>
       </c>
       <c r="O190" s="81">
-        <f t="shared" ref="O190:O191" si="250">IF(N185=0,
+        <f t="shared" ref="O190:O191" si="251">IF(N185=0,
 IF(O185=0,0,IF(O185&gt;0,1,-1)),
 (O185-N185)/ABS(N185)
 )</f>
         <v>0</v>
       </c>
       <c r="P190" s="81">
-        <f t="shared" ref="P190:P191" si="251">IF(O185=0,
+        <f t="shared" ref="P190:P191" si="252">IF(O185=0,
 IF(P185=0,0,IF(P185&gt;0,1,-1)),
 (P185-O185)/ABS(O185)
 )</f>
         <v>1</v>
       </c>
       <c r="Q190" s="81">
-        <f t="shared" ref="Q190:Q191" si="252">IF(P185=0,
+        <f t="shared" ref="Q190:Q191" si="253">IF(P185=0,
 IF(Q185=0,0,IF(Q185&gt;0,1,-1)),
 (Q185-P185)/ABS(P185)
 )</f>
         <v>0.4377575044143614</v>
       </c>
       <c r="T190" s="81">
-        <f t="shared" ref="T190:T191" si="253">IF(S185=0,
+        <f t="shared" ref="T190:T191" si="254">IF(S185=0,
 IF(T185=0,0,IF(T185&gt;0,1,-1)),
 (T185-S185)/ABS(S185)
 )</f>
         <v>1</v>
       </c>
       <c r="U190" s="81">
-        <f t="shared" ref="U190:U191" si="254">IF(T185=0,
+        <f t="shared" ref="U190:U191" si="255">IF(T185=0,
 IF(U185=0,0,IF(U185&gt;0,1,-1)),
 (U185-T185)/ABS(T185)
 )</f>
         <v>9.7345132743362831E-2</v>
       </c>
       <c r="V190" s="81">
-        <f t="shared" ref="V190:V191" si="255">IF(U185=0,
+        <f t="shared" ref="V190:V191" si="256">IF(U185=0,
 IF(V185=0,0,IF(V185&gt;0,1,-1)),
 (V185-U185)/ABS(U185)
 )</f>
         <v>-6.9700460829493091E-2</v>
       </c>
       <c r="W190" s="81">
-        <f t="shared" ref="W190:W191" si="256">IF(V185=0,
+        <f t="shared" ref="W190:W191" si="257">IF(V185=0,
 IF(W185=0,0,IF(W185&gt;0,1,-1)),
 (W185-V185)/ABS(V185)
 )</f>
         <v>0.15356037151702787</v>
       </c>
       <c r="X190" s="81">
-        <f t="shared" ref="X190:X191" si="257">IF(W185=0,
+        <f t="shared" ref="X190:X191" si="258">IF(W185=0,
 IF(X185=0,0,IF(X185&gt;0,1,-1)),
 (X185-W185)/ABS(W185)
 )</f>
         <v>0.13472893183038109</v>
       </c>
       <c r="Y190" s="81">
-        <f t="shared" ref="Y190:Y191" si="258">IF(X185=0,
+        <f t="shared" ref="Y190:Y191" si="259">IF(X185=0,
 IF(Y185=0,0,IF(Y185&gt;0,1,-1)),
 (Y185-X185)/ABS(X185)
 )</f>
         <v>5.2034058656575212E-2</v>
       </c>
       <c r="Z190" s="81">
-        <f t="shared" ref="Z190:Z191" si="259">IF(Y185=0,
+        <f t="shared" ref="Z190:Z191" si="260">IF(Y185=0,
 IF(Z185=0,0,IF(Z185&gt;0,1,-1)),
 (Z185-Y185)/ABS(Y185)
 )</f>
         <v>0.12410071942446044</v>
       </c>
       <c r="AA190" s="81">
-        <f t="shared" ref="AA190:AA191" si="260">IF(Z185=0,
+        <f t="shared" ref="AA190:AA191" si="261">IF(Z185=0,
 IF(AA185=0,0,IF(AA185&gt;0,1,-1)),
 (AA185-Z185)/ABS(Z185)
 )</f>
@@ -32681,59 +32681,59 @@
         <v>Edge &amp; IoT</v>
       </c>
       <c r="L191" s="81">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0</v>
       </c>
       <c r="M191" s="81">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>0</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v>0</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v>0</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>1</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" si="252"/>
+        <f t="shared" si="253"/>
         <v>5.434782608695652E-2</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>1</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>6.8376068376068376E-3</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>-7.4702886247877756E-2</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>6.6055045871559637E-2</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" si="257"/>
+        <f t="shared" si="258"/>
         <v>-0.11359724612736662</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.16699029126213591</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" si="259"/>
+        <f t="shared" si="260"/>
         <v>1.8302828618968387E-2</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" si="260"/>
+        <f t="shared" si="261"/>
         <v>0.1388888888888889</v>
       </c>
       <c r="AC191" s="49"/>
@@ -32784,30 +32784,30 @@
       <c r="J195" s="81"/>
       <c r="K195" s="81"/>
       <c r="L195" s="81">
-        <f t="shared" ref="L195:Q195" si="261">IF(K63=0,
+        <f t="shared" ref="L195:Q195" si="262">IF(K63=0,
 IF(L63=0,0,IF(L63&gt;0,1,-1)),
 (L63-K63)/K63
 )</f>
         <v>-1</v>
       </c>
       <c r="M195" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>-6.0092449922958396E-2</v>
       </c>
       <c r="N195" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>-4.5901639344262293E-2</v>
       </c>
       <c r="O195" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>5.1546391752577319E-3</v>
       </c>
       <c r="P195" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>2.564102564102564E-2</v>
       </c>
       <c r="Q195" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>5.6666666666666664E-2</v>
       </c>
       <c r="T195" s="49"/>
@@ -33093,7 +33093,7 @@
         <v>195</v>
       </c>
       <c r="AC206" s="62">
-        <f t="shared" ref="AC206:AC207" si="262">SUM(X206:AA206)</f>
+        <f t="shared" ref="AC206:AC207" si="263">SUM(X206:AA206)</f>
         <v>694.4</v>
       </c>
     </row>
@@ -33153,7 +33153,7 @@
         <v>23</v>
       </c>
       <c r="AC207" s="62">
-        <f t="shared" si="262"/>
+        <f t="shared" si="263"/>
         <v>94</v>
       </c>
     </row>
@@ -33198,19 +33198,19 @@
       <c r="J209" s="62"/>
       <c r="K209" s="62"/>
       <c r="L209" s="63" t="e">
-        <f t="shared" ref="L209:O209" si="263">L185/L206</f>
+        <f t="shared" ref="L209:O209" si="264">L185/L206</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M209" s="63" t="e">
-        <f t="shared" si="263"/>
+        <f t="shared" si="264"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N209" s="63" t="e">
-        <f t="shared" si="263"/>
+        <f t="shared" si="264"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O209" s="63" t="e">
-        <f t="shared" si="263"/>
+        <f t="shared" si="264"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P209" s="63">
@@ -33222,39 +33222,39 @@
         <v>14.058992805755397</v>
       </c>
       <c r="T209" s="63">
-        <f t="shared" ref="T209:Z209" si="264">T185/T206</f>
+        <f t="shared" ref="T209:Z209" si="265">T185/T206</f>
         <v>13.87719298245614</v>
       </c>
       <c r="U209" s="63">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>13.777777777777779</v>
       </c>
       <c r="V209" s="63">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>13.503344481605351</v>
       </c>
       <c r="W209" s="63">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>13.598540145985401</v>
       </c>
       <c r="X209" s="63">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>13.29559748427673</v>
       </c>
       <c r="Y209" s="63">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>13.478787878787879</v>
       </c>
       <c r="Z209" s="63">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>14.253135689851767</v>
       </c>
       <c r="AA209" s="63">
-        <f t="shared" ref="AA209:AC209" si="265">AA185/AA206</f>
+        <f t="shared" ref="AA209:AC209" si="266">AA185/AA206</f>
         <v>15.041025641025641</v>
       </c>
       <c r="AC209" s="63">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v>14.071140552995391</v>
       </c>
     </row>
@@ -33339,15 +33339,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="242"/>
-      <c r="E4" s="242" t="s">
+      <c r="C4" s="245"/>
+      <c r="E4" s="245" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33355,7 +33355,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>217288.71000000002</v>
+        <v>210240.33000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33391,7 +33391,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>219149.71000000002</v>
+        <v>212101.33000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>66.054034582132559</v>
+        <v>63.911383285302591</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33431,7 +33431,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>17.197610701107013</v>
+        <v>16.639757072570728</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>96.040798338717124</v>
+        <v>92.92544070143056</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33471,7 +33471,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>17.970455924559246</v>
+        <v>17.392482984829851</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33480,18 +33480,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>53.529484611626778</v>
+        <v>51.80784807034685</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="242"/>
-      <c r="E15" s="242" t="s">
+      <c r="C15" s="245"/>
+      <c r="E15" s="245" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="242"/>
+      <c r="F15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33542,14 +33542,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="242" t="s">
+      <c r="B21" s="245" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="242"/>
-      <c r="E21" s="242" t="s">
+      <c r="C21" s="245"/>
+      <c r="E21" s="245" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="242"/>
+      <c r="F21" s="245"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33618,14 +33618,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="242" t="s">
+      <c r="B29" s="245" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="242"/>
-      <c r="E29" s="242" t="s">
+      <c r="C29" s="245"/>
+      <c r="E29" s="245" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="242"/>
+      <c r="F29" s="245"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33701,14 +33701,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="245" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="242"/>
-      <c r="E37" s="242" t="s">
+      <c r="C37" s="245"/>
+      <c r="E37" s="245" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="242"/>
+      <c r="F37" s="245"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33716,7 +33716,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.513912066577228E-2</v>
+        <v>1.564666493816862E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -33732,7 +33732,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.3309481196699082E-2</v>
+        <v>1.3755686171154696E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -33748,7 +33748,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.1848870564881162E-3</v>
+        <v>3.2916614999605452E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>8.0998225816702573E-4</v>
+        <v>8.3713719437179335E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33773,18 +33773,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.7277592563368799E-3</v>
+        <v>3.8527336786429128E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="242" t="s">
+      <c r="B45" s="245" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="242"/>
-      <c r="E45" s="242" t="s">
+      <c r="C45" s="245"/>
+      <c r="E45" s="245" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="242"/>
+      <c r="F45" s="245"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33817,18 +33817,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-8.5646419457320166E-3</v>
+        <v>-8.8517745382153835E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="245" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="242"/>
-      <c r="E51" s="242" t="s">
+      <c r="C51" s="245"/>
+      <c r="E51" s="245" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="242"/>
+      <c r="F51" s="245"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>916.83</v>
+        <v>887.09</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34025,7 +34025,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>217288.71000000002</v>
+        <v>210240.33000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34054,7 +34054,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>219149.71000000002</v>
+        <v>212101.33000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34083,7 +34083,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>66.054034582132559</v>
+        <v>63.911383285302591</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>17.197610701107013</v>
+        <v>16.639757072570728</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34141,7 +34141,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>96.040798338717124</v>
+        <v>92.92544070143056</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34170,7 +34170,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>17.970455924559246</v>
+        <v>17.392482984829851</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34199,7 +34199,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>53.529484611626778</v>
+        <v>51.80784807034685</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34972,7 +34972,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.513912066577228E-2</v>
+        <v>1.564666493816862E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35001,7 +35001,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.3309481196699082E-2</v>
+        <v>1.3755686171154696E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35030,7 +35030,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.1848870564881162E-3</v>
+        <v>3.2916614999605452E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>8.0998225816702573E-4</v>
+        <v>8.3713719437179335E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35088,7 +35088,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.7277592563368799E-3</v>
+        <v>3.8527336786429128E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35324,7 +35324,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-8.5646419457320166E-3</v>
+        <v>-8.8517745382153835E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35786,14 +35786,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="248" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35860,19 +35860,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="249">
+      <c r="C7" s="246">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="250"/>
-      <c r="F7" s="249">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="250"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -35899,19 +35899,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="249">
+      <c r="C9" s="246">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="250"/>
-      <c r="F9" s="249">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="250"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -35938,19 +35938,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="249">
+      <c r="C11" s="246">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="F11" s="249">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="250"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -35977,19 +35977,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="249">
+      <c r="C13" s="246">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="250"/>
-      <c r="F13" s="249">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="250"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36016,19 +36016,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="249">
+      <c r="C15" s="246">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="250"/>
-      <c r="F15" s="249">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="250"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36055,19 +36055,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="249">
+      <c r="C17" s="246">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="250"/>
-      <c r="F17" s="249">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="250"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36094,22 +36094,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="250"/>
-      <c r="F19" s="249">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="250"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36136,22 +36136,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="249">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="F21" s="249">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="250"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36200,22 +36200,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="249">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="250"/>
-      <c r="F25" s="249">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="250"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36243,25 +36243,37 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="249">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="250"/>
-      <c r="F27" s="249">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="250"/>
+      <c r="G27" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36272,18 +36284,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C34A69-959C-BE46-9A07-DE601F7E0470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E389723-900C-6647-9A4A-78C8F6036E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2411,12 +2411,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2424,6 +2418,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2444,14 +2444,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12638,11 +12638,11 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>209</v>
-    <v>2.1294</v>
-    <v>38.1</v>
-    <v>4.4877E-2</v>
-    <v>-1.08</v>
-    <v>-1.217E-3</v>
+    <v>2.1074999999999999</v>
+    <v>8.1750000000000007</v>
+    <v>1.0551E-2</v>
+    <v>-1.44</v>
+    <v>-1.8390000000000001E-3</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12650,25 +12650,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>903</v>
+    <v>789.59</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46300.894407117972</v>
+    <v>46304.999813657028</v>
     <v>0</v>
-    <v>875</v>
-    <v>203179891981</v>
+    <v>766.09</v>
+    <v>179339024700</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>876</v>
-    <v>63.801499999999997</v>
-    <v>848.99</v>
-    <v>887.09</v>
-    <v>886.01</v>
+    <v>784.16</v>
+    <v>55.726999999999997</v>
+    <v>774.82500000000005</v>
+    <v>783</v>
+    <v>781.56</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>5585185</v>
-    <v>4012182</v>
+    <v>3925559</v>
+    <v>4452952</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -12690,19 +12690,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12924,9 +12924,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>210240.33000000002</v>
+        <v>185571</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>132.17834199816471</v>
+        <v>133.61475963954348</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>212101.33000000002</v>
+        <v>187432</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>210.43934123311055</v>
+        <v>211.65294555265203</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>145.39237984946135</v>
+        <v>146.22784814424364</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13594,14 +13594,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>886.01</v>
+        <v>781.56</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>63.911383285302591</v>
+        <v>56.41210374639769</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>225.43558658156454</v>
+        <v>226.7483527374697</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13618,14 +13618,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>38.1</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>16.639757072570728</v>
+        <v>14.687269372693727</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>216.68876753496247</v>
+        <v>217.94369583753516</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13642,14 +13642,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.08</v>
+        <v>-1.44</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.3755686171154696E-2</v>
+        <v>1.5584331603537191E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>186.02688343945272</v>
+        <v>187.23752038228881</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13666,14 +13666,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.4877E-2</v>
+        <v>1.0551E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>1.564666493816862E-2</v>
+        <v>1.772669220945083E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.79029536637832387</v>
+        <v>-0.76087162147855836</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13690,14 +13690,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.217E-3</v>
+        <v>-1.8390000000000001E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>8.3713719437179335E-4</v>
+        <v>9.4842405332729788E-4</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13713,14 +13713,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>3.2916614999605452E-3</v>
+        <v>3.7292464878671775E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.388520370471173</v>
+        <v>23.63025672251576</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1294</v>
+        <v>2.1074999999999999</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="I13" s="209">
         <f>'Reverse DCF'!C17</f>
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4012182</v>
+        <v>4452952</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-8.8517745382153835E-3</v>
+        <v>-1.0028506609330122E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18258,12 +18258,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18271,6 +18265,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19330,16 +19330,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>210240.33000000002</v>
+        <v>185571</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1294</v>
+        <v>2.1074999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.6674046432799405E-2</v>
+        <v>1.8848870653920987E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98332595356720054</v>
+        <v>0.98115112934607907</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.148593</v>
+        <v>0.14727750000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14690570321932572</v>
+        <v>0.14539492192126302</v>
       </c>
     </row>
   </sheetData>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>29853.633676182126</v>
+        <v>30199.523767396149</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19842,23 +19842,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3777.4362996154919</v>
+        <v>3782.4187558904941</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4616.0573057824331</v>
+        <v>4628.2425393421718</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4381.2041859152223</v>
+        <v>4398.5635497612438</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3413.6892760007327</v>
+        <v>3431.735630569794</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1955.0423476258457</v>
+        <v>1967.9699561608309</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19877,7 +19877,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15043.837638625319</v>
+        <v>15318.767602847271</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14690570321932572</v>
+        <v>0.14539492192126302</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -19915,7 +19915,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18143.429414939725</v>
+        <v>18208.930431724533</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15043.837638625319</v>
+        <v>15318.767602847271</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33187.26705356504</v>
+        <v>33527.698034571804</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31326.26705356504</v>
+        <v>31666.698034571804</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>132.17834199816471</v>
+        <v>133.61475963954348</v>
       </c>
     </row>
   </sheetData>
@@ -20247,23 +20247,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3777.4362996154919</v>
+        <v>3782.4187558904941</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4616.0573057824331</v>
+        <v>4628.2425393421718</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4381.2041859152223</v>
+        <v>4398.5635497612438</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3413.6892760007327</v>
+        <v>3431.735630569794</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1955.0423476258457</v>
+        <v>1967.9699561608309</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14690570321932572</v>
+        <v>0.14539492192126302</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35546.736804933324</v>
+        <v>35781.787620414827</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>51735.123872247204</v>
+        <v>52022.748095978532</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>49874.123872247204</v>
+        <v>50161.748095978532</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>210.43934123311055</v>
+        <v>211.65294555265203</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.148593</v>
+        <v>0.14727750000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>145.39237984946135</v>
+        <v>146.22784814424364</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21212,7 +21212,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14690570321932572</v>
+        <v>0.14539492192126302</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39100.846952516913</v>
+        <v>39359.399123216615</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21247,7 +21247,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55289.234019830794</v>
+        <v>55600.35959878032</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53428.234019830794</v>
+        <v>53739.35959878032</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21292,7 +21292,7 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>225.43558658156454</v>
+        <v>226.7483527374697</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14690570321932572</v>
+        <v>0.14539492192126302</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37027.850838472223</v>
+        <v>37272.695437932125</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53216.237905786104</v>
+        <v>53513.65591349583</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51355.237905786104</v>
+        <v>51652.65591349583</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21396,22 +21396,22 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>216.68876753496247</v>
+        <v>217.94369583753516</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>132.17834199816471</v>
+        <v>133.61475963954348</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>210.43934123311055</v>
+        <v>211.65294555265203</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>145.39237984946135</v>
+        <v>146.22784814424364</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>225.43558658156454</v>
+        <v>226.7483527374697</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21497,7 +21497,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>216.68876753496247</v>
+        <v>217.94369583753516</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>186.02688343945272</v>
+        <v>187.23752038228881</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.79029536637832387</v>
+        <v>-0.76087162147855836</v>
       </c>
     </row>
   </sheetData>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.148593</v>
+        <v>0.14727750000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.388520370471173</v>
+        <v>23.63025672251576</v>
       </c>
     </row>
   </sheetData>
@@ -22200,23 +22200,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>5113.7968997289972</v>
+        <v>4959.7668726287257</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>8488.9028535501366</v>
+        <v>7985.2246649322478</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>14091.578736893229</v>
+        <v>12856.211710540918</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>23392.020703242761</v>
+        <v>20698.500853970876</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>38830.754367382986</v>
+        <v>33324.586374893108</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22248,7 +22248,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>298798.41978750192</v>
+        <v>259400.09528086442</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22302,23 +22302,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4458.7771125165227</v>
+        <v>4330.1806020837867</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6453.5122512700664</v>
+        <v>6086.6262246569822</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9340.6374273296897</v>
+        <v>8555.5366399392678</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13519.383577781491</v>
+        <v>12025.908031089648</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>19567.586660457651</v>
+        <v>16903.961733632779</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22337,15 +22337,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>150570.44521676627</v>
+        <v>131581.20659021966</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="257" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="258"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>890.08520813269467</v>
+        <v>782.47762035956896</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22370,22 +22370,22 @@
         <v>323</v>
       </c>
       <c r="C17" s="156">
-        <v>0.66</v>
-      </c>
-      <c r="E17" s="257" t="s">
+        <v>0.61</v>
+      </c>
+      <c r="E17" s="259" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="257" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="258"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14690570321932572</v>
+        <v>0.14539492192126302</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22419,7 +22419,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>201369.43</v>
+        <v>177741</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22446,15 +22446,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>203230.43</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="257" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="258"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22462,7 +22462,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>53339.897029355423</v>
+        <v>47902.213231402464</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>150570.44521676627</v>
+        <v>131581.20659021966</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>203910.3422461217</v>
+        <v>179483.41982162214</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>202049.3422461217</v>
+        <v>177622.41982162214</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22525,21 +22525,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>890.08520813269467</v>
+        <v>782.47762035956896</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29319,7 +29319,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30762,7 +30762,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>63.911383285302591</v>
+        <v>56.41210374639769</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30803,7 +30803,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>16.639757072570728</v>
+        <v>14.687269372693727</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30868,7 +30868,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>92.92544070143056</v>
+        <v>82.021688970927556</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30933,7 +30933,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>210240.33000000002</v>
+        <v>185571</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>212101.33000000002</v>
+        <v>187432</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31039,7 +31039,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>17.392482984829851</v>
+        <v>15.369577695776957</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31080,7 +31080,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>51.80784807034685</v>
+        <v>45.782120175867121</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31227,7 +31227,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>72.697209543568476</v>
+        <v>64.16701244813278</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31268,7 +31268,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>68.850643602732589</v>
+        <v>60.842682277133171</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31309,7 +31309,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.3755686171154696E-2</v>
+        <v>1.5584331603537191E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31350,7 +31350,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.564666493816862E-2</v>
+        <v>1.772669220945083E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31391,7 +31391,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>3.2916614999605452E-3</v>
+        <v>3.7292464878671775E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31432,7 +31432,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>8.3713719437179335E-4</v>
+        <v>9.4842405332729788E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31473,7 +31473,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>3.8527336786429128E-3</v>
+        <v>4.3649061545176782E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32020,7 +32020,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-8.8517745382153835E-3</v>
+        <v>-1.0028506609330122E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33355,7 +33355,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>210240.33000000002</v>
+        <v>185571</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33391,7 +33391,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>212101.33000000002</v>
+        <v>187432</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>63.911383285302591</v>
+        <v>56.41210374639769</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33431,7 +33431,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>16.639757072570728</v>
+        <v>14.687269372693727</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>92.92544070143056</v>
+        <v>82.021688970927556</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33471,7 +33471,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>17.392482984829851</v>
+        <v>15.369577695776957</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33480,7 +33480,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>51.80784807034685</v>
+        <v>45.782120175867121</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33716,7 +33716,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.564666493816862E-2</v>
+        <v>1.772669220945083E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -33732,7 +33732,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.3755686171154696E-2</v>
+        <v>1.5584331603537191E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -33748,7 +33748,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.2916614999605452E-3</v>
+        <v>3.7292464878671775E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>8.3713719437179335E-4</v>
+        <v>9.4842405332729788E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.8527336786429128E-3</v>
+        <v>4.3649061545176782E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33817,7 +33817,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-8.8517745382153835E-3</v>
+        <v>-1.0028506609330122E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>887.09</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34025,7 +34025,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>210240.33000000002</v>
+        <v>185571</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34054,7 +34054,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>212101.33000000002</v>
+        <v>187432</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34083,7 +34083,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>63.911383285302591</v>
+        <v>56.41210374639769</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>16.639757072570728</v>
+        <v>14.687269372693727</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34141,7 +34141,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>92.92544070143056</v>
+        <v>82.021688970927556</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34170,7 +34170,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>17.392482984829851</v>
+        <v>15.369577695776957</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34199,7 +34199,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>51.80784807034685</v>
+        <v>45.782120175867121</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34972,7 +34972,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.564666493816862E-2</v>
+        <v>1.772669220945083E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35001,7 +35001,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.3755686171154696E-2</v>
+        <v>1.5584331603537191E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35030,7 +35030,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.2916614999605452E-3</v>
+        <v>3.7292464878671775E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>8.3713719437179335E-4</v>
+        <v>9.4842405332729788E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35088,7 +35088,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.8527336786429128E-3</v>
+        <v>4.3649061545176782E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35324,7 +35324,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-8.8517745382153835E-3</v>
+        <v>-1.0028506609330122E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35786,14 +35786,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="F3" s="250" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="249"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35860,19 +35860,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="249">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -35899,19 +35899,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="249">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -35938,19 +35938,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="249">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -35977,19 +35977,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="249">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36016,19 +36016,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="249">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36055,19 +36055,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="249">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36094,22 +36094,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36136,22 +36136,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36200,22 +36200,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36243,37 +36243,25 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36284,6 +36272,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E389723-900C-6647-9A4A-78C8F6036E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69874247-61DE-974E-941E-974304C9D902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="440">
   <si>
     <t>Ticker</t>
   </si>
@@ -1466,6 +1466,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1507,7 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1649,6 +1673,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2072,11 +2104,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2399,6 +2432,14 @@
     <xf numFmtId="38" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2411,6 +2452,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2418,12 +2465,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2444,17 +2485,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12639,10 +12681,10 @@
     <v>1145</v>
     <v>209</v>
     <v>2.1074999999999999</v>
-    <v>8.1750000000000007</v>
-    <v>1.0551E-2</v>
-    <v>-1.44</v>
-    <v>-1.8390000000000001E-3</v>
+    <v>-29.75</v>
+    <v>-3.7995000000000001E-2</v>
+    <v>-0.75</v>
+    <v>-9.9569999999999997E-4</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12650,25 +12692,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>789.59</v>
+    <v>770</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46304.999813657028</v>
+    <v>46307.863929385938</v>
     <v>0</v>
-    <v>766.09</v>
-    <v>179339024700</v>
+    <v>750.678</v>
+    <v>172525057925</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>784.16</v>
-    <v>55.726999999999997</v>
-    <v>774.82500000000005</v>
+    <v>767</v>
+    <v>54.175400000000003</v>
     <v>783</v>
-    <v>781.56</v>
+    <v>753.25</v>
+    <v>752.5</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>3925559</v>
-    <v>4452952</v>
+    <v>4073019</v>
+    <v>4491188</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -12924,9 +12966,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13486,7 +13528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I75"/>
+  <dimension ref="B1:K75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13498,25 +13540,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="242" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="243"/>
-      <c r="E2" s="242" t="s">
+      <c r="C2" s="247"/>
+      <c r="E2" s="246" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="243"/>
-      <c r="H2" s="242" t="s">
+      <c r="F2" s="247"/>
+      <c r="H2" s="246" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="243"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="247"/>
+      <c r="K2" s="132" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
         <v>11</v>
       </c>
@@ -13529,7 +13576,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>185571</v>
+        <v>178520.25</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13537,10 +13584,13 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>133.61475963954348</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+        <v>133.68487440491052</v>
+      </c>
+      <c r="K3" s="244" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="181" t="s">
         <v>0</v>
       </c>
@@ -13553,7 +13603,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>187432</v>
+        <v>180381.25</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13561,16 +13611,19 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>211.65294555265203</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+        <v>211.71173167457522</v>
+      </c>
+      <c r="K4" s="244" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="181" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13587,21 +13640,24 @@
         <f ca="1">'AVG target price'!C7</f>
         <v>146.22784814424364</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="244" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>781.56</v>
+        <v>752.5</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>56.41210374639769</v>
+        <v>54.268731988472616</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13609,23 +13665,26 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>226.7483527374697</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+        <v>226.81194344631837</v>
+      </c>
+      <c r="K6" s="245" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="181" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>8.1750000000000007</v>
+        <v>-29.75</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>14.687269372693727</v>
+        <v>14.129228167281674</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13633,23 +13692,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>217.94369583753516</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+        <v>218.00448418809651</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.44</v>
+        <v>-0.75</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.5584331603537191E-2</v>
+        <v>1.6199842874967965E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13657,23 +13716,23 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>187.23752038228881</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+        <v>187.28817637162885</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="181" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.0551E-2</v>
+        <v>-3.7995000000000001E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>1.772669220945083E-2</v>
+        <v>1.8426817125788253E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13681,26 +13740,26 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.76087162147855836</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-0.7513598720589062</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.8390000000000001E-3</v>
+        <v>-9.9569999999999997E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>9.4842405332729788E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>9.8588255393995921E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="181" t="s">
         <v>7</v>
       </c>
@@ -13713,7 +13772,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>3.7292464878671775E-3</v>
+        <v>3.8765350149352804E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
@@ -13723,7 +13782,7 @@
         <v>23.63025672251576</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="181" t="s">
         <v>8</v>
       </c>
@@ -13739,7 +13798,7 @@
         <v>0.31929402326514245</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="181" t="s">
         <v>9</v>
       </c>
@@ -13762,13 +13821,13 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="182" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4452952</v>
+        <v>4491188</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13778,16 +13837,16 @@
         <v>0.87701105809469215</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="181" t="s">
         <v>289</v>
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-1.0028506609330122E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-1.0424587686831046E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="182" t="s">
         <v>294</v>
       </c>
@@ -13795,12 +13854,16 @@
         <f>Statement!AC173</f>
         <v>-8.1982378854625555</v>
       </c>
+      <c r="H16" s="246" t="s">
+        <v>432</v>
+      </c>
+      <c r="I16" s="247"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="244" t="s">
+      <c r="B17" s="248" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="244"/>
+      <c r="C17" s="248"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -13808,6 +13871,13 @@
         <f>Statement!AC169</f>
         <v>8.4388185654008432E-3</v>
       </c>
+      <c r="H17" s="181" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="242">
+        <f ca="1">DCF!C15</f>
+        <v>0.14532202426816559</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="180" t="s">
@@ -13823,7 +13893,13 @@
         <f>Statement!AC142</f>
         <v>36.179012534437547</v>
       </c>
-      <c r="I18" s="50"/>
+      <c r="H18" s="182" t="s">
+        <v>433</v>
+      </c>
+      <c r="I18" s="243">
+        <f ca="1">Multiples!C54</f>
+        <v>0.14727750000000001</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="180" t="s">
@@ -13873,14 +13949,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="244" t="s">
+      <c r="B25" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="244"/>
-      <c r="E25" s="242" t="s">
+      <c r="C25" s="248"/>
+      <c r="E25" s="246" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="243"/>
+      <c r="F25" s="247"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14164,13 +14240,14 @@
       <c r="H75" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14183,6 +14260,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{C9A0330F-AEB1-8041-B346-9F46F64AF0AE}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{8DA827DE-CD1B-C34D-9ED3-B447BC124A4C}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{EC678545-5E05-A343-9D81-8A31E6DBE3A9}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{827FA968-8C22-8945-B26F-5E75F8B24E34}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14192,18 +14275,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="244" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="244" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="244" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="244" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="245" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{7E2A1D8D-1CDD-1E4F-B51B-E3B8BA9957A6}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{C625FB63-EE93-664B-BF74-E83DD6A6F311}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{69DF3F5D-47B5-5B40-AEE2-A99380EE7ACD}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{3EEDFC26-E5BA-7840-B6FE-F1C7AA1A05B2}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{0F4F0629-A024-8043-AE13-C4547026861D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14240,36 +14362,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="245" t="s">
+      <c r="S2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245"/>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
-      <c r="AA2" s="245" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="245"/>
-      <c r="AC2" s="245"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14280,32 +14402,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="252" t="s">
+      <c r="S4" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
+      <c r="AA4" s="257"/>
+      <c r="AB4" s="257"/>
+      <c r="AC4" s="257"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14696,33 +14818,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="251" t="s">
+      <c r="C10" s="255" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="251"/>
-      <c r="L10" s="251"/>
+      <c r="D10" s="255"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="255"/>
+      <c r="J10" s="255"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="255"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="252" t="s">
+      <c r="S10" s="256" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="253"/>
-      <c r="U10" s="253"/>
-      <c r="V10" s="253"/>
-      <c r="W10" s="253"/>
-      <c r="X10" s="253"/>
-      <c r="Y10" s="253"/>
-      <c r="Z10" s="253"/>
-      <c r="AA10" s="253"/>
-      <c r="AB10" s="253"/>
-      <c r="AC10" s="253"/>
+      <c r="T10" s="257"/>
+      <c r="U10" s="257"/>
+      <c r="V10" s="257"/>
+      <c r="W10" s="257"/>
+      <c r="X10" s="257"/>
+      <c r="Y10" s="257"/>
+      <c r="Z10" s="257"/>
+      <c r="AA10" s="257"/>
+      <c r="AB10" s="257"/>
+      <c r="AC10" s="257"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -15075,32 +15197,32 @@
     <row r="17" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="86"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="251" t="s">
+      <c r="C17" s="255" t="s">
         <v>395</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="255"/>
+      <c r="K17" s="255"/>
+      <c r="L17" s="255"/>
       <c r="O17" s="5"/>
-      <c r="S17" s="252" t="s">
+      <c r="S17" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="T17" s="253"/>
-      <c r="U17" s="253"/>
-      <c r="V17" s="253"/>
-      <c r="W17" s="253"/>
-      <c r="X17" s="253"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
-      <c r="AA17" s="253"/>
-      <c r="AB17" s="253"/>
-      <c r="AC17" s="253"/>
+      <c r="T17" s="257"/>
+      <c r="U17" s="257"/>
+      <c r="V17" s="257"/>
+      <c r="W17" s="257"/>
+      <c r="X17" s="257"/>
+      <c r="Y17" s="257"/>
+      <c r="Z17" s="257"/>
+      <c r="AA17" s="257"/>
+      <c r="AB17" s="257"/>
+      <c r="AC17" s="257"/>
       <c r="AE17" s="87"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -15592,35 +15714,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
-      <c r="P2" s="245" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="245"/>
-      <c r="R2" s="245"/>
-      <c r="S2" s="245"/>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15629,31 +15751,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="P4" s="253" t="s">
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="P4" s="257" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="253"/>
-      <c r="R4" s="253"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
+      <c r="Q4" s="257"/>
+      <c r="R4" s="257"/>
+      <c r="S4" s="257"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -15848,32 +15970,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="251" t="s">
+      <c r="C9" s="255" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="253" t="s">
+      <c r="P9" s="257" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="253"/>
-      <c r="R9" s="253"/>
-      <c r="S9" s="253"/>
-      <c r="T9" s="253"/>
-      <c r="U9" s="253"/>
-      <c r="V9" s="253"/>
-      <c r="W9" s="253"/>
-      <c r="X9" s="253"/>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
+      <c r="Q9" s="257"/>
+      <c r="R9" s="257"/>
+      <c r="S9" s="257"/>
+      <c r="T9" s="257"/>
+      <c r="U9" s="257"/>
+      <c r="V9" s="257"/>
+      <c r="W9" s="257"/>
+      <c r="X9" s="257"/>
+      <c r="Y9" s="257"/>
+      <c r="Z9" s="257"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16350,31 +16472,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="251" t="s">
+      <c r="C17" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
-      <c r="P17" s="253" t="s">
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="255"/>
+      <c r="K17" s="255"/>
+      <c r="L17" s="255"/>
+      <c r="P17" s="257" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="253"/>
-      <c r="R17" s="253"/>
-      <c r="S17" s="253"/>
-      <c r="T17" s="253"/>
-      <c r="U17" s="253"/>
-      <c r="V17" s="253"/>
-      <c r="W17" s="253"/>
-      <c r="X17" s="253"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
+      <c r="Q17" s="257"/>
+      <c r="R17" s="257"/>
+      <c r="S17" s="257"/>
+      <c r="T17" s="257"/>
+      <c r="U17" s="257"/>
+      <c r="V17" s="257"/>
+      <c r="W17" s="257"/>
+      <c r="X17" s="257"/>
+      <c r="Y17" s="257"/>
+      <c r="Z17" s="257"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16852,60 +16974,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="245"/>
-      <c r="J3" s="245"/>
-      <c r="K3" s="245"/>
-      <c r="L3" s="245"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="256"/>
-      <c r="S3" s="256"/>
-      <c r="T3" s="256"/>
-      <c r="U3" s="256"/>
-      <c r="V3" s="256"/>
-      <c r="W3" s="256"/>
-      <c r="X3" s="256"/>
-      <c r="Y3" s="256"/>
-      <c r="Z3" s="256"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
-      <c r="P5" s="256"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="256"/>
-      <c r="S5" s="256"/>
-      <c r="T5" s="256"/>
-      <c r="U5" s="256"/>
-      <c r="V5" s="256"/>
-      <c r="W5" s="256"/>
-      <c r="X5" s="256"/>
-      <c r="Y5" s="256"/>
-      <c r="Z5" s="256"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17091,30 +17213,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="255" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="256"/>
-      <c r="Q11" s="256"/>
-      <c r="R11" s="256"/>
-      <c r="S11" s="256"/>
-      <c r="T11" s="256"/>
-      <c r="U11" s="256"/>
-      <c r="V11" s="256"/>
-      <c r="W11" s="256"/>
-      <c r="X11" s="256"/>
-      <c r="Y11" s="256"/>
-      <c r="Z11" s="256"/>
+      <c r="P11" s="260"/>
+      <c r="Q11" s="260"/>
+      <c r="R11" s="260"/>
+      <c r="S11" s="260"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="260"/>
+      <c r="W11" s="260"/>
+      <c r="X11" s="260"/>
+      <c r="Y11" s="260"/>
+      <c r="Z11" s="260"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17356,18 +17478,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="251" t="s">
+      <c r="C18" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17580,23 +17702,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="256"/>
-      <c r="C25" s="256"/>
+      <c r="B25" s="260"/>
+      <c r="C25" s="260"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="251" t="s">
+      <c r="C26" s="255" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="251"/>
-      <c r="E26" s="251"/>
-      <c r="F26" s="251"/>
-      <c r="G26" s="251"/>
-      <c r="H26" s="251"/>
-      <c r="I26" s="251"/>
-      <c r="J26" s="251"/>
-      <c r="K26" s="251"/>
-      <c r="L26" s="251"/>
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="255"/>
+      <c r="H26" s="255"/>
+      <c r="I26" s="255"/>
+      <c r="J26" s="255"/>
+      <c r="K26" s="255"/>
+      <c r="L26" s="255"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17788,18 +17910,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="251" t="s">
+      <c r="C33" s="255" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="251"/>
-      <c r="E33" s="251"/>
-      <c r="F33" s="251"/>
-      <c r="G33" s="251"/>
-      <c r="H33" s="251"/>
-      <c r="I33" s="251"/>
-      <c r="J33" s="251"/>
-      <c r="K33" s="251"/>
-      <c r="L33" s="251"/>
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="255"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="255"/>
+      <c r="J33" s="255"/>
+      <c r="K33" s="255"/>
+      <c r="L33" s="255"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17983,18 +18105,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="251" t="s">
+      <c r="C40" s="255" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="251"/>
-      <c r="E40" s="251"/>
-      <c r="F40" s="251"/>
-      <c r="G40" s="251"/>
-      <c r="H40" s="251"/>
-      <c r="I40" s="251"/>
-      <c r="J40" s="251"/>
-      <c r="K40" s="251"/>
-      <c r="L40" s="251"/>
+      <c r="D40" s="255"/>
+      <c r="E40" s="255"/>
+      <c r="F40" s="255"/>
+      <c r="G40" s="255"/>
+      <c r="H40" s="255"/>
+      <c r="I40" s="255"/>
+      <c r="J40" s="255"/>
+      <c r="K40" s="255"/>
+      <c r="L40" s="255"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18258,6 +18380,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18265,12 +18393,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18308,60 +18430,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256"/>
-      <c r="AB2" s="256"/>
-      <c r="AC2" s="256"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
+      <c r="AA2" s="260"/>
+      <c r="AB2" s="260"/>
+      <c r="AC2" s="260"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="S4" s="256"/>
-      <c r="T4" s="256"/>
-      <c r="U4" s="256"/>
-      <c r="V4" s="256"/>
-      <c r="W4" s="256"/>
-      <c r="X4" s="256"/>
-      <c r="Y4" s="256"/>
-      <c r="Z4" s="256"/>
-      <c r="AA4" s="256"/>
-      <c r="AB4" s="256"/>
-      <c r="AC4" s="256"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18724,18 +18846,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="251" t="s">
+      <c r="C13" s="255" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="E13" s="251"/>
-      <c r="F13" s="251"/>
-      <c r="G13" s="251"/>
-      <c r="H13" s="251"/>
-      <c r="I13" s="251"/>
-      <c r="J13" s="251"/>
-      <c r="K13" s="251"/>
-      <c r="L13" s="251"/>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="255"/>
+      <c r="G13" s="255"/>
+      <c r="H13" s="255"/>
+      <c r="I13" s="255"/>
+      <c r="J13" s="255"/>
+      <c r="K13" s="255"/>
+      <c r="L13" s="255"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18828,18 +18950,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="251" t="s">
+      <c r="C18" s="255" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19031,18 +19153,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="251" t="s">
+      <c r="C25" s="255" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="251"/>
-      <c r="G25" s="251"/>
-      <c r="H25" s="251"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="251"/>
-      <c r="K25" s="251"/>
-      <c r="L25" s="251"/>
+      <c r="D25" s="255"/>
+      <c r="E25" s="255"/>
+      <c r="F25" s="255"/>
+      <c r="G25" s="255"/>
+      <c r="H25" s="255"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="255"/>
+      <c r="K25" s="255"/>
+      <c r="L25" s="255"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19180,18 +19302,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="251" t="s">
+      <c r="C31" s="255" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="251"/>
-      <c r="E31" s="251"/>
-      <c r="F31" s="251"/>
-      <c r="G31" s="251"/>
-      <c r="H31" s="251"/>
-      <c r="I31" s="251"/>
-      <c r="J31" s="251"/>
-      <c r="K31" s="251"/>
-      <c r="L31" s="251"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="255"/>
+      <c r="G31" s="255"/>
+      <c r="H31" s="255"/>
+      <c r="I31" s="255"/>
+      <c r="J31" s="255"/>
+      <c r="K31" s="255"/>
+      <c r="L31" s="255"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19330,16 +19452,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19353,18 +19475,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="244" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="244" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="244" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="244" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="245" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>163</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{49A696FB-E039-DA4B-881E-86EEEEE6C609}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{C3CCB56E-2AEE-8949-BD10-EF263C026A35}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{C8C05393-7849-D247-B056-022C9E876583}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{9BB8D394-56D3-A343-9E64-0ADE70E8655D}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{0B03BB47-2A50-8D4E-8BB1-0258E1F908FD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19402,10 +19563,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="245" t="s">
+      <c r="B4" s="249" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="245"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19422,7 +19583,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19431,7 +19592,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>185571</v>
+        <v>178520.25</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19490,10 +19651,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="245" t="s">
+      <c r="B15" s="249" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="245"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19501,7 +19662,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.8848870653920987E-2</v>
+        <v>1.9578741276407616E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19510,7 +19671,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98115112934607907</v>
+        <v>0.98042125872359243</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19537,7 +19698,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14539492192126302</v>
+        <v>0.14532202426816559</v>
       </c>
     </row>
   </sheetData>
@@ -19582,60 +19743,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="245"/>
-      <c r="J3" s="245"/>
-      <c r="K3" s="245"/>
-      <c r="L3" s="245"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="256"/>
-      <c r="S3" s="256"/>
-      <c r="T3" s="256"/>
-      <c r="U3" s="256"/>
-      <c r="V3" s="256"/>
-      <c r="W3" s="256"/>
-      <c r="X3" s="256"/>
-      <c r="Y3" s="256"/>
-      <c r="Z3" s="256"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="255" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
-      <c r="P5" s="256"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="256"/>
-      <c r="S5" s="256"/>
-      <c r="T5" s="256"/>
-      <c r="U5" s="256"/>
-      <c r="V5" s="256"/>
-      <c r="W5" s="256"/>
-      <c r="X5" s="256"/>
-      <c r="Y5" s="256"/>
-      <c r="Z5" s="256"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19788,7 +19949,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30199.523767396149</v>
+        <v>30216.416341154618</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -19842,23 +20003,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3782.4187558904941</v>
+        <v>3782.659499929719</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4628.2425393421718</v>
+        <v>4628.8317164452037</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4398.5635497612438</v>
+        <v>4399.403484806272</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3431.735630569794</v>
+        <v>3432.6094087844576</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1967.9699561608309</v>
+        <v>1968.5963243405902</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -19877,14 +20038,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15318.767602847271</v>
+        <v>15332.21479965755</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="245" t="s">
+      <c r="B13" s="249" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="245"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19900,14 +20061,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14539492192126302</v>
+        <v>0.14532202426816559</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="245" t="s">
+      <c r="B18" s="249" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="245"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19915,7 +20076,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18208.930431724533</v>
+        <v>18212.100434306241</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19924,7 +20085,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15318.767602847271</v>
+        <v>15332.21479965755</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19933,7 +20094,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33527.698034571804</v>
+        <v>33544.315233963789</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19960,7 +20121,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31666.698034571804</v>
+        <v>31683.315233963789</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19978,7 +20139,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>133.61475963954348</v>
+        <v>133.68487440491052</v>
       </c>
     </row>
   </sheetData>
@@ -20021,37 +20182,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="255" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20247,23 +20408,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3782.4187558904941</v>
+        <v>3782.659499929719</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4628.2425393421718</v>
+        <v>4628.8317164452037</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4398.5635497612438</v>
+        <v>4399.403484806272</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3431.735630569794</v>
+        <v>3432.6094087844576</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1967.9699561608309</v>
+        <v>1968.5963243405902</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20271,18 +20432,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="255" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20476,18 +20637,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="251" t="s">
+      <c r="C17" s="255" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="255"/>
+      <c r="K17" s="255"/>
+      <c r="L17" s="255"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20621,18 +20782,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="251" t="s">
+      <c r="C22" s="255" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="251"/>
-      <c r="E22" s="251"/>
-      <c r="F22" s="251"/>
-      <c r="G22" s="251"/>
-      <c r="H22" s="251"/>
-      <c r="I22" s="251"/>
-      <c r="J22" s="251"/>
-      <c r="K22" s="251"/>
-      <c r="L22" s="251"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="255"/>
+      <c r="F22" s="255"/>
+      <c r="G22" s="255"/>
+      <c r="H22" s="255"/>
+      <c r="I22" s="255"/>
+      <c r="J22" s="255"/>
+      <c r="K22" s="255"/>
+      <c r="L22" s="255"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20716,18 +20877,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="251" t="s">
+      <c r="C27" s="255" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="251"/>
-      <c r="G27" s="251"/>
-      <c r="H27" s="251"/>
-      <c r="I27" s="251"/>
-      <c r="J27" s="251"/>
-      <c r="K27" s="251"/>
-      <c r="L27" s="251"/>
+      <c r="D27" s="255"/>
+      <c r="E27" s="255"/>
+      <c r="F27" s="255"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="255"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="255"/>
+      <c r="K27" s="255"/>
+      <c r="L27" s="255"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21028,10 +21189,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="245" t="s">
+      <c r="B39" s="249" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="245"/>
+      <c r="C39" s="249"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21049,7 +21210,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14539492192126302</v>
+        <v>0.14532202426816559</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21075,7 +21236,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35781.787620414827</v>
+        <v>35793.176296908678</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21084,7 +21245,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>52022.748095978532</v>
+        <v>52036.680406874329</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21111,7 +21272,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50161.748095978532</v>
+        <v>50175.680406874329</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21129,14 +21290,14 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>211.65294555265203</v>
+        <v>211.71173167457522</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="245" t="s">
+      <c r="B52" s="249" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="245"/>
+      <c r="C52" s="249"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21192,10 +21353,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="245" t="s">
+      <c r="B60" s="249" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="245"/>
+      <c r="C60" s="249"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21212,7 +21373,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14539492192126302</v>
+        <v>0.14532202426816559</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21238,7 +21399,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39359.399123216615</v>
+        <v>39371.926486811804</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21247,7 +21408,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55600.35959878032</v>
+        <v>55615.430596777456</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21274,7 +21435,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53739.35959878032</v>
+        <v>53754.430596777456</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21292,14 +21453,14 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>226.7483527374697</v>
+        <v>226.81194344631837</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="245" t="s">
+      <c r="B73" s="249" t="s">
         <v>428</v>
       </c>
-      <c r="C73" s="245"/>
+      <c r="C73" s="249"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21316,7 +21477,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14539492192126302</v>
+        <v>0.14532202426816559</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21342,7 +21503,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37272.695437932125</v>
+        <v>37284.558642613221</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21351,7 +21512,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53513.65591349583</v>
+        <v>53528.062752578873</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21378,7 +21539,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51652.65591349583</v>
+        <v>51667.062752578873</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21396,22 +21557,22 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>217.94369583753516</v>
+        <v>218.00448418809651</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21449,10 +21610,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="245" t="s">
+      <c r="B4" s="249" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="245"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21461,7 +21622,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>133.61475963954348</v>
+        <v>133.68487440491052</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21470,7 +21631,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>211.65294555265203</v>
+        <v>211.71173167457522</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21488,7 +21649,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>226.7483527374697</v>
+        <v>226.81194344631837</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21497,7 +21658,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>217.94369583753516</v>
+        <v>218.00448418809651</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21506,7 +21667,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>187.23752038228881</v>
+        <v>187.28817637162885</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21515,7 +21676,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21524,7 +21685,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.76087162147855836</v>
+        <v>-0.7513598720589062</v>
       </c>
     </row>
   </sheetData>
@@ -21540,18 +21701,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="244" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="244" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="244" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="244" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="245" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{78DA7ED1-F921-F44A-A294-208CD2D1C067}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{26CDD6BA-06DF-6F4B-ADA9-87A8D1C58344}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{865A684D-6882-9E40-B817-6A42BD68F9AE}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{72181239-CE13-8344-B650-FFA87C48B2DC}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{0A7A90C0-CC97-1C4E-BBA7-7C308D1A3CED}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21580,37 +21780,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="255" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="255" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21723,18 +21923,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="251" t="s">
+      <c r="C9" s="255" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="251"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21855,18 +22055,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="251" t="s">
+      <c r="C14" s="255" t="s">
         <v>365</v>
       </c>
-      <c r="D14" s="251"/>
-      <c r="E14" s="251"/>
-      <c r="F14" s="251"/>
-      <c r="G14" s="251"/>
-      <c r="H14" s="251"/>
-      <c r="I14" s="251"/>
-      <c r="J14" s="251"/>
-      <c r="K14" s="251"/>
-      <c r="L14" s="251"/>
+      <c r="D14" s="255"/>
+      <c r="E14" s="255"/>
+      <c r="F14" s="255"/>
+      <c r="G14" s="255"/>
+      <c r="H14" s="255"/>
+      <c r="I14" s="255"/>
+      <c r="J14" s="255"/>
+      <c r="K14" s="255"/>
+      <c r="L14" s="255"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -21956,10 +22156,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="245" t="s">
+      <c r="B20" s="249" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="245"/>
+      <c r="C20" s="249"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22060,60 +22260,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="255" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="245"/>
-      <c r="J3" s="245"/>
-      <c r="K3" s="245"/>
-      <c r="L3" s="245"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="256"/>
-      <c r="S3" s="256"/>
-      <c r="T3" s="256"/>
-      <c r="U3" s="256"/>
-      <c r="V3" s="256"/>
-      <c r="W3" s="256"/>
-      <c r="X3" s="256"/>
-      <c r="Y3" s="256"/>
-      <c r="Z3" s="256"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="255" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
-      <c r="P5" s="256"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="256"/>
-      <c r="S5" s="256"/>
-      <c r="T5" s="256"/>
-      <c r="U5" s="256"/>
-      <c r="V5" s="256"/>
-      <c r="W5" s="256"/>
-      <c r="X5" s="256"/>
-      <c r="Y5" s="256"/>
-      <c r="Z5" s="256"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22248,7 +22448,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>259400.09528086442</v>
+        <v>259545.19476244025</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22302,23 +22502,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4330.1806020837867</v>
+        <v>4330.4562101631655</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6086.6262246569822</v>
+        <v>6087.4010545790952</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>8555.5366399392678</v>
+        <v>8557.1703767198342</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12025.908031089648</v>
+        <v>12028.970031657382</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>16903.961733632779</v>
+        <v>16909.341949783269</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22337,15 +22537,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>131581.20659021966</v>
+        <v>131696.71185979655</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="257" t="s">
+      <c r="B14" s="262" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="258"/>
+      <c r="C14" s="263"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22353,7 +22553,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22362,7 +22562,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>782.47762035956896</v>
+        <v>783.03546908678095</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22372,20 +22572,20 @@
       <c r="C17" s="156">
         <v>0.61</v>
       </c>
-      <c r="E17" s="259" t="s">
+      <c r="E17" s="261" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="257" t="s">
+      <c r="B19" s="262" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="258"/>
+      <c r="C19" s="263"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22401,7 +22601,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14539492192126302</v>
+        <v>0.14532202426816559</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22419,7 +22619,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>177741</v>
+        <v>170987.75</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22446,15 +22646,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>179602</v>
+        <v>172848.75</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="257" t="s">
+      <c r="B28" s="262" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="258"/>
+      <c r="C28" s="263"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22462,7 +22662,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>47902.213231402464</v>
+        <v>47913.339622902742</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22471,7 +22671,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>131581.20659021966</v>
+        <v>131696.71185979655</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22480,7 +22680,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>179483.41982162214</v>
+        <v>179610.05148269929</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22507,7 +22707,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>177622.41982162214</v>
+        <v>177749.05148269929</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22525,21 +22725,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>782.47762035956896</v>
+        <v>783.03546908678095</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29319,7 +29519,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29393,7 +29593,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30762,7 +30962,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>56.41210374639769</v>
+        <v>54.268731988472616</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30803,7 +31003,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>14.687269372693727</v>
+        <v>14.129228167281674</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30868,7 +31068,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>82.021688970927556</v>
+        <v>78.905283802491923</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30933,7 +31133,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>185571</v>
+        <v>178520.25</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30998,7 +31198,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>187432</v>
+        <v>180381.25</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31039,7 +31239,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>15.369577695776957</v>
+        <v>14.79141041410414</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31080,7 +31280,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>45.782120175867121</v>
+        <v>44.059904738641912</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31227,7 +31427,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>64.16701244813278</v>
+        <v>61.72899377593361</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31268,7 +31468,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>60.842682277133171</v>
+        <v>58.553923996447395</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31309,7 +31509,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.5584331603537191E-2</v>
+        <v>1.6199842874967965E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31350,7 +31550,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.772669220945083E-2</v>
+        <v>1.8426817125788253E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31391,7 +31591,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>3.7292464878671775E-3</v>
+        <v>3.8765350149352804E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31432,7 +31632,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>9.4842405332729788E-4</v>
+        <v>9.8588255393995921E-4</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31473,7 +31673,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>4.3649061545176782E-3</v>
+        <v>4.537300390291858E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32020,7 +32220,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.0028506609330122E-2</v>
+        <v>-1.0424587686831046E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33304,18 +33504,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="244" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="244" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="244" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="244" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="245" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>231</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{251D58DD-32C8-2140-B84C-BE7C425C40AF}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{14CFDF64-2EA4-0442-8B8D-E537BF6B2D37}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{66302CD3-F76E-4D41-8C04-2D48B6B76C30}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{167D24A7-9C93-B24B-92B1-A504314798FB}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{8CE0858A-BEBE-6746-81D0-913C93F9219D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -33339,15 +33578,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="245" t="s">
+      <c r="B4" s="249" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="245"/>
-      <c r="E4" s="245" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33355,7 +33594,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33371,7 +33610,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>185571</v>
+        <v>178520.25</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33391,7 +33630,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>187432</v>
+        <v>180381.25</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33411,7 +33650,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>56.41210374639769</v>
+        <v>54.268731988472616</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33431,7 +33670,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>14.687269372693727</v>
+        <v>14.129228167281674</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33451,7 +33690,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>82.021688970927556</v>
+        <v>78.905283802491923</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33471,7 +33710,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>15.369577695776957</v>
+        <v>14.79141041410414</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33480,18 +33719,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>45.782120175867121</v>
+        <v>44.059904738641912</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="245" t="s">
+      <c r="B15" s="249" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="245"/>
-      <c r="E15" s="245" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="245"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33542,14 +33781,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="245" t="s">
+      <c r="B21" s="249" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="245"/>
-      <c r="E21" s="245" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="245"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33618,14 +33857,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="245" t="s">
+      <c r="B29" s="249" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="245"/>
-      <c r="E29" s="245" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="245"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33701,14 +33940,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="245" t="s">
+      <c r="B37" s="249" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="245"/>
-      <c r="E37" s="245" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="245"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33716,7 +33955,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.772669220945083E-2</v>
+        <v>1.8426817125788253E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -33732,7 +33971,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.5584331603537191E-2</v>
+        <v>1.6199842874967965E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -33748,7 +33987,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.7292464878671775E-3</v>
+        <v>3.8765350149352804E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -33764,7 +34003,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>9.4842405332729788E-4</v>
+        <v>9.8588255393995921E-4</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33773,18 +34012,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>4.3649061545176782E-3</v>
+        <v>4.537300390291858E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="245" t="s">
+      <c r="B45" s="249" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="245"/>
-      <c r="E45" s="245" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="245"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33817,18 +34056,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-1.0028506609330122E-2</v>
+        <v>-1.0424587686831046E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="245" t="s">
+      <c r="B51" s="249" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="245"/>
-      <c r="E51" s="245" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="245"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33996,7 +34235,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>783</v>
+        <v>753.25</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34025,7 +34264,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>185571</v>
+        <v>178520.25</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34054,7 +34293,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>187432</v>
+        <v>180381.25</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34083,7 +34322,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>56.41210374639769</v>
+        <v>54.268731988472616</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34112,7 +34351,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>14.687269372693727</v>
+        <v>14.129228167281674</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34141,7 +34380,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>82.021688970927556</v>
+        <v>78.905283802491923</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34170,7 +34409,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>15.369577695776957</v>
+        <v>14.79141041410414</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34199,7 +34438,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>45.782120175867121</v>
+        <v>44.059904738641912</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34972,7 +35211,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.772669220945083E-2</v>
+        <v>1.8426817125788253E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35001,7 +35240,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.5584331603537191E-2</v>
+        <v>1.6199842874967965E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35030,7 +35269,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.7292464878671775E-3</v>
+        <v>3.8765350149352804E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35059,7 +35298,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>9.4842405332729788E-4</v>
+        <v>9.8588255393995921E-4</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35088,7 +35327,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>4.3649061545176782E-3</v>
+        <v>4.537300390291858E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35324,7 +35563,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.0028506609330122E-2</v>
+        <v>-1.0424587686831046E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35786,14 +36025,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="252" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="253"/>
+      <c r="F3" s="254" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="253"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35860,19 +36099,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="249">
+      <c r="C7" s="250">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="250"/>
-      <c r="F7" s="249">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="250"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -35899,19 +36138,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="249">
+      <c r="C9" s="250">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="250"/>
-      <c r="F9" s="249">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="250"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -35938,19 +36177,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="249">
+      <c r="C11" s="250">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="F11" s="249">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="250"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -35977,19 +36216,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="249">
+      <c r="C13" s="250">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="250"/>
-      <c r="F13" s="249">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="250"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36016,19 +36255,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="249">
+      <c r="C15" s="250">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="250"/>
-      <c r="F15" s="249">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="250"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36055,19 +36294,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="249">
+      <c r="C17" s="250">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="250"/>
-      <c r="F17" s="249">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="250"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36094,22 +36333,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="250"/>
-      <c r="F19" s="249">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="250"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36136,22 +36375,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="249">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="F21" s="249">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="250"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36200,22 +36439,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="249">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="250"/>
-      <c r="F25" s="249">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="250"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36243,25 +36482,37 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="249">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="250"/>
-      <c r="F27" s="249">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="250"/>
+      <c r="G27" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36272,18 +36523,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69874247-61DE-974E-941E-974304C9D902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F40004B-F03F-E745-9B4A-7BA75D0CF613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2452,12 +2452,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2465,6 +2459,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2485,14 +2485,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12680,11 +12680,11 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>209</v>
-    <v>2.1074999999999999</v>
-    <v>-29.75</v>
-    <v>-3.7995000000000001E-2</v>
-    <v>-0.75</v>
-    <v>-9.9569999999999997E-4</v>
+    <v>2.1537000000000002</v>
+    <v>21.8</v>
+    <v>3.4114999999999999E-2</v>
+    <v>0.09</v>
+    <v>1.362E-4</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12692,25 +12692,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>770</v>
+    <v>675.70659999999998</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46307.863929385938</v>
+    <v>46314.919582036717</v>
     <v>0</v>
-    <v>750.678</v>
-    <v>172525057925</v>
+    <v>654.52</v>
+    <v>151352517129</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>767</v>
-    <v>54.175400000000003</v>
-    <v>783</v>
-    <v>753.25</v>
-    <v>752.5</v>
+    <v>665</v>
+    <v>45.9589</v>
+    <v>639.01</v>
+    <v>660.81</v>
+    <v>660.9</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>4073019</v>
-    <v>4491188</v>
+    <v>4127674</v>
+    <v>4841848</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -12734,17 +12734,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>0.09</v>
+    <v>1.769E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>51.33</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>50.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.14</v>
+    <v>50.89</v>
+    <v>50.98</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13528,6 +13528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:K75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -13576,7 +13577,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>178520.25</v>
+        <v>156611.97</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13584,7 +13585,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>133.68487440491052</v>
+        <v>133.36063643452346</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>435</v>
@@ -13603,7 +13604,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>180381.25</v>
+        <v>158472.97</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13611,7 +13612,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>211.71173167457522</v>
+        <v>211.43953054210223</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>436</v>
@@ -13623,7 +13624,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13638,7 +13639,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>146.22784814424364</v>
+        <v>145.83400832217521</v>
       </c>
       <c r="K5" s="244" t="s">
         <v>437</v>
@@ -13650,14 +13651,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>752.5</v>
+        <v>660.9</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>54.268731988472616</v>
+        <v>47.608789625360224</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13665,7 +13666,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>226.81194344631837</v>
+        <v>226.51749630369039</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>438</v>
@@ -13677,14 +13678,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-29.75</v>
+        <v>21.8</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>14.129228167281674</v>
+        <v>12.395267527675276</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13692,7 +13693,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>218.00448418809651</v>
+        <v>217.72301241502359</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13701,14 +13702,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.75</v>
+        <v>0.09</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.6199842874967965E-2</v>
+        <v>1.8466021466941512E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13716,7 +13717,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>187.28817637162885</v>
+        <v>186.97493680350297</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13725,14 +13726,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.7995000000000001E-2</v>
+        <v>3.4114999999999999E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>1.8426817125788253E-2</v>
+        <v>2.100452474992812E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13740,7 +13741,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.7513598720589062</v>
+        <v>-0.71705189569845651</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13749,14 +13750,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-9.9569999999999997E-4</v>
+        <v>1.362E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>9.8588255393995921E-4</v>
+        <v>1.1237966037972705E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13772,14 +13773,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>3.8765350149352804E-3</v>
+        <v>4.4188193277946769E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.63025672251576</v>
+        <v>23.515889801519197</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13804,7 +13805,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1074999999999999</v>
+        <v>2.1537000000000002</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13827,7 +13828,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4491188</v>
+        <v>4841848</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13843,7 +13844,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-1.0424587686831046E-2</v>
+        <v>-1.1882872043560911E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13876,7 +13877,7 @@
       </c>
       <c r="I17" s="242">
         <f ca="1">DCF!C15</f>
-        <v>0.14532202426816559</v>
+        <v>0.14565978630451679</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -13898,7 +13899,7 @@
       </c>
       <c r="I18" s="243">
         <f ca="1">Multiples!C54</f>
-        <v>0.14727750000000001</v>
+        <v>0.14789649999999999</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -13970,7 +13971,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13985,7 +13986,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.0979999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14272,7 +14273,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B54B610-4F16-C34E-B8D9-992F7812B5AD}">
-  <sheetPr>
+  <sheetPr codeName="Sheet10">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -14332,6 +14333,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66282D1-ADA2-D843-8696-3FC058E17FA6}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -15688,6 +15690,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABDC400-6556-6848-BEEB-E2541EF30223}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16943,6 +16946,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECA4AF9-34CA-DC41-86C9-B346AEC194A1}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:AB46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -18380,12 +18384,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18393,6 +18391,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18401,6 +18405,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D0CC1-03C8-8940-8079-159588699646}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:AE34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19452,16 +19457,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19472,7 +19477,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C2FB80D-D3C0-DD46-8304-4441946EF9E3}">
-  <sheetPr>
+  <sheetPr codeName="Sheet15">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -19532,6 +19537,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9236FE7C-2B1B-7C49-B055-001352253955}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19583,7 +19589,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19592,7 +19598,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>178520.25</v>
+        <v>156611.97</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19610,7 +19616,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.0979999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19619,7 +19625,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1074999999999999</v>
+        <v>2.1537000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19662,7 +19668,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.9578741276407616E-2</v>
+        <v>2.2256632773113388E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19671,7 +19677,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98042125872359243</v>
+        <v>0.97774336722688659</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19689,7 +19695,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14727750000000001</v>
+        <v>0.14789649999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19698,7 +19704,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14532202426816559</v>
+        <v>0.14565978630451679</v>
       </c>
     </row>
   </sheetData>
@@ -19712,6 +19718,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE76C87-6799-634E-8DEB-EF0E693AF74F}">
+  <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19949,7 +19956,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30216.416341154618</v>
+        <v>30138.305404321778</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20003,23 +20010,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3782.659499929719</v>
+        <v>3781.5443008184361</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4628.8317164452037</v>
+        <v>4626.1027856074834</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4399.403484806272</v>
+        <v>4395.5135513701534</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3432.6094087844576</v>
+        <v>3428.5632075058943</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1968.5963243405902</v>
+        <v>1965.6961389336327</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20038,7 +20045,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15332.21479965755</v>
+        <v>15270.050850746456</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20061,7 +20068,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14532202426816559</v>
+        <v>0.14565978630451679</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20076,7 +20083,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18212.100434306241</v>
+        <v>18197.419984235599</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20085,7 +20092,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15332.21479965755</v>
+        <v>15270.050850746456</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20094,7 +20101,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33544.315233963789</v>
+        <v>33467.470834982058</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20121,7 +20128,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31683.315233963789</v>
+        <v>31606.470834982058</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20139,7 +20146,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>133.68487440491052</v>
+        <v>133.36063643452346</v>
       </c>
     </row>
   </sheetData>
@@ -20160,6 +20167,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -20408,23 +20416,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3782.659499929719</v>
+        <v>3781.5443008184361</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4628.8317164452037</v>
+        <v>4626.1027856074834</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4399.403484806272</v>
+        <v>4395.5135513701534</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3432.6094087844576</v>
+        <v>3428.5632075058943</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1968.5963243405902</v>
+        <v>1965.6961389336327</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21210,7 +21218,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14532202426816559</v>
+        <v>0.14565978630451679</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21236,7 +21244,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35793.176296908678</v>
+        <v>35740.44489317626</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21245,7 +21253,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>52036.680406874329</v>
+        <v>51972.168738478227</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21272,7 +21280,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50175.680406874329</v>
+        <v>50111.168738478227</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21290,7 +21298,7 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>211.71173167457522</v>
+        <v>211.43953054210223</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21314,7 +21322,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14727750000000001</v>
+        <v>0.14789649999999999</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21349,7 +21357,7 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>146.22784814424364</v>
+        <v>145.83400832217521</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21373,7 +21381,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14532202426816559</v>
+        <v>0.14565978630451679</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21399,7 +21407,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39371.926486811804</v>
+        <v>39313.922778672655</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21408,7 +21416,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55615.430596777456</v>
+        <v>55545.646623974622</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21435,7 +21443,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53754.430596777456</v>
+        <v>53684.646623974622</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21453,7 +21461,7 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>226.81194344631837</v>
+        <v>226.51749630369039</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21477,7 +21485,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14532202426816559</v>
+        <v>0.14565978630451679</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21503,7 +21511,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37284.558642613221</v>
+        <v>37229.630097058624</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21512,7 +21520,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53528.062752578873</v>
+        <v>53461.353942360591</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21539,7 +21547,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51667.062752578873</v>
+        <v>51600.353942360591</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21557,22 +21565,22 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>218.00448418809651</v>
+        <v>217.72301241502359</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21583,6 +21591,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -21622,7 +21631,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>133.68487440491052</v>
+        <v>133.36063643452346</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21631,7 +21640,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>211.71173167457522</v>
+        <v>211.43953054210223</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21640,7 +21649,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>146.22784814424364</v>
+        <v>145.83400832217521</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21649,7 +21658,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>226.81194344631837</v>
+        <v>226.51749630369039</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21658,7 +21667,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>218.00448418809651</v>
+        <v>217.72301241502359</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21667,7 +21676,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>187.28817637162885</v>
+        <v>186.97493680350297</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21676,7 +21685,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21685,7 +21694,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.7513598720589062</v>
+        <v>-0.71705189569845651</v>
       </c>
     </row>
   </sheetData>
@@ -21698,7 +21707,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03335612-A5F6-ED42-8E7B-33A97D1D2D90}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -21758,6 +21767,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B6E4A1-F7CC-5043-8E79-210959816CC1}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -22194,7 +22204,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14727750000000001</v>
+        <v>0.14789649999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22211,7 +22221,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.63025672251576</v>
+        <v>23.515889801519197</v>
       </c>
     </row>
   </sheetData>
@@ -22229,6 +22239,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -22448,7 +22459,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>259545.19476244025</v>
+        <v>258874.2575445894</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22502,23 +22513,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4330.4562101631655</v>
+        <v>4329.1795102865008</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6087.4010545790952</v>
+        <v>6083.8122232114756</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>8557.1703767198342</v>
+        <v>8549.6041638725874</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12028.970031657382</v>
+        <v>12014.790837893786</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>16909.341949783269</v>
+        <v>16884.430683741743</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22537,15 +22548,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>131696.71185979655</v>
+        <v>131162.75197371442</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="262" t="s">
+      <c r="B14" s="261" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="263"/>
+      <c r="C14" s="262"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22553,7 +22564,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22562,7 +22573,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>783.03546908678095</v>
+        <v>780.45625283136792</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22572,20 +22583,20 @@
       <c r="C17" s="156">
         <v>0.61</v>
       </c>
-      <c r="E17" s="261" t="s">
+      <c r="E17" s="263" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="261"/>
-      <c r="G17" s="261"/>
-      <c r="H17" s="261"/>
-      <c r="I17" s="261"/>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="263"/>
+      <c r="I17" s="263"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="262" t="s">
+      <c r="B19" s="261" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="263"/>
+      <c r="C19" s="262"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22601,7 +22612,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14532202426816559</v>
+        <v>0.14565978630451679</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22619,7 +22630,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>170987.75</v>
+        <v>150003.87</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22646,15 +22657,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>172848.75</v>
+        <v>151864.87</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="262" t="s">
+      <c r="B28" s="261" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="263"/>
+      <c r="C28" s="262"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22662,7 +22673,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>47913.339622902742</v>
+        <v>47861.817419006096</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22671,7 +22682,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>131696.71185979655</v>
+        <v>131162.75197371442</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22680,7 +22691,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>179610.05148269929</v>
+        <v>179024.56939272053</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22707,7 +22718,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>177749.05148269929</v>
+        <v>177163.56939272053</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22725,21 +22736,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>783.03546908678095</v>
+        <v>780.45625283136792</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -22749,6 +22760,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AE211"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -29519,7 +29531,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29593,7 +29605,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30962,7 +30974,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>54.268731988472616</v>
+        <v>47.608789625360224</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31003,7 +31015,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>14.129228167281674</v>
+        <v>12.395267527675276</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31068,7 +31080,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>78.905283802491923</v>
+        <v>69.221905860636824</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31133,7 +31145,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>178520.25</v>
+        <v>156611.97</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31198,7 +31210,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>180381.25</v>
+        <v>158472.97</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31239,7 +31251,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>14.79141041410414</v>
+        <v>12.994913489134891</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31280,7 +31292,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>44.059904738641912</v>
+        <v>38.708590620420125</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31427,7 +31439,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>61.72899377593361</v>
+        <v>54.153516597510375</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31468,7 +31480,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>58.553923996447395</v>
+        <v>51.442232720259383</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31509,7 +31521,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.6199842874967965E-2</v>
+        <v>1.8466021466941512E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31550,7 +31562,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>1.8426817125788253E-2</v>
+        <v>2.100452474992812E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31591,7 +31603,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>3.8765350149352804E-3</v>
+        <v>4.4188193277946769E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31632,7 +31644,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>9.8588255393995921E-4</v>
+        <v>1.1237966037972705E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31673,7 +31685,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>4.537300390291858E-3</v>
+        <v>5.1720184606578925E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32220,7 +32232,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.0424587686831046E-2</v>
+        <v>-1.1882872043560911E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33501,7 +33513,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{757210FB-34E3-D04A-8896-321D81878D88}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -33561,6 +33573,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="B1:G54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -33594,7 +33607,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33610,7 +33623,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>178520.25</v>
+        <v>156611.97</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33630,7 +33643,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>180381.25</v>
+        <v>158472.97</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33650,7 +33663,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>54.268731988472616</v>
+        <v>47.608789625360224</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33670,7 +33683,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>14.129228167281674</v>
+        <v>12.395267527675276</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33690,7 +33703,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>78.905283802491923</v>
+        <v>69.221905860636824</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33710,7 +33723,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>14.79141041410414</v>
+        <v>12.994913489134891</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33719,7 +33732,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>44.059904738641912</v>
+        <v>38.708590620420125</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33955,7 +33968,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.8426817125788253E-2</v>
+        <v>2.100452474992812E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -33971,7 +33984,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.6199842874967965E-2</v>
+        <v>1.8466021466941512E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -33987,7 +34000,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.8765350149352804E-3</v>
+        <v>4.4188193277946769E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34003,7 +34016,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>9.8588255393995921E-4</v>
+        <v>1.1237966037972705E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34012,7 +34025,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>4.537300390291858E-3</v>
+        <v>5.1720184606578925E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34056,7 +34069,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-1.0424587686831046E-2</v>
+        <v>-1.1882872043560911E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34136,6 +34149,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="B1:I93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -34235,7 +34249,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>753.25</v>
+        <v>660.81</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34264,7 +34278,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>178520.25</v>
+        <v>156611.97</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34293,7 +34307,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>180381.25</v>
+        <v>158472.97</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34322,7 +34336,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>54.268731988472616</v>
+        <v>47.608789625360224</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34351,7 +34365,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>14.129228167281674</v>
+        <v>12.395267527675276</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34380,7 +34394,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>78.905283802491923</v>
+        <v>69.221905860636824</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34409,7 +34423,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>14.79141041410414</v>
+        <v>12.994913489134891</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34438,7 +34452,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>44.059904738641912</v>
+        <v>38.708590620420125</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35211,7 +35225,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>1.8426817125788253E-2</v>
+        <v>2.100452474992812E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35240,7 +35254,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.6199842874967965E-2</v>
+        <v>1.8466021466941512E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35269,7 +35283,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>3.8765350149352804E-3</v>
+        <v>4.4188193277946769E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35298,7 +35312,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>9.8588255393995921E-4</v>
+        <v>1.1237966037972705E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35327,7 +35341,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>4.537300390291858E-3</v>
+        <v>5.1720184606578925E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35563,7 +35577,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.0424587686831046E-2</v>
+        <v>-1.1882872043560911E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36009,6 +36023,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A593F86-70CC-F54A-91FC-45975067BFCE}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="B1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -36025,14 +36040,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="250" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="F3" s="254" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="253"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36099,19 +36114,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="253">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36138,19 +36153,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="253">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36177,19 +36192,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="253">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36216,19 +36231,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="253">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36255,19 +36270,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="253">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36294,19 +36309,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="253">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36333,22 +36348,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36375,22 +36390,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36439,22 +36454,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36482,37 +36497,25 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36523,6 +36526,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -36533,6 +36548,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59D4CD5-3D15-DF4B-A135-ED758F2E1A8D}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="B55:L72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -37357,6 +37373,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0C9119-3B3B-094C-BA34-9489CF595CBC}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="B55:J65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F40004B-F03F-E745-9B4A-7BA75D0CF613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1020F86A-FA10-8942-B689-E9A1C9EDD4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2452,6 +2482,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2459,12 +2495,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2485,14 +2515,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12661,7 +12691,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12680,11 +12710,9 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>209</v>
-    <v>2.1537000000000002</v>
-    <v>21.8</v>
-    <v>3.4114999999999999E-2</v>
-    <v>0.09</v>
-    <v>1.362E-4</v>
+    <v>2.1414</v>
+    <v>15.955</v>
+    <v>2.4145E-2</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12692,35 +12720,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>675.70659999999998</v>
+    <v>679.8</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46314.919582036717</v>
+    <v>46315.694664108596</v>
     <v>0</v>
-    <v>654.52</v>
-    <v>151352517129</v>
+    <v>642.41999999999996</v>
+    <v>155006864688</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>665</v>
-    <v>45.9589</v>
-    <v>639.01</v>
+    <v>657.17</v>
+    <v>48.674500000000002</v>
     <v>660.81</v>
-    <v>660.9</v>
+    <v>676.76499999999999</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>4127674</v>
-    <v>4841848</v>
+    <v>2232223</v>
+    <v>4841084</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12734,28 +12776,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.09</v>
-    <v>1.769E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>51.33</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>50.67</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.14</v>
-    <v>50.89</v>
+    <v>50.9</v>
     <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12777,8 +12819,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12799,7 +12839,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12809,6 +12848,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12844,7 +12888,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12855,16 +12899,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12958,19 +12999,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13042,9 +13077,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13052,9 +13084,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13577,7 +13606,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>156611.97</v>
+        <v>160393.30499999999</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13585,7 +13614,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>133.36063643452346</v>
+        <v>133.47386617275473</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>435</v>
@@ -13604,7 +13633,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>158472.97</v>
+        <v>162254.30499999999</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13612,7 +13641,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>211.43953054210223</v>
+        <v>211.53468998587189</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>436</v>
@@ -13624,7 +13653,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13639,7 +13668,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>145.83400832217521</v>
+        <v>145.94426947147235</v>
       </c>
       <c r="K5" s="244" t="s">
         <v>437</v>
@@ -13649,16 +13678,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>660.9</v>
+      <c r="C6" s="204" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>47.608789625360224</v>
+        <v>48.758285302593656</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13666,7 +13695,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>226.51749630369039</v>
+        <v>226.62043250032397</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>438</v>
@@ -13678,14 +13707,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>21.8</v>
+        <v>15.955</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>12.395267527675276</v>
+        <v>12.69454643296433</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13693,23 +13722,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>217.72301241502359</v>
+        <v>217.82141268626447</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.09</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.8466021466941512E-2</v>
+        <v>1.8030677776731393E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13717,7 +13746,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>186.97493680350297</v>
+        <v>187.07893416333746</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13726,14 +13755,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.4114999999999999E-2</v>
+        <v>2.4145E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>2.100452474992812E-2</v>
+        <v>2.050933485035426E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13741,23 +13770,23 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.71705189569845651</v>
+        <v>-0.72356883975480779</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.362E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>1.1237966037972705E-3</v>
+        <v>1.0973026586115924E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13773,14 +13802,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>4.4188193277946769E-3</v>
+        <v>4.3146439310543542E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.515889801519197</v>
+        <v>23.547833984482043</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13805,7 +13834,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1537000000000002</v>
+        <v>2.1414</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13828,7 +13857,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4841848</v>
+        <v>4841084</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13844,7 +13873,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1882872043560911E-2</v>
+        <v>-1.1602728679978257E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13877,7 +13906,7 @@
       </c>
       <c r="I17" s="242">
         <f ca="1">DCF!C15</f>
-        <v>0.14565978630451679</v>
+        <v>0.14554164361796129</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -13899,7 +13928,7 @@
       </c>
       <c r="I18" s="243">
         <f ca="1">Multiples!C54</f>
-        <v>0.14789649999999999</v>
+        <v>0.14772299999999999</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -13966,12 +13995,12 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="2">
+      <c r="E26" s="181" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>50.98</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13986,7 +14015,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.0979999999999998E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18384,6 +18413,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18391,12 +18426,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19457,16 +19486,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19589,7 +19618,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19598,7 +19627,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>156611.97</v>
+        <v>160393.30499999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19616,7 +19645,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.0979999999999998E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19625,7 +19654,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1537000000000002</v>
+        <v>2.1414</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19668,7 +19697,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.2256632773113388E-2</v>
+        <v>2.1743332855264638E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19677,7 +19706,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97774336722688659</v>
+        <v>0.97825666714473536</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19695,7 +19724,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14789649999999999</v>
+        <v>0.14772299999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19704,7 +19733,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14565978630451679</v>
+        <v>0.14554164361796129</v>
       </c>
     </row>
   </sheetData>
@@ -19956,7 +19985,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30138.305404321778</v>
+        <v>30165.581147678571</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20010,23 +20039,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3781.5443008184361</v>
+        <v>3781.9343013090484</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4626.1027856074834</v>
+        <v>4627.057038815954</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4395.5135513701534</v>
+        <v>4396.8736538361281</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3428.5632075058943</v>
+        <v>3429.9778128577291</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1965.6961389336327</v>
+        <v>1966.7099847878962</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20045,7 +20074,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15270.050850746456</v>
+        <v>15291.753491336116</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20068,7 +20097,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14565978630451679</v>
+        <v>0.14554164361796129</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20083,7 +20112,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18197.419984235599</v>
+        <v>18202.552791606755</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20092,7 +20121,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15270.050850746456</v>
+        <v>15291.753491336116</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20101,7 +20130,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33467.470834982058</v>
+        <v>33494.306282942867</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20128,7 +20157,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31606.470834982058</v>
+        <v>31633.306282942867</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20146,7 +20175,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>133.36063643452346</v>
+        <v>133.47386617275473</v>
       </c>
     </row>
   </sheetData>
@@ -20416,23 +20445,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3781.5443008184361</v>
+        <v>3781.9343013090484</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4626.1027856074834</v>
+        <v>4627.057038815954</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4395.5135513701534</v>
+        <v>4396.8736538361281</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3428.5632075058943</v>
+        <v>3429.9778128577291</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1965.6961389336327</v>
+        <v>1966.7099847878962</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21218,7 +21247,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14565978630451679</v>
+        <v>0.14554164361796129</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21244,7 +21273,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35740.44489317626</v>
+        <v>35758.878719832777</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21253,7 +21282,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>51972.168738478227</v>
+        <v>51994.721526651636</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21280,7 +21309,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50111.168738478227</v>
+        <v>50133.721526651636</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21298,7 +21327,7 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>211.43953054210223</v>
+        <v>211.53468998587189</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21322,7 +21351,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14789649999999999</v>
+        <v>0.14772299999999999</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21357,7 +21386,7 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>145.83400832217521</v>
+        <v>145.94426947147235</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21381,7 +21410,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14565978630451679</v>
+        <v>0.14554164361796129</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21407,7 +21436,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39313.922778672655</v>
+        <v>39334.199695757925</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21416,7 +21445,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55545.646623974622</v>
+        <v>55570.042502576784</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21443,7 +21472,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53684.646623974622</v>
+        <v>53709.042502576784</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21461,7 +21490,7 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>226.51749630369039</v>
+        <v>226.62043250032397</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21485,7 +21514,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14565978630451679</v>
+        <v>0.14554164361796129</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21511,7 +21540,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37229.630097058624</v>
+        <v>37248.831999825823</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21520,7 +21549,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53461.353942360591</v>
+        <v>53484.674806644682</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21547,7 +21576,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51600.353942360591</v>
+        <v>51623.674806644682</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21565,22 +21594,22 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>217.72301241502359</v>
+        <v>217.82141268626447</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21631,7 +21660,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>133.36063643452346</v>
+        <v>133.47386617275473</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21640,7 +21669,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>211.43953054210223</v>
+        <v>211.53468998587189</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21649,7 +21678,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>145.83400832217521</v>
+        <v>145.94426947147235</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21658,7 +21687,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>226.51749630369039</v>
+        <v>226.62043250032397</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21667,7 +21696,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>217.72301241502359</v>
+        <v>217.82141268626447</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21676,7 +21705,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>186.97493680350297</v>
+        <v>187.07893416333746</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21685,7 +21714,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21694,7 +21723,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.71705189569845651</v>
+        <v>-0.72356883975480779</v>
       </c>
     </row>
   </sheetData>
@@ -22204,7 +22233,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14789649999999999</v>
+        <v>0.14772299999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22221,7 +22250,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.515889801519197</v>
+        <v>23.547833984482043</v>
       </c>
     </row>
   </sheetData>
@@ -22459,7 +22488,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>258874.2575445894</v>
+        <v>259108.54370354029</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22513,23 +22542,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4329.1795102865008</v>
+        <v>4329.6259898193721</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6083.8122232114756</v>
+        <v>6085.0671666493508</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>8549.6041638725874</v>
+        <v>8552.249665375537</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12014.790837893786</v>
+        <v>12019.748071111262</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>16884.430683741743</v>
+        <v>16893.139155875997</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22548,15 +22577,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>131162.75197371442</v>
+        <v>131349.16772914704</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="261" t="s">
+      <c r="B14" s="262" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="262"/>
+      <c r="C14" s="263"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22564,7 +22593,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22573,7 +22602,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>780.45625283136792</v>
+        <v>781.3568184051918</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22583,20 +22612,20 @@
       <c r="C17" s="156">
         <v>0.61</v>
       </c>
-      <c r="E17" s="263" t="s">
+      <c r="E17" s="261" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="263"/>
-      <c r="G17" s="263"/>
-      <c r="H17" s="263"/>
-      <c r="I17" s="263"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="261" t="s">
+      <c r="B19" s="262" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="262"/>
+      <c r="C19" s="263"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22612,7 +22641,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14565978630451679</v>
+        <v>0.14554164361796129</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22630,7 +22659,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>150003.87</v>
+        <v>153625.655</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22657,15 +22686,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>151864.87</v>
+        <v>155486.655</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="261" t="s">
+      <c r="B28" s="262" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="262"/>
+      <c r="C28" s="263"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22673,7 +22702,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>47861.817419006096</v>
+        <v>47879.830048831514</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22682,7 +22711,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>131162.75197371442</v>
+        <v>131349.16772914704</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22691,7 +22720,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>179024.56939272053</v>
+        <v>179228.99777797854</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22718,7 +22747,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>177163.56939272053</v>
+        <v>177367.99777797854</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22736,21 +22765,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>780.45625283136792</v>
+        <v>781.3568184051918</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29531,7 +29560,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29605,7 +29634,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30974,7 +31003,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>47.608789625360224</v>
+        <v>48.758285302593656</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31015,7 +31044,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>12.395267527675276</v>
+        <v>12.69454643296433</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31080,7 +31109,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>69.221905860636824</v>
+        <v>70.893241808952467</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31145,7 +31174,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>156611.97</v>
+        <v>160393.30499999999</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31210,7 +31239,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>158472.97</v>
+        <v>162254.30499999999</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31251,7 +31280,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>12.994913489134891</v>
+        <v>13.304986059860598</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31292,7 +31321,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>38.708590620420125</v>
+        <v>39.632219101123596</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31439,7 +31468,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>54.153516597510375</v>
+        <v>55.46103215767635</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31480,7 +31509,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>51.442232720259383</v>
+        <v>52.669699556170023</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31521,7 +31550,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.8466021466941512E-2</v>
+        <v>1.8030677776731393E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31562,7 +31591,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.100452474992812E-2</v>
+        <v>2.050933485035426E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31603,7 +31632,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>4.4188193277946769E-3</v>
+        <v>4.3146439310543542E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31644,7 +31673,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>1.1237966037972705E-3</v>
+        <v>1.0973026586115924E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31685,7 +31714,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>5.1720184606578925E-3</v>
+        <v>5.0500860992919875E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32232,7 +32261,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.1882872043560911E-2</v>
+        <v>-1.1602728679978257E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33607,7 +33636,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33623,7 +33652,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>156611.97</v>
+        <v>160393.30499999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33643,7 +33672,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>158472.97</v>
+        <v>162254.30499999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33663,7 +33692,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>47.608789625360224</v>
+        <v>48.758285302593656</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33683,7 +33712,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.395267527675276</v>
+        <v>12.69454643296433</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33703,7 +33732,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>69.221905860636824</v>
+        <v>70.893241808952467</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33723,7 +33752,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.994913489134891</v>
+        <v>13.304986059860598</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33732,7 +33761,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>38.708590620420125</v>
+        <v>39.632219101123596</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33968,7 +33997,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.100452474992812E-2</v>
+        <v>2.050933485035426E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -33984,7 +34013,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.8466021466941512E-2</v>
+        <v>1.8030677776731393E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34000,7 +34029,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.4188193277946769E-3</v>
+        <v>4.3146439310543542E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34016,7 +34045,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.1237966037972705E-3</v>
+        <v>1.0973026586115924E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34025,7 +34054,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.1720184606578925E-3</v>
+        <v>5.0500860992919875E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34069,7 +34098,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1882872043560911E-2</v>
+        <v>-1.1602728679978257E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34249,7 +34278,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>660.81</v>
+        <v>676.76499999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34278,7 +34307,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>156611.97</v>
+        <v>160393.30499999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34307,7 +34336,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>158472.97</v>
+        <v>162254.30499999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34336,7 +34365,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>47.608789625360224</v>
+        <v>48.758285302593656</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34365,7 +34394,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.395267527675276</v>
+        <v>12.69454643296433</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34394,7 +34423,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>69.221905860636824</v>
+        <v>70.893241808952467</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34423,7 +34452,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.994913489134891</v>
+        <v>13.304986059860598</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34452,7 +34481,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>38.708590620420125</v>
+        <v>39.632219101123596</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35225,7 +35254,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.100452474992812E-2</v>
+        <v>2.050933485035426E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35254,7 +35283,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.8466021466941512E-2</v>
+        <v>1.8030677776731393E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35283,7 +35312,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.4188193277946769E-3</v>
+        <v>4.3146439310543542E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35312,7 +35341,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.1237966037972705E-3</v>
+        <v>1.0973026586115924E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35341,7 +35370,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.1720184606578925E-3</v>
+        <v>5.0500860992919875E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35577,7 +35606,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1882872043560911E-2</v>
+        <v>-1.1602728679978257E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36040,14 +36069,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="250" t="s">
+      <c r="C3" s="252" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="F3" s="252" t="s">
+      <c r="D3" s="253"/>
+      <c r="F3" s="254" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="251"/>
+      <c r="G3" s="253"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36114,19 +36143,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="253">
+      <c r="C7" s="250">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="F7" s="253">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="254"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36153,19 +36182,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="250">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="F9" s="253">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="254"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36192,19 +36221,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="253">
+      <c r="C11" s="250">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="F11" s="253">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="254"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36231,19 +36260,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="253">
+      <c r="C13" s="250">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="F13" s="253">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="254"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36270,19 +36299,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="253">
+      <c r="C15" s="250">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="F15" s="253">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="254"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36309,19 +36338,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="250">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="F17" s="253">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="254"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36348,22 +36377,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="F19" s="253">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="254"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36390,22 +36419,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="253">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="F21" s="253">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="254"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36454,22 +36483,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="F25" s="253">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="254"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36497,25 +36526,37 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="253">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="F27" s="253">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="254"/>
+      <c r="G27" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36526,18 +36567,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1020F86A-FA10-8942-B689-E9A1C9EDD4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891BE828-A4EC-C14E-83E7-C6903F323618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -200,7 +200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="441">
   <si>
     <t>Ticker</t>
   </si>
@@ -1520,6 +1520,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2142,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2482,12 +2485,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2495,6 +2492,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2515,15 +2518,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12711,8 +12717,8 @@
     <v>1145</v>
     <v>209</v>
     <v>2.1414</v>
-    <v>15.955</v>
-    <v>2.4145E-2</v>
+    <v>17.48</v>
+    <v>2.6452E-2</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12723,20 +12729,20 @@
     <v>679.8</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46315.694664108596</v>
+    <v>46315.728864015626</v>
     <v>0</v>
     <v>642.41999999999996</v>
-    <v>155006864688</v>
+    <v>155356152061</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>657.17</v>
-    <v>48.674500000000002</v>
+    <v>48.784199999999998</v>
     <v>660.81</v>
-    <v>676.76499999999999</v>
+    <v>678.29</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>2232223</v>
+    <v>2553182</v>
     <v>4841084</v>
     <v>2017</v>
   </rv>
@@ -13568,7 +13574,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13606,7 +13612,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>160393.30499999999</v>
+        <v>160754.72999999998</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13614,7 +13620,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>133.47386617275473</v>
+        <v>133.46926393304309</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>435</v>
@@ -13633,7 +13639,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>162254.30499999999</v>
+        <v>162615.72999999998</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13641,7 +13647,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>211.53468998587189</v>
+        <v>211.53082435034173</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>436</v>
@@ -13653,7 +13659,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13687,7 +13693,7 @@
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>48.758285302593656</v>
+        <v>48.868155619596536</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13695,7 +13701,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>226.62043250032397</v>
+        <v>226.61625094600302</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>438</v>
@@ -13707,14 +13713,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>15.955</v>
+        <v>17.48</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>12.69454643296433</v>
+        <v>12.723151906519066</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13722,7 +13728,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>217.82141268626447</v>
+        <v>217.81741539703339</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13738,7 +13744,7 @@
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.8030677776731393E-2</v>
+        <v>1.7990139388122516E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13746,7 +13752,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>187.07893416333746</v>
+        <v>187.0756048195787</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13755,14 +13761,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.4145E-2</v>
+        <v>2.6452E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>2.050933485035426E-2</v>
+        <v>2.0463223694879774E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13770,7 +13776,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.72356883975480779</v>
+        <v>-0.72419524861109741</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13786,7 +13792,7 @@
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>1.0973026586115924E-3</v>
+        <v>1.094835592084911E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13802,7 +13808,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>4.3146439310543542E-3</v>
+        <v>4.3049433133320559E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
@@ -13843,12 +13849,12 @@
         <f>Statement!AC123</f>
         <v>1.4693124134748501</v>
       </c>
-      <c r="H13" s="180" t="s">
+      <c r="H13" s="266" t="s">
         <v>431</v>
       </c>
-      <c r="I13" s="209">
+      <c r="I13" s="264">
         <f>'Reverse DCF'!C17</f>
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -13866,6 +13872,13 @@
         <f>Statement!AC138</f>
         <v>0.87701105809469215</v>
       </c>
+      <c r="H14" s="182" t="s">
+        <v>440</v>
+      </c>
+      <c r="I14" s="265">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>674.11482508273377</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="181" t="s">
@@ -13873,7 +13886,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1602728679978257E-2</v>
+        <v>-1.1576642254943294E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13906,7 +13919,7 @@
       </c>
       <c r="I17" s="242">
         <f ca="1">DCF!C15</f>
-        <v>0.14554164361796129</v>
+        <v>0.14554644156115643</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -18413,12 +18426,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18426,6 +18433,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19486,16 +19499,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19618,7 +19631,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19627,7 +19640,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>160393.30499999999</v>
+        <v>160754.72999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19697,7 +19710,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.1743332855264638E-2</v>
+        <v>2.1695507897925591E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19706,7 +19719,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97825666714473536</v>
+        <v>0.97830449210207437</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19733,7 +19746,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14554164361796129</v>
+        <v>0.14554644156115643</v>
       </c>
     </row>
   </sheetData>
@@ -19985,7 +19998,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30165.581147678571</v>
+        <v>30164.472479046442</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20039,23 +20052,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3781.9343013090484</v>
+        <v>3781.9184612651293</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4627.057038815954</v>
+        <v>4627.0182794788616</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4396.8736538361281</v>
+        <v>4396.8184072021068</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3429.9778128577291</v>
+        <v>3429.9203495032298</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1966.7099847878962</v>
+        <v>1966.6687988376693</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20074,7 +20087,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15291.753491336116</v>
+        <v>15290.871255844222</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20097,7 +20110,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554164361796129</v>
+        <v>0.14554644156115643</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20112,7 +20125,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18202.552791606755</v>
+        <v>18202.344296286996</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20121,7 +20134,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15291.753491336116</v>
+        <v>15290.871255844222</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20130,7 +20143,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33494.306282942867</v>
+        <v>33493.215552131216</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20157,7 +20170,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31633.306282942867</v>
+        <v>31632.215552131216</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20175,7 +20188,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>133.47386617275473</v>
+        <v>133.46926393304309</v>
       </c>
     </row>
   </sheetData>
@@ -20445,23 +20458,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3781.9343013090484</v>
+        <v>3781.9184612651293</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4627.057038815954</v>
+        <v>4627.0182794788616</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4396.8736538361281</v>
+        <v>4396.8184072021068</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3429.9778128577291</v>
+        <v>3429.9203495032298</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1966.7099847878962</v>
+        <v>1966.6687988376693</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21247,7 +21260,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554164361796129</v>
+        <v>0.14554644156115643</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21273,7 +21286,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35758.878719832777</v>
+        <v>35758.129873581667</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21282,7 +21295,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>51994.721526651636</v>
+        <v>51993.805371030991</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21309,7 +21322,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50133.721526651636</v>
+        <v>50132.805371030991</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21327,7 +21340,7 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>211.53468998587189</v>
+        <v>211.53082435034173</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21410,7 +21423,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554164361796129</v>
+        <v>0.14554644156115643</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21436,7 +21449,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39334.199695757925</v>
+        <v>39333.375976753385</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21445,7 +21458,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55570.042502576784</v>
+        <v>55569.051474202715</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21472,7 +21485,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53709.042502576784</v>
+        <v>53708.051474202715</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21490,7 +21503,7 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>226.62043250032397</v>
+        <v>226.61625094600302</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21514,7 +21527,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554164361796129</v>
+        <v>0.14554644156115643</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21540,7 +21553,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37248.831999825823</v>
+        <v>37248.051951647583</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21549,7 +21562,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53484.674806644682</v>
+        <v>53483.727449096914</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21576,7 +21589,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51623.674806644682</v>
+        <v>51622.727449096914</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21594,22 +21607,22 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>217.82141268626447</v>
+        <v>217.81741539703339</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21660,7 +21673,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>133.47386617275473</v>
+        <v>133.46926393304309</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21669,7 +21682,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>211.53468998587189</v>
+        <v>211.53082435034173</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21687,7 +21700,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>226.62043250032397</v>
+        <v>226.61625094600302</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21696,7 +21709,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>217.82141268626447</v>
+        <v>217.81741539703339</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21705,7 +21718,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>187.07893416333746</v>
+        <v>187.0756048195787</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21714,7 +21727,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21723,7 +21736,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.72356883975480779</v>
+        <v>-0.72419524861109741</v>
       </c>
     </row>
   </sheetData>
@@ -22440,23 +22453,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>4959.7668726287257</v>
+        <v>4805.736845528455</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>7985.2246649322478</v>
+        <v>7496.9494790243898</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>12856.211710540918</v>
+        <v>11695.241187278049</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>20698.500853970876</v>
+        <v>18244.576252153758</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>33324.586374893108</v>
+        <v>28461.538953359865</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22488,7 +22501,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>259108.54370354029</v>
+        <v>221288.77426449829</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22542,23 +22555,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4329.6259898193721</v>
+        <v>4195.1479845541426</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>6085.0671666493508</v>
+        <v>5712.9336869011422</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>8552.249665375537</v>
+        <v>7779.8474406853584</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12019.748071111262</v>
+        <v>10594.561309037275</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>16893.139155875997</v>
+        <v>14427.626015383863</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22577,15 +22590,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>131349.16772914704</v>
+        <v>112174.94885721877</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="262" t="s">
+      <c r="B14" s="261" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="263"/>
+      <c r="C14" s="262"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22593,7 +22606,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22602,7 +22615,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>781.3568184051918</v>
+        <v>674.11482508273377</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22610,22 +22623,22 @@
         <v>323</v>
       </c>
       <c r="C17" s="156">
-        <v>0.61</v>
-      </c>
-      <c r="E17" s="261" t="s">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E17" s="263" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="261"/>
-      <c r="G17" s="261"/>
-      <c r="H17" s="261"/>
-      <c r="I17" s="261"/>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="263"/>
+      <c r="I17" s="263"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="262" t="s">
+      <c r="B19" s="261" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="263"/>
+      <c r="C19" s="262"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22641,7 +22654,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554164361796129</v>
+        <v>0.14554644156115643</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22659,7 +22672,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>153625.655</v>
+        <v>153971.82999999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22686,15 +22699,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>155486.655</v>
+        <v>155832.82999999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="262" t="s">
+      <c r="B28" s="261" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="263"/>
+      <c r="C28" s="262"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22702,7 +22715,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>47879.830048831514</v>
+        <v>42710.116436561781</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22711,7 +22724,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>131349.16772914704</v>
+        <v>112174.94885721877</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22720,7 +22733,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>179228.99777797854</v>
+        <v>154885.06529378056</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22747,7 +22760,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>177367.99777797854</v>
+        <v>153024.06529378056</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22765,21 +22778,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>781.3568184051918</v>
+        <v>674.11482508273377</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29560,7 +29573,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29634,7 +29647,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31003,7 +31016,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>48.758285302593656</v>
+        <v>48.868155619596536</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31044,7 +31057,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>12.69454643296433</v>
+        <v>12.723151906519066</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31109,7 +31122,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>70.893241808952467</v>
+        <v>71.052990309183201</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31174,7 +31187,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>160393.30499999999</v>
+        <v>160754.72999999998</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31239,7 +31252,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>162254.30499999999</v>
+        <v>162615.72999999998</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31280,7 +31293,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>13.304986059860598</v>
+        <v>13.334623206232061</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31321,7 +31334,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>39.632219101123596</v>
+        <v>39.720500732779676</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31468,7 +31481,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>55.46103215767635</v>
+        <v>55.586006224066381</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31509,7 +31522,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>52.669699556170023</v>
+        <v>52.787022459633747</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31550,7 +31563,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.8030677776731393E-2</v>
+        <v>1.7990139388122516E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31591,7 +31604,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.050933485035426E-2</v>
+        <v>2.0463223694879774E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31632,7 +31645,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>4.3146439310543542E-3</v>
+        <v>4.3049433133320559E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31673,7 +31686,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>1.0973026586115924E-3</v>
+        <v>1.094835592084911E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31714,7 +31727,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>5.0500860992919875E-3</v>
+        <v>5.0387319862998745E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32261,7 +32274,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.1602728679978257E-2</v>
+        <v>-1.1576642254943294E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33636,7 +33649,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33652,7 +33665,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>160393.30499999999</v>
+        <v>160754.72999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33672,7 +33685,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>162254.30499999999</v>
+        <v>162615.72999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33692,7 +33705,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>48.758285302593656</v>
+        <v>48.868155619596536</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33712,7 +33725,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.69454643296433</v>
+        <v>12.723151906519066</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33732,7 +33745,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>70.893241808952467</v>
+        <v>71.052990309183201</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33752,7 +33765,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.304986059860598</v>
+        <v>13.334623206232061</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33761,7 +33774,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>39.632219101123596</v>
+        <v>39.720500732779676</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33997,7 +34010,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.050933485035426E-2</v>
+        <v>2.0463223694879774E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34013,7 +34026,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.8030677776731393E-2</v>
+        <v>1.7990139388122516E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34029,7 +34042,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.3146439310543542E-3</v>
+        <v>4.3049433133320559E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34045,7 +34058,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.0973026586115924E-3</v>
+        <v>1.094835592084911E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34054,7 +34067,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.0500860992919875E-3</v>
+        <v>5.0387319862998745E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34098,7 +34111,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1602728679978257E-2</v>
+        <v>-1.1576642254943294E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34278,7 +34291,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>676.76499999999999</v>
+        <v>678.29</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34307,7 +34320,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>160393.30499999999</v>
+        <v>160754.72999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34336,7 +34349,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>162254.30499999999</v>
+        <v>162615.72999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34365,7 +34378,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>48.758285302593656</v>
+        <v>48.868155619596536</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34394,7 +34407,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.69454643296433</v>
+        <v>12.723151906519066</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34423,7 +34436,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>70.893241808952467</v>
+        <v>71.052990309183201</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34452,7 +34465,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.304986059860598</v>
+        <v>13.334623206232061</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34481,7 +34494,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>39.632219101123596</v>
+        <v>39.720500732779676</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35254,7 +35267,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.050933485035426E-2</v>
+        <v>2.0463223694879774E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35283,7 +35296,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.8030677776731393E-2</v>
+        <v>1.7990139388122516E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35312,7 +35325,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.3146439310543542E-3</v>
+        <v>4.3049433133320559E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35341,7 +35354,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.0973026586115924E-3</v>
+        <v>1.094835592084911E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35370,7 +35383,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.0500860992919875E-3</v>
+        <v>5.0387319862998745E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35606,7 +35619,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1602728679978257E-2</v>
+        <v>-1.1576642254943294E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36069,14 +36082,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="250" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="F3" s="254" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="253"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36143,19 +36156,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="253">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36182,19 +36195,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="253">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36221,19 +36234,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="253">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36260,19 +36273,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="253">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36299,19 +36312,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="253">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36338,19 +36351,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="253">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36377,22 +36390,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36419,22 +36432,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36483,22 +36496,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36526,37 +36539,25 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36567,6 +36568,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891BE828-A4EC-C14E-83E7-C6903F323618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C6605B-D3A9-EE4F-96F1-7D28F175514F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,28 +148,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -179,21 +158,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2473,6 +2443,9 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2527,9 +2500,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12697,7 +12667,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12715,10 +12685,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>1145</v>
-    <v>209</v>
-    <v>2.1414</v>
-    <v>17.48</v>
-    <v>2.6452E-2</v>
+    <v>217.67</v>
+    <v>2.1520000000000001</v>
+    <v>-11.65</v>
+    <v>-1.8142000000000002E-2</v>
+    <v>-0.4</v>
+    <v>-6.3439999999999992E-4</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12726,49 +12698,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>679.8</v>
+    <v>655.6</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46315.728864015626</v>
+    <v>46318.953264421092</v>
     <v>0</v>
-    <v>642.41999999999996</v>
-    <v>155356152061</v>
+    <v>621.00009999999997</v>
+    <v>144407997041</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>657.17</v>
-    <v>48.784199999999998</v>
-    <v>660.81</v>
-    <v>678.29</v>
+    <v>633</v>
+    <v>45.346299999999999</v>
+    <v>642.14</v>
+    <v>630.49</v>
+    <v>630.09</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>2553182</v>
-    <v>4841084</v>
+    <v>5569310</v>
+    <v>4901617</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12782,28 +12740,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>6</v>
-    <v>50.9</v>
+    <v>3</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12825,6 +12783,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12845,6 +12805,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12854,11 +12815,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12894,7 +12850,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12905,13 +12861,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13005,13 +12964,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13083,6 +13048,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13090,6 +13058,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13583,18 +13554,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="246" t="s">
+      <c r="B2" s="249" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="247"/>
-      <c r="E2" s="246" t="s">
+      <c r="C2" s="250"/>
+      <c r="E2" s="249" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="247"/>
-      <c r="H2" s="246" t="s">
+      <c r="F2" s="250"/>
+      <c r="H2" s="249" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="247"/>
+      <c r="I2" s="250"/>
       <c r="K2" s="132" t="s">
         <v>434</v>
       </c>
@@ -13612,7 +13583,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>160754.72999999998</v>
+        <v>149426.13</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13620,7 +13591,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>133.46926393304309</v>
+        <v>134.90700212028807</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>435</v>
@@ -13639,7 +13610,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>162615.72999999998</v>
+        <v>151287.13</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13647,7 +13618,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>211.53082435034173</v>
+        <v>212.7297108409131</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>436</v>
@@ -13659,7 +13630,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13674,7 +13645,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>145.94426947147235</v>
+        <v>146.80755643991765</v>
       </c>
       <c r="K5" s="244" t="s">
         <v>437</v>
@@ -13684,16 +13655,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="204" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>630.09</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>48.868155619596536</v>
+        <v>45.424351585014406</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13701,7 +13672,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>226.61625094600302</v>
+        <v>227.91314035012334</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>438</v>
@@ -13713,14 +13684,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>17.48</v>
+        <v>-11.65</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>12.723151906519066</v>
+        <v>11.826534440344403</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13728,23 +13699,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>217.81741539703339</v>
+        <v>219.05714290956459</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.4</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.7990139388122516E-2</v>
+        <v>1.9354044704229439E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13752,7 +13723,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>187.0756048195787</v>
+        <v>188.28291053216134</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13761,14 +13732,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.6452E-2</v>
+        <v>-1.8142000000000002E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>2.0463223694879774E-2</v>
+        <v>2.2014623546765217E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13776,23 +13747,23 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.72419524861109741</v>
+        <v>-0.70137050463582085</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-6.3439999999999992E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>1.094835592084911E-3</v>
+        <v>1.177839511737338E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13808,14 +13779,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>4.3049433133320559E-3</v>
+        <v>4.6313184983108376E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.547833984482043</v>
+        <v>23.799952520376671</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13824,7 +13795,7 @@
       </c>
       <c r="C12" s="205" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>209</v>
+        <v>217.67</v>
       </c>
       <c r="E12" s="181" t="s">
         <v>101</v>
@@ -13840,7 +13811,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1414</v>
+        <v>2.1520000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13849,10 +13820,10 @@
         <f>Statement!AC123</f>
         <v>1.4693124134748501</v>
       </c>
-      <c r="H13" s="266" t="s">
+      <c r="H13" s="248" t="s">
         <v>431</v>
       </c>
-      <c r="I13" s="264">
+      <c r="I13" s="246">
         <f>'Reverse DCF'!C17</f>
         <v>0.56000000000000005</v>
       </c>
@@ -13863,7 +13834,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4841084</v>
+        <v>4901617</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13875,9 +13846,9 @@
       <c r="H14" s="182" t="s">
         <v>440</v>
       </c>
-      <c r="I14" s="265">
+      <c r="I14" s="247">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>674.11482508273377</v>
+        <v>683.91677475151334</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -13886,7 +13857,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1576642254943294E-2</v>
+        <v>-1.2454314382631738E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13897,16 +13868,16 @@
         <f>Statement!AC173</f>
         <v>-8.1982378854625555</v>
       </c>
-      <c r="H16" s="246" t="s">
+      <c r="H16" s="249" t="s">
         <v>432</v>
       </c>
-      <c r="I16" s="247"/>
+      <c r="I16" s="250"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="248" t="s">
+      <c r="B17" s="251" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="248"/>
+      <c r="C17" s="251"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -13919,7 +13890,7 @@
       </c>
       <c r="I17" s="242">
         <f ca="1">DCF!C15</f>
-        <v>0.14554644156115643</v>
+        <v>0.14406380061445392</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -13941,7 +13912,7 @@
       </c>
       <c r="I18" s="243">
         <f ca="1">Multiples!C54</f>
-        <v>0.14772299999999999</v>
+        <v>0.14637</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -13992,14 +13963,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="248" t="s">
+      <c r="B25" s="251" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="248"/>
-      <c r="E25" s="246" t="s">
+      <c r="C25" s="251"/>
+      <c r="E25" s="249" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="247"/>
+      <c r="F25" s="250"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14008,12 +13979,12 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="5">
+      <c r="E26" s="181" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14028,7 +13999,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14406,36 +14377,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="249" t="s">
+      <c r="S2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249" t="s">
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14446,32 +14417,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="255" t="s">
+      <c r="C4" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="255"/>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="256" t="s">
+      <c r="S4" s="259" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="257"/>
-      <c r="U4" s="257"/>
-      <c r="V4" s="257"/>
-      <c r="W4" s="257"/>
-      <c r="X4" s="257"/>
-      <c r="Y4" s="257"/>
-      <c r="Z4" s="257"/>
-      <c r="AA4" s="257"/>
-      <c r="AB4" s="257"/>
-      <c r="AC4" s="257"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14862,33 +14833,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="255" t="s">
+      <c r="C10" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="255"/>
-      <c r="E10" s="255"/>
-      <c r="F10" s="255"/>
-      <c r="G10" s="255"/>
-      <c r="H10" s="255"/>
-      <c r="I10" s="255"/>
-      <c r="J10" s="255"/>
-      <c r="K10" s="255"/>
-      <c r="L10" s="255"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="256" t="s">
+      <c r="S10" s="259" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="257"/>
-      <c r="U10" s="257"/>
-      <c r="V10" s="257"/>
-      <c r="W10" s="257"/>
-      <c r="X10" s="257"/>
-      <c r="Y10" s="257"/>
-      <c r="Z10" s="257"/>
-      <c r="AA10" s="257"/>
-      <c r="AB10" s="257"/>
-      <c r="AC10" s="257"/>
+      <c r="T10" s="260"/>
+      <c r="U10" s="260"/>
+      <c r="V10" s="260"/>
+      <c r="W10" s="260"/>
+      <c r="X10" s="260"/>
+      <c r="Y10" s="260"/>
+      <c r="Z10" s="260"/>
+      <c r="AA10" s="260"/>
+      <c r="AB10" s="260"/>
+      <c r="AC10" s="260"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -15241,32 +15212,32 @@
     <row r="17" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="86"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="255" t="s">
+      <c r="C17" s="258" t="s">
         <v>395</v>
       </c>
-      <c r="D17" s="255"/>
-      <c r="E17" s="255"/>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
-      <c r="J17" s="255"/>
-      <c r="K17" s="255"/>
-      <c r="L17" s="255"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
       <c r="O17" s="5"/>
-      <c r="S17" s="256" t="s">
+      <c r="S17" s="259" t="s">
         <v>115</v>
       </c>
-      <c r="T17" s="257"/>
-      <c r="U17" s="257"/>
-      <c r="V17" s="257"/>
-      <c r="W17" s="257"/>
-      <c r="X17" s="257"/>
-      <c r="Y17" s="257"/>
-      <c r="Z17" s="257"/>
-      <c r="AA17" s="257"/>
-      <c r="AB17" s="257"/>
-      <c r="AC17" s="257"/>
+      <c r="T17" s="260"/>
+      <c r="U17" s="260"/>
+      <c r="V17" s="260"/>
+      <c r="W17" s="260"/>
+      <c r="X17" s="260"/>
+      <c r="Y17" s="260"/>
+      <c r="Z17" s="260"/>
+      <c r="AA17" s="260"/>
+      <c r="AB17" s="260"/>
+      <c r="AC17" s="260"/>
       <c r="AE17" s="87"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -15759,35 +15730,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="P2" s="249" t="s">
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="249"/>
-      <c r="R2" s="249"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249" t="s">
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15796,31 +15767,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="255" t="s">
+      <c r="C4" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="255"/>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
-      <c r="P4" s="257" t="s">
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="P4" s="260" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="257"/>
-      <c r="R4" s="257"/>
-      <c r="S4" s="257"/>
-      <c r="T4" s="257"/>
-      <c r="U4" s="257"/>
-      <c r="V4" s="257"/>
-      <c r="W4" s="257"/>
-      <c r="X4" s="257"/>
-      <c r="Y4" s="257"/>
-      <c r="Z4" s="257"/>
+      <c r="Q4" s="260"/>
+      <c r="R4" s="260"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -16015,32 +15986,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="255" t="s">
+      <c r="C9" s="258" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="255"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="255"/>
-      <c r="G9" s="255"/>
-      <c r="H9" s="255"/>
-      <c r="I9" s="255"/>
-      <c r="J9" s="255"/>
-      <c r="K9" s="255"/>
-      <c r="L9" s="255"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="257" t="s">
+      <c r="P9" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="257"/>
-      <c r="R9" s="257"/>
-      <c r="S9" s="257"/>
-      <c r="T9" s="257"/>
-      <c r="U9" s="257"/>
-      <c r="V9" s="257"/>
-      <c r="W9" s="257"/>
-      <c r="X9" s="257"/>
-      <c r="Y9" s="257"/>
-      <c r="Z9" s="257"/>
+      <c r="Q9" s="260"/>
+      <c r="R9" s="260"/>
+      <c r="S9" s="260"/>
+      <c r="T9" s="260"/>
+      <c r="U9" s="260"/>
+      <c r="V9" s="260"/>
+      <c r="W9" s="260"/>
+      <c r="X9" s="260"/>
+      <c r="Y9" s="260"/>
+      <c r="Z9" s="260"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16517,31 +16488,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="255" t="s">
+      <c r="C17" s="258" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="255"/>
-      <c r="E17" s="255"/>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
-      <c r="J17" s="255"/>
-      <c r="K17" s="255"/>
-      <c r="L17" s="255"/>
-      <c r="P17" s="257" t="s">
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
+      <c r="P17" s="260" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="257"/>
-      <c r="R17" s="257"/>
-      <c r="S17" s="257"/>
-      <c r="T17" s="257"/>
-      <c r="U17" s="257"/>
-      <c r="V17" s="257"/>
-      <c r="W17" s="257"/>
-      <c r="X17" s="257"/>
-      <c r="Y17" s="257"/>
-      <c r="Z17" s="257"/>
+      <c r="Q17" s="260"/>
+      <c r="R17" s="260"/>
+      <c r="S17" s="260"/>
+      <c r="T17" s="260"/>
+      <c r="U17" s="260"/>
+      <c r="V17" s="260"/>
+      <c r="W17" s="260"/>
+      <c r="X17" s="260"/>
+      <c r="Y17" s="260"/>
+      <c r="Z17" s="260"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17020,60 +16991,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="P3" s="260"/>
-      <c r="Q3" s="260"/>
-      <c r="R3" s="260"/>
-      <c r="S3" s="260"/>
-      <c r="T3" s="260"/>
-      <c r="U3" s="260"/>
-      <c r="V3" s="260"/>
-      <c r="W3" s="260"/>
-      <c r="X3" s="260"/>
-      <c r="Y3" s="260"/>
-      <c r="Z3" s="260"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="255" t="s">
+      <c r="C5" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="255"/>
-      <c r="J5" s="255"/>
-      <c r="K5" s="255"/>
-      <c r="L5" s="255"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-      <c r="R5" s="260"/>
-      <c r="S5" s="260"/>
-      <c r="T5" s="260"/>
-      <c r="U5" s="260"/>
-      <c r="V5" s="260"/>
-      <c r="W5" s="260"/>
-      <c r="X5" s="260"/>
-      <c r="Y5" s="260"/>
-      <c r="Z5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17259,30 +17230,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="255" t="s">
+      <c r="C11" s="258" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="255"/>
-      <c r="E11" s="255"/>
-      <c r="F11" s="255"/>
-      <c r="G11" s="255"/>
-      <c r="H11" s="255"/>
-      <c r="I11" s="255"/>
-      <c r="J11" s="255"/>
-      <c r="K11" s="255"/>
-      <c r="L11" s="255"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="260"/>
-      <c r="Q11" s="260"/>
-      <c r="R11" s="260"/>
-      <c r="S11" s="260"/>
-      <c r="T11" s="260"/>
-      <c r="U11" s="260"/>
-      <c r="V11" s="260"/>
-      <c r="W11" s="260"/>
-      <c r="X11" s="260"/>
-      <c r="Y11" s="260"/>
-      <c r="Z11" s="260"/>
+      <c r="P11" s="263"/>
+      <c r="Q11" s="263"/>
+      <c r="R11" s="263"/>
+      <c r="S11" s="263"/>
+      <c r="T11" s="263"/>
+      <c r="U11" s="263"/>
+      <c r="V11" s="263"/>
+      <c r="W11" s="263"/>
+      <c r="X11" s="263"/>
+      <c r="Y11" s="263"/>
+      <c r="Z11" s="263"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17524,18 +17495,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="255" t="s">
+      <c r="C18" s="258" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="255"/>
-      <c r="E18" s="255"/>
-      <c r="F18" s="255"/>
-      <c r="G18" s="255"/>
-      <c r="H18" s="255"/>
-      <c r="I18" s="255"/>
-      <c r="J18" s="255"/>
-      <c r="K18" s="255"/>
-      <c r="L18" s="255"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17748,23 +17719,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="260"/>
-      <c r="C25" s="260"/>
+      <c r="B25" s="263"/>
+      <c r="C25" s="263"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="255" t="s">
+      <c r="C26" s="258" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="255"/>
-      <c r="E26" s="255"/>
-      <c r="F26" s="255"/>
-      <c r="G26" s="255"/>
-      <c r="H26" s="255"/>
-      <c r="I26" s="255"/>
-      <c r="J26" s="255"/>
-      <c r="K26" s="255"/>
-      <c r="L26" s="255"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17956,18 +17927,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="255" t="s">
+      <c r="C33" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="255"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="255"/>
-      <c r="G33" s="255"/>
-      <c r="H33" s="255"/>
-      <c r="I33" s="255"/>
-      <c r="J33" s="255"/>
-      <c r="K33" s="255"/>
-      <c r="L33" s="255"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18151,18 +18122,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="255" t="s">
+      <c r="C40" s="258" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="255"/>
-      <c r="E40" s="255"/>
-      <c r="F40" s="255"/>
-      <c r="G40" s="255"/>
-      <c r="H40" s="255"/>
-      <c r="I40" s="255"/>
-      <c r="J40" s="255"/>
-      <c r="K40" s="255"/>
-      <c r="L40" s="255"/>
+      <c r="D40" s="258"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="258"/>
+      <c r="G40" s="258"/>
+      <c r="H40" s="258"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18477,60 +18448,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="S2" s="260"/>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="260"/>
-      <c r="X2" s="260"/>
-      <c r="Y2" s="260"/>
-      <c r="Z2" s="260"/>
-      <c r="AA2" s="260"/>
-      <c r="AB2" s="260"/>
-      <c r="AC2" s="260"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="263"/>
+      <c r="AB2" s="263"/>
+      <c r="AC2" s="263"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="255" t="s">
+      <c r="C4" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="255"/>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
-      <c r="S4" s="260"/>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
-      <c r="AA4" s="260"/>
-      <c r="AB4" s="260"/>
-      <c r="AC4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="S4" s="263"/>
+      <c r="T4" s="263"/>
+      <c r="U4" s="263"/>
+      <c r="V4" s="263"/>
+      <c r="W4" s="263"/>
+      <c r="X4" s="263"/>
+      <c r="Y4" s="263"/>
+      <c r="Z4" s="263"/>
+      <c r="AA4" s="263"/>
+      <c r="AB4" s="263"/>
+      <c r="AC4" s="263"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18893,18 +18864,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="255" t="s">
+      <c r="C13" s="258" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="255"/>
-      <c r="E13" s="255"/>
-      <c r="F13" s="255"/>
-      <c r="G13" s="255"/>
-      <c r="H13" s="255"/>
-      <c r="I13" s="255"/>
-      <c r="J13" s="255"/>
-      <c r="K13" s="255"/>
-      <c r="L13" s="255"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18997,18 +18968,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="255" t="s">
+      <c r="C18" s="258" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="255"/>
-      <c r="E18" s="255"/>
-      <c r="F18" s="255"/>
-      <c r="G18" s="255"/>
-      <c r="H18" s="255"/>
-      <c r="I18" s="255"/>
-      <c r="J18" s="255"/>
-      <c r="K18" s="255"/>
-      <c r="L18" s="255"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19200,18 +19171,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="255" t="s">
+      <c r="C25" s="258" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="255"/>
-      <c r="E25" s="255"/>
-      <c r="F25" s="255"/>
-      <c r="G25" s="255"/>
-      <c r="H25" s="255"/>
-      <c r="I25" s="255"/>
-      <c r="J25" s="255"/>
-      <c r="K25" s="255"/>
-      <c r="L25" s="255"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19349,18 +19320,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="255" t="s">
+      <c r="C31" s="258" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="255"/>
-      <c r="E31" s="255"/>
-      <c r="F31" s="255"/>
-      <c r="G31" s="255"/>
-      <c r="H31" s="255"/>
-      <c r="I31" s="255"/>
-      <c r="J31" s="255"/>
-      <c r="K31" s="255"/>
-      <c r="L31" s="255"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="258"/>
+      <c r="G31" s="258"/>
+      <c r="H31" s="258"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19611,10 +19582,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19631,7 +19602,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19640,7 +19611,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>160754.72999999998</v>
+        <v>149426.13</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19658,7 +19629,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19667,7 +19638,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1414</v>
+        <v>2.1520000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19699,10 +19670,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="249"/>
+      <c r="C15" s="252"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19710,7 +19681,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.1695507897925591E-2</v>
+        <v>2.3302004501829614E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19719,7 +19690,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97830449210207437</v>
+        <v>0.97669799549817038</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19737,7 +19708,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14772299999999999</v>
+        <v>0.14637</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19746,7 +19717,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14554644156115643</v>
+        <v>0.14406380061445392</v>
       </c>
     </row>
   </sheetData>
@@ -19792,60 +19763,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="P3" s="260"/>
-      <c r="Q3" s="260"/>
-      <c r="R3" s="260"/>
-      <c r="S3" s="260"/>
-      <c r="T3" s="260"/>
-      <c r="U3" s="260"/>
-      <c r="V3" s="260"/>
-      <c r="W3" s="260"/>
-      <c r="X3" s="260"/>
-      <c r="Y3" s="260"/>
-      <c r="Z3" s="260"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="255" t="s">
+      <c r="C5" s="258" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="255"/>
-      <c r="J5" s="255"/>
-      <c r="K5" s="255"/>
-      <c r="L5" s="255"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-      <c r="R5" s="260"/>
-      <c r="S5" s="260"/>
-      <c r="T5" s="260"/>
-      <c r="U5" s="260"/>
-      <c r="V5" s="260"/>
-      <c r="W5" s="260"/>
-      <c r="X5" s="260"/>
-      <c r="Y5" s="260"/>
-      <c r="Z5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19998,7 +19969,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30164.472479046442</v>
+        <v>30510.991656540005</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20052,23 +20023,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3781.9184612651293</v>
+        <v>3786.8196102786287</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4627.0182794788616</v>
+        <v>4639.0187500391494</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4396.8184072021068</v>
+        <v>4413.9346417391207</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3429.9203495032298</v>
+        <v>3447.7348607503491</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1966.6687988376693</v>
+        <v>1979.4453200085995</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20087,14 +20058,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15290.871255844222</v>
+        <v>15567.006319692429</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="249" t="s">
+      <c r="B13" s="252" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="249"/>
+      <c r="C13" s="252"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20110,14 +20081,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554644156115643</v>
+        <v>0.14406380061445392</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="249" t="s">
+      <c r="B18" s="252" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="249"/>
+      <c r="C18" s="252"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20125,7 +20096,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18202.344296286996</v>
+        <v>18266.953182815847</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20134,7 +20105,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15290.871255844222</v>
+        <v>15567.006319692429</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20143,7 +20114,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33493.215552131216</v>
+        <v>33833.959502508274</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20170,7 +20141,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31632.215552131216</v>
+        <v>31972.959502508274</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20188,7 +20159,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>133.46926393304309</v>
+        <v>134.90700212028807</v>
       </c>
     </row>
   </sheetData>
@@ -20232,37 +20203,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="255" t="s">
+      <c r="C4" s="258" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="255"/>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20458,23 +20429,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3781.9184612651293</v>
+        <v>3786.8196102786287</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4627.0182794788616</v>
+        <v>4639.0187500391494</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4396.8184072021068</v>
+        <v>4413.9346417391207</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3429.9203495032298</v>
+        <v>3447.7348607503491</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1966.6687988376693</v>
+        <v>1979.4453200085995</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20482,18 +20453,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="255" t="s">
+      <c r="C11" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="255"/>
-      <c r="E11" s="255"/>
-      <c r="F11" s="255"/>
-      <c r="G11" s="255"/>
-      <c r="H11" s="255"/>
-      <c r="I11" s="255"/>
-      <c r="J11" s="255"/>
-      <c r="K11" s="255"/>
-      <c r="L11" s="255"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20687,18 +20658,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="255" t="s">
+      <c r="C17" s="258" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="255"/>
-      <c r="E17" s="255"/>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
-      <c r="J17" s="255"/>
-      <c r="K17" s="255"/>
-      <c r="L17" s="255"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20832,18 +20803,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="255" t="s">
+      <c r="C22" s="258" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="255"/>
-      <c r="E22" s="255"/>
-      <c r="F22" s="255"/>
-      <c r="G22" s="255"/>
-      <c r="H22" s="255"/>
-      <c r="I22" s="255"/>
-      <c r="J22" s="255"/>
-      <c r="K22" s="255"/>
-      <c r="L22" s="255"/>
+      <c r="D22" s="258"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="258"/>
+      <c r="G22" s="258"/>
+      <c r="H22" s="258"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="258"/>
+      <c r="K22" s="258"/>
+      <c r="L22" s="258"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20927,18 +20898,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="255" t="s">
+      <c r="C27" s="258" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="255"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="255"/>
-      <c r="J27" s="255"/>
-      <c r="K27" s="255"/>
-      <c r="L27" s="255"/>
+      <c r="D27" s="258"/>
+      <c r="E27" s="258"/>
+      <c r="F27" s="258"/>
+      <c r="G27" s="258"/>
+      <c r="H27" s="258"/>
+      <c r="I27" s="258"/>
+      <c r="J27" s="258"/>
+      <c r="K27" s="258"/>
+      <c r="L27" s="258"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21239,10 +21210,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="249" t="s">
+      <c r="B39" s="252" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="249"/>
+      <c r="C39" s="252"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21260,7 +21231,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554644156115643</v>
+        <v>0.14406380061445392</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21286,7 +21257,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35758.129873581667</v>
+        <v>35990.433606489161</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21295,7 +21266,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>51993.805371030991</v>
+        <v>52277.941469296406</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21322,7 +21293,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50132.805371030991</v>
+        <v>50416.941469296406</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21340,14 +21311,14 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>211.53082435034173</v>
+        <v>212.7297108409131</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="249" t="s">
+      <c r="B52" s="252" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="249"/>
+      <c r="C52" s="252"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21364,7 +21335,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14772299999999999</v>
+        <v>0.14637</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21399,14 +21370,14 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>145.94426947147235</v>
+        <v>146.80755643991765</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="249" t="s">
+      <c r="B60" s="252" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="249"/>
+      <c r="C60" s="252"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21423,7 +21394,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554644156115643</v>
+        <v>0.14406380061445392</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21449,7 +21420,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39333.375976753385</v>
+        <v>39588.906400171989</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21458,7 +21429,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55569.051474202715</v>
+        <v>55876.414262979233</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21485,7 +21456,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53708.051474202715</v>
+        <v>54015.414262979233</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21503,14 +21474,14 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>226.61625094600302</v>
+        <v>227.91314035012334</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="249" t="s">
+      <c r="B73" s="252" t="s">
         <v>428</v>
       </c>
-      <c r="C73" s="249"/>
+      <c r="C73" s="252"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21527,7 +21498,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554644156115643</v>
+        <v>0.14406380061445392</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21553,7 +21524,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37248.051951647583</v>
+        <v>37490.035006759557</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21562,7 +21533,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53483.727449096914</v>
+        <v>53777.542869566809</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21589,7 +21560,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51622.727449096914</v>
+        <v>51916.542869566809</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21607,7 +21578,7 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>217.81741539703339</v>
+        <v>219.05714290956459</v>
       </c>
     </row>
   </sheetData>
@@ -21661,10 +21632,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21673,7 +21644,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>133.46926393304309</v>
+        <v>134.90700212028807</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21682,7 +21653,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>211.53082435034173</v>
+        <v>212.7297108409131</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21691,7 +21662,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>145.94426947147235</v>
+        <v>146.80755643991765</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21700,7 +21671,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>226.61625094600302</v>
+        <v>227.91314035012334</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21709,7 +21680,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>217.81741539703339</v>
+        <v>219.05714290956459</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21718,7 +21689,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>187.0756048195787</v>
+        <v>188.28291053216134</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21727,7 +21698,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21736,7 +21707,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.72419524861109741</v>
+        <v>-0.70137050463582085</v>
       </c>
     </row>
   </sheetData>
@@ -21832,37 +21803,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="255" t="s">
+      <c r="C4" s="258" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="255"/>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21975,18 +21946,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="255" t="s">
+      <c r="C9" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="255"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="255"/>
-      <c r="G9" s="255"/>
-      <c r="H9" s="255"/>
-      <c r="I9" s="255"/>
-      <c r="J9" s="255"/>
-      <c r="K9" s="255"/>
-      <c r="L9" s="255"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22107,18 +22078,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="255" t="s">
+      <c r="C14" s="258" t="s">
         <v>365</v>
       </c>
-      <c r="D14" s="255"/>
-      <c r="E14" s="255"/>
-      <c r="F14" s="255"/>
-      <c r="G14" s="255"/>
-      <c r="H14" s="255"/>
-      <c r="I14" s="255"/>
-      <c r="J14" s="255"/>
-      <c r="K14" s="255"/>
-      <c r="L14" s="255"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="258"/>
+      <c r="F14" s="258"/>
+      <c r="G14" s="258"/>
+      <c r="H14" s="258"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="258"/>
+      <c r="K14" s="258"/>
+      <c r="L14" s="258"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22208,10 +22179,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="249" t="s">
+      <c r="B20" s="252" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="249"/>
+      <c r="C20" s="252"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22246,7 +22217,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14772299999999999</v>
+        <v>0.14637</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22263,7 +22234,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.547833984482043</v>
+        <v>23.799952520376671</v>
       </c>
     </row>
   </sheetData>
@@ -22313,60 +22284,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="P3" s="260"/>
-      <c r="Q3" s="260"/>
-      <c r="R3" s="260"/>
-      <c r="S3" s="260"/>
-      <c r="T3" s="260"/>
-      <c r="U3" s="260"/>
-      <c r="V3" s="260"/>
-      <c r="W3" s="260"/>
-      <c r="X3" s="260"/>
-      <c r="Y3" s="260"/>
-      <c r="Z3" s="260"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="255" t="s">
+      <c r="C5" s="258" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="255"/>
-      <c r="J5" s="255"/>
-      <c r="K5" s="255"/>
-      <c r="L5" s="255"/>
-      <c r="P5" s="260"/>
-      <c r="Q5" s="260"/>
-      <c r="R5" s="260"/>
-      <c r="S5" s="260"/>
-      <c r="T5" s="260"/>
-      <c r="U5" s="260"/>
-      <c r="V5" s="260"/>
-      <c r="W5" s="260"/>
-      <c r="X5" s="260"/>
-      <c r="Y5" s="260"/>
-      <c r="Z5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22501,7 +22472,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>221288.77426449829</v>
+        <v>223830.86427120928</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22555,23 +22526,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4195.1479845541426</v>
+        <v>4200.584655285299</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>5712.9336869011422</v>
+        <v>5727.7505491613565</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>7779.8474406853584</v>
+        <v>7810.1333613499082</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10594.561309037275</v>
+        <v>10649.5879313393</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14427.626015383863</v>
+        <v>14521.355508291239</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22590,15 +22561,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>112174.94885721877</v>
+        <v>114200.69586316642</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="261" t="s">
+      <c r="B14" s="264" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="262"/>
+      <c r="C14" s="265"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22606,7 +22577,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22615,7 +22586,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>674.11482508273377</v>
+        <v>683.91677475151334</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22625,20 +22596,20 @@
       <c r="C17" s="156">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E17" s="263" t="s">
+      <c r="E17" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="263"/>
-      <c r="G17" s="263"/>
-      <c r="H17" s="263"/>
-      <c r="I17" s="263"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="261" t="s">
+      <c r="B19" s="264" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="262"/>
+      <c r="C19" s="265"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22654,7 +22625,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14554644156115643</v>
+        <v>0.14406380061445392</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22672,7 +22643,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>153971.82999999999</v>
+        <v>143121.23000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22699,15 +22670,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>155832.82999999999</v>
+        <v>144982.23000000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="261" t="s">
+      <c r="B28" s="264" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="262"/>
+      <c r="C28" s="265"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22715,7 +22686,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>42710.116436561781</v>
+        <v>42909.412005427104</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22724,7 +22695,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>112174.94885721877</v>
+        <v>114200.69586316642</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22733,7 +22704,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>154885.06529378056</v>
+        <v>157110.10786859354</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22760,7 +22731,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>153024.06529378056</v>
+        <v>155249.10786859354</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22778,7 +22749,7 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>674.11482508273377</v>
+        <v>683.91677475151334</v>
       </c>
     </row>
   </sheetData>
@@ -29573,7 +29544,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29647,7 +29618,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31016,7 +30987,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>48.868155619596536</v>
+        <v>45.424351585014406</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31057,7 +31028,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>12.723151906519066</v>
+        <v>11.826534440344403</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31122,7 +31093,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>71.052990309183201</v>
+        <v>66.045791416705129</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31187,7 +31158,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>160754.72999999998</v>
+        <v>149426.13</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31252,7 +31223,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>162615.72999999998</v>
+        <v>151287.13</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31293,7 +31264,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>13.334623206232061</v>
+        <v>12.405668716687167</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31334,7 +31305,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>39.720500732779676</v>
+        <v>36.95337811431363</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31481,7 +31452,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>55.586006224066381</v>
+        <v>51.668786307053942</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31522,7 +31493,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>52.787022459633747</v>
+        <v>49.109622600246183</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31563,7 +31534,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.7990139388122516E-2</v>
+        <v>1.9354044704229439E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31604,7 +31575,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.0463223694879774E-2</v>
+        <v>2.2014623546765217E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31645,7 +31616,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>4.3049433133320559E-3</v>
+        <v>4.6313184983108376E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31686,7 +31657,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>1.094835592084911E-3</v>
+        <v>1.177839511737338E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31727,7 +31698,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>5.0387319862998745E-3</v>
+        <v>5.420738661972976E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32274,7 +32245,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.1576642254943294E-2</v>
+        <v>-1.2454314382631738E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33633,15 +33604,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="249"/>
-      <c r="E4" s="249" t="s">
+      <c r="C4" s="252"/>
+      <c r="E4" s="252" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33649,7 +33620,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33665,7 +33636,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>160754.72999999998</v>
+        <v>149426.13</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33685,7 +33656,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>162615.72999999998</v>
+        <v>151287.13</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33705,7 +33676,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>48.868155619596536</v>
+        <v>45.424351585014406</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33725,7 +33696,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.723151906519066</v>
+        <v>11.826534440344403</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33745,7 +33716,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>71.052990309183201</v>
+        <v>66.045791416705129</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33765,7 +33736,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.334623206232061</v>
+        <v>12.405668716687167</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33774,18 +33745,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>39.720500732779676</v>
+        <v>36.95337811431363</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="249"/>
-      <c r="E15" s="249" t="s">
+      <c r="C15" s="252"/>
+      <c r="E15" s="252" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="249"/>
+      <c r="F15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33836,14 +33807,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="249" t="s">
+      <c r="B21" s="252" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="249"/>
-      <c r="E21" s="249" t="s">
+      <c r="C21" s="252"/>
+      <c r="E21" s="252" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="249"/>
+      <c r="F21" s="252"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33912,14 +33883,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="249" t="s">
+      <c r="B29" s="252" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="249"/>
-      <c r="E29" s="249" t="s">
+      <c r="C29" s="252"/>
+      <c r="E29" s="252" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="249"/>
+      <c r="F29" s="252"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33995,14 +33966,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="252" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="249"/>
-      <c r="E37" s="249" t="s">
+      <c r="C37" s="252"/>
+      <c r="E37" s="252" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="249"/>
+      <c r="F37" s="252"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34010,7 +33981,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.0463223694879774E-2</v>
+        <v>2.2014623546765217E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34026,7 +33997,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.7990139388122516E-2</v>
+        <v>1.9354044704229439E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34042,7 +34013,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.3049433133320559E-3</v>
+        <v>4.6313184983108376E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34058,7 +34029,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.094835592084911E-3</v>
+        <v>1.177839511737338E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34067,18 +34038,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.0387319862998745E-3</v>
+        <v>5.420738661972976E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="249" t="s">
+      <c r="B45" s="252" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="249"/>
-      <c r="E45" s="249" t="s">
+      <c r="C45" s="252"/>
+      <c r="E45" s="252" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="249"/>
+      <c r="F45" s="252"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34111,18 +34082,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1576642254943294E-2</v>
+        <v>-1.2454314382631738E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="249" t="s">
+      <c r="B51" s="252" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="249"/>
-      <c r="E51" s="249" t="s">
+      <c r="C51" s="252"/>
+      <c r="E51" s="252" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="249"/>
+      <c r="F51" s="252"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34291,7 +34262,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>678.29</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34320,7 +34291,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>160754.72999999998</v>
+        <v>149426.13</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34349,7 +34320,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>162615.72999999998</v>
+        <v>151287.13</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34378,7 +34349,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>48.868155619596536</v>
+        <v>45.424351585014406</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34407,7 +34378,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.723151906519066</v>
+        <v>11.826534440344403</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34436,7 +34407,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>71.052990309183201</v>
+        <v>66.045791416705129</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34465,7 +34436,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.334623206232061</v>
+        <v>12.405668716687167</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34494,7 +34465,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>39.720500732779676</v>
+        <v>36.95337811431363</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35267,7 +35238,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.0463223694879774E-2</v>
+        <v>2.2014623546765217E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35296,7 +35267,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.7990139388122516E-2</v>
+        <v>1.9354044704229439E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35325,7 +35296,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.3049433133320559E-3</v>
+        <v>4.6313184983108376E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35354,7 +35325,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.094835592084911E-3</v>
+        <v>1.177839511737338E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35383,7 +35354,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.0387319862998745E-3</v>
+        <v>5.420738661972976E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35619,7 +35590,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.1576642254943294E-2</v>
+        <v>-1.2454314382631738E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36082,14 +36053,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="250" t="s">
+      <c r="C3" s="253" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="F3" s="252" t="s">
+      <c r="D3" s="254"/>
+      <c r="F3" s="255" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="251"/>
+      <c r="G3" s="254"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36156,19 +36127,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="253">
+      <c r="C7" s="256">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="F7" s="253">
+      <c r="D7" s="257"/>
+      <c r="F7" s="256">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="254"/>
+      <c r="G7" s="257"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36195,19 +36166,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="256">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="F9" s="253">
+      <c r="D9" s="257"/>
+      <c r="F9" s="256">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="254"/>
+      <c r="G9" s="257"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36234,19 +36205,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="253">
+      <c r="C11" s="256">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="F11" s="253">
+      <c r="D11" s="257"/>
+      <c r="F11" s="256">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="254"/>
+      <c r="G11" s="257"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36273,19 +36244,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="253">
+      <c r="C13" s="256">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="F13" s="253">
+      <c r="D13" s="257"/>
+      <c r="F13" s="256">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="254"/>
+      <c r="G13" s="257"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36312,19 +36283,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="253">
+      <c r="C15" s="256">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="F15" s="253">
+      <c r="D15" s="257"/>
+      <c r="F15" s="256">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="254"/>
+      <c r="G15" s="257"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36351,19 +36322,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="256">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="F17" s="253">
+      <c r="D17" s="257"/>
+      <c r="F17" s="256">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="254"/>
+      <c r="G17" s="257"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36390,22 +36361,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="256">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="F19" s="253">
+      <c r="D19" s="257"/>
+      <c r="F19" s="256">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="254"/>
+      <c r="G19" s="257"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36432,22 +36403,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="253">
+      <c r="C21" s="256">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="F21" s="253">
+      <c r="D21" s="257"/>
+      <c r="F21" s="256">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="254"/>
+      <c r="G21" s="257"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36496,22 +36467,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="256">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="F25" s="253">
+      <c r="D25" s="257"/>
+      <c r="F25" s="256">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="254"/>
+      <c r="G25" s="257"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36539,22 +36510,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="253">
+      <c r="C27" s="256">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="F27" s="253">
+      <c r="D27" s="257"/>
+      <c r="F27" s="256">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="254"/>
+      <c r="G27" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C6605B-D3A9-EE4F-96F1-7D28F175514F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635D4911-B368-C542-91F0-7A0457F3C9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -12686,11 +12686,11 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>217.67</v>
-    <v>2.1520000000000001</v>
+    <v>2.1669999999999998</v>
     <v>-11.65</v>
     <v>-1.8142000000000002E-2</v>
-    <v>-0.4</v>
-    <v>-6.3439999999999992E-4</v>
+    <v>0.51</v>
+    <v>8.0889999999999998E-4</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12701,21 +12701,20 @@
     <v>655.6</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46318.953264421092</v>
+    <v>46318.999900555471</v>
     <v>0</v>
     <v>621.00009999999997</v>
-    <v>144407997041</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>633</v>
-    <v>45.346299999999999</v>
+    <v>46.184100000000001</v>
     <v>642.14</v>
     <v>630.49</v>
-    <v>630.09</v>
+    <v>631</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>5569310</v>
+    <v>5572336</v>
     <v>4901617</v>
     <v>2017</v>
   </rv>
@@ -12740,17 +12739,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12798,7 +12797,6 @@
     <k n="Last trade time"/>
     <k n="LearnMoreOnLink" t="r"/>
     <k n="Low"/>
-    <k n="Market cap"/>
     <k n="Name" t="s"/>
     <k n="Official name" t="s"/>
     <k n="Open"/>
@@ -12850,7 +12848,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="44">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12880,7 +12878,6 @@
       <v t="s">52 week low</v>
       <v t="s">Volume</v>
       <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
       <v t="s">Beta</v>
       <v t="s">P/E</v>
       <v t="s">Shares outstanding</v>
@@ -12955,14 +12952,13 @@
       <v>4</v>
       <v>4</v>
       <v>5</v>
-      <v>6</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
       <v>4</v>
+      <v>6</v>
       <v>7</v>
       <v>8</v>
-      <v>9</v>
       <v>4</v>
       <v>1</v>
       <v>1</v>
@@ -12972,9 +12968,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -12999,7 +12995,7 @@
       <v>1</v>
       <v>1</v>
       <v>1</v>
-      <v>9</v>
+      <v>8</v>
     </spb>
     <spb s="7">
       <v>from previous close</v>
@@ -13039,7 +13035,6 @@
     <k n="Volume" t="i"/>
     <k n="Employees" t="i"/>
     <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
     <k n="52 week low" t="i"/>
     <k n="52 week high" t="i"/>
     <k n="Previous close" t="i"/>
@@ -13130,9 +13125,6 @@
       <rpv i="0">#,##0</rpv>
     </rSty>
     <rSty dxfid="3"/>
-    <rSty dxfid="1">
-      <rpv i="0">_([$$-en-US]* #,##0_);_([$$-en-US]* (#,##0);_([$$-en-US]* "-"_);_(@_)</rpv>
-    </rSty>
     <rSty dxfid="2"/>
     <rSty dxfid="6">
       <rpv i="0">0</rpv>
@@ -13591,7 +13583,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>134.90700212028807</v>
+        <v>133.9327675614613</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>435</v>
@@ -13618,7 +13610,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>212.7297108409131</v>
+        <v>211.91923684881951</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>436</v>
@@ -13645,7 +13637,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>146.80755643991765</v>
+        <v>146.15299051680003</v>
       </c>
       <c r="K5" s="244" t="s">
         <v>437</v>
@@ -13657,7 +13649,7 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>630.09</v>
+        <v>631</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
@@ -13672,7 +13664,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>227.91314035012334</v>
+        <v>227.03640893522405</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>438</v>
@@ -13699,7 +13691,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>219.05714290956459</v>
+        <v>218.21905728061432</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13708,7 +13700,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.4</v>
+        <v>0.51</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
@@ -13723,7 +13715,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>188.28291053216134</v>
+        <v>187.45209222858384</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13747,7 +13739,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.70137050463582085</v>
+        <v>-0.70268823894338706</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13756,7 +13748,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.3439999999999992E-4</v>
+        <v>8.0889999999999998E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
@@ -13786,7 +13778,7 @@
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.799952520376671</v>
+        <v>23.608461870560067</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13811,7 +13803,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1520000000000001</v>
+        <v>2.1669999999999998</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13848,7 +13840,7 @@
       </c>
       <c r="I14" s="247">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>683.91677475151334</v>
+        <v>677.27257217592853</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -13890,7 +13882,7 @@
       </c>
       <c r="I17" s="242">
         <f ca="1">DCF!C15</f>
-        <v>0.14406380061445392</v>
+        <v>0.14506491605983957</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -13912,7 +13904,7 @@
       </c>
       <c r="I18" s="243">
         <f ca="1">Multiples!C54</f>
-        <v>0.14637</v>
+        <v>0.147395</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -13984,7 +13976,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13999,7 +13991,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19629,7 +19621,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19638,7 +19630,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1520000000000001</v>
+        <v>2.1669999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19708,7 +19700,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14637</v>
+        <v>0.147395</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19717,7 +19709,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14406380061445392</v>
+        <v>0.14506491605983957</v>
       </c>
     </row>
   </sheetData>
@@ -19969,7 +19961,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30510.991656540005</v>
+        <v>30276.147196352598</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20023,23 +20015,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3786.8196102786287</v>
+        <v>3783.5088428735944</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4639.0187500391494</v>
+        <v>4630.910627821946</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4413.9346417391207</v>
+        <v>4402.3676226342159</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3447.7348607503491</v>
+        <v>3435.6934237919982</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1979.4453200085995</v>
+        <v>1970.8074200263175</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20058,7 +20050,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15567.006319692429</v>
+        <v>15379.777974918255</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20081,7 +20073,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406380061445392</v>
+        <v>0.14506491605983957</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20096,7 +20088,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18266.953182815847</v>
+        <v>18223.28793714807</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20105,7 +20097,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15567.006319692429</v>
+        <v>15379.777974918255</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20114,7 +20106,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33833.959502508274</v>
+        <v>33603.065912066326</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20141,7 +20133,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31972.959502508274</v>
+        <v>31742.065912066326</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20159,7 +20151,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>134.90700212028807</v>
+        <v>133.9327675614613</v>
       </c>
     </row>
   </sheetData>
@@ -20429,23 +20421,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3786.8196102786287</v>
+        <v>3783.5088428735944</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4639.0187500391494</v>
+        <v>4630.910627821946</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4413.9346417391207</v>
+        <v>4402.3676226342159</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3447.7348607503491</v>
+        <v>3435.6934237919982</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1979.4453200085995</v>
+        <v>1970.8074200263175</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21231,7 +21223,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406380061445392</v>
+        <v>0.14506491605983957</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21257,7 +21249,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35990.433606489161</v>
+        <v>35833.378616048474</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21266,7 +21258,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>52277.941469296406</v>
+        <v>52085.859133170226</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21293,7 +21285,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50416.941469296406</v>
+        <v>50224.859133170226</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21311,7 +21303,7 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>212.7297108409131</v>
+        <v>211.91923684881951</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21335,7 +21327,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14637</v>
+        <v>0.147395</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21370,7 +21362,7 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>146.80755643991765</v>
+        <v>146.15299051680003</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21394,7 +21386,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406380061445392</v>
+        <v>0.14506491605983957</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21420,7 +21412,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39588.906400171989</v>
+        <v>39416.148400526348</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21429,7 +21421,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55876.414262979233</v>
+        <v>55668.6289176481</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21456,7 +21448,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>54015.414262979233</v>
+        <v>53807.6289176481</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21474,7 +21466,7 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>227.91314035012334</v>
+        <v>227.03640893522405</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21498,7 +21490,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406380061445392</v>
+        <v>0.14506491605983957</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21524,7 +21516,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37490.035006759557</v>
+        <v>37326.436058383842</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21533,7 +21525,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53777.542869566809</v>
+        <v>53578.916575505595</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21560,7 +21552,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51916.542869566809</v>
+        <v>51717.916575505595</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21578,7 +21570,7 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>219.05714290956459</v>
+        <v>218.21905728061432</v>
       </c>
     </row>
   </sheetData>
@@ -21644,7 +21636,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>134.90700212028807</v>
+        <v>133.9327675614613</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21653,7 +21645,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>212.7297108409131</v>
+        <v>211.91923684881951</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21662,7 +21654,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>146.80755643991765</v>
+        <v>146.15299051680003</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21671,7 +21663,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>227.91314035012334</v>
+        <v>227.03640893522405</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21680,7 +21672,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>219.05714290956459</v>
+        <v>218.21905728061432</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21689,7 +21681,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>188.28291053216134</v>
+        <v>187.45209222858384</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21707,7 +21699,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.70137050463582085</v>
+        <v>-0.70268823894338706</v>
       </c>
     </row>
   </sheetData>
@@ -22217,7 +22209,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14637</v>
+        <v>0.147395</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22234,7 +22226,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.799952520376671</v>
+        <v>23.608461870560067</v>
       </c>
     </row>
   </sheetData>
@@ -22472,7 +22464,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>223830.86427120928</v>
+        <v>222108.02815087669</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22526,23 +22518,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4200.584655285299</v>
+        <v>4196.9121384532173</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>5727.7505491613565</v>
+        <v>5717.7395308868854</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>7810.1333613499082</v>
+        <v>7789.6663700745248</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10649.5879313393</v>
+        <v>10612.393556804442</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14521.355508291239</v>
+        <v>14457.987242838353</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22561,7 +22553,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>114200.69586316642</v>
+        <v>112827.17504487834</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22586,7 +22578,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>683.91677475151334</v>
+        <v>677.27257217592853</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22625,7 +22617,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14406380061445392</v>
+        <v>0.14506491605983957</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22686,7 +22678,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>42909.412005427104</v>
+        <v>42774.698839057419</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22695,7 +22687,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>114200.69586316642</v>
+        <v>112827.17504487834</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22704,7 +22696,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>157110.10786859354</v>
+        <v>155601.87388393577</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22731,7 +22723,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>155249.10786859354</v>
+        <v>153740.87388393577</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22749,7 +22741,7 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>683.91677475151334</v>
+        <v>677.27257217592853</v>
       </c>
     </row>
   </sheetData>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635D4911-B368-C542-91F0-7A0457F3C9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7244815B-49E3-A041-BC91-8783C0FAFB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="445">
   <si>
     <t>Ticker</t>
   </si>
@@ -1493,6 +1493,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -12687,10 +12699,10 @@
     <v>1145</v>
     <v>217.67</v>
     <v>2.1669999999999998</v>
-    <v>-11.65</v>
-    <v>-1.8142000000000002E-2</v>
-    <v>0.51</v>
-    <v>8.0889999999999998E-4</v>
+    <v>13.72</v>
+    <v>2.1760999999999999E-2</v>
+    <v>2.92</v>
+    <v>4.5329999999999997E-3</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12698,24 +12710,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>655.6</v>
+    <v>665.55</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46318.999900555471</v>
+    <v>46321.962421435157</v>
     <v>0</v>
-    <v>621.00009999999997</v>
+    <v>621.65</v>
+    <v>147550438189</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>633</v>
-    <v>46.184100000000001</v>
-    <v>642.14</v>
+    <v>632.25</v>
+    <v>46.332999999999998</v>
     <v>630.49</v>
-    <v>631</v>
+    <v>644.21</v>
+    <v>647.13</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>5572336</v>
-    <v>4901617</v>
+    <v>4275042</v>
+    <v>4845451</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -12739,17 +12752,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12797,6 +12810,7 @@
     <k n="Last trade time"/>
     <k n="LearnMoreOnLink" t="r"/>
     <k n="Low"/>
+    <k n="Market cap"/>
     <k n="Name" t="s"/>
     <k n="Official name" t="s"/>
     <k n="Open"/>
@@ -12848,7 +12862,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="44">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12878,6 +12892,7 @@
       <v t="s">52 week low</v>
       <v t="s">Volume</v>
       <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
       <v t="s">Beta</v>
       <v t="s">P/E</v>
       <v t="s">Shares outstanding</v>
@@ -12952,13 +12967,14 @@
       <v>4</v>
       <v>4</v>
       <v>5</v>
+      <v>6</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
       <v>4</v>
-      <v>6</v>
       <v>7</v>
       <v>8</v>
+      <v>9</v>
       <v>4</v>
       <v>1</v>
       <v>1</v>
@@ -12968,9 +12984,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -12995,7 +13011,7 @@
       <v>1</v>
       <v>1</v>
       <v>1</v>
-      <v>8</v>
+      <v>9</v>
     </spb>
     <spb s="7">
       <v>from previous close</v>
@@ -13035,6 +13051,7 @@
     <k n="Volume" t="i"/>
     <k n="Employees" t="i"/>
     <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
     <k n="52 week low" t="i"/>
     <k n="52 week high" t="i"/>
     <k n="Previous close" t="i"/>
@@ -13125,6 +13142,9 @@
       <rpv i="0">#,##0</rpv>
     </rSty>
     <rSty dxfid="3"/>
+    <rSty dxfid="1">
+      <rpv i="0">_([$$-en-US]* #,##0_);_([$$-en-US]* (#,##0);_([$$-en-US]* "-"_);_(@_)</rpv>
+    </rSty>
     <rSty dxfid="2"/>
     <rSty dxfid="6">
       <rpv i="0">0</rpv>
@@ -13575,7 +13595,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>149426.13</v>
+        <v>152677.77000000002</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13583,7 +13603,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>133.9327675614613</v>
+        <v>133.90480950793841</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>435</v>
@@ -13602,7 +13622,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>151287.13</v>
+        <v>154538.77000000002</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13610,7 +13630,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>211.91923684881951</v>
+        <v>211.89585997034459</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>436</v>
@@ -13622,7 +13642,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13637,7 +13657,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>146.15299051680003</v>
+        <v>146.16572899252222</v>
       </c>
       <c r="K5" s="244" t="s">
         <v>437</v>
@@ -13649,14 +13669,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>631</v>
+        <v>647.13</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>45.424351585014406</v>
+        <v>46.412824207492797</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13664,7 +13684,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>227.03640893522405</v>
+        <v>227.01112128904242</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>438</v>
@@ -13676,14 +13696,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-11.65</v>
+        <v>13.72</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>11.826534440344403</v>
+        <v>12.08388991389914</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13691,7 +13711,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>218.21905728061432</v>
+        <v>218.19488412269172</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13700,14 +13720,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.51</v>
+        <v>2.92</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.9354044704229439E-2</v>
+        <v>1.8941853814081772E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13715,7 +13735,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>187.45209222858384</v>
+        <v>187.43448077650788</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13724,14 +13744,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.8142000000000002E-2</v>
+        <v>2.1760999999999999E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>2.2014623546765217E-2</v>
+        <v>2.1545769236739572E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13739,7 +13759,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.70268823894338706</v>
+        <v>-0.70904754540210824</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13748,14 +13768,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>8.0889999999999998E-4</v>
+        <v>4.5329999999999997E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>1.177839511737338E-3</v>
+        <v>1.1527545889620996E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13771,14 +13791,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>4.6313184983108376E-3</v>
+        <v>4.532683441734838E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.608461870560067</v>
+        <v>23.612168792934252</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13826,7 +13846,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4901617</v>
+        <v>4845451</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13840,7 +13860,7 @@
       </c>
       <c r="I14" s="247">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>677.27257217592853</v>
+        <v>677.08203934263577</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -13849,7 +13869,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-1.2454314382631738E-2</v>
+        <v>-1.2189069829877655E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13882,7 +13902,7 @@
       </c>
       <c r="I17" s="242">
         <f ca="1">DCF!C15</f>
-        <v>0.14506491605983957</v>
+        <v>0.14509386484731418</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -13904,7 +13924,7 @@
       </c>
       <c r="I18" s="243">
         <f ca="1">Multiples!C54</f>
-        <v>0.147395</v>
+        <v>0.14737499999999998</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -13976,7 +13996,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13991,7 +14011,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19594,7 +19614,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19603,7 +19623,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>149426.13</v>
+        <v>152677.77000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19621,7 +19641,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19673,7 +19693,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.3302004501829614E-2</v>
+        <v>2.2817055790805549E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19682,7 +19702,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97669799549817038</v>
+        <v>0.97718294420919449</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19700,7 +19720,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.147395</v>
+        <v>0.14737499999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19709,7 +19729,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14506491605983957</v>
+        <v>0.14509386484731418</v>
       </c>
     </row>
   </sheetData>
@@ -19961,7 +19981,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30276.147196352598</v>
+        <v>30269.4100781052</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20015,23 +20035,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3783.5088428735944</v>
+        <v>3783.4131930786189</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4630.910627821946</v>
+        <v>4630.676485351818</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4402.3676226342159</v>
+        <v>4402.0337461195213</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3435.6934237919982</v>
+        <v>3435.3460098715427</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1970.8074200263175</v>
+        <v>1970.5583155540774</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20050,7 +20070,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15379.777974918255</v>
+        <v>15374.412103405823</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20073,7 +20093,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14506491605983957</v>
+        <v>0.14509386484731418</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20088,7 +20108,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18223.28793714807</v>
+        <v>18222.027749975579</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20097,7 +20117,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15379.777974918255</v>
+        <v>15374.412103405823</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20106,7 +20126,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33603.065912066326</v>
+        <v>33596.439853381402</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20133,7 +20153,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31742.065912066326</v>
+        <v>31735.439853381402</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20151,7 +20171,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>133.9327675614613</v>
+        <v>133.90480950793841</v>
       </c>
     </row>
   </sheetData>
@@ -20421,23 +20441,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3783.5088428735944</v>
+        <v>3783.4131930786189</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4630.910627821946</v>
+        <v>4630.676485351818</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4402.3676226342159</v>
+        <v>4402.0337461195213</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3435.6934237919982</v>
+        <v>3435.3460098715427</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1970.8074200263175</v>
+        <v>1970.5583155540774</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21223,7 +21243,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14506491605983957</v>
+        <v>0.14509386484731418</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21249,7 +21269,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35833.378616048474</v>
+        <v>35828.849378550163</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21258,7 +21278,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>52085.859133170226</v>
+        <v>52080.318812971665</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21285,7 +21305,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50224.859133170226</v>
+        <v>50219.318812971665</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21303,7 +21323,7 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>211.91923684881951</v>
+        <v>211.89585997034459</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21327,7 +21347,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.147395</v>
+        <v>0.14737499999999998</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21362,7 +21382,7 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>146.15299051680003</v>
+        <v>146.16572899252222</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21386,7 +21406,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14506491605983957</v>
+        <v>0.14509386484731418</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21412,7 +21432,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39416.148400526348</v>
+        <v>39411.16631108155</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21421,7 +21441,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55668.6289176481</v>
+        <v>55662.635745503052</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21448,7 +21468,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53807.6289176481</v>
+        <v>53801.635745503052</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21466,7 +21486,7 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>227.03640893522405</v>
+        <v>227.01112128904242</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21490,7 +21510,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14506491605983957</v>
+        <v>0.14509386484731418</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21516,7 +21536,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37326.436058383842</v>
+        <v>37321.718102656436</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21525,7 +21545,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53578.916575505595</v>
+        <v>53573.187537077938</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21552,7 +21572,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51717.916575505595</v>
+        <v>51712.187537077938</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21570,7 +21590,7 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>218.21905728061432</v>
+        <v>218.19488412269172</v>
       </c>
     </row>
   </sheetData>
@@ -21636,7 +21656,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>133.9327675614613</v>
+        <v>133.90480950793841</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21645,7 +21665,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>211.91923684881951</v>
+        <v>211.89585997034459</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21654,7 +21674,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>146.15299051680003</v>
+        <v>146.16572899252222</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21663,7 +21683,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>227.03640893522405</v>
+        <v>227.01112128904242</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21672,7 +21692,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>218.21905728061432</v>
+        <v>218.19488412269172</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21681,7 +21701,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>187.45209222858384</v>
+        <v>187.43448077650788</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21690,7 +21710,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21699,7 +21719,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.70268823894338706</v>
+        <v>-0.70904754540210824</v>
       </c>
     </row>
   </sheetData>
@@ -22209,7 +22229,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.147395</v>
+        <v>0.14737499999999998</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22226,7 +22246,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.608461870560067</v>
+        <v>23.612168792934252</v>
       </c>
     </row>
   </sheetData>
@@ -22464,7 +22484,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>222108.02815087669</v>
+        <v>222058.60415912358</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22518,23 +22538,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4196.9121384532173</v>
+        <v>4196.8060375288514</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>5717.7395308868854</v>
+        <v>5717.4504374957787</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>7789.6663700745248</v>
+        <v>7789.0756000886422</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10612.393556804442</v>
+        <v>10611.320442065666</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14457.987242838353</v>
+        <v>14456.159794227602</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22553,7 +22573,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>112827.17504487834</v>
+        <v>112787.81061937175</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22569,7 +22589,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22578,7 +22598,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>677.27257217592853</v>
+        <v>677.08203934263577</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22617,7 +22637,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14506491605983957</v>
+        <v>0.14509386484731418</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22635,7 +22655,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>143121.23000000001</v>
+        <v>146235.67000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22662,7 +22682,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>144982.23000000001</v>
+        <v>148096.67000000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22678,7 +22698,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>42774.698839057419</v>
+        <v>42770.812311406538</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22687,7 +22707,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>112827.17504487834</v>
+        <v>112787.81061937175</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22696,7 +22716,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>155601.87388393577</v>
+        <v>155558.62293077831</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22723,7 +22743,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>153740.87388393577</v>
+        <v>153697.62293077831</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22741,7 +22761,7 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>677.27257217592853</v>
+        <v>677.08203934263577</v>
       </c>
     </row>
   </sheetData>
@@ -29536,7 +29556,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29610,7 +29630,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30979,7 +30999,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>45.424351585014406</v>
+        <v>46.412824207492797</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31020,7 +31040,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>11.826534440344403</v>
+        <v>12.08388991389914</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31085,7 +31105,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>66.045791416705129</v>
+        <v>67.483004153207204</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31150,7 +31170,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>149426.13</v>
+        <v>152677.77000000002</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31215,7 +31235,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>151287.13</v>
+        <v>154538.77000000002</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31256,7 +31276,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>12.405668716687167</v>
+        <v>12.672305863058632</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31297,7 +31317,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>36.95337811431363</v>
+        <v>37.747623351245728</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31444,7 +31464,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>51.668786307053942</v>
+        <v>52.793143153526977</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31485,7 +31505,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>49.109622600246183</v>
+        <v>50.165144066162455</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31526,7 +31546,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.9354044704229439E-2</v>
+        <v>1.8941853814081772E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31567,7 +31587,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.2014623546765217E-2</v>
+        <v>2.1545769236739572E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31608,7 +31628,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>4.6313184983108376E-3</v>
+        <v>4.532683441734838E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31649,7 +31669,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>1.177839511737338E-3</v>
+        <v>1.1527545889620996E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31690,7 +31710,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>5.420738661972976E-3</v>
+        <v>5.3052910060187534E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32237,7 +32257,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.2454314382631738E-2</v>
+        <v>-1.2189069829877655E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33579,7 +33599,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -33612,7 +33632,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33628,7 +33648,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>149426.13</v>
+        <v>152677.77000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33648,7 +33668,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>151287.13</v>
+        <v>154538.77000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33668,7 +33688,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>45.424351585014406</v>
+        <v>46.412824207492797</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33688,7 +33708,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.826534440344403</v>
+        <v>12.08388991389914</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33708,7 +33728,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>66.045791416705129</v>
+        <v>67.483004153207204</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33728,7 +33748,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.405668716687167</v>
+        <v>12.672305863058632</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33737,7 +33757,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>36.95337811431363</v>
+        <v>37.747623351245728</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33973,7 +33993,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.2014623546765217E-2</v>
+        <v>2.1545769236739572E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -33989,7 +34009,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.9354044704229439E-2</v>
+        <v>1.8941853814081772E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34005,7 +34025,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.6313184983108376E-3</v>
+        <v>4.532683441734838E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34021,7 +34041,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.177839511737338E-3</v>
+        <v>1.1527545889620996E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34030,7 +34050,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.420738661972976E-3</v>
+        <v>5.3052910060187534E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34074,7 +34094,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-1.2454314382631738E-2</v>
+        <v>-1.2189069829877655E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34128,8 +34148,51 @@
         <v>2.0615942028985508</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="252" t="s">
+        <v>441</v>
+      </c>
+      <c r="C57" s="252"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58" s="170">
+        <f ca="1">Statement!AC157</f>
+        <v>52.793143153526977</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C59" s="170">
+        <f ca="1">Statement!AC158</f>
+        <v>50.165144066162455</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="C60" s="171">
+        <f>Statement!AC164</f>
+        <v>0.25261177056215006</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="C61" s="171">
+        <f>Statement!AC165</f>
+        <v>0.23714637146371464</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -34155,7 +34218,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="B1:I93"/>
+  <dimension ref="B1:I99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -34254,7 +34317,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>630.49</v>
+        <v>644.21</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34283,7 +34346,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>149426.13</v>
+        <v>152677.77000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34312,7 +34375,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>151287.13</v>
+        <v>154538.77000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34341,7 +34404,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>45.424351585014406</v>
+        <v>46.412824207492797</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34370,7 +34433,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.826534440344403</v>
+        <v>12.08388991389914</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34399,7 +34462,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>66.045791416705129</v>
+        <v>67.483004153207204</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34428,7 +34491,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.405668716687167</v>
+        <v>12.672305863058632</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34457,7 +34520,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>36.95337811431363</v>
+        <v>37.747623351245728</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35230,7 +35293,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.2014623546765217E-2</v>
+        <v>2.1545769236739572E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35259,7 +35322,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.9354044704229439E-2</v>
+        <v>1.8941853814081772E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35288,7 +35351,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.6313184983108376E-3</v>
+        <v>4.532683441734838E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35317,7 +35380,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.177839511737338E-3</v>
+        <v>1.1527545889620996E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35346,7 +35409,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.420738661972976E-3</v>
+        <v>5.3052910060187534E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35582,7 +35645,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.2454314382631738E-2</v>
+        <v>-1.2189069829877655E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35919,107 +35982,234 @@
       </c>
       <c r="I85" s="193"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C88" s="170">
+        <f>Statement!M157</f>
+        <v>13.011644562334217</v>
+      </c>
+      <c r="D88" s="170">
+        <f>Statement!N157</f>
+        <v>25.062798434442271</v>
+      </c>
+      <c r="E88" s="170">
+        <f>Statement!O157</f>
+        <v>40.961843575418989</v>
+      </c>
+      <c r="F88" s="170">
+        <f>Statement!P157</f>
+        <v>49.893074433656956</v>
+      </c>
+      <c r="G88" s="170">
+        <f>Statement!Q157</f>
+        <v>67.212282157676341</v>
+      </c>
+      <c r="I88" s="170">
+        <f ca="1">Statement!AC157</f>
+        <v>52.793143153526977</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" s="170">
+        <f>Statement!M158</f>
+        <v>14.659365949397982</v>
+      </c>
+      <c r="D89" s="170">
+        <f>Statement!N158</f>
+        <v>17.180029498525073</v>
+      </c>
+      <c r="E89" s="170">
+        <f>Statement!O158</f>
+        <v>35.737599041631057</v>
+      </c>
+      <c r="F89" s="170">
+        <f>Statement!P158</f>
+        <v>40.813593878239608</v>
+      </c>
+      <c r="G89" s="170">
+        <f>Statement!Q158</f>
+        <v>63.70151446907547</v>
+      </c>
+      <c r="I89" s="170">
+        <f ca="1">Statement!AC158</f>
+        <v>50.165144066162455</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="C90" s="171">
+        <f>Statement!M164</f>
+        <v>0.11551912298693807</v>
+      </c>
+      <c r="D90" s="171">
+        <f>Statement!N164</f>
+        <v>0.13773022751895991</v>
+      </c>
+      <c r="E90" s="171">
+        <f>Statement!O164</f>
+        <v>0.1123904232821475</v>
+      </c>
+      <c r="F90" s="171">
+        <f>Statement!P164</f>
+        <v>9.4100951040925501E-2</v>
+      </c>
+      <c r="G90" s="171">
+        <f>Statement!Q164</f>
+        <v>0.25261177056215006</v>
+      </c>
+      <c r="I90" s="171">
+        <f>Statement!AC164</f>
+        <v>0.25261177056215006</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="C91" s="171">
+        <f>Statement!M165</f>
+        <v>9.6989966555183951E-2</v>
+      </c>
+      <c r="D91" s="171">
+        <f>Statement!N165</f>
+        <v>6.9203683640303354E-2</v>
+      </c>
+      <c r="E91" s="171">
+        <f>Statement!O165</f>
+        <v>8.1972217981987477E-2</v>
+      </c>
+      <c r="F91" s="171">
+        <f>Statement!P165</f>
+        <v>6.7934483895789821E-2</v>
+      </c>
+      <c r="G91" s="171">
+        <f>Statement!Q165</f>
+        <v>0.23714637146371464</v>
+      </c>
+      <c r="I91" s="171">
+        <f>Statement!AC165</f>
+        <v>0.23714637146371464</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C94" s="171">
+        <f>Statement!M195</f>
+        <v>-6.0092449922958396E-2</v>
+      </c>
+      <c r="D94" s="171">
+        <f>Statement!N195</f>
+        <v>-4.5901639344262293E-2</v>
+      </c>
+      <c r="E94" s="171">
+        <f>Statement!O195</f>
+        <v>5.1546391752577319E-3</v>
+      </c>
+      <c r="F94" s="171">
+        <f>Statement!P195</f>
+        <v>2.564102564102564E-2</v>
+      </c>
+      <c r="G94" s="171">
+        <f>Statement!Q195</f>
+        <v>5.6666666666666664E-2</v>
+      </c>
+      <c r="I94" s="193"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
         <f>Statement!B190</f>
         <v>Datacenter</v>
       </c>
-      <c r="C89" s="171">
+      <c r="C98" s="171">
         <f>Statement!M190</f>
         <v>0</v>
       </c>
-      <c r="D89" s="171">
+      <c r="D98" s="171">
         <f>Statement!N190</f>
         <v>0</v>
       </c>
-      <c r="E89" s="171">
+      <c r="E98" s="171">
         <f>Statement!O190</f>
         <v>0</v>
       </c>
-      <c r="F89" s="171">
+      <c r="F98" s="171">
         <f>Statement!P190</f>
         <v>1</v>
       </c>
-      <c r="G89" s="171">
+      <c r="G98" s="171">
         <f>Statement!Q190</f>
         <v>0.4377575044143614</v>
       </c>
-      <c r="I89" s="193"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
+      <c r="I98" s="193"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
         <f>Statement!B191</f>
         <v>Edge &amp; IoT</v>
       </c>
-      <c r="C90" s="171">
+      <c r="C99" s="171">
         <f>Statement!M191</f>
         <v>0</v>
       </c>
-      <c r="D90" s="171">
+      <c r="D99" s="171">
         <f>Statement!N191</f>
         <v>0</v>
       </c>
-      <c r="E90" s="171">
+      <c r="E99" s="171">
         <f>Statement!O191</f>
         <v>0</v>
       </c>
-      <c r="F90" s="171">
+      <c r="F99" s="171">
         <f>Statement!P191</f>
         <v>1</v>
       </c>
-      <c r="G90" s="171">
+      <c r="G99" s="171">
         <f>Statement!Q191</f>
         <v>5.434782608695652E-2</v>
       </c>
-      <c r="I90" s="193"/>
-    </row>
-    <row r="92" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="I92" s="14"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="C93" s="171">
-        <f>Statement!M195</f>
-        <v>-6.0092449922958396E-2</v>
-      </c>
-      <c r="D93" s="171">
-        <f>Statement!N195</f>
-        <v>-4.5901639344262293E-2</v>
-      </c>
-      <c r="E93" s="171">
-        <f>Statement!O195</f>
-        <v>5.1546391752577319E-3</v>
-      </c>
-      <c r="F93" s="171">
-        <f>Statement!P195</f>
-        <v>2.564102564102564E-2</v>
-      </c>
-      <c r="G93" s="171">
-        <f>Statement!Q195</f>
-        <v>5.6666666666666664E-2</v>
-      </c>
-      <c r="I93" s="193"/>
+      <c r="I99" s="193"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7244815B-49E3-A041-BC91-8783C0FAFB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D236EA2-0E50-2244-8578-858B5C94B58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2458,6 +2488,9 @@
     <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2467,7 +2500,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2477,12 +2513,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2503,14 +2533,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12679,7 +12709,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12698,11 +12728,9 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>217.67</v>
-    <v>2.1669999999999998</v>
-    <v>13.72</v>
-    <v>2.1760999999999999E-2</v>
-    <v>2.92</v>
-    <v>4.5329999999999997E-3</v>
+    <v>2.1471</v>
+    <v>32.56</v>
+    <v>5.0542999999999998E-2</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12710,35 +12738,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>665.55</v>
+    <v>687.05</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46321.962421435157</v>
+    <v>46322.699459212497</v>
     <v>0</v>
-    <v>621.65</v>
-    <v>147550438189</v>
+    <v>648.03</v>
+    <v>155008009893</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>632.25</v>
-    <v>46.332999999999998</v>
-    <v>630.49</v>
+    <v>650.01</v>
+    <v>48.674799999999998</v>
     <v>644.21</v>
-    <v>647.13</v>
+    <v>676.77</v>
     <v>229040900</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>4275042</v>
-    <v>4845451</v>
+    <v>3848191</v>
+    <v>4848790</v>
     <v>2017</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12757,7 +12799,7 @@
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
-    <v>3</v>
+    <v>6</v>
     <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
     <v>50.03</v>
@@ -12767,13 +12809,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12795,8 +12837,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12817,7 +12857,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12827,6 +12866,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12862,7 +12906,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12873,16 +12917,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12976,19 +13017,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13060,9 +13095,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13070,9 +13102,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13566,18 +13595,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="250"/>
-      <c r="E2" s="249" t="s">
+      <c r="C2" s="251"/>
+      <c r="E2" s="250" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="250"/>
-      <c r="H2" s="249" t="s">
+      <c r="F2" s="251"/>
+      <c r="H2" s="250" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="250"/>
+      <c r="I2" s="251"/>
       <c r="K2" s="132" t="s">
         <v>434</v>
       </c>
@@ -13595,7 +13624,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>152677.77000000002</v>
+        <v>160394.49</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13603,7 +13632,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>133.90480950793841</v>
+        <v>134.6512323282559</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>435</v>
@@ -13622,7 +13651,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>154538.77000000002</v>
+        <v>162255.49</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13630,7 +13659,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>211.89585997034459</v>
+        <v>212.51770731536101</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>436</v>
@@ -13642,7 +13671,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13657,7 +13686,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>146.16572899252222</v>
+        <v>146.73746204659241</v>
       </c>
       <c r="K5" s="244" t="s">
         <v>437</v>
@@ -13667,16 +13696,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>647.13</v>
+      <c r="C6" s="204" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>46.412824207492797</v>
+        <v>48.758645533141205</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13684,7 +13713,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>227.01112128904242</v>
+        <v>227.6838031105919</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>438</v>
@@ -13696,14 +13725,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>13.72</v>
+        <v>32.56</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>12.08388991389914</v>
+        <v>12.694640221402214</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13711,23 +13740,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>218.19488412269172</v>
+        <v>218.83791585802089</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>2.92</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>1.8941853814081772E-2</v>
+        <v>1.8030544565464813E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13735,7 +13764,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>187.43448077650788</v>
+        <v>188.08562413176443</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13744,14 +13773,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.1760999999999999E-2</v>
+        <v>5.0542999999999998E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>2.1545769236739572E-2</v>
+        <v>2.0509183326684104E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13759,23 +13788,23 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.70904754540210824</v>
+        <v>-0.72208339002650168</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>4.5329999999999997E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>1.1527545889620996E-3</v>
+        <v>1.0972945517018697E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13791,14 +13820,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>4.532683441734838E-3</v>
+        <v>4.3146120543168286E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>23.612168792934252</v>
+        <v>23.779347641317369</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13823,7 +13852,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1669999999999998</v>
+        <v>2.1471</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13846,7 +13875,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4845451</v>
+        <v>4848790</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13860,7 +13889,7 @@
       </c>
       <c r="I14" s="247">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>677.08203934263577</v>
+        <v>682.17153793007083</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -13869,7 +13898,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-1.2189069829877655E-2</v>
+        <v>-1.1602642958620337E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13880,16 +13909,16 @@
         <f>Statement!AC173</f>
         <v>-8.1982378854625555</v>
       </c>
-      <c r="H16" s="249" t="s">
+      <c r="H16" s="250" t="s">
         <v>432</v>
       </c>
-      <c r="I16" s="250"/>
+      <c r="I16" s="251"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="251" t="s">
+      <c r="B17" s="252" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="251"/>
+      <c r="C17" s="252"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -13902,7 +13931,7 @@
       </c>
       <c r="I17" s="242">
         <f ca="1">DCF!C15</f>
-        <v>0.14509386484731418</v>
+        <v>0.14432519702247792</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -13924,7 +13953,7 @@
       </c>
       <c r="I18" s="243">
         <f ca="1">Multiples!C54</f>
-        <v>0.14737499999999998</v>
+        <v>0.14647949999999998</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -13975,14 +14004,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="251" t="s">
+      <c r="B25" s="252" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="251"/>
-      <c r="E25" s="249" t="s">
+      <c r="C25" s="252"/>
+      <c r="E25" s="250" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="250"/>
+      <c r="F25" s="251"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -13991,7 +14020,7 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="2">
+      <c r="E26" s="181" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
@@ -14389,36 +14418,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="261"/>
       <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="252" t="s">
+      <c r="S2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15742,35 +15771,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="261"/>
       <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="P2" s="252" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -17003,20 +17032,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
       <c r="G3" s="261"/>
       <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -18409,6 +18438,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18416,12 +18451,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18460,20 +18489,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="261"/>
       <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -19482,16 +19511,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19594,10 +19623,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19614,7 +19643,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19623,7 +19652,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>152677.77000000002</v>
+        <v>160394.49</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19650,7 +19679,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1669999999999998</v>
+        <v>2.1471</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19682,10 +19711,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="252"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19693,7 +19722,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>2.2817055790805549E-2</v>
+        <v>2.1743175707609242E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19702,7 +19731,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.97718294420919449</v>
+        <v>0.9782568242923908</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19720,7 +19749,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14737499999999998</v>
+        <v>0.14647949999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19729,7 +19758,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14509386484731418</v>
+        <v>0.14432519702247792</v>
       </c>
     </row>
   </sheetData>
@@ -19775,20 +19804,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
       <c r="G3" s="261"/>
       <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -19981,7 +20010,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>30269.4100781052</v>
+        <v>30449.321821056339</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20035,23 +20064,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3783.4131930786189</v>
+        <v>3785.9545930208269</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>4630.676485351818</v>
+        <v>4636.8996245625694</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>4402.0337461195213</v>
+        <v>4410.9105281584762</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>3435.3460098715427</v>
+        <v>3444.5856973499631</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>1970.5583155540774</v>
+        <v>1977.1855447059222</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20070,14 +20099,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>15374.412103405823</v>
+        <v>15517.806073998889</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="249" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="252"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20093,14 +20122,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14509386484731418</v>
+        <v>0.14432519702247792</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="249" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="252"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20108,7 +20137,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>18222.027749975579</v>
+        <v>18255.535987797757</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20117,7 +20146,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>15374.412103405823</v>
+        <v>15517.806073998889</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20126,7 +20155,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>33596.439853381402</v>
+        <v>33773.342061796648</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20153,7 +20182,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>31735.439853381402</v>
+        <v>31912.342061796648</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20171,7 +20200,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C24/C25</f>
-        <v>133.90480950793841</v>
+        <v>134.6512323282559</v>
       </c>
     </row>
   </sheetData>
@@ -20215,20 +20244,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="261"/>
       <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20441,23 +20470,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>3783.4131930786189</v>
+        <v>3785.9545930208269</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>4630.676485351818</v>
+        <v>4636.8996245625694</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>4402.0337461195213</v>
+        <v>4410.9105281584762</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>3435.3460098715427</v>
+        <v>3444.5856973499631</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1970.5583155540774</v>
+        <v>1977.1855447059222</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21222,10 +21251,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="252" t="s">
+      <c r="B39" s="249" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="252"/>
+      <c r="C39" s="249"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21243,7 +21272,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14509386484731418</v>
+        <v>0.14432519702247792</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21269,7 +21298,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>35828.849378550163</v>
+        <v>35949.346190648728</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21278,7 +21307,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>52080.318812971665</v>
+        <v>52227.696633740561</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21305,7 +21334,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>50219.318812971665</v>
+        <v>50366.696633740561</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21323,14 +21352,14 @@
       </c>
       <c r="C50" s="241">
         <f ca="1">C48/C49</f>
-        <v>211.89585997034459</v>
+        <v>212.51770731536101</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="249" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="252"/>
+      <c r="C52" s="249"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21347,7 +21376,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14737499999999998</v>
+        <v>0.14647949999999998</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21382,14 +21411,14 @@
       </c>
       <c r="C58" s="241">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>146.16572899252222</v>
+        <v>146.73746204659241</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="252" t="s">
+      <c r="B60" s="249" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="252"/>
+      <c r="C60" s="249"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21406,7 +21435,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14509386484731418</v>
+        <v>0.14432519702247792</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21432,7 +21461,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>39411.16631108155</v>
+        <v>39543.710894118449</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21441,7 +21470,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>55662.635745503052</v>
+        <v>55822.061337210282</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21468,7 +21497,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>53801.635745503052</v>
+        <v>53961.061337210282</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21486,14 +21515,14 @@
       </c>
       <c r="C71" s="241">
         <f ca="1">C69/C70</f>
-        <v>227.01112128904242</v>
+        <v>227.6838031105919</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="252" t="s">
+      <c r="B73" s="249" t="s">
         <v>428</v>
       </c>
-      <c r="C73" s="252"/>
+      <c r="C73" s="249"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21510,7 +21539,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14509386484731418</v>
+        <v>0.14432519702247792</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21536,7 +21565,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>37321.718102656436</v>
+        <v>37447.235615259109</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21545,7 +21574,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>53573.187537077938</v>
+        <v>53725.586058350949</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21572,7 +21601,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>51712.187537077938</v>
+        <v>51864.586058350949</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21590,22 +21619,22 @@
       </c>
       <c r="C84" s="241">
         <f ca="1">C82/C83</f>
-        <v>218.19488412269172</v>
+        <v>218.83791585802089</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21644,10 +21673,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21656,7 +21685,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>133.90480950793841</v>
+        <v>134.6512323282559</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21665,7 +21694,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>211.89585997034459</v>
+        <v>212.51770731536101</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21674,7 +21703,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>146.16572899252222</v>
+        <v>146.73746204659241</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21683,7 +21712,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>227.01112128904242</v>
+        <v>227.6838031105919</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21692,7 +21721,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>218.19488412269172</v>
+        <v>218.83791585802089</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21701,7 +21730,7 @@
       </c>
       <c r="C10" s="241">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>187.43448077650788</v>
+        <v>188.08562413176443</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21710,7 +21739,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21719,7 +21748,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.70904754540210824</v>
+        <v>-0.72208339002650168</v>
       </c>
     </row>
   </sheetData>
@@ -21815,20 +21844,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="261"/>
       <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22191,10 +22220,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="252" t="s">
+      <c r="B20" s="249" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="252"/>
+      <c r="C20" s="249"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22229,7 +22258,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14737499999999998</v>
+        <v>0.14647949999999998</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22246,7 +22275,7 @@
       </c>
       <c r="C26" s="241">
         <f ca="1">C23/(C24-C25)</f>
-        <v>23.612168792934252</v>
+        <v>23.779347641317369</v>
       </c>
     </row>
   </sheetData>
@@ -22296,20 +22325,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
       <c r="G3" s="261"/>
       <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -22484,7 +22513,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>222058.60415912358</v>
+        <v>223378.44985180403</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22538,23 +22567,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4196.8060375288514</v>
+        <v>4199.6251223279287</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>5717.4504374957787</v>
+        <v>5725.134085903449</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>7789.0756000886422</v>
+        <v>7804.782414341913</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10611.320442065666</v>
+        <v>10639.860590375712</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14456.159794227602</v>
+        <v>14504.777631546005</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22573,15 +22602,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>112787.81061937175</v>
+        <v>113839.75926563107</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="264" t="s">
+      <c r="B14" s="265" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="265"/>
+      <c r="C14" s="266"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22589,7 +22618,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22598,7 +22627,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>677.08203934263577</v>
+        <v>682.17153793007083</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22608,20 +22637,20 @@
       <c r="C17" s="156">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E17" s="266" t="s">
+      <c r="E17" s="264" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
+      <c r="F17" s="264"/>
+      <c r="G17" s="264"/>
+      <c r="H17" s="264"/>
+      <c r="I17" s="264"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="264" t="s">
+      <c r="B19" s="265" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="265"/>
+      <c r="C19" s="266"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22637,7 +22666,7 @@
       </c>
       <c r="C21" s="218">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14509386484731418</v>
+        <v>0.14432519702247792</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22655,7 +22684,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>146235.67000000001</v>
+        <v>153626.79</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22682,15 +22711,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>148096.67000000001</v>
+        <v>155487.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="264" t="s">
+      <c r="B28" s="265" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="265"/>
+      <c r="C28" s="266"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22698,7 +22727,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>42770.812311406538</v>
+        <v>42874.179844495011</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22707,7 +22736,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>112787.81061937175</v>
+        <v>113839.75926563107</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22716,7 +22745,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>155558.62293077831</v>
+        <v>156713.93911012608</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22743,7 +22772,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>153697.62293077831</v>
+        <v>154852.93911012608</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22761,21 +22790,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>677.08203934263577</v>
+        <v>682.17153793007083</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29556,7 +29585,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29630,7 +29659,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30999,7 +31028,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>46.412824207492797</v>
+        <v>48.758645533141205</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31040,7 +31069,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>12.08388991389914</v>
+        <v>12.694640221402214</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31105,7 +31134,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>67.483004153207204</v>
+        <v>70.893765574526995</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31170,7 +31199,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>152677.77000000002</v>
+        <v>160394.49</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31235,7 +31264,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>154538.77000000002</v>
+        <v>162255.49</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31276,7 +31305,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>12.672305863058632</v>
+        <v>13.305083230832308</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31317,7 +31346,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>37.747623351245728</v>
+        <v>39.632508549096237</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31464,7 +31493,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>52.793143153526977</v>
+        <v>55.461441908713688</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31505,7 +31534,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>50.165144066162455</v>
+        <v>52.670084221427281</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31546,7 +31575,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>1.8941853814081772E-2</v>
+        <v>1.8030544565464813E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31587,7 +31616,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.1545769236739572E-2</v>
+        <v>2.0509183326684104E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31628,7 +31657,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>4.532683441734838E-3</v>
+        <v>4.3146120543168286E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31669,7 +31698,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>1.1527545889620996E-3</v>
+        <v>1.0972945517018697E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31710,7 +31739,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>5.3052910060187534E-3</v>
+        <v>5.0500487890824683E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32257,7 +32286,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-1.2189069829877655E-2</v>
+        <v>-1.1602642958620337E-2</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33616,15 +33645,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="E4" s="252" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33632,7 +33661,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33648,7 +33677,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>152677.77000000002</v>
+        <v>160394.49</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33668,7 +33697,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>154538.77000000002</v>
+        <v>162255.49</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33688,7 +33717,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>46.412824207492797</v>
+        <v>48.758645533141205</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33708,7 +33737,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.08388991389914</v>
+        <v>12.694640221402214</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33728,7 +33757,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>67.483004153207204</v>
+        <v>70.893765574526995</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33748,7 +33777,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.672305863058632</v>
+        <v>13.305083230832308</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33757,18 +33786,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>37.747623351245728</v>
+        <v>39.632508549096237</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="252"/>
-      <c r="E15" s="252" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="252"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33819,14 +33848,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="249" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="252"/>
-      <c r="E21" s="252" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="252"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33895,14 +33924,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="252" t="s">
+      <c r="B29" s="249" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="252"/>
-      <c r="E29" s="252" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="252"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33978,14 +34007,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="252"/>
-      <c r="E37" s="252" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="252"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33993,7 +34022,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.1545769236739572E-2</v>
+        <v>2.0509183326684104E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34009,7 +34038,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>1.8941853814081772E-2</v>
+        <v>1.8030544565464813E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34025,7 +34054,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.532683441734838E-3</v>
+        <v>4.3146120543168286E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34041,7 +34070,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.1527545889620996E-3</v>
+        <v>1.0972945517018697E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34050,18 +34079,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.3052910060187534E-3</v>
+        <v>5.0500487890824683E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="252" t="s">
+      <c r="B45" s="249" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="252"/>
-      <c r="E45" s="252" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="252"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34094,18 +34123,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-1.2189069829877655E-2</v>
+        <v>-1.1602642958620337E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="252" t="s">
+      <c r="B51" s="249" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="252"/>
-      <c r="E51" s="252" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="252"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34149,10 +34178,10 @@
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="252" t="s">
+      <c r="B57" s="249" t="s">
         <v>441</v>
       </c>
-      <c r="C57" s="252"/>
+      <c r="C57" s="249"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
@@ -34160,7 +34189,7 @@
       </c>
       <c r="C58" s="170">
         <f ca="1">Statement!AC157</f>
-        <v>52.793143153526977</v>
+        <v>55.461441908713688</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.2">
@@ -34169,7 +34198,7 @@
       </c>
       <c r="C59" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>50.165144066162455</v>
+        <v>52.670084221427281</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
@@ -34317,7 +34346,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>644.21</v>
+        <v>676.77</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34346,7 +34375,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>152677.77000000002</v>
+        <v>160394.49</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34375,7 +34404,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>154538.77000000002</v>
+        <v>162255.49</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34404,7 +34433,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>46.412824207492797</v>
+        <v>48.758645533141205</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34433,7 +34462,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>12.08388991389914</v>
+        <v>12.694640221402214</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34462,7 +34491,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>67.483004153207204</v>
+        <v>70.893765574526995</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34491,7 +34520,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.672305863058632</v>
+        <v>13.305083230832308</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34520,7 +34549,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>37.747623351245728</v>
+        <v>39.632508549096237</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35293,7 +35322,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.1545769236739572E-2</v>
+        <v>2.0509183326684104E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35322,7 +35351,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>1.8941853814081772E-2</v>
+        <v>1.8030544565464813E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35351,7 +35380,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.532683441734838E-3</v>
+        <v>4.3146120543168286E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35380,7 +35409,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.1527545889620996E-3</v>
+        <v>1.0972945517018697E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35409,7 +35438,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>5.3052910060187534E-3</v>
+        <v>5.0500487890824683E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35645,7 +35674,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-1.2189069829877655E-2</v>
+        <v>-1.1602642958620337E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36019,7 +36048,7 @@
       </c>
       <c r="I88" s="170">
         <f ca="1">Statement!AC157</f>
-        <v>52.793143153526977</v>
+        <v>55.461441908713688</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
@@ -36048,7 +36077,7 @@
       </c>
       <c r="I89" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>50.165144066162455</v>
+        <v>52.670084221427281</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
@@ -36235,14 +36264,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="255" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="F3" s="255" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="254"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36309,19 +36338,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="256">
+      <c r="C7" s="253">
         <f>Statement!AA88</f>
         <v>0.16613110539845757</v>
       </c>
-      <c r="D7" s="257"/>
-      <c r="F7" s="256">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.484860883797054</v>
       </c>
-      <c r="G7" s="257"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36348,19 +36377,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="256">
+      <c r="C9" s="253">
         <f>Statement!AA89</f>
         <v>3.9639639639639637E-2</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="F9" s="256">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13137254901960785</v>
       </c>
-      <c r="G9" s="257"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36387,19 +36416,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="256">
+      <c r="C11" s="253">
         <f>Statement!AA90</f>
         <v>0.31167933655839669</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="F11" s="256">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0765864332603938</v>
       </c>
-      <c r="G11" s="257"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36426,19 +36455,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="256">
+      <c r="C13" s="253">
         <f>Statement!AA93</f>
         <v>-0.24498886414253898</v>
       </c>
-      <c r="D13" s="257"/>
-      <c r="F13" s="256">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-2.023121387283237E-2</v>
       </c>
-      <c r="G13" s="257"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36465,19 +36494,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="256">
+      <c r="C15" s="253">
         <f>Statement!AA94</f>
         <v>0.56212424849699394</v>
       </c>
-      <c r="D15" s="257"/>
-      <c r="F15" s="256">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.744718309859155</v>
       </c>
-      <c r="G15" s="257"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36504,19 +36533,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="256">
+      <c r="C17" s="253">
         <f>Statement!AA96</f>
         <v>0.72994652406417115</v>
       </c>
-      <c r="D17" s="257"/>
-      <c r="F17" s="256">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.651639344262295</v>
       </c>
-      <c r="G17" s="257"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36543,22 +36572,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>1.3100436681222707E-2</v>
       </c>
-      <c r="D19" s="257"/>
-      <c r="F19" s="256">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>6.4220183486238536E-2</v>
       </c>
-      <c r="G19" s="257"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36585,22 +36614,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="256">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.70642201834862384</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="F21" s="256">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.4910714285714284</v>
       </c>
-      <c r="G21" s="257"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36649,22 +36678,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="256">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17319999999999999</v>
       </c>
-      <c r="D25" s="257"/>
-      <c r="F25" s="256">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.57434245840042941</v>
       </c>
-      <c r="G25" s="257"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36692,25 +36721,37 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="256">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1388888888888889</v>
       </c>
-      <c r="D27" s="257"/>
-      <c r="F27" s="256">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.19965576592082615</v>
       </c>
-      <c r="G27" s="257"/>
+      <c r="G27" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36721,18 +36762,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/STX.xlsx
+++ b/STX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5CBA74-5CA8-3247-87D9-581912DCB61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7199A9D9-EFC0-B245-A314-468842524E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="1" activeTab="10" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1714,7 +1714,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1826,12 +1826,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2145,7 +2139,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2479,8 +2473,6 @@
     <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="38" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2493,12 +2485,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2506,6 +2492,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2526,14 +2518,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2871,16 +2863,16 @@
                   <c:v>1649</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-529</c:v>
+                  <c:v>-719</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>335</c:v>
+                  <c:v>-10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1469</c:v>
+                  <c:v>1450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3184</c:v>
+                  <c:v>3044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3519,13 +3511,13 @@
                   <c:v>1017</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>736.2696629213483</c:v>
+                  <c:v>316.70175438596488</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>856.03635161929924</c:v>
+                  <c:v>825.14746543778801</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3080.6005420054198</c:v>
+                  <c:v>2923.4431202600217</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3950,16 +3942,16 @@
                   <c:v>0.1414115427493354</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-7.164138678223185E-2</c:v>
+                  <c:v>-9.73726977248104E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1137230957105782E-2</c:v>
+                  <c:v>-1.5264845061822622E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.16148180718918326</c:v>
+                  <c:v>0.15939320655161043</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.26109061090610908</c:v>
+                  <c:v>0.24961049610496105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4640,16 +4632,16 @@
                   <c:v>0.18436940966010734</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-7.0010587612493388E-2</c:v>
+                  <c:v>-9.5156167284277393E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3287246414265401E-2</c:v>
+                  <c:v>-1.2921566093810569E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18309859154929578</c:v>
+                  <c:v>0.18073040009971333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.31929402326514245</c:v>
+                  <c:v>0.30525471319695147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4715,16 +4707,16 @@
                   <c:v>15.128440366972477</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.44120100083402836</c:v>
+                  <c:v>0.59966638865721433</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.22468142186452042</c:v>
+                  <c:v>6.7069081153588199E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-3.2428256070640176</c:v>
+                  <c:v>-3.2008830022075054</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4693124134748501</c:v>
+                  <c:v>1.4047069681587447</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4793,13 +4785,13 @@
                   <c:v>-9.867282169648009E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.12044943820224721</c:v>
+                  <c:v>-2.8070175438596509E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5026119834618733</c:v>
+                  <c:v>0.49415159283423393</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.87701105809469215</c:v>
+                  <c:v>0.83799481635055162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5152,16 +5144,16 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-34.782608695652172</c:v>
+                  <c:v>-47.193341734929618</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.467391304347828</c:v>
+                  <c:v>-0.64089417555373007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>91.983695652173907</c:v>
+                  <c:v>90.788419154478063</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>188.85869565217394</c:v>
+                  <c:v>180.60565786975508</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5594,25 +5586,25 @@
                   <c:v>336</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>340</c:v>
+                  <c:v>339</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>488</c:v>
+                  <c:v>484</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>549</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>593</c:v>
+                  <c:v>644</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>748</c:v>
+                  <c:v>762</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1294</c:v>
+                  <c:v>1273</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1761</c:v>
+                  <c:v>1698</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6045,25 +6037,25 @@
                   <c:v>0.14451612903225808</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.15740740740740741</c:v>
+                  <c:v>0.15694444444444444</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.19967266775777415</c:v>
+                  <c:v>0.19803600654664485</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.20882464815519208</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.20991150442477877</c:v>
+                  <c:v>0.22796460176991151</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.24035989717223649</c:v>
+                  <c:v>0.24485861182519281</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35657205841829703</c:v>
+                  <c:v>0.35078534031413611</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.41601700921332391</c:v>
+                  <c:v>0.4011339475549256</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12721,11 +12713,11 @@
     <v>Powered by Refinitiv</v>
     <v>1145</v>
     <v>228.61</v>
-    <v>2.1227999999999998</v>
-    <v>2.5</v>
-    <v>3.5820000000000001E-3</v>
-    <v>-22.47</v>
-    <v>-3.2078000000000002E-2</v>
+    <v>2.1787999999999998</v>
+    <v>-55.89</v>
+    <v>-7.9788999999999999E-2</v>
+    <v>4.9196999999999997</v>
+    <v>7.6319999999999999E-3</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -12733,25 +12725,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>718.65</v>
+    <v>678.48990000000003</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46324.904922892965</v>
+    <v>46325.999933275001</v>
     <v>0</v>
-    <v>675.41</v>
-    <v>160436279223</v>
+    <v>625.29629999999997</v>
+    <v>147970493838</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>687.27</v>
+    <v>652</v>
     <v>36.798299999999998</v>
-    <v>697.97</v>
     <v>700.47</v>
-    <v>678</v>
-    <v>229040900</v>
+    <v>644.58000000000004</v>
+    <v>649.49969999999996</v>
+    <v>229561100</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>5318878</v>
-    <v>5301942</v>
+    <v>5786132</v>
+    <v>5393230</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -12775,17 +12767,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.56</v>
-    <v>0.52</v>
-    <v>1.0415000000000001E-2</v>
+    <v>-0.6</v>
+    <v>-1.2025999999999998E-2</v>
     <v>US</v>
-    <v>50.49</v>
+    <v>49.58</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.91</v>
+    <v>49.08</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.99</v>
-    <v>49.93</v>
-    <v>50.45</v>
+    <v>49.21</v>
+    <v>49.89</v>
+    <v>49.29</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13007,9 +12999,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13589,18 +13581,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="249" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="252"/>
-      <c r="E2" s="251" t="s">
+      <c r="C2" s="250"/>
+      <c r="E2" s="249" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="252"/>
-      <c r="H2" s="251" t="s">
+      <c r="F2" s="250"/>
+      <c r="H2" s="249" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="252"/>
+      <c r="I2" s="250"/>
       <c r="K2" s="132" t="s">
         <v>432</v>
       </c>
@@ -13618,15 +13610,15 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>166011.39000000001</v>
+        <v>150831.72</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
       <c r="I3" s="207">
-        <f ca="1">'AVG target price'!C5</f>
-        <v>163.20468609971843</v>
+        <f>'AVG target price'!C5</f>
+        <v>203.13844026800334</v>
       </c>
       <c r="K3" s="244" t="s">
         <v>433</v>
@@ -13645,15 +13637,15 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>167104.39000000001</v>
+        <v>151924.72</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
       <c r="I4" s="207">
-        <f ca="1">'AVG target price'!C6</f>
-        <v>252.67105031739115</v>
+        <f>'AVG target price'!C6</f>
+        <v>287.42300261320821</v>
       </c>
       <c r="K4" s="244" t="s">
         <v>434</v>
@@ -13665,22 +13657,22 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="185">
+      <c r="F5" s="186">
         <f>Statement!AC25</f>
-        <v>19.04</v>
+        <v>18.958106803297959</v>
       </c>
       <c r="H5" s="181" t="str">
         <f>'AVG target price'!B7</f>
         <v>PS price</v>
       </c>
       <c r="I5" s="207">
-        <f ca="1">'AVG target price'!C7</f>
-        <v>169.72180525769809</v>
+        <f>'AVG target price'!C7</f>
+        <v>198.15120647147131</v>
       </c>
       <c r="K5" s="244" t="s">
         <v>435</v>
@@ -13692,22 +13684,22 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>678</v>
+        <v>649.49969999999996</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>36.789390756302524</v>
+        <v>34.000230439036699</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
       <c r="I6" s="207">
-        <f ca="1">'AVG target price'!C8</f>
-        <v>271.17526997650612</v>
+        <f>'AVG target price'!C8</f>
+        <v>309.21638468575696</v>
       </c>
       <c r="K6" s="245" t="s">
         <v>436</v>
@@ -13719,22 +13711,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>2.5</v>
+        <v>-55.89</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>11.688036633089355</v>
+        <v>10.755456554822814</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
         <v>EV/Sales</v>
       </c>
       <c r="I7" s="207">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>259.95645619283232</v>
+        <f>'AVG target price'!C9</f>
+        <v>295.98619006415151</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13743,22 +13735,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-22.47</v>
+        <v>4.9196999999999997</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.3691145529231458E-2</v>
+        <v>2.6075417027665002E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I8" s="208">
-        <f ca="1">'AVG target price'!C10</f>
-        <v>223.34585356882923</v>
+        <f>'AVG target price'!C10</f>
+        <v>258.78304482051828</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13767,14 +13759,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.5820000000000001E-3</v>
+        <v>-7.9788999999999999E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>2.7181749396833554E-2</v>
+        <v>2.9411565365506154E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13782,7 +13774,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.68114858085452734</v>
+        <v>-0.59852455114878178</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13791,14 +13783,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.2078000000000002E-2</v>
+        <v>7.6319999999999999E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>3.29495464136527E-3</v>
+        <v>3.6265581271631721E-3</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13814,14 +13806,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>4.1971818921581229E-3</v>
+        <v>4.5611095597133016E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>361</v>
       </c>
       <c r="I11" s="208">
-        <f ca="1">DDM!C26</f>
-        <v>23.874388772464595</v>
+        <f>DDM!C26</f>
+        <v>30.076000000000004</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13837,7 +13829,7 @@
       </c>
       <c r="F12" s="188">
         <f>Statement!AC121</f>
-        <v>0.42572147975982955</v>
+        <v>0.42388146426496226</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
@@ -13846,21 +13838,21 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1227999999999998</v>
+        <v>2.1787999999999998</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
       </c>
       <c r="F13" s="188">
         <f>Statement!AC123</f>
-        <v>1.2730958586736172</v>
+        <v>1.2675933970460469</v>
       </c>
       <c r="H13" s="248" t="s">
         <v>429</v>
       </c>
       <c r="I13" s="246">
         <f>'Reverse DCF'!C17</f>
-        <v>0.56000000000000005</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -13869,21 +13861,21 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5301942</v>
+        <v>5393230</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
       </c>
       <c r="F14" s="189">
         <f>Statement!AC138</f>
-        <v>1.0446242852597505</v>
+        <v>1.0026439594544252</v>
       </c>
       <c r="H14" s="182" t="s">
         <v>438</v>
       </c>
       <c r="I14" s="247">
-        <f ca="1">'Reverse DCF'!C16</f>
-        <v>683.73137526123378</v>
+        <f>'Reverse DCF'!C16</f>
+        <v>648.60259842364871</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -13892,7 +13884,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>-6.5838855996567455E-3</v>
+        <v>-7.2464863491578562E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -13901,31 +13893,31 @@
       </c>
       <c r="F16" s="187">
         <f>Statement!AC173</f>
-        <v>-4.8149779735682818</v>
-      </c>
-      <c r="H16" s="251" t="s">
+        <v>-4.7521739130434781</v>
+      </c>
+      <c r="H16" s="249" t="s">
         <v>430</v>
       </c>
-      <c r="I16" s="252"/>
+      <c r="I16" s="250"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="253" t="s">
+      <c r="B17" s="251" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="253"/>
+      <c r="C17" s="251"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
       <c r="F17" s="190">
         <f>Statement!AC169</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.5470085470085479E-3</v>
       </c>
       <c r="H17" s="181" t="s">
         <v>164</v>
       </c>
       <c r="I17" s="242">
-        <f ca="1">DCF!C15</f>
-        <v>0.14459949200436034</v>
+        <f>DCF!C15</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -13946,8 +13938,8 @@
         <v>431</v>
       </c>
       <c r="I18" s="243">
-        <f ca="1">Multiples!C54</f>
-        <v>0.14597599999999999</v>
+        <f>Multiples!C54</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,14 +13990,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="253" t="s">
+      <c r="B25" s="251" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="253"/>
-      <c r="E25" s="251" t="s">
+      <c r="C25" s="251"/>
+      <c r="E25" s="249" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="252"/>
+      <c r="F25" s="250"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14019,7 +14011,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>50.45</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14034,7 +14026,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.0450000000000002E-2</v>
+        <v>4.929E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14042,7 +14034,7 @@
         <v>342</v>
       </c>
       <c r="C28" s="217">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -14050,7 +14042,7 @@
         <v>360</v>
       </c>
       <c r="C29" s="217">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -14456,36 +14448,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="254" t="s">
+      <c r="S2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254" t="s">
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14496,32 +14488,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="261" t="s">
+      <c r="S4" s="259" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14657,11 +14649,11 @@
       </c>
       <c r="K6" s="64">
         <f t="shared" si="1"/>
-        <v>20357.605064671876</v>
+        <v>21375.48531790547</v>
       </c>
       <c r="L6" s="64">
         <f t="shared" si="1"/>
-        <v>17405.752330294454</v>
+        <v>18276.039946809175</v>
       </c>
       <c r="N6" s="90" t="s">
         <v>392</v>
@@ -14854,11 +14846,11 @@
       </c>
       <c r="K8" s="94">
         <f>SUM(K6:K7)</f>
-        <v>24574.195064671876</v>
+        <v>25592.07531790547</v>
       </c>
       <c r="L8" s="94">
         <f>SUM(L6:L7)</f>
-        <v>21200.683330294454</v>
+        <v>22070.970946809175</v>
       </c>
       <c r="O8" s="5"/>
       <c r="R8" s="16" t="s">
@@ -14912,33 +14904,33 @@
       <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C10" s="260" t="s">
+      <c r="C10" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="260"/>
-      <c r="J10" s="260"/>
-      <c r="K10" s="260"/>
-      <c r="L10" s="260"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="91"/>
-      <c r="S10" s="261" t="s">
+      <c r="S10" s="259" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="262"/>
-      <c r="U10" s="262"/>
-      <c r="V10" s="262"/>
-      <c r="W10" s="262"/>
-      <c r="X10" s="262"/>
-      <c r="Y10" s="262"/>
-      <c r="Z10" s="262"/>
-      <c r="AA10" s="262"/>
-      <c r="AB10" s="262"/>
-      <c r="AC10" s="262"/>
+      <c r="T10" s="260"/>
+      <c r="U10" s="260"/>
+      <c r="V10" s="260"/>
+      <c r="W10" s="260"/>
+      <c r="X10" s="260"/>
+      <c r="Y10" s="260"/>
+      <c r="Z10" s="260"/>
+      <c r="AA10" s="260"/>
+      <c r="AB10" s="260"/>
+      <c r="AC10" s="260"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
@@ -15070,11 +15062,11 @@
       </c>
       <c r="K12" s="95">
         <f t="shared" si="6"/>
-        <v>-5.0000000000000044E-2</v>
+        <v>-2.5000000000000577E-3</v>
       </c>
       <c r="L12" s="95">
         <f t="shared" si="6"/>
-        <v>-0.14500000000000002</v>
+        <v>-0.14500000000000013</v>
       </c>
       <c r="O12" s="5"/>
       <c r="Q12" s="91"/>
@@ -15232,11 +15224,11 @@
       </c>
       <c r="K14" s="103">
         <f>K8/J8-1</f>
-        <v>-3.4217636404694884E-2</v>
+        <v>5.7857408875352512E-3</v>
       </c>
       <c r="L14" s="103">
         <f>L8/K8-1</f>
-        <v>-0.13727862603431584</v>
+        <v>-0.13758573024489174</v>
       </c>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
@@ -15291,32 +15283,32 @@
     <row r="17" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="86"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="260" t="s">
+      <c r="C17" s="258" t="s">
         <v>393</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
-      <c r="J17" s="260"/>
-      <c r="K17" s="260"/>
-      <c r="L17" s="260"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
       <c r="O17" s="5"/>
-      <c r="S17" s="261" t="s">
+      <c r="S17" s="259" t="s">
         <v>115</v>
       </c>
-      <c r="T17" s="262"/>
-      <c r="U17" s="262"/>
-      <c r="V17" s="262"/>
-      <c r="W17" s="262"/>
-      <c r="X17" s="262"/>
-      <c r="Y17" s="262"/>
-      <c r="Z17" s="262"/>
-      <c r="AA17" s="262"/>
-      <c r="AB17" s="262"/>
-      <c r="AC17" s="262"/>
+      <c r="T17" s="260"/>
+      <c r="U17" s="260"/>
+      <c r="V17" s="260"/>
+      <c r="W17" s="260"/>
+      <c r="X17" s="260"/>
+      <c r="Y17" s="260"/>
+      <c r="Z17" s="260"/>
+      <c r="AA17" s="260"/>
+      <c r="AB17" s="260"/>
+      <c r="AC17" s="260"/>
       <c r="AE17" s="87"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -15451,11 +15443,11 @@
       </c>
       <c r="K19" s="236">
         <f t="shared" si="12"/>
-        <v>1175.41875</v>
+        <v>1234.1896875</v>
       </c>
       <c r="L19" s="236">
         <f t="shared" si="12"/>
-        <v>1057.8768750000002</v>
+        <v>1110.77071875</v>
       </c>
       <c r="N19" s="90" t="s">
         <v>394</v>
@@ -15642,7 +15634,7 @@
         <v>0.1</v>
       </c>
       <c r="K21" s="97">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L21" s="97">
         <v>-0.1</v>
@@ -15809,35 +15801,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="P2" s="254" t="s">
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="254"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254" t="s">
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15846,31 +15838,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="P4" s="262" t="s">
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="P4" s="260" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
+      <c r="Q4" s="260"/>
+      <c r="R4" s="260"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -16005,11 +15997,11 @@
       </c>
       <c r="K6" s="92">
         <f>Revenue!K8</f>
-        <v>24574.195064671876</v>
+        <v>25592.07531790547</v>
       </c>
       <c r="L6" s="92">
         <f>Revenue!L8</f>
-        <v>21200.683330294454</v>
+        <v>22070.970946809175</v>
       </c>
       <c r="N6" s="91"/>
       <c r="O6" s="16" t="s">
@@ -16065,32 +16057,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="258" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="262" t="s">
+      <c r="P9" s="260" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="262"/>
-      <c r="W9" s="262"/>
-      <c r="X9" s="262"/>
-      <c r="Y9" s="262"/>
-      <c r="Z9" s="262"/>
+      <c r="Q9" s="260"/>
+      <c r="R9" s="260"/>
+      <c r="S9" s="260"/>
+      <c r="T9" s="260"/>
+      <c r="U9" s="260"/>
+      <c r="V9" s="260"/>
+      <c r="W9" s="260"/>
+      <c r="X9" s="260"/>
+      <c r="Y9" s="260"/>
+      <c r="Z9" s="260"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16232,11 +16224,11 @@
       </c>
       <c r="K11" s="108">
         <f t="shared" si="3"/>
-        <v>12041.355581689219</v>
+        <v>12540.116905773681</v>
       </c>
       <c r="L11" s="108">
         <f t="shared" si="3"/>
-        <v>11660.375831661951</v>
+        <v>12139.034020745048</v>
       </c>
       <c r="N11" s="91"/>
       <c r="O11" s="16" t="str">
@@ -16325,11 +16317,11 @@
       </c>
       <c r="K12" s="24">
         <f>K6*K20</f>
-        <v>1965.9356051737502</v>
+        <v>2047.3660254324377</v>
       </c>
       <c r="L12" s="24">
         <f>L6*L20</f>
-        <v>2120.0683330294455</v>
+        <v>2207.0970946809175</v>
       </c>
       <c r="N12" s="91"/>
       <c r="O12" s="39" t="str">
@@ -16418,11 +16410,11 @@
       </c>
       <c r="K13" s="24">
         <f>K6*K21</f>
-        <v>1720.1936545270314</v>
+        <v>1791.4452722533831</v>
       </c>
       <c r="L13" s="24">
         <f>L6*L21</f>
-        <v>2332.0751663323899</v>
+        <v>2427.8068041490092</v>
       </c>
       <c r="M13" s="90"/>
       <c r="N13" s="90"/>
@@ -16511,11 +16503,11 @@
       </c>
       <c r="K14" s="108">
         <f>SUM(K12:K13)</f>
-        <v>3686.1292597007814</v>
+        <v>3838.811297685821</v>
       </c>
       <c r="L14" s="108">
         <f>SUM(L12:L13)</f>
-        <v>4452.143499361835</v>
+        <v>4634.9038988299271</v>
       </c>
       <c r="M14" s="90"/>
       <c r="N14" s="90"/>
@@ -16567,31 +16559,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="260" t="s">
+      <c r="C17" s="258" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
-      <c r="J17" s="260"/>
-      <c r="K17" s="260"/>
-      <c r="L17" s="260"/>
-      <c r="P17" s="262" t="s">
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
+      <c r="P17" s="260" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="262"/>
-      <c r="R17" s="262"/>
-      <c r="S17" s="262"/>
-      <c r="T17" s="262"/>
-      <c r="U17" s="262"/>
-      <c r="V17" s="262"/>
-      <c r="W17" s="262"/>
-      <c r="X17" s="262"/>
-      <c r="Y17" s="262"/>
-      <c r="Z17" s="262"/>
+      <c r="Q17" s="260"/>
+      <c r="R17" s="260"/>
+      <c r="S17" s="260"/>
+      <c r="T17" s="260"/>
+      <c r="U17" s="260"/>
+      <c r="V17" s="260"/>
+      <c r="W17" s="260"/>
+      <c r="X17" s="260"/>
+      <c r="Y17" s="260"/>
+      <c r="Z17" s="260"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -16970,11 +16962,11 @@
       </c>
       <c r="K22" s="103">
         <f t="shared" si="11"/>
-        <v>0.15</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="L22" s="103">
         <f t="shared" si="11"/>
-        <v>0.21</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="O22" s="16" t="str">
         <f t="shared" ref="O22" si="12">O14</f>
@@ -17070,60 +17062,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17222,11 +17214,11 @@
       </c>
       <c r="K7" s="92">
         <f>Revenue!K8</f>
-        <v>24574.195064671876</v>
+        <v>25592.07531790547</v>
       </c>
       <c r="L7" s="92">
         <f>Revenue!L8</f>
-        <v>21200.683330294454</v>
+        <v>22070.970946809175</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -17281,11 +17273,11 @@
       </c>
       <c r="K8" s="112">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>12041.355581689219</v>
+        <v>12540.116905773681</v>
       </c>
       <c r="L8" s="112">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>11660.375831661951</v>
+        <v>12139.034020745048</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -17309,30 +17301,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="265"/>
-      <c r="Q11" s="265"/>
-      <c r="R11" s="265"/>
-      <c r="S11" s="265"/>
-      <c r="T11" s="265"/>
-      <c r="U11" s="265"/>
-      <c r="V11" s="265"/>
-      <c r="W11" s="265"/>
-      <c r="X11" s="265"/>
-      <c r="Y11" s="265"/>
-      <c r="Z11" s="265"/>
+      <c r="P11" s="263"/>
+      <c r="Q11" s="263"/>
+      <c r="R11" s="263"/>
+      <c r="S11" s="263"/>
+      <c r="T11" s="263"/>
+      <c r="U11" s="263"/>
+      <c r="V11" s="263"/>
+      <c r="W11" s="263"/>
+      <c r="X11" s="263"/>
+      <c r="Y11" s="263"/>
+      <c r="Z11" s="263"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17432,11 +17424,11 @@
       </c>
       <c r="K13" s="25">
         <f>K20*K7/365</f>
-        <v>2827.7155964827912</v>
+        <v>2944.8415434302183</v>
       </c>
       <c r="L13" s="25">
         <f>L20*L7/365</f>
-        <v>2439.5306845818277</v>
+        <v>2539.6733692218777</v>
       </c>
       <c r="N13" s="91"/>
       <c r="O13" s="16"/>
@@ -17491,11 +17483,11 @@
       </c>
       <c r="K14" s="126">
         <f t="shared" si="2"/>
-        <v>2804.1512998454341</v>
+        <v>2920.3011972349668</v>
       </c>
       <c r="L14" s="126">
         <f t="shared" si="2"/>
-        <v>2715.4299881952488</v>
+        <v>2826.8983335981616</v>
       </c>
       <c r="N14" s="91"/>
       <c r="O14" s="16"/>
@@ -17550,11 +17542,11 @@
       </c>
       <c r="K15" s="24">
         <f>K22*K8/365</f>
-        <v>3200.0314833530251</v>
+        <v>3332.5790133151972</v>
       </c>
       <c r="L15" s="24">
         <f>L22*L8/365</f>
-        <v>3098.7848100581077</v>
+        <v>3225.9898630473144</v>
       </c>
       <c r="N15" s="91"/>
       <c r="P15" s="117"/>
@@ -17574,18 +17566,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17798,23 +17790,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="265"/>
-      <c r="C25" s="265"/>
+      <c r="B25" s="263"/>
+      <c r="C25" s="263"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="258" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17899,11 +17891,11 @@
       </c>
       <c r="K28" s="126">
         <f t="shared" si="7"/>
-        <v>100.18586773125026</v>
+        <v>-16.940079216176855</v>
       </c>
       <c r="L28" s="126">
         <f t="shared" si="7"/>
-        <v>388.18491190096347</v>
+        <v>405.16817420834059</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
@@ -17944,11 +17936,11 @@
       </c>
       <c r="K29" s="126">
         <f t="shared" si="7"/>
-        <v>-19.15931186088801</v>
+        <v>-135.30920925042074</v>
       </c>
       <c r="L29" s="126">
         <f t="shared" si="7"/>
-        <v>88.721311650185271</v>
+        <v>93.40286363680525</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
@@ -17989,11 +17981,11 @@
       </c>
       <c r="K30" s="64">
         <f t="shared" si="8"/>
-        <v>21.864155888308233</v>
+        <v>154.41168585048035</v>
       </c>
       <c r="L30" s="64">
         <f t="shared" si="8"/>
-        <v>-101.2466732949174</v>
+        <v>-106.58915026788281</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
@@ -18006,18 +17998,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="260"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="260"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18102,11 +18094,11 @@
       </c>
       <c r="K35" s="126">
         <f t="shared" si="10"/>
-        <v>594.37461305210809</v>
+        <v>514.00390374199219</v>
       </c>
       <c r="L35" s="126">
         <f t="shared" si="10"/>
-        <v>799.6732168621204</v>
+        <v>833.40130651344657</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
@@ -18147,11 +18139,11 @@
       </c>
       <c r="K36" s="64">
         <f>K7*K37</f>
-        <v>491.48390129343755</v>
+        <v>511.84150635810943</v>
       </c>
       <c r="L36" s="64">
         <f>L7*L37</f>
-        <v>424.01366660588911</v>
+        <v>441.41941893618349</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
@@ -18201,18 +18193,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="258" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="258"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="258"/>
+      <c r="G40" s="258"/>
+      <c r="H40" s="258"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18297,11 +18289,11 @@
       </c>
       <c r="K42" s="25">
         <f>K7*K43</f>
-        <v>737.2258519401563</v>
+        <v>767.76225953716403</v>
       </c>
       <c r="L42" s="25">
         <f>L7*L43</f>
-        <v>636.02049990883359</v>
+        <v>662.12912840427521</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -18374,15 +18366,15 @@
       </c>
       <c r="I44" s="123">
         <f t="shared" si="13"/>
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J44" s="123">
         <f t="shared" si="13"/>
-        <v>0.66666666666666663</v>
+        <v>0.54545454545454553</v>
       </c>
       <c r="K44" s="123">
         <f t="shared" si="13"/>
-        <v>0.66666666666666674</v>
+        <v>0.59999999999999987</v>
       </c>
       <c r="L44" s="123">
         <f t="shared" si="13"/>
@@ -18419,19 +18411,19 @@
       </c>
       <c r="I45" s="25">
         <f>I7*I46</f>
-        <v>1151.9172270000001</v>
+        <v>1439.8965337500001</v>
       </c>
       <c r="J45" s="25">
         <f>J7*J46</f>
-        <v>1145.0186083265626</v>
+        <v>1399.4671879546875</v>
       </c>
       <c r="K45" s="25">
         <f>K7*K46</f>
-        <v>1105.8387779102343</v>
+        <v>1279.6037658952737</v>
       </c>
       <c r="L45" s="25">
         <f>L7*L46</f>
-        <v>954.03074986325043</v>
+        <v>993.19369260641281</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
@@ -18462,13 +18454,13 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="I46" s="97">
-        <v>4.8000000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="J46" s="97">
-        <v>4.4999999999999998E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K46" s="97">
-        <v>4.4999999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="L46" s="97">
         <v>4.4999999999999998E-2</v>
@@ -18476,12 +18468,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18489,6 +18475,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18527,60 +18519,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="S2" s="265"/>
-      <c r="T2" s="265"/>
-      <c r="U2" s="265"/>
-      <c r="V2" s="265"/>
-      <c r="W2" s="265"/>
-      <c r="X2" s="265"/>
-      <c r="Y2" s="265"/>
-      <c r="Z2" s="265"/>
-      <c r="AA2" s="265"/>
-      <c r="AB2" s="265"/>
-      <c r="AC2" s="265"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="263"/>
+      <c r="AB2" s="263"/>
+      <c r="AC2" s="263"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="S4" s="265"/>
-      <c r="T4" s="265"/>
-      <c r="U4" s="265"/>
-      <c r="V4" s="265"/>
-      <c r="W4" s="265"/>
-      <c r="X4" s="265"/>
-      <c r="Y4" s="265"/>
-      <c r="Z4" s="265"/>
-      <c r="AA4" s="265"/>
-      <c r="AB4" s="265"/>
-      <c r="AC4" s="265"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="S4" s="263"/>
+      <c r="T4" s="263"/>
+      <c r="U4" s="263"/>
+      <c r="V4" s="263"/>
+      <c r="W4" s="263"/>
+      <c r="X4" s="263"/>
+      <c r="Y4" s="263"/>
+      <c r="Z4" s="263"/>
+      <c r="AA4" s="263"/>
+      <c r="AB4" s="263"/>
+      <c r="AC4" s="263"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18679,11 +18671,11 @@
       </c>
       <c r="K6" s="92">
         <f>Revenue!K8</f>
-        <v>24574.195064671876</v>
+        <v>25592.07531790547</v>
       </c>
       <c r="L6" s="92">
         <f>Revenue!L8</f>
-        <v>21200.683330294454</v>
+        <v>22070.970946809175</v>
       </c>
       <c r="N6" s="90" t="s">
         <v>153</v>
@@ -18740,11 +18732,11 @@
       </c>
       <c r="K7" s="112">
         <f>'COGS &amp; OpEx'!K11</f>
-        <v>12041.355581689219</v>
+        <v>12540.116905773681</v>
       </c>
       <c r="L7" s="112">
         <f>'COGS &amp; OpEx'!L11</f>
-        <v>11660.375831661951</v>
+        <v>12139.034020745048</v>
       </c>
       <c r="N7" s="90" t="s">
         <v>154</v>
@@ -18801,11 +18793,11 @@
       </c>
       <c r="K8" s="94">
         <f t="shared" si="1"/>
-        <v>12532.839482982658</v>
+        <v>13051.958412131789</v>
       </c>
       <c r="L8" s="94">
         <f t="shared" si="1"/>
-        <v>9540.3074986325028</v>
+        <v>9931.936926064127</v>
       </c>
       <c r="N8" s="90"/>
       <c r="Q8" s="90"/>
@@ -18860,11 +18852,11 @@
       </c>
       <c r="K9" s="112">
         <f>'COGS &amp; OpEx'!K14</f>
-        <v>3686.1292597007814</v>
+        <v>3838.811297685821</v>
       </c>
       <c r="L9" s="112">
         <f>'COGS &amp; OpEx'!L14</f>
-        <v>4452.143499361835</v>
+        <v>4634.9038988299271</v>
       </c>
       <c r="N9" s="128" t="s">
         <v>154</v>
@@ -18921,11 +18913,11 @@
       </c>
       <c r="K10" s="94">
         <f t="shared" si="2"/>
-        <v>8846.7102232818761</v>
+        <v>9213.1471144459683</v>
       </c>
       <c r="L10" s="94">
         <f t="shared" si="2"/>
-        <v>5088.1639992706678</v>
+        <v>5297.0330272341998</v>
       </c>
       <c r="N10" s="90"/>
       <c r="Q10" s="90"/>
@@ -18943,18 +18935,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="258" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19012,15 +19004,15 @@
       </c>
       <c r="E15" s="129">
         <f>Statement!O82</f>
-        <v>0.24719101123595505</v>
+        <v>1.1754385964912282</v>
       </c>
       <c r="F15" s="129">
         <f>Statement!P82</f>
-        <v>2.9081295439524125E-2</v>
+        <v>4.5424621461487819E-2</v>
       </c>
       <c r="G15" s="130">
         <f>Statement!Q82</f>
-        <v>0.13712737127371274</v>
+        <v>0.17551462621885158</v>
       </c>
       <c r="H15" s="129">
         <f>Overview!$C$26</f>
@@ -19047,18 +19039,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19143,11 +19135,11 @@
       </c>
       <c r="K20" s="88">
         <f>'WC &amp; Investments'!K42</f>
-        <v>737.2258519401563</v>
+        <v>767.76225953716403</v>
       </c>
       <c r="L20" s="88">
         <f>'WC &amp; Investments'!L42</f>
-        <v>636.02049990883359</v>
+        <v>662.12912840427521</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>159</v>
@@ -19183,19 +19175,19 @@
       </c>
       <c r="I21" s="88">
         <f>'WC &amp; Investments'!I45</f>
-        <v>1151.9172270000001</v>
+        <v>1439.8965337500001</v>
       </c>
       <c r="J21" s="88">
         <f>'WC &amp; Investments'!J45</f>
-        <v>1145.0186083265626</v>
+        <v>1399.4671879546875</v>
       </c>
       <c r="K21" s="88">
         <f>'WC &amp; Investments'!K45</f>
-        <v>1105.8387779102343</v>
+        <v>1279.6037658952737</v>
       </c>
       <c r="L21" s="88">
         <f>'WC &amp; Investments'!L45</f>
-        <v>954.03074986325043</v>
+        <v>993.19369260641281</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>159</v>
@@ -19239,29 +19231,29 @@
       </c>
       <c r="K22" s="88">
         <f>'WC &amp; Investments'!K35</f>
-        <v>594.37461305210809</v>
+        <v>514.00390374199219</v>
       </c>
       <c r="L22" s="88">
         <f>'WC &amp; Investments'!L35</f>
-        <v>799.6732168621204</v>
+        <v>833.40130651344657</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="260" t="s">
+      <c r="C25" s="258" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19322,15 +19314,15 @@
       </c>
       <c r="E27" s="126">
         <f t="shared" si="6"/>
-        <v>340.26966292134836</v>
+        <v>-79.298245614035139</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="6"/>
-        <v>1835.0363516192995</v>
+        <v>1804.147465437788</v>
       </c>
       <c r="G27" s="131">
         <f t="shared" si="6"/>
-        <v>3532.6005420054198</v>
+        <v>3375.4431202600217</v>
       </c>
       <c r="H27" s="126">
         <f t="shared" si="6"/>
@@ -19346,11 +19338,11 @@
       </c>
       <c r="K27" s="126">
         <f t="shared" si="6"/>
-        <v>6988.9010763926826</v>
+        <v>7278.3862204123152</v>
       </c>
       <c r="L27" s="126">
         <f t="shared" si="6"/>
-        <v>4019.6495594238277</v>
+        <v>4184.6560915150185</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -19367,15 +19359,15 @@
       </c>
       <c r="E28" s="94">
         <f t="shared" si="7"/>
-        <v>736.2696629213483</v>
+        <v>316.70175438596488</v>
       </c>
       <c r="F28" s="94">
         <f t="shared" si="7"/>
-        <v>856.03635161929924</v>
+        <v>825.14746543778801</v>
       </c>
       <c r="G28" s="127">
         <f t="shared" si="7"/>
-        <v>3080.6005420054198</v>
+        <v>2923.4431202600217</v>
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
@@ -19383,34 +19375,34 @@
       </c>
       <c r="I28" s="94">
         <f t="shared" si="7"/>
-        <v>7248.0192638324506</v>
+        <v>6960.0399570824502</v>
       </c>
       <c r="J28" s="94">
         <f t="shared" si="7"/>
-        <v>8216.8205534406425</v>
+        <v>7962.3719738125174</v>
       </c>
       <c r="K28" s="94">
         <f t="shared" si="7"/>
-        <v>7214.6627634747128</v>
+        <v>7280.5486177961975</v>
       </c>
       <c r="L28" s="94">
         <f t="shared" si="7"/>
-        <v>4501.3125263315314</v>
+        <v>4686.992833826328</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="258" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="258"/>
+      <c r="G31" s="258"/>
+      <c r="H31" s="258"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19540,25 +19532,25 @@
       </c>
       <c r="K34" s="212">
         <f t="shared" si="10"/>
-        <v>0.36000000000000004</v>
+        <v>0.36</v>
       </c>
       <c r="L34" s="212">
         <f t="shared" si="10"/>
-        <v>0.23999999999999994</v>
+        <v>0.23999999999999991</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19661,10 +19653,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="252" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="252"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19672,7 +19664,7 @@
       </c>
       <c r="C5" s="136">
         <f>Statement!AC77</f>
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19681,7 +19673,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19690,7 +19682,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>166011.39000000001</v>
+        <v>150831.72</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19708,7 +19700,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.0450000000000002E-2</v>
+        <v>4.929E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19717,7 +19709,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1227999999999998</v>
+        <v>2.1787999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19749,10 +19741,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="252" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="254"/>
+      <c r="C15" s="252"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19760,7 +19752,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>1.3963926266430405E-2</v>
+        <v>1.5347684125206812E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19769,7 +19761,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.98603607373356961</v>
+        <v>0.98465231587479318</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19787,7 +19779,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14597599999999999</v>
+        <v>0.14733599999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19796,7 +19788,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14459949200436034</v>
+        <v>0.14580221383926331</v>
       </c>
     </row>
   </sheetData>
@@ -19842,60 +19834,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -19970,15 +19962,15 @@
       </c>
       <c r="E7" s="112">
         <f>'FCF &amp; Other'!E28</f>
-        <v>736.2696629213483</v>
+        <v>316.70175438596488</v>
       </c>
       <c r="F7" s="112">
         <f>'FCF &amp; Other'!F28</f>
-        <v>856.03635161929924</v>
+        <v>825.14746543778801</v>
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3080.6005420054198</v>
+        <v>2923.4431202600217</v>
       </c>
       <c r="H7" s="112">
         <f>'FCF &amp; Other'!H28</f>
@@ -19986,19 +19978,19 @@
       </c>
       <c r="I7" s="112">
         <f>'FCF &amp; Other'!I28</f>
-        <v>7248.0192638324506</v>
+        <v>6960.0399570824502</v>
       </c>
       <c r="J7" s="112">
         <f>'FCF &amp; Other'!J28</f>
-        <v>8216.8205534406425</v>
+        <v>7962.3719738125174</v>
       </c>
       <c r="K7" s="112">
         <f>'FCF &amp; Other'!K28</f>
-        <v>7214.6627634747128</v>
+        <v>7280.5486177961975</v>
       </c>
       <c r="L7" s="112">
         <f>'FCF &amp; Other'!L28</f>
-        <v>4501.3125263315314</v>
+        <v>4686.992833826328</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -20047,8 +20039,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="126">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>35253.473170039797</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>45307.597393654505</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20101,24 +20093,24 @@
       <c r="F10" s="137"/>
       <c r="G10" s="138"/>
       <c r="H10" s="126">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>4321.3283511242207</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>4416.2412816793058</v>
       </c>
       <c r="I10" s="126">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>5532.3830400966581</v>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
+        <v>5548.5012412965953</v>
       </c>
       <c r="J10" s="126">
-        <f t="shared" ca="1" si="0"/>
-        <v>5479.5280705484656</v>
+        <f t="shared" si="0"/>
+        <v>5667.4590967028307</v>
       </c>
       <c r="K10" s="126">
-        <f t="shared" ca="1" si="0"/>
-        <v>4203.4108439431766</v>
+        <f t="shared" si="0"/>
+        <v>4626.9202673147893</v>
       </c>
       <c r="L10" s="126">
-        <f t="shared" ca="1" si="0"/>
-        <v>2291.2444339359713</v>
+        <f t="shared" si="0"/>
+        <v>2659.5256064736805</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20136,15 +20128,15 @@
       <c r="J11" s="137"/>
       <c r="K11" s="137"/>
       <c r="L11" s="126">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>17944.615865984772</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>25708.747529245578</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="254" t="s">
+      <c r="B13" s="252" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="254"/>
+      <c r="C13" s="252"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20159,23 +20151,23 @@
         <v>164</v>
       </c>
       <c r="C15" s="135">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14459949200436034</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="254" t="s">
+      <c r="B18" s="252" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="254"/>
+      <c r="C18" s="252"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C19" s="64">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>21827.894739648495</v>
+        <f>SUM(H10:L10)</f>
+        <v>22918.647493467201</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20183,8 +20175,8 @@
         <v>182</v>
       </c>
       <c r="C20" s="64">
-        <f ca="1">L11</f>
-        <v>17944.615865984772</v>
+        <f>L11</f>
+        <v>25708.747529245578</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20192,8 +20184,8 @@
         <v>187</v>
       </c>
       <c r="C21" s="94">
-        <f ca="1">C19+C20</f>
-        <v>39772.510605633266</v>
+        <f>C19+C20</f>
+        <v>48627.395022712779</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20219,8 +20211,8 @@
         <v>190</v>
       </c>
       <c r="C24" s="94">
-        <f ca="1">C21+C22-C23</f>
-        <v>38679.510605633266</v>
+        <f>C21+C22-C23</f>
+        <v>47534.395022712779</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20229,7 +20221,7 @@
       </c>
       <c r="C25" s="88">
         <f>Statement!AC77</f>
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
@@ -20237,8 +20229,8 @@
         <v>191</v>
       </c>
       <c r="C26" s="241">
-        <f ca="1">C24/C25</f>
-        <v>163.20468609971843</v>
+        <f>C24/C25</f>
+        <v>203.13844026800334</v>
       </c>
     </row>
   </sheetData>
@@ -20282,37 +20274,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20397,11 +20389,11 @@
       </c>
       <c r="K6" s="92">
         <f>Revenue!K8</f>
-        <v>24574.195064671876</v>
+        <v>25592.07531790547</v>
       </c>
       <c r="L6" s="92">
         <f>Revenue!L8</f>
-        <v>21200.683330294454</v>
+        <v>22070.970946809175</v>
       </c>
       <c r="N6" s="91"/>
     </row>
@@ -20443,11 +20435,11 @@
       </c>
       <c r="K7" s="92">
         <f>'FCF &amp; Other'!K10</f>
-        <v>8846.7102232818761</v>
+        <v>9213.1471144459683</v>
       </c>
       <c r="L7" s="92">
         <f>'FCF &amp; Other'!L10</f>
-        <v>5088.1639992706678</v>
+        <v>5297.0330272341998</v>
       </c>
       <c r="N7" s="91"/>
     </row>
@@ -20465,15 +20457,15 @@
       </c>
       <c r="E8" s="92">
         <f>'FCF &amp; Other'!E28</f>
-        <v>736.2696629213483</v>
+        <v>316.70175438596488</v>
       </c>
       <c r="F8" s="92">
         <f>'FCF &amp; Other'!F28</f>
-        <v>856.03635161929924</v>
+        <v>825.14746543778801</v>
       </c>
       <c r="G8" s="93">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3080.6005420054198</v>
+        <v>2923.4431202600217</v>
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
@@ -20481,19 +20473,19 @@
       </c>
       <c r="I8" s="92">
         <f>'FCF &amp; Other'!I28</f>
-        <v>7248.0192638324506</v>
+        <v>6960.0399570824502</v>
       </c>
       <c r="J8" s="92">
         <f>'FCF &amp; Other'!J28</f>
-        <v>8216.8205534406425</v>
+        <v>7962.3719738125174</v>
       </c>
       <c r="K8" s="92">
         <f>'FCF &amp; Other'!K28</f>
-        <v>7214.6627634747128</v>
+        <v>7280.5486177961975</v>
       </c>
       <c r="L8" s="92">
         <f>'FCF &amp; Other'!L28</f>
-        <v>4501.3125263315314</v>
+        <v>4686.992833826328</v>
       </c>
       <c r="N8" s="91"/>
     </row>
@@ -20507,24 +20499,24 @@
       <c r="F9" s="137"/>
       <c r="G9" s="138"/>
       <c r="H9" s="92">
-        <f ca="1">DCF!H10</f>
-        <v>4321.3283511242207</v>
+        <f>DCF!H10</f>
+        <v>4416.2412816793058</v>
       </c>
       <c r="I9" s="92">
-        <f ca="1">DCF!I10</f>
-        <v>5532.3830400966581</v>
+        <f>DCF!I10</f>
+        <v>5548.5012412965953</v>
       </c>
       <c r="J9" s="92">
-        <f ca="1">DCF!J10</f>
-        <v>5479.5280705484656</v>
+        <f>DCF!J10</f>
+        <v>5667.4590967028307</v>
       </c>
       <c r="K9" s="92">
-        <f ca="1">DCF!K10</f>
-        <v>4203.4108439431766</v>
+        <f>DCF!K10</f>
+        <v>4626.9202673147893</v>
       </c>
       <c r="L9" s="92">
-        <f ca="1">DCF!L10</f>
-        <v>2291.2444339359713</v>
+        <f>DCF!L10</f>
+        <v>2659.5256064736805</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20532,18 +20524,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20627,11 +20619,11 @@
       </c>
       <c r="K13" s="95">
         <f t="shared" si="1"/>
-        <v>-3.4217636404694933E-2</v>
+        <v>5.785740887535174E-3</v>
       </c>
       <c r="L13" s="95">
         <f t="shared" si="1"/>
-        <v>-0.1372786260343159</v>
+        <v>-0.13758573024489176</v>
       </c>
       <c r="N13" s="91"/>
     </row>
@@ -20676,11 +20668,11 @@
       </c>
       <c r="K14" s="95">
         <f t="shared" si="2"/>
-        <v>-0.1519959734285127</v>
+        <v>-0.11687105678167667</v>
       </c>
       <c r="L14" s="95">
         <f t="shared" si="2"/>
-        <v>-0.42485241735621077</v>
+        <v>-0.42505715349659468</v>
       </c>
       <c r="N14" s="91"/>
     </row>
@@ -20701,35 +20693,35 @@
 IF(E8=0,0,IF(E8&gt;0,1,-1)),
 (E8-D8)/ABS(D8)
 )</f>
-        <v>-0.27603769624252872</v>
+        <v>-0.68859217857820554</v>
       </c>
       <c r="F15" s="95">
         <f t="shared" si="3"/>
-        <v>0.16266687971733662</v>
+        <v>1.6054401467955861</v>
       </c>
       <c r="G15" s="96">
         <f t="shared" si="3"/>
-        <v>2.5986795843168116</v>
+        <v>2.542934133244859</v>
       </c>
       <c r="H15" s="95">
         <f t="shared" si="3"/>
-        <v>0.6055928602352757</v>
+        <v>0.69190575359676931</v>
       </c>
       <c r="I15" s="95">
         <f t="shared" si="3"/>
-        <v>0.46537414025036294</v>
+        <v>0.40715169165058607</v>
       </c>
       <c r="J15" s="95">
         <f t="shared" si="3"/>
-        <v>0.13366428183248646</v>
+        <v>0.14401239402513868</v>
       </c>
       <c r="K15" s="95">
         <f t="shared" si="3"/>
-        <v>-0.12196418109025084</v>
+        <v>-8.5630683703144223E-2</v>
       </c>
       <c r="L15" s="95">
         <f t="shared" si="3"/>
-        <v>-0.37608829769284774</v>
+        <v>-0.35623081722582217</v>
       </c>
       <c r="N15" s="91"/>
     </row>
@@ -20737,18 +20729,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="260" t="s">
+      <c r="C17" s="258" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="260"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
-      <c r="J17" s="260"/>
-      <c r="K17" s="260"/>
-      <c r="L17" s="260"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20882,18 +20874,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="260" t="s">
+      <c r="C22" s="258" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="260"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="260"/>
-      <c r="G22" s="260"/>
-      <c r="H22" s="260"/>
-      <c r="I22" s="260"/>
-      <c r="J22" s="260"/>
-      <c r="K22" s="260"/>
-      <c r="L22" s="260"/>
+      <c r="D22" s="258"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="258"/>
+      <c r="G22" s="258"/>
+      <c r="H22" s="258"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="258"/>
+      <c r="K22" s="258"/>
+      <c r="L22" s="258"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20977,18 +20969,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="260" t="s">
+      <c r="C27" s="258" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="260"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="260"/>
-      <c r="G27" s="260"/>
-      <c r="H27" s="260"/>
-      <c r="I27" s="260"/>
-      <c r="J27" s="260"/>
-      <c r="K27" s="260"/>
-      <c r="L27" s="260"/>
+      <c r="D27" s="258"/>
+      <c r="E27" s="258"/>
+      <c r="F27" s="258"/>
+      <c r="G27" s="258"/>
+      <c r="H27" s="258"/>
+      <c r="I27" s="258"/>
+      <c r="J27" s="258"/>
+      <c r="K27" s="258"/>
+      <c r="L27" s="258"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21234,15 +21226,15 @@
       </c>
       <c r="E35" s="147">
         <f t="shared" si="13"/>
-        <v>35.597337931876446</v>
+        <v>82.756851318413482</v>
       </c>
       <c r="F35" s="147">
         <f t="shared" si="13"/>
-        <v>40.648367250033395</v>
+        <v>42.170013794490018</v>
       </c>
       <c r="G35" s="148">
         <f t="shared" si="13"/>
-        <v>61.57164403941934</v>
+        <v>64.881590712505243</v>
       </c>
       <c r="H35" s="137"/>
       <c r="I35" s="137"/>
@@ -21289,10 +21281,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="254" t="s">
+      <c r="B39" s="252" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="254"/>
+      <c r="C39" s="252"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21301,7 +21293,7 @@
       </c>
       <c r="C40" s="64">
         <f>L7</f>
-        <v>5088.1639992706678</v>
+        <v>5297.0330272341998</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -21309,8 +21301,8 @@
         <v>164</v>
       </c>
       <c r="C41" s="135">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14459949200436034</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21327,7 +21319,7 @@
       </c>
       <c r="C43" s="24">
         <f>(C40*C42)</f>
-        <v>81410.623988330684</v>
+        <v>84752.528435747197</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21335,8 +21327,8 @@
         <v>422</v>
       </c>
       <c r="C44" s="24">
-        <f ca="1">C43/(1+C41)^5</f>
-        <v>41439.388619509176</v>
+        <f>C43/(1+C41)^5</f>
+        <v>48090.860724497201</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21344,8 +21336,8 @@
         <v>423</v>
       </c>
       <c r="C45" s="108">
-        <f ca="1">SUM(H9:K9)+C44</f>
-        <v>60976.038925221699</v>
+        <f>SUM(H9:K9)+C44</f>
+        <v>68349.982611490719</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21371,8 +21363,8 @@
         <v>190</v>
       </c>
       <c r="C48" s="108">
-        <f ca="1">C45+C46-C47</f>
-        <v>59883.038925221699</v>
+        <f>C45+C46-C47</f>
+        <v>67256.982611490719</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21381,7 +21373,7 @@
       </c>
       <c r="C49" s="88">
         <f>Statement!AC77</f>
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
@@ -21389,15 +21381,15 @@
         <v>208</v>
       </c>
       <c r="C50" s="241">
-        <f ca="1">C48/C49</f>
-        <v>252.67105031739115</v>
+        <f>C48/C49</f>
+        <v>287.42300261320821</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="254" t="s">
+      <c r="B52" s="252" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="254"/>
+      <c r="C52" s="252"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21405,7 +21397,7 @@
       </c>
       <c r="C53" s="64">
         <f>L6</f>
-        <v>21200.683330294454</v>
+        <v>22070.970946809175</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -21413,8 +21405,8 @@
         <v>343</v>
       </c>
       <c r="C54" s="135">
-        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14597599999999999</v>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21440,7 +21432,7 @@
       </c>
       <c r="C57" s="24">
         <f>(C53*C55)/C56</f>
-        <v>335.4403127716464</v>
+        <v>349.2101307410436</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -21448,15 +21440,15 @@
         <v>208</v>
       </c>
       <c r="C58" s="241">
-        <f ca="1">C57/(1+C54)^5</f>
-        <v>169.72180525769809</v>
+        <f>C57/(1+C54)^5</f>
+        <v>198.15120647147131</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="254" t="s">
+      <c r="B60" s="252" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="254"/>
+      <c r="C60" s="252"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21464,7 +21456,7 @@
       </c>
       <c r="C61" s="64">
         <f>L8</f>
-        <v>4501.3125263315314</v>
+        <v>4686.992833826328</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -21472,8 +21464,8 @@
         <v>164</v>
       </c>
       <c r="C62" s="135">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14459949200436034</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21490,7 +21482,7 @@
       </c>
       <c r="C64" s="24">
         <f>(C61*C63)</f>
-        <v>90026.250526630625</v>
+        <v>93739.856676526557</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -21498,8 +21490,8 @@
         <v>422</v>
       </c>
       <c r="C65" s="24">
-        <f ca="1">C64/(1+C62)^5</f>
-        <v>45824.888678719428</v>
+        <f>C64/(1+C62)^5</f>
+        <v>53190.512129473602</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21507,8 +21499,8 @@
         <v>423</v>
       </c>
       <c r="C66" s="108">
-        <f ca="1">SUM(H9:K9)+C65</f>
-        <v>65361.538984431951</v>
+        <f>SUM(H9:K9)+C65</f>
+        <v>73449.634016467127</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21534,8 +21526,8 @@
         <v>190</v>
       </c>
       <c r="C69" s="108">
-        <f ca="1">C66+C67-C68</f>
-        <v>64268.538984431943</v>
+        <f>C66+C67-C68</f>
+        <v>72356.634016467127</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21544,7 +21536,7 @@
       </c>
       <c r="C70" s="88">
         <f>Statement!AC77</f>
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.2">
@@ -21552,15 +21544,15 @@
         <v>208</v>
       </c>
       <c r="C71" s="241">
-        <f ca="1">C69/C70</f>
-        <v>271.17526997650612</v>
+        <f>C69/C70</f>
+        <v>309.21638468575696</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="254" t="s">
+      <c r="B73" s="252" t="s">
         <v>426</v>
       </c>
-      <c r="C73" s="254"/>
+      <c r="C73" s="252"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21568,7 +21560,7 @@
       </c>
       <c r="C74" s="64">
         <f>L6</f>
-        <v>21200.683330294454</v>
+        <v>22070.970946809175</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.2">
@@ -21576,8 +21568,8 @@
         <v>164</v>
       </c>
       <c r="C75" s="135">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14459949200436034</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21594,7 +21586,7 @@
       </c>
       <c r="C77" s="24">
         <f>(C74*C76)</f>
-        <v>84802.733321177817</v>
+        <v>88283.8837872367</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.2">
@@ -21602,8 +21594,8 @@
         <v>422</v>
       </c>
       <c r="C78" s="24">
-        <f ca="1">C77/(1+C75)^5</f>
-        <v>43166.029811988737</v>
+        <f>C77/(1+C75)^5</f>
+        <v>50094.646588017938</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21611,8 +21603,8 @@
         <v>423</v>
       </c>
       <c r="C79" s="108">
-        <f ca="1">SUM(H9:K9)+C78</f>
-        <v>62702.68011770126</v>
+        <f>SUM(H9:K9)+C78</f>
+        <v>70353.768475011457</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21638,8 +21630,8 @@
         <v>190</v>
       </c>
       <c r="C82" s="108">
-        <f ca="1">C79+C80-C81</f>
-        <v>61609.68011770126</v>
+        <f>C79+C80-C81</f>
+        <v>69260.768475011457</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21648,7 +21640,7 @@
       </c>
       <c r="C83" s="88">
         <f>Statement!AC77</f>
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.2">
@@ -21656,23 +21648,23 @@
         <v>208</v>
       </c>
       <c r="C84" s="241">
-        <f ca="1">C82/C83</f>
-        <v>259.95645619283232</v>
+        <f>C82/C83</f>
+        <v>295.98619006415151</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21711,10 +21703,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="252" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="254"/>
+      <c r="C4" s="252"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21722,8 +21714,8 @@
         <v>214</v>
       </c>
       <c r="C5" s="133">
-        <f ca="1">DCF!C26</f>
-        <v>163.20468609971843</v>
+        <f>DCF!C26</f>
+        <v>203.13844026800334</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21731,8 +21723,8 @@
         <v>215</v>
       </c>
       <c r="C6" s="133">
-        <f ca="1">Multiples!C50</f>
-        <v>252.67105031739115</v>
+        <f>Multiples!C50</f>
+        <v>287.42300261320821</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21740,8 +21732,8 @@
         <v>216</v>
       </c>
       <c r="C7" s="133">
-        <f ca="1">Multiples!C58</f>
-        <v>169.72180525769809</v>
+        <f>Multiples!C58</f>
+        <v>198.15120647147131</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21749,8 +21741,8 @@
         <v>322</v>
       </c>
       <c r="C8" s="133">
-        <f ca="1">Multiples!C71</f>
-        <v>271.17526997650612</v>
+        <f>Multiples!C71</f>
+        <v>309.21638468575696</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21758,8 +21750,8 @@
         <v>425</v>
       </c>
       <c r="C9" s="133">
-        <f ca="1">Multiples!C84</f>
-        <v>259.95645619283232</v>
+        <f>Multiples!C84</f>
+        <v>295.98619006415151</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21767,8 +21759,8 @@
         <v>217</v>
       </c>
       <c r="C10" s="241">
-        <f ca="1">AVERAGE(C5:C9)</f>
-        <v>223.34585356882923</v>
+        <f>AVERAGE(C5:C9)</f>
+        <v>258.78304482051828</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21777,7 +21769,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21786,7 +21778,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.68114858085452734</v>
+        <v>-0.59852455114878178</v>
       </c>
     </row>
   </sheetData>
@@ -21882,37 +21874,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="264" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21969,19 +21961,19 @@
       </c>
       <c r="D6" s="226">
         <f>Statement!N25</f>
-        <v>-2.56</v>
+        <v>-3.4734299516908211</v>
       </c>
       <c r="E6" s="226">
         <f>Statement!O25</f>
-        <v>1.58</v>
+        <v>-4.716981132075472E-2</v>
       </c>
       <c r="F6" s="226">
         <f>Statement!P25</f>
-        <v>6.77</v>
+        <v>6.6820276497695854</v>
       </c>
       <c r="G6" s="227">
         <f>Statement!Q25</f>
-        <v>13.9</v>
+        <v>13.292576419213974</v>
       </c>
       <c r="H6" s="137"/>
       <c r="I6" s="137"/>
@@ -22025,18 +22017,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22092,19 +22084,19 @@
       <c r="C11" s="137"/>
       <c r="D11" s="95">
         <f>(D6-C6)/C6</f>
-        <v>-1.3478260869565217</v>
+        <v>-1.4719334173492962</v>
       </c>
       <c r="E11" s="95">
         <f>(E6-D6)/D6</f>
-        <v>-1.6171875000000002</v>
+        <v>-0.98641981788122912</v>
       </c>
       <c r="F11" s="95">
         <f>(F6-E6)/E6</f>
-        <v>3.2848101265822782</v>
+        <v>-142.65898617511519</v>
       </c>
       <c r="G11" s="96">
         <f>(G6-F6)/F6</f>
-        <v>1.0531757754800593</v>
+        <v>0.98930281584098778</v>
       </c>
       <c r="H11" s="137"/>
       <c r="I11" s="137"/>
@@ -22157,18 +22149,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="260" t="s">
+      <c r="C14" s="258" t="s">
         <v>364</v>
       </c>
-      <c r="D14" s="260"/>
-      <c r="E14" s="260"/>
-      <c r="F14" s="260"/>
-      <c r="G14" s="260"/>
-      <c r="H14" s="260"/>
-      <c r="I14" s="260"/>
-      <c r="J14" s="260"/>
-      <c r="K14" s="260"/>
-      <c r="L14" s="260"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="258"/>
+      <c r="F14" s="258"/>
+      <c r="G14" s="258"/>
+      <c r="H14" s="258"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="258"/>
+      <c r="K14" s="258"/>
+      <c r="L14" s="258"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22227,19 +22219,19 @@
       </c>
       <c r="D16" s="95">
         <f t="shared" ref="D16:G16" si="2">D7/D6</f>
-        <v>-1.09375</v>
+        <v>-0.8061196105702364</v>
       </c>
       <c r="E16" s="95">
         <f t="shared" si="2"/>
-        <v>1.7721518987341771</v>
+        <v>-59.359999999999992</v>
       </c>
       <c r="F16" s="95">
         <f t="shared" si="2"/>
-        <v>0.42245199409158052</v>
+        <v>0.42801379310344823</v>
       </c>
       <c r="G16" s="96">
         <f t="shared" si="2"/>
-        <v>0.21007194244604316</v>
+        <v>0.21967148488830485</v>
       </c>
       <c r="H16" s="137"/>
       <c r="I16" s="137"/>
@@ -22258,10 +22250,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="252" t="s">
         <v>366</v>
       </c>
-      <c r="C20" s="254"/>
+      <c r="C20" s="252"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22295,8 +22287,8 @@
         <v>343</v>
       </c>
       <c r="C24" s="135">
-        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.14597599999999999</v>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22312,8 +22304,8 @@
         <v>208</v>
       </c>
       <c r="C26" s="241">
-        <f ca="1">C23/(C24-C25)</f>
-        <v>23.874388772464595</v>
+        <f>C23/(C24-C25)</f>
+        <v>30.076000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -22363,60 +22355,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="254" t="s">
+      <c r="C3" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="263"/>
-      <c r="H3" s="264" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="P3" s="265"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="265"/>
-      <c r="S3" s="265"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="P5" s="265"/>
-      <c r="Q5" s="265"/>
-      <c r="R5" s="265"/>
-      <c r="S5" s="265"/>
-      <c r="T5" s="265"/>
-      <c r="U5" s="265"/>
-      <c r="V5" s="265"/>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22491,35 +22483,35 @@
       </c>
       <c r="E7" s="112">
         <f>'FCF &amp; Other'!E28</f>
-        <v>736.2696629213483</v>
+        <v>316.70175438596488</v>
       </c>
       <c r="F7" s="112">
         <f>'FCF &amp; Other'!F28</f>
-        <v>856.03635161929924</v>
+        <v>825.14746543778801</v>
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3080.6005420054198</v>
+        <v>2923.4431202600217</v>
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>4805.736845528455</v>
+        <v>4326.6958179848325</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>7496.9494790243898</v>
+        <v>6403.5098106175519</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>11695.241187278049</v>
+        <v>9477.1945197139776</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>18244.576252153758</v>
+        <v>14026.247889176686</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>28461.538953359865</v>
+        <v>20758.846875981493</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22550,8 +22542,8 @@
       <c r="J8" s="137"/>
       <c r="K8" s="137"/>
       <c r="L8" s="126">
-        <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>222905.67340100621</v>
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>200668.85313448776</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22604,24 +22596,24 @@
       <c r="F10" s="137"/>
       <c r="G10" s="138"/>
       <c r="H10" s="126">
-        <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>4198.6187125707265</v>
+        <f>H7/(1+$C$21)^H9</f>
+        <v>3863.1212660578858</v>
       </c>
       <c r="I10" s="126">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>5722.390440817514</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>5104.8388158622056</v>
       </c>
       <c r="J10" s="126">
-        <f t="shared" ca="1" si="1"/>
-        <v>7799.1726800812839</v>
+        <f t="shared" si="1"/>
+        <v>6745.6798638179143</v>
       </c>
       <c r="K10" s="126">
-        <f t="shared" ca="1" si="1"/>
-        <v>10629.665193736129</v>
+        <f t="shared" si="1"/>
+        <v>8913.9341057593865</v>
       </c>
       <c r="L10" s="126">
-        <f t="shared" ca="1" si="1"/>
-        <v>14487.406134691168</v>
+        <f t="shared" si="1"/>
+        <v>11779.127211182045</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22639,16 +22631,16 @@
       <c r="J11" s="137"/>
       <c r="K11" s="137"/>
       <c r="L11" s="126">
-        <f ca="1">L8/(1+C21)^L9</f>
-        <v>113462.76902240326</v>
+        <f>L8/(1+C21)^L9</f>
+        <v>113864.89637475976</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="267" t="s">
+      <c r="B14" s="264" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="268"/>
+      <c r="C14" s="265"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22656,7 +22648,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22664,8 +22656,8 @@
         <v>223</v>
       </c>
       <c r="C16" s="154">
-        <f ca="1">C36</f>
-        <v>683.73137526123378</v>
+        <f>C36</f>
+        <v>648.60259842364871</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22673,7 +22665,7 @@
         <v>323</v>
       </c>
       <c r="C17" s="156">
-        <v>0.56000000000000005</v>
+        <v>0.48</v>
       </c>
       <c r="E17" s="266" t="s">
         <v>224</v>
@@ -22685,10 +22677,10 @@
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="267" t="s">
+      <c r="B19" s="264" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="268"/>
+      <c r="C19" s="265"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22703,8 +22695,8 @@
         <v>164</v>
       </c>
       <c r="C21" s="218">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14459949200436034</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22713,7 +22705,7 @@
       </c>
       <c r="C22" s="219">
         <f>Statement!AC74</f>
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
@@ -22722,7 +22714,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>159006.69</v>
+        <v>148253.40000000002</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22749,23 +22741,23 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>160099.69</v>
+        <v>149346.40000000002</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="267" t="s">
+      <c r="B28" s="264" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="268"/>
+      <c r="C28" s="265"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
         <v>186</v>
       </c>
       <c r="C29" s="159">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>42837.253161896821</v>
+        <f>SUM(H10:L10)</f>
+        <v>36406.701262679439</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22773,8 +22765,8 @@
         <v>182</v>
       </c>
       <c r="C30" s="159">
-        <f ca="1">L11</f>
-        <v>113462.76902240326</v>
+        <f>L11</f>
+        <v>113864.89637475976</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22782,8 +22774,8 @@
         <v>187</v>
       </c>
       <c r="C31" s="162">
-        <f ca="1">C29+C30</f>
-        <v>156300.02218430006</v>
+        <f>C29+C30</f>
+        <v>150271.5976374392</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22809,8 +22801,8 @@
         <v>190</v>
       </c>
       <c r="C34" s="162">
-        <f ca="1">C31+C32-C33</f>
-        <v>155207.02218430006</v>
+        <f>C31+C32-C33</f>
+        <v>149178.5976374392</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22819,7 +22811,7 @@
       </c>
       <c r="C35" s="159">
         <f>C22</f>
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22827,22 +22819,22 @@
         <v>191</v>
       </c>
       <c r="C36" s="165">
-        <f ca="1">C34/C35</f>
-        <v>683.73137526123378</v>
+        <f>C34/C35</f>
+        <v>648.60259842364871</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23578,47 +23570,44 @@
         <v>-29</v>
       </c>
       <c r="N13" s="62">
-        <f>190-41</f>
-        <v>149</v>
+        <v>-41</v>
       </c>
       <c r="O13" s="62">
-        <f>417-29-78</f>
-        <v>310</v>
+        <v>-78</v>
       </c>
       <c r="P13" s="62">
-        <v>-81</v>
+        <v>-75</v>
       </c>
       <c r="Q13" s="62">
-        <v>-150</v>
+        <v>2</v>
       </c>
       <c r="T13" s="62">
         <v>-62</v>
       </c>
       <c r="U13" s="62">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="V13" s="62">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="W13" s="62">
         <v>-7</v>
       </c>
       <c r="X13" s="62">
-        <v>-71</v>
+        <v>-5</v>
       </c>
       <c r="Y13" s="62">
-        <v>-72</v>
+        <v>-3</v>
       </c>
       <c r="Z13" s="62">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA13" s="62">
-        <f>-44-4</f>
-        <v>-48</v>
+        <v>-4</v>
       </c>
       <c r="AC13" s="62">
         <f t="shared" si="0"/>
-        <v>-191</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.2">
@@ -23642,16 +23631,17 @@
         <v>1679</v>
       </c>
       <c r="N14" s="61">
-        <v>-496</v>
+        <v>-686</v>
       </c>
       <c r="O14" s="61">
-        <v>445</v>
+        <f>O11+O12+O13</f>
+        <v>57</v>
       </c>
       <c r="P14" s="18">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="Q14" s="18">
-        <v>3690</v>
+        <v>3692</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -23659,30 +23649,30 @@
         <v>350</v>
       </c>
       <c r="U14" s="18">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="V14" s="18">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="W14" s="18">
         <v>614</v>
       </c>
       <c r="X14" s="18">
-        <v>707</v>
+        <v>773</v>
       </c>
       <c r="Y14" s="18">
-        <v>864</v>
+        <v>933</v>
       </c>
       <c r="Z14" s="18">
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="AA14" s="18">
-        <v>1982</v>
+        <v>2026</v>
       </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="18">
         <f t="shared" si="0"/>
-        <v>5058</v>
+        <v>5247</v>
       </c>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
@@ -23710,41 +23700,41 @@
         <v>-33</v>
       </c>
       <c r="O15" s="62">
-        <v>-110</v>
+        <v>-67</v>
       </c>
       <c r="P15" s="62">
-        <v>-44</v>
+        <v>-69</v>
       </c>
       <c r="Q15" s="62">
-        <v>-506</v>
+        <v>-648</v>
       </c>
       <c r="T15" s="62">
         <v>-14</v>
       </c>
       <c r="U15" s="62">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="V15" s="62">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="W15" s="62">
         <v>-65</v>
       </c>
       <c r="X15" s="62">
-        <v>-114</v>
+        <v>-129</v>
       </c>
       <c r="Y15" s="62">
-        <v>-116</v>
+        <v>-171</v>
       </c>
       <c r="Z15" s="62">
-        <v>-211</v>
+        <v>-242</v>
       </c>
       <c r="AA15" s="62">
-        <v>-221</v>
+        <v>-328</v>
       </c>
       <c r="AC15" s="62">
         <f t="shared" si="0"/>
-        <v>-662</v>
+        <v>-870</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
@@ -23828,16 +23818,18 @@
         <v>1649</v>
       </c>
       <c r="N17" s="61">
-        <v>-529</v>
+        <v>-719</v>
       </c>
       <c r="O17" s="61">
-        <v>335</v>
+        <f>O14+O15</f>
+        <v>-10</v>
       </c>
       <c r="P17" s="18">
-        <v>1469</v>
+        <v>1450</v>
       </c>
       <c r="Q17" s="18">
-        <v>3184</v>
+        <f>Q14+Q15</f>
+        <v>3044</v>
       </c>
       <c r="R17" s="60"/>
       <c r="S17" s="60"/>
@@ -23845,30 +23837,32 @@
         <v>336</v>
       </c>
       <c r="U17" s="18">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="V17" s="18">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="W17" s="18">
         <v>549</v>
       </c>
       <c r="X17" s="18">
-        <v>593</v>
+        <f>X14+X15</f>
+        <v>644</v>
       </c>
       <c r="Y17" s="18">
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="Z17" s="18">
-        <v>1294</v>
+        <f>Z14+Z15</f>
+        <v>1273</v>
       </c>
       <c r="AA17" s="18">
-        <v>1761</v>
+        <v>1698</v>
       </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="61">
         <f t="shared" si="0"/>
-        <v>4396</v>
+        <v>4377</v>
       </c>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
@@ -24217,44 +24211,45 @@
         <v>7.5</v>
       </c>
       <c r="N22" s="63">
-        <v>-2.56</v>
+        <v>-3.4734299516908211</v>
       </c>
       <c r="O22" s="63">
-        <v>1.6</v>
+        <v>-4.784688995215311E-2</v>
       </c>
       <c r="P22" s="26">
-        <v>6.93</v>
+        <v>6.8396226415094343</v>
       </c>
       <c r="Q22" s="26">
-        <v>14.54</v>
+        <f>Q17/Q18</f>
+        <v>13.899543378995434</v>
       </c>
       <c r="T22" s="26">
         <v>1.58</v>
       </c>
       <c r="U22" s="26">
-        <v>1.6</v>
+        <v>1.5990566037735849</v>
       </c>
       <c r="V22" s="26">
-        <v>2.2999999999999998</v>
+        <v>2.2830188679245285</v>
       </c>
       <c r="W22" s="26">
         <v>2.58</v>
       </c>
       <c r="X22" s="26">
-        <v>2.75</v>
+        <v>2.9814814814814814</v>
       </c>
       <c r="Y22" s="26">
-        <v>3.38</v>
+        <v>3.4479638009049776</v>
       </c>
       <c r="Z22" s="26">
-        <v>5.75</v>
+        <v>5.6577777777777776</v>
       </c>
       <c r="AA22" s="26">
-        <v>7.72</v>
+        <v>7.4473684210526319</v>
       </c>
       <c r="AC22" s="26">
         <f>SUM(X22:AA22)</f>
-        <v>19.599999999999998</v>
+        <v>19.534591481216868</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
@@ -24280,19 +24275,19 @@
       </c>
       <c r="N23" s="65">
         <f t="shared" si="13"/>
-        <v>-2.56</v>
+        <v>-3.4734299516908211</v>
       </c>
       <c r="O23" s="65">
         <f t="shared" si="13"/>
-        <v>1.6</v>
+        <v>-4.784688995215311E-2</v>
       </c>
       <c r="P23" s="65">
         <f t="shared" si="13"/>
-        <v>6.93</v>
+        <v>6.8396226415094343</v>
       </c>
       <c r="Q23" s="65">
         <f t="shared" si="13"/>
-        <v>14.54</v>
+        <v>13.899543378995434</v>
       </c>
       <c r="T23" s="65">
         <f t="shared" ref="T23:Y23" si="14">T22/T$84</f>
@@ -24300,11 +24295,11 @@
       </c>
       <c r="U23" s="65">
         <f t="shared" si="14"/>
-        <v>1.6</v>
+        <v>1.5990566037735849</v>
       </c>
       <c r="V23" s="65">
         <f t="shared" si="14"/>
-        <v>2.2999999999999998</v>
+        <v>2.2830188679245285</v>
       </c>
       <c r="W23" s="65">
         <f t="shared" si="14"/>
@@ -24312,23 +24307,23 @@
       </c>
       <c r="X23" s="65">
         <f t="shared" si="14"/>
-        <v>2.75</v>
+        <v>2.9814814814814814</v>
       </c>
       <c r="Y23" s="65">
         <f t="shared" si="14"/>
-        <v>3.38</v>
+        <v>3.4479638009049776</v>
       </c>
       <c r="Z23" s="65">
         <f t="shared" ref="Z23:AA23" si="15">Z22/Z$84</f>
-        <v>5.75</v>
+        <v>5.6577777777777776</v>
       </c>
       <c r="AA23" s="65">
         <f t="shared" si="15"/>
-        <v>7.72</v>
+        <v>7.4473684210526319</v>
       </c>
       <c r="AC23" s="65">
         <f>AC22/AC$84</f>
-        <v>19.599999999999998</v>
+        <v>19.534591481216868</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
@@ -24351,44 +24346,44 @@
         <v>7.36</v>
       </c>
       <c r="N24" s="63">
-        <v>-2.56</v>
+        <v>-3.4734299516908211</v>
       </c>
       <c r="O24" s="63">
-        <v>1.58</v>
+        <v>-4.716981132075472E-2</v>
       </c>
       <c r="P24" s="26">
-        <v>6.77</v>
+        <v>6.6820276497695854</v>
       </c>
       <c r="Q24" s="26">
-        <v>13.9</v>
+        <v>13.292576419213974</v>
       </c>
       <c r="T24" s="26">
         <v>1.55</v>
       </c>
       <c r="U24" s="63">
-        <v>1.57</v>
+        <v>1.5694444444444444</v>
       </c>
       <c r="V24" s="26">
-        <v>2.2400000000000002</v>
+        <v>2.2201834862385321</v>
       </c>
       <c r="W24" s="26">
         <v>2.4300000000000002</v>
       </c>
       <c r="X24" s="26">
-        <v>2.6</v>
+        <v>2.8245614035087718</v>
       </c>
       <c r="Y24" s="26">
-        <v>3.27</v>
+        <v>3.3275109170305677</v>
       </c>
       <c r="Z24" s="26">
-        <v>5.58</v>
+        <v>5.4870689655172411</v>
       </c>
       <c r="AA24" s="26">
-        <v>7.59</v>
+        <v>7.318965517241379</v>
       </c>
       <c r="AC24" s="26">
         <f>SUM(X24:AA24)</f>
-        <v>19.04</v>
+        <v>18.958106803297959</v>
       </c>
     </row>
     <row r="25" spans="1:31" s="30" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24415,19 +24410,19 @@
       </c>
       <c r="N25" s="66">
         <f t="shared" si="16"/>
-        <v>-2.56</v>
+        <v>-3.4734299516908211</v>
       </c>
       <c r="O25" s="66">
         <f t="shared" si="16"/>
-        <v>1.58</v>
+        <v>-4.716981132075472E-2</v>
       </c>
       <c r="P25" s="66">
         <f t="shared" si="16"/>
-        <v>6.77</v>
+        <v>6.6820276497695854</v>
       </c>
       <c r="Q25" s="66">
         <f t="shared" si="16"/>
-        <v>13.9</v>
+        <v>13.292576419213974</v>
       </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -24437,11 +24432,11 @@
       </c>
       <c r="U25" s="66">
         <f t="shared" si="17"/>
-        <v>1.57</v>
+        <v>1.5694444444444444</v>
       </c>
       <c r="V25" s="66">
         <f t="shared" si="17"/>
-        <v>2.2400000000000002</v>
+        <v>2.2201834862385321</v>
       </c>
       <c r="W25" s="66">
         <f t="shared" si="17"/>
@@ -24449,24 +24444,24 @@
       </c>
       <c r="X25" s="66">
         <f t="shared" si="17"/>
-        <v>2.6</v>
+        <v>2.8245614035087718</v>
       </c>
       <c r="Y25" s="66">
         <f t="shared" si="17"/>
-        <v>3.27</v>
+        <v>3.3275109170305677</v>
       </c>
       <c r="Z25" s="66">
         <f t="shared" ref="Z25:AA25" si="18">Z24/Z$84</f>
-        <v>5.58</v>
+        <v>5.4870689655172411</v>
       </c>
       <c r="AA25" s="66">
         <f t="shared" si="18"/>
-        <v>7.59</v>
+        <v>7.318965517241379</v>
       </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="66">
         <f>AC24/AC$84</f>
-        <v>19.04</v>
+        <v>18.958106803297959</v>
       </c>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
@@ -25513,7 +25508,7 @@
       <c r="Z43" s="62">
         <v>0</v>
       </c>
-      <c r="AA43" s="249">
+      <c r="AA43" s="62">
         <v>0</v>
       </c>
       <c r="AC43" s="62">
@@ -25573,7 +25568,7 @@
       <c r="Z44" s="62">
         <v>0</v>
       </c>
-      <c r="AA44" s="249">
+      <c r="AA44" s="62">
         <v>0</v>
       </c>
       <c r="AC44" s="62">
@@ -25633,12 +25628,12 @@
       <c r="Z45" s="21">
         <v>8078</v>
       </c>
-      <c r="AA45" s="250">
-        <v>8078</v>
+      <c r="AA45" s="21">
+        <v>8194</v>
       </c>
       <c r="AC45" s="62">
         <f t="shared" si="19"/>
-        <v>8078</v>
+        <v>8194</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
@@ -25693,12 +25688,12 @@
       <c r="Z46" s="62">
         <v>-5911</v>
       </c>
-      <c r="AA46" s="249">
-        <v>-5911</v>
+      <c r="AA46" s="62">
+        <v>-4737</v>
       </c>
       <c r="AC46" s="62">
         <f t="shared" si="19"/>
-        <v>-5911</v>
+        <v>-4737</v>
       </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
@@ -25753,7 +25748,7 @@
       <c r="Z47" s="62">
         <v>0</v>
       </c>
-      <c r="AA47" s="249">
+      <c r="AA47" s="62">
         <v>0</v>
       </c>
       <c r="AC47" s="62">
@@ -26879,19 +26874,19 @@
       </c>
       <c r="N68" s="64">
         <f t="shared" si="29"/>
-        <v>-529</v>
+        <v>-719</v>
       </c>
       <c r="O68" s="64">
         <f t="shared" si="29"/>
-        <v>335</v>
+        <v>-10</v>
       </c>
       <c r="P68" s="64">
         <f t="shared" si="29"/>
-        <v>1469</v>
+        <v>1450</v>
       </c>
       <c r="Q68" s="64">
         <f t="shared" ref="Q68" si="30">Q5-Q6-Q10+Q12+Q13+Q15-Q16</f>
-        <v>3184</v>
+        <v>3194</v>
       </c>
       <c r="T68" s="64">
         <f t="shared" ref="T68:Z68" si="31">T5-T6-T10+T12+T13+T15-T16</f>
@@ -26899,11 +26894,11 @@
       </c>
       <c r="U68" s="64">
         <f t="shared" si="31"/>
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="V68" s="64">
         <f t="shared" si="31"/>
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="W68" s="64">
         <f t="shared" si="31"/>
@@ -26911,23 +26906,23 @@
       </c>
       <c r="X68" s="64">
         <f t="shared" si="31"/>
-        <v>593</v>
+        <v>644</v>
       </c>
       <c r="Y68" s="64">
         <f t="shared" si="31"/>
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="Z68" s="64">
         <f t="shared" si="31"/>
-        <v>1294</v>
+        <v>1273</v>
       </c>
       <c r="AA68" s="64">
         <f t="shared" ref="AA68:AC68" si="32">AA5-AA6-AA10+AA12+AA13+AA15-AA16</f>
-        <v>1761</v>
+        <v>1698</v>
       </c>
       <c r="AC68" s="64">
         <f t="shared" si="32"/>
-        <v>4396</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="69" spans="1:31" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -26993,7 +26988,7 @@
       </c>
       <c r="Q69" s="40">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -27216,12 +27211,12 @@
       <c r="Z73" s="21">
         <v>227</v>
       </c>
-      <c r="AA73" s="250">
-        <v>227</v>
+      <c r="AA73" s="21">
+        <v>230</v>
       </c>
       <c r="AC73" s="24">
         <f>AA73</f>
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="1:31" x14ac:dyDescent="0.2">
@@ -27291,11 +27286,11 @@
       </c>
       <c r="AA74" s="25">
         <f t="shared" si="46"/>
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AC74" s="24">
         <f>AA74</f>
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.2">
@@ -27350,12 +27345,12 @@
       <c r="Z75" s="21">
         <v>10</v>
       </c>
-      <c r="AA75" s="250">
-        <v>10</v>
+      <c r="AA75" s="21">
+        <v>4</v>
       </c>
       <c r="AC75" s="21">
         <f>AA75</f>
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
@@ -27425,11 +27420,11 @@
       </c>
       <c r="AA76" s="25">
         <f t="shared" ref="AA76" si="49">AA75*AA84</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AC76" s="24">
         <f>AA76</f>
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
@@ -27499,11 +27494,11 @@
       </c>
       <c r="AA77" s="25">
         <f t="shared" ref="AA77" si="52">AA74+AA76</f>
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AC77" s="24">
         <f>AA77</f>
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
@@ -27788,15 +27783,15 @@
       </c>
       <c r="O82" s="46">
         <f t="shared" si="61"/>
-        <v>0.24719101123595505</v>
+        <v>1.1754385964912282</v>
       </c>
       <c r="P82" s="46">
         <f t="shared" si="61"/>
-        <v>2.9081295439524125E-2</v>
+        <v>4.5424621461487819E-2</v>
       </c>
       <c r="Q82" s="46">
         <f t="shared" si="60"/>
-        <v>0.13712737127371274</v>
+        <v>0.17551462621885158</v>
       </c>
       <c r="T82" s="46">
         <f t="shared" ref="T82:Y82" si="62">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
@@ -27804,11 +27799,11 @@
       </c>
       <c r="U82" s="46">
         <f t="shared" si="62"/>
-        <v>4.2253521126760563E-2</v>
+        <v>5.5710306406685235E-2</v>
       </c>
       <c r="V82" s="46">
         <f t="shared" si="62"/>
-        <v>8.130081300813009E-3</v>
+        <v>2.2222222222222223E-2</v>
       </c>
       <c r="W82" s="46">
         <f t="shared" si="62"/>
@@ -27816,23 +27811,23 @@
       </c>
       <c r="X82" s="46">
         <f t="shared" si="62"/>
-        <v>0.16124469589816123</v>
+        <v>0.16688227684346701</v>
       </c>
       <c r="Y82" s="46">
         <f t="shared" si="62"/>
-        <v>0.13425925925925927</v>
+        <v>0.18327974276527331</v>
       </c>
       <c r="Z82" s="46">
         <f t="shared" ref="Z82:AA82" si="63">IF(AND(Z14&gt;0,Z15&lt;0),-(Z15)/Z14,0)</f>
-        <v>0.14019933554817277</v>
+        <v>0.15973597359735975</v>
       </c>
       <c r="AA82" s="46">
         <f t="shared" si="63"/>
-        <v>0.11150353178607467</v>
+        <v>0.16189536031589338</v>
       </c>
       <c r="AC82" s="46">
         <f>IF(AND(AC14&gt;0,AC15&lt;0),-(AC15)/AC14,0)</f>
-        <v>0.13088177145116647</v>
+        <v>0.16580903373356204</v>
       </c>
     </row>
     <row r="83" spans="1:31" x14ac:dyDescent="0.2">
@@ -28566,19 +28561,19 @@
       </c>
       <c r="N95" s="52">
         <f t="shared" si="81"/>
-        <v>-1.2954139368671829</v>
+        <v>-1.4085765336509828</v>
       </c>
       <c r="O95" s="52">
         <f t="shared" si="81"/>
-        <v>1.8971774193548387</v>
+        <v>1.0830903790087463</v>
       </c>
       <c r="P95" s="52">
         <f t="shared" si="81"/>
-        <v>2.4</v>
+        <v>25.649122807017545</v>
       </c>
       <c r="Q95" s="52">
         <f t="shared" si="81"/>
-        <v>1.4388631857237277</v>
+        <v>1.4305464121132323</v>
       </c>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
@@ -28594,49 +28589,49 @@
 IF(U14=0,0,IF(U14&gt;0,1,-1)),
 (U14-T14)/ABS(T14)
 )</f>
-        <v>1.4285714285714285E-2</v>
+        <v>2.5714285714285714E-2</v>
       </c>
       <c r="V95" s="52">
         <f t="shared" ref="V95" si="84">IF(U14=0,
 IF(V14=0,0,IF(V14&gt;0,1,-1)),
 (V14-U14)/ABS(U14)
 )</f>
-        <v>0.38591549295774646</v>
+        <v>0.37883008356545961</v>
       </c>
       <c r="W95" s="52">
         <f t="shared" ref="W95" si="85">IF(V14=0,
 IF(W14=0,0,IF(W14&gt;0,1,-1)),
 (W14-V14)/ABS(V14)
 )</f>
-        <v>0.24796747967479674</v>
+        <v>0.2404040404040404</v>
       </c>
       <c r="X95" s="52">
         <f t="shared" ref="X95" si="86">IF(W14=0,
 IF(X14=0,0,IF(X14&gt;0,1,-1)),
 (X14-W14)/ABS(W14)
 )</f>
-        <v>0.15146579804560262</v>
+        <v>0.25895765472312704</v>
       </c>
       <c r="Y95" s="52">
         <f t="shared" ref="Y95" si="87">IF(X14=0,
 IF(Y14=0,0,IF(Y14&gt;0,1,-1)),
 (Y14-X14)/ABS(X14)
 )</f>
-        <v>0.22206506364922207</v>
+        <v>0.20698576972833119</v>
       </c>
       <c r="Z95" s="52">
         <f t="shared" ref="Z95" si="88">IF(Y14=0,
 IF(Z14=0,0,IF(Z14&gt;0,1,-1)),
 (Z14-Y14)/ABS(Y14)
 )</f>
-        <v>0.74189814814814814</v>
+        <v>0.6237942122186495</v>
       </c>
       <c r="AA95" s="52">
         <f t="shared" ref="AA95" si="89">IF(Z14=0,
 IF(AA14=0,0,IF(AA14&gt;0,1,-1)),
 (AA14-Z14)/ABS(Z14)
 )</f>
-        <v>0.31694352159468436</v>
+        <v>0.33729372937293728</v>
       </c>
       <c r="AB95" s="1"/>
       <c r="AC95" s="67"/>
@@ -28670,19 +28665,19 @@
       </c>
       <c r="N96" s="52">
         <f t="shared" si="90"/>
-        <v>-1.3208004851425106</v>
+        <v>-1.4360218314129776</v>
       </c>
       <c r="O96" s="52">
         <f t="shared" si="90"/>
-        <v>1.6332703213610587</v>
+        <v>0.98609179415855353</v>
       </c>
       <c r="P96" s="52">
         <f t="shared" si="90"/>
-        <v>3.3850746268656717</v>
+        <v>146</v>
       </c>
       <c r="Q96" s="52">
         <f t="shared" si="90"/>
-        <v>1.1674608577263446</v>
+        <v>1.0993103448275863</v>
       </c>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
@@ -28698,49 +28693,49 @@
 IF(U17=0,0,IF(U17&gt;0,1,-1)),
 (U17-T17)/ABS(T17)
 )</f>
-        <v>1.1904761904761904E-2</v>
+        <v>8.9285714285714281E-3</v>
       </c>
       <c r="V96" s="52">
         <f t="shared" ref="V96" si="93">IF(U17=0,
 IF(V17=0,0,IF(V17&gt;0,1,-1)),
 (V17-U17)/ABS(U17)
 )</f>
-        <v>0.43529411764705883</v>
+        <v>0.42772861356932151</v>
       </c>
       <c r="W96" s="52">
         <f t="shared" ref="W96" si="94">IF(V17=0,
 IF(W17=0,0,IF(W17&gt;0,1,-1)),
 (W17-V17)/ABS(V17)
 )</f>
-        <v>0.125</v>
+        <v>0.13429752066115702</v>
       </c>
       <c r="X96" s="52">
         <f t="shared" ref="X96" si="95">IF(W17=0,
 IF(X17=0,0,IF(X17&gt;0,1,-1)),
 (X17-W17)/ABS(W17)
 )</f>
-        <v>8.0145719489981782E-2</v>
+        <v>0.17304189435336975</v>
       </c>
       <c r="Y96" s="52">
         <f t="shared" ref="Y96" si="96">IF(X17=0,
 IF(Y17=0,0,IF(Y17&gt;0,1,-1)),
 (Y17-X17)/ABS(X17)
 )</f>
-        <v>0.26138279932546377</v>
+        <v>0.18322981366459629</v>
       </c>
       <c r="Z96" s="52">
         <f t="shared" ref="Z96" si="97">IF(Y17=0,
 IF(Z17=0,0,IF(Z17&gt;0,1,-1)),
 (Z17-Y17)/ABS(Y17)
 )</f>
-        <v>0.72994652406417115</v>
+        <v>0.67060367454068237</v>
       </c>
       <c r="AA96" s="52">
         <f t="shared" ref="AA96" si="98">IF(Z17=0,
 IF(AA17=0,0,IF(AA17&gt;0,1,-1)),
 (AA17-Z17)/ABS(Z17)
 )</f>
-        <v>0.36089644513137559</v>
+        <v>0.33385703063629224</v>
       </c>
       <c r="AB96" s="1"/>
       <c r="AC96" s="67"/>
@@ -28933,19 +28928,19 @@
       </c>
       <c r="N101" s="55">
         <f t="shared" si="105"/>
-        <v>-7.164138678223185E-2</v>
+        <v>-9.73726977248104E-2</v>
       </c>
       <c r="O101" s="55">
         <f t="shared" si="105"/>
-        <v>5.1137230957105782E-2</v>
+        <v>-1.5264845061822622E-3</v>
       </c>
       <c r="P101" s="55">
         <f t="shared" si="105"/>
-        <v>0.16148180718918326</v>
+        <v>0.15939320655161043</v>
       </c>
       <c r="Q101" s="55">
         <f t="shared" si="105"/>
-        <v>0.26109061090610908</v>
+        <v>0.24961049610496105</v>
       </c>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
@@ -28955,11 +28950,11 @@
       </c>
       <c r="U101" s="55">
         <f t="shared" si="106"/>
-        <v>0.15740740740740741</v>
+        <v>0.15694444444444444</v>
       </c>
       <c r="V101" s="55">
         <f t="shared" si="106"/>
-        <v>0.19967266775777415</v>
+        <v>0.19803600654664485</v>
       </c>
       <c r="W101" s="55">
         <f t="shared" si="106"/>
@@ -28967,24 +28962,24 @@
       </c>
       <c r="X101" s="55">
         <f t="shared" si="106"/>
-        <v>0.20991150442477877</v>
+        <v>0.22796460176991151</v>
       </c>
       <c r="Y101" s="55">
         <f t="shared" si="106"/>
-        <v>0.24035989717223649</v>
+        <v>0.24485861182519281</v>
       </c>
       <c r="Z101" s="55">
         <f t="shared" ref="Z101:AA101" si="107">Z109/Z5</f>
-        <v>0.35657205841829703</v>
+        <v>0.35078534031413611</v>
       </c>
       <c r="AA101" s="55">
         <f t="shared" si="107"/>
-        <v>0.41601700921332391</v>
+        <v>0.4011339475549256</v>
       </c>
       <c r="AB101" s="1"/>
       <c r="AC101" s="55">
         <f>AC109/AC5</f>
-        <v>0.31857380969635479</v>
+        <v>0.31719689832596565</v>
       </c>
       <c r="AD101" s="1"/>
       <c r="AE101" s="1"/>
@@ -29057,15 +29052,15 @@
       </c>
       <c r="O104" s="81">
         <f t="shared" si="109"/>
-        <v>0.24719101123595505</v>
+        <v>1.1754385964912282</v>
       </c>
       <c r="P104" s="81">
         <f t="shared" si="109"/>
-        <v>2.9081295439524125E-2</v>
+        <v>4.5424621461487819E-2</v>
       </c>
       <c r="Q104" s="81">
         <f t="shared" si="108"/>
-        <v>0.13712737127371274</v>
+        <v>0.17551462621885158</v>
       </c>
       <c r="T104" s="81">
         <f t="shared" ref="T104:Y104" si="110">IF(AND(T82&gt;=0,T11&gt;=0),T82,0)</f>
@@ -29073,11 +29068,11 @@
       </c>
       <c r="U104" s="81">
         <f t="shared" si="110"/>
-        <v>4.2253521126760563E-2</v>
+        <v>5.5710306406685235E-2</v>
       </c>
       <c r="V104" s="81">
         <f t="shared" si="110"/>
-        <v>8.130081300813009E-3</v>
+        <v>2.2222222222222223E-2</v>
       </c>
       <c r="W104" s="81">
         <f t="shared" si="110"/>
@@ -29085,23 +29080,23 @@
       </c>
       <c r="X104" s="81">
         <f t="shared" si="110"/>
-        <v>0.16124469589816123</v>
+        <v>0.16688227684346701</v>
       </c>
       <c r="Y104" s="81">
         <f t="shared" si="110"/>
-        <v>0.13425925925925927</v>
+        <v>0.18327974276527331</v>
       </c>
       <c r="Z104" s="81">
         <f t="shared" ref="Z104:AA104" si="111">IF(AND(Z82&gt;=0,Z11&gt;=0),Z82,0)</f>
-        <v>0.14019933554817277</v>
+        <v>0.15973597359735975</v>
       </c>
       <c r="AA104" s="81">
         <f t="shared" si="111"/>
-        <v>0.11150353178607467</v>
+        <v>0.16189536031589338</v>
       </c>
       <c r="AC104" s="81">
         <f>IF(AND(AC82&gt;=0,AC11&gt;=0),AC82,0)</f>
-        <v>0.13088177145116647</v>
+        <v>0.16580903373356204</v>
       </c>
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.2">
@@ -29297,15 +29292,15 @@
       </c>
       <c r="O107" s="126">
         <f t="shared" si="118"/>
-        <v>340.26966292134836</v>
+        <v>-79.298245614035139</v>
       </c>
       <c r="P107" s="25">
         <f t="shared" si="118"/>
-        <v>1835.0363516192995</v>
+        <v>1804.147465437788</v>
       </c>
       <c r="Q107" s="25">
         <f t="shared" si="118"/>
-        <v>3532.6005420054198</v>
+        <v>3375.4431202600217</v>
       </c>
       <c r="T107" s="67"/>
       <c r="U107" s="67"/>
@@ -29317,7 +29312,7 @@
       <c r="AA107" s="67"/>
       <c r="AC107" s="25">
         <f>AC11*(1-AC104)</f>
-        <v>4748.8620007908257</v>
+        <v>4558.019439679817</v>
       </c>
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.2">
@@ -29417,19 +29412,19 @@
       </c>
       <c r="N109" s="126">
         <f t="shared" si="122"/>
-        <v>-529</v>
+        <v>-719</v>
       </c>
       <c r="O109" s="126">
         <f t="shared" si="122"/>
-        <v>335</v>
+        <v>-10</v>
       </c>
       <c r="P109" s="126">
         <f t="shared" si="122"/>
-        <v>1469</v>
+        <v>1450</v>
       </c>
       <c r="Q109" s="126">
         <f t="shared" si="122"/>
-        <v>3184</v>
+        <v>3044</v>
       </c>
       <c r="T109" s="126">
         <f t="shared" ref="T109:Y109" si="123">T16+T17</f>
@@ -29437,11 +29432,11 @@
       </c>
       <c r="U109" s="126">
         <f t="shared" si="123"/>
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="V109" s="126">
         <f t="shared" si="123"/>
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="W109" s="126">
         <f t="shared" si="123"/>
@@ -29449,23 +29444,23 @@
       </c>
       <c r="X109" s="126">
         <f t="shared" si="123"/>
-        <v>593</v>
+        <v>644</v>
       </c>
       <c r="Y109" s="126">
         <f t="shared" si="123"/>
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="Z109" s="126">
         <f t="shared" ref="Z109:AA109" si="124">Z16+Z17</f>
-        <v>1294</v>
+        <v>1273</v>
       </c>
       <c r="AA109" s="126">
         <f t="shared" si="124"/>
-        <v>1761</v>
+        <v>1698</v>
       </c>
       <c r="AC109" s="126">
         <f>AC16+AC17</f>
-        <v>4396</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
@@ -29624,7 +29619,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29698,7 +29693,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29747,19 +29742,19 @@
       </c>
       <c r="N119" s="74">
         <f t="shared" si="131"/>
-        <v>-7.164138678223185E-2</v>
+        <v>-9.73726977248104E-2</v>
       </c>
       <c r="O119" s="74">
         <f t="shared" si="131"/>
-        <v>5.1137230957105782E-2</v>
+        <v>-1.5264845061822622E-3</v>
       </c>
       <c r="P119" s="74">
         <f t="shared" si="131"/>
-        <v>0.16148180718918326</v>
+        <v>0.15939320655161043</v>
       </c>
       <c r="Q119" s="74">
         <f t="shared" si="131"/>
-        <v>0.26109061090610908</v>
+        <v>0.24961049610496105</v>
       </c>
       <c r="T119" s="77"/>
       <c r="U119" s="77"/>
@@ -29771,7 +29766,7 @@
       <c r="AA119" s="77"/>
       <c r="AC119" s="74">
         <f>AC109/AC5</f>
-        <v>0.31857380969635479</v>
+        <v>0.31719689832596565</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -29829,19 +29824,19 @@
       </c>
       <c r="N121" s="76">
         <f t="shared" si="133"/>
-        <v>-7.0010587612493388E-2</v>
+        <v>-9.5156167284277393E-2</v>
       </c>
       <c r="O121" s="76">
         <f t="shared" si="133"/>
-        <v>4.3287246414265401E-2</v>
+        <v>-1.2921566093810569E-3</v>
       </c>
       <c r="P121" s="76">
         <f>P119*P120</f>
-        <v>0.18309859154929578</v>
+        <v>0.18073040009971333</v>
       </c>
       <c r="Q121" s="76">
         <f>Q119*Q120</f>
-        <v>0.31929402326514245</v>
+        <v>0.30525471319695147</v>
       </c>
       <c r="T121" s="79"/>
       <c r="U121" s="79"/>
@@ -29853,7 +29848,7 @@
       <c r="AA121" s="79"/>
       <c r="AC121" s="76">
         <f>AC119*AC120</f>
-        <v>0.42572147975982955</v>
+        <v>0.42388146426496226</v>
       </c>
     </row>
     <row r="122" spans="1:31" x14ac:dyDescent="0.2">
@@ -29911,19 +29906,19 @@
       </c>
       <c r="N123" s="76">
         <f t="shared" si="135"/>
-        <v>0.44120100083402836</v>
+        <v>0.59966638865721433</v>
       </c>
       <c r="O123" s="76">
         <f t="shared" si="135"/>
-        <v>-0.22468142186452042</v>
+        <v>6.7069081153588199E-3</v>
       </c>
       <c r="P123" s="76">
         <f>P121*P122</f>
-        <v>-3.2428256070640176</v>
+        <v>-3.2008830022075054</v>
       </c>
       <c r="Q123" s="76">
         <f>Q121*Q122</f>
-        <v>1.4693124134748501</v>
+        <v>1.4047069681587447</v>
       </c>
       <c r="T123" s="79"/>
       <c r="U123" s="79"/>
@@ -29935,7 +29930,7 @@
       <c r="AA123" s="79"/>
       <c r="AC123" s="76">
         <f>AC121*AC122</f>
-        <v>1.2730958586736172</v>
+        <v>1.2675933970460469</v>
       </c>
     </row>
     <row r="125" spans="1:31" x14ac:dyDescent="0.2">
@@ -30277,11 +30272,11 @@
       <c r="Q133" s="49"/>
       <c r="T133" s="225">
         <f t="shared" ref="T133" si="145">U24</f>
-        <v>1.57</v>
+        <v>1.5694444444444444</v>
       </c>
       <c r="U133" s="225">
         <f t="shared" ref="U133" si="146">V24</f>
-        <v>2.2400000000000002</v>
+        <v>2.2201834862385321</v>
       </c>
       <c r="V133" s="225">
         <f t="shared" ref="V133" si="147">W24</f>
@@ -30289,19 +30284,19 @@
       </c>
       <c r="W133" s="225">
         <f t="shared" ref="W133" si="148">X24</f>
-        <v>2.6</v>
+        <v>2.8245614035087718</v>
       </c>
       <c r="X133" s="225">
         <f t="shared" ref="X133" si="149">Y24</f>
-        <v>3.27</v>
+        <v>3.3275109170305677</v>
       </c>
       <c r="Y133" s="225">
         <f t="shared" ref="Y133" si="150">Z24</f>
-        <v>5.58</v>
+        <v>5.4870689655172411</v>
       </c>
       <c r="Z133" s="225">
         <f t="shared" ref="Z133" si="151">AA24</f>
-        <v>7.59</v>
+        <v>7.318965517241379</v>
       </c>
       <c r="AA133" s="225">
         <f t="shared" ref="AA133" si="152">AB24</f>
@@ -30342,7 +30337,7 @@
       </c>
       <c r="W134" s="221" t="str">
         <f t="shared" si="153"/>
-        <v>MET</v>
+        <v>BEAT</v>
       </c>
       <c r="X134" s="221" t="str">
         <f t="shared" si="153"/>
@@ -30354,7 +30349,7 @@
       </c>
       <c r="Z134" s="221" t="str">
         <f>IF(Z133&gt;Z132, "BEAT", IF(Z133&lt;Z131, "MISSED", "MET"))</f>
-        <v>BEAT</v>
+        <v>MET</v>
       </c>
       <c r="AA134" s="221" t="str">
         <f>IF(AA133&gt;AA132, "BEAT", IF(AA133&lt;AA131, "MISSED", "MET"))</f>
@@ -30421,15 +30416,15 @@
       </c>
       <c r="O138" s="81">
         <f t="shared" si="154"/>
-        <v>0.12044943820224721</v>
+        <v>-2.8070175438596509E-2</v>
       </c>
       <c r="P138" s="81">
         <f t="shared" si="154"/>
-        <v>0.5026119834618733</v>
+        <v>0.49415159283423393</v>
       </c>
       <c r="Q138" s="81">
         <f t="shared" si="154"/>
-        <v>0.87701105809469215</v>
+        <v>0.83799481635055162</v>
       </c>
       <c r="T138" s="49"/>
       <c r="U138" s="49"/>
@@ -30441,7 +30436,7 @@
       <c r="AA138" s="49"/>
       <c r="AC138" s="81">
         <f>AC107/(AC106+AC110-AC105)</f>
-        <v>1.0446242852597505</v>
+        <v>1.0026439594544252</v>
       </c>
     </row>
     <row r="139" spans="2:29" x14ac:dyDescent="0.2">
@@ -31043,19 +31038,19 @@
       </c>
       <c r="N148" s="72">
         <f>N115/Statement!N25</f>
-        <v>-24.16796875</v>
+        <v>-17.812364394993047</v>
       </c>
       <c r="O148" s="72">
         <f>O115/Statement!O25</f>
-        <v>65.360759493670884</v>
+        <v>-2189.3239999999996</v>
       </c>
       <c r="P148" s="72">
         <f>P115/Statement!P25</f>
-        <v>20.892171344165437</v>
+        <v>21.167227586206895</v>
       </c>
       <c r="Q148" s="72">
         <f>Q115/Statement!Q25</f>
-        <v>59.004316546762588</v>
+        <v>61.700604467805512</v>
       </c>
       <c r="T148" s="49"/>
       <c r="U148" s="49"/>
@@ -31067,7 +31062,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>36.789390756302524</v>
+        <v>34.000230439036699</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31108,7 +31103,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>11.688036633089355</v>
+        <v>10.755456554822814</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31169,11 +31164,11 @@
       </c>
       <c r="AA150" s="72">
         <f>AA115/(Statement!AA48/Statement!AA74)</f>
-        <v>55.812548508543294</v>
+        <v>56.550159281783962</v>
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>46.048853171155521</v>
+        <v>42.934665508253694</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31234,11 +31229,11 @@
       </c>
       <c r="AA151" s="141">
         <f>Statement!AA115*Statement!AA77</f>
-        <v>201210.63</v>
+        <v>198663.66</v>
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>166011.39000000001</v>
+        <v>150831.72</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31299,11 +31294,11 @@
       </c>
       <c r="AA152" s="141">
         <f t="shared" si="189"/>
-        <v>202303.63</v>
+        <v>199756.66</v>
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>167104.39000000001</v>
+        <v>151924.72</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31344,7 +31339,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>12.10989129647076</v>
+        <v>11.009835495325749</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31385,7 +31380,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>30.582794655929725</v>
+        <v>27.804670571010249</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31471,15 +31466,15 @@
       </c>
       <c r="O156" s="64">
         <f t="shared" si="195"/>
-        <v>736.2696629213483</v>
+        <v>316.70175438596488</v>
       </c>
       <c r="P156" s="64">
         <f t="shared" si="195"/>
-        <v>856.03635161929924</v>
+        <v>825.14746543778801</v>
       </c>
       <c r="Q156" s="64">
         <f t="shared" si="195"/>
-        <v>3080.6005420054198</v>
+        <v>2923.4431202600217</v>
       </c>
       <c r="T156" s="49"/>
       <c r="U156" s="49"/>
@@ -31491,7 +31486,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="64">
         <f t="shared" ref="AC156" si="196">AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
-        <v>4125.8620007908257</v>
+        <v>3935.019439679817</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31532,7 +31527,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="199">AC151/AC155</f>
-        <v>42.20986270022884</v>
+        <v>38.350297482837526</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31553,15 +31548,15 @@
       </c>
       <c r="O158" s="72">
         <f t="shared" si="200"/>
-        <v>35.737599041631057</v>
+        <v>83.082930977177043</v>
       </c>
       <c r="P158" s="72">
         <f t="shared" si="200"/>
-        <v>40.813593878239608</v>
+        <v>42.341425579564046</v>
       </c>
       <c r="Q158" s="72">
         <f t="shared" ref="Q158" si="201">Q152/Q156</f>
-        <v>63.70151446907547</v>
+        <v>67.125957963753976</v>
       </c>
       <c r="T158" s="49"/>
       <c r="U158" s="49"/>
@@ -31573,7 +31568,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="199"/>
-        <v>40.501691517547179</v>
+        <v>38.608378517276584</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31614,7 +31609,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="204">AC155/AC151</f>
-        <v>2.3691145529231458E-2</v>
+        <v>2.6075417027665002E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31631,19 +31626,19 @@
       </c>
       <c r="N160" s="74">
         <f t="shared" si="205"/>
-        <v>-4.1377080976240509E-2</v>
+        <v>-5.6140778272035258E-2</v>
       </c>
       <c r="O160" s="74">
         <f t="shared" si="205"/>
-        <v>1.529969981601627E-2</v>
+        <v>-4.5676199594029944E-4</v>
       </c>
       <c r="P160" s="74">
         <f t="shared" si="205"/>
-        <v>4.7864819004524883E-2</v>
+        <v>4.7242842546447859E-2</v>
       </c>
       <c r="Q160" s="74">
         <f t="shared" si="205"/>
-        <v>1.6947912602419041E-2</v>
+        <v>1.6207296648475877E-2</v>
       </c>
       <c r="T160" s="49"/>
       <c r="U160" s="49"/>
@@ -31655,7 +31650,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.7181749396833554E-2</v>
+        <v>2.9411565365506154E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31696,7 +31691,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>4.1971818921581229E-3</v>
+        <v>4.5611095597133016E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31737,7 +31732,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>3.29495464136527E-3</v>
+        <v>3.6265581271631721E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31778,7 +31773,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>7.2043249562575191E-3</v>
+        <v>7.929366581512165E-3</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31799,15 +31794,15 @@
       </c>
       <c r="O164" s="152">
         <f t="shared" si="209"/>
-        <v>0.1123904232821475</v>
+        <v>4.834403211509157E-2</v>
       </c>
       <c r="P164" s="152">
         <f t="shared" si="209"/>
-        <v>9.4100951040925501E-2</v>
+        <v>9.0705448547629769E-2</v>
       </c>
       <c r="Q164" s="152">
         <f t="shared" si="209"/>
-        <v>0.25261177056215006</v>
+        <v>0.23972473310865286</v>
       </c>
       <c r="T164" s="49"/>
       <c r="U164" s="49"/>
@@ -31819,7 +31814,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="152">
         <f>AC156/AC5</f>
-        <v>0.29899717376555007</v>
+        <v>0.28516700048407978</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32024,7 +32019,7 @@
       <c r="AA169" s="49"/>
       <c r="AC169" s="152">
         <f>AC79/AC77</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.5470085470085479E-3</v>
       </c>
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
@@ -32085,11 +32080,11 @@
       </c>
       <c r="AA170" s="72">
         <f t="shared" si="217"/>
-        <v>5.5418502202643172</v>
+        <v>5.4695652173913043</v>
       </c>
       <c r="AC170" s="72">
         <f>AC105/AC74</f>
-        <v>5.5418502202643172</v>
+        <v>5.4695652173913043</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -32280,11 +32275,11 @@
       </c>
       <c r="AA173" s="72">
         <f t="shared" si="226"/>
-        <v>-4.8149779735682818</v>
+        <v>-4.7521739130434781</v>
       </c>
       <c r="AC173" s="72">
         <f>(AC105-AC106)/AC74</f>
-        <v>-4.8149779735682818</v>
+        <v>-4.7521739130434781</v>
       </c>
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
@@ -32325,7 +32320,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>-6.5838855996567455E-3</v>
+        <v>-7.2464863491578562E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33244,19 +33239,19 @@
       </c>
       <c r="N201" s="141">
         <f>100*(1+((N25-$M25)/ABS($M25)))</f>
-        <v>-34.782608695652172</v>
+        <v>-47.193341734929618</v>
       </c>
       <c r="O201" s="141">
         <f>100*(1+((O25-$M25)/ABS($M25)))</f>
-        <v>21.467391304347828</v>
+        <v>-0.64089417555373007</v>
       </c>
       <c r="P201" s="141">
         <f>100*(1+((P25-$M25)/ABS($M25)))</f>
-        <v>91.983695652173907</v>
+        <v>90.788419154478063</v>
       </c>
       <c r="Q201" s="141">
         <f>100*(1+((Q25-$M25)/ABS($M25)))</f>
-        <v>188.85869565217394</v>
+        <v>180.60565786975508</v>
       </c>
       <c r="T201" s="49"/>
       <c r="U201" s="49"/>
@@ -33684,15 +33679,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="254" t="s">
+      <c r="B4" s="252" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="254"/>
-      <c r="E4" s="254" t="s">
+      <c r="C4" s="252"/>
+      <c r="E4" s="252" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33700,7 +33695,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33716,7 +33711,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>166011.39000000001</v>
+        <v>150831.72</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33736,14 +33731,14 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>167104.39000000001</v>
+        <v>151924.72</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="174">
         <f>IF(OR(Statement!M17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(4, Statement!M17, Statement!Q17))</f>
-        <v>0.17879449999109109</v>
+        <v>0.16561733633857845</v>
       </c>
       <c r="G7" s="174" t="str">
         <f>IF(OR(Statement!H17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(9, Statement!H17, Statement!Q17))</f>
@@ -33756,14 +33751,14 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>36.789390756302524</v>
+        <v>34.000230439036699</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
       </c>
       <c r="F8" s="174">
         <f>IF(OR(Statement!M25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(4, Statement!M25, Statement!Q25))</f>
-        <v>0.17228780316506631</v>
+        <v>0.15926530380333648</v>
       </c>
       <c r="G8" s="174" t="str">
         <f>IF(OR(Statement!H25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(9, Statement!H25, Statement!Q25))</f>
@@ -33776,7 +33771,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.688036633089355</v>
+        <v>10.755456554822814</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33796,7 +33791,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>46.048853171155521</v>
+        <v>42.934665508253694</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33816,7 +33811,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.10989129647076</v>
+        <v>11.009835495325749</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33825,18 +33820,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>30.582794655929725</v>
+        <v>27.804670571010249</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="254" t="s">
+      <c r="B15" s="252" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="254"/>
-      <c r="E15" s="254" t="s">
+      <c r="C15" s="252"/>
+      <c r="E15" s="252" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="254"/>
+      <c r="F15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33851,7 +33846,7 @@
       </c>
       <c r="F16" s="169">
         <f>Statement!AC17</f>
-        <v>4396</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -33876,25 +33871,25 @@
       </c>
       <c r="C18" s="171">
         <f>Statement!AC101</f>
-        <v>0.31857380969635479</v>
+        <v>0.31719689832596565</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>253</v>
       </c>
       <c r="F18" s="173">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
-        <v>-436</v>
+        <v>-455</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="254" t="s">
+      <c r="B21" s="252" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="254"/>
-      <c r="E21" s="254" t="s">
+      <c r="C21" s="252"/>
+      <c r="E21" s="252" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="254"/>
+      <c r="F21" s="252"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33902,14 +33897,14 @@
       </c>
       <c r="C22" s="171">
         <f>Statement!AC119</f>
-        <v>0.31857380969635479</v>
+        <v>0.31719689832596565</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>101</v>
       </c>
       <c r="F22" s="171">
         <f>C24</f>
-        <v>0.42572147975982955</v>
+        <v>0.42388146426496226</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
@@ -33925,7 +33920,7 @@
       </c>
       <c r="F23" s="171">
         <f>C26</f>
-        <v>1.2730958586736172</v>
+        <v>1.2675933970460469</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
@@ -33934,14 +33929,14 @@
       </c>
       <c r="C24" s="172">
         <f>Statement!AC121</f>
-        <v>0.42572147975982955</v>
+        <v>0.42388146426496226</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>104</v>
       </c>
       <c r="F24" s="171">
         <f>Statement!AC138</f>
-        <v>1.0446242852597505</v>
+        <v>1.0026439594544252</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
@@ -33959,18 +33954,18 @@
       </c>
       <c r="C26" s="172">
         <f>Statement!AC123</f>
-        <v>1.2730958586736172</v>
+        <v>1.2675933970460469</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="254" t="s">
+      <c r="B29" s="252" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="254"/>
-      <c r="E29" s="254" t="s">
+      <c r="C29" s="252"/>
+      <c r="E29" s="252" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="254"/>
+      <c r="F29" s="252"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34046,14 +34041,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="252" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="254"/>
-      <c r="E37" s="254" t="s">
+      <c r="C37" s="252"/>
+      <c r="E37" s="252" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="254"/>
+      <c r="F37" s="252"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34061,7 +34056,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.7181749396833554E-2</v>
+        <v>2.9411565365506154E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34077,7 +34072,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.3691145529231458E-2</v>
+        <v>2.6075417027665002E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34093,7 +34088,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.1971818921581229E-3</v>
+        <v>4.5611095597133016E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34109,7 +34104,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>3.29495464136527E-3</v>
+        <v>3.6265581271631721E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34118,18 +34113,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>7.2043249562575191E-3</v>
+        <v>7.929366581512165E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="254" t="s">
+      <c r="B45" s="252" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="254"/>
-      <c r="E45" s="254" t="s">
+      <c r="C45" s="252"/>
+      <c r="E45" s="252" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="254"/>
+      <c r="F45" s="252"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34137,14 +34132,14 @@
       </c>
       <c r="C46" s="171">
         <f>Statement!AC169</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.5470085470085479E-3</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>277</v>
       </c>
       <c r="F46" s="170">
         <f>Statement!AC170</f>
-        <v>5.5418502202643172</v>
+        <v>5.4695652173913043</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
@@ -34153,7 +34148,7 @@
       </c>
       <c r="F47" s="170">
         <f>Statement!AC173</f>
-        <v>-4.8149779735682818</v>
+        <v>-4.7521739130434781</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
@@ -34162,18 +34157,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>-6.5838855996567455E-3</v>
+        <v>-7.2464863491578562E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="254" t="s">
+      <c r="B51" s="252" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="254"/>
-      <c r="E51" s="254" t="s">
+      <c r="C51" s="252"/>
+      <c r="E51" s="252" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="254"/>
+      <c r="F51" s="252"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34217,10 +34212,10 @@
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="254" t="s">
+      <c r="B57" s="252" t="s">
         <v>439</v>
       </c>
-      <c r="C57" s="254"/>
+      <c r="C57" s="252"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
@@ -34228,7 +34223,7 @@
       </c>
       <c r="C58" s="170">
         <f ca="1">Statement!AC157</f>
-        <v>42.20986270022884</v>
+        <v>38.350297482837526</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.2">
@@ -34237,7 +34232,7 @@
       </c>
       <c r="C59" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>40.501691517547179</v>
+        <v>38.608378517276584</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
@@ -34246,7 +34241,7 @@
       </c>
       <c r="C60" s="171">
         <f>Statement!AC164</f>
-        <v>0.29899717376555007</v>
+        <v>0.28516700048407978</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.2">
@@ -34385,7 +34380,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>700.47</v>
+        <v>644.58000000000004</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34414,7 +34409,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>166011.39000000001</v>
+        <v>150831.72</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34443,7 +34438,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>167104.39000000001</v>
+        <v>151924.72</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34456,23 +34451,23 @@
       </c>
       <c r="D9" s="170">
         <f>Statement!N148</f>
-        <v>-24.16796875</v>
+        <v>-17.812364394993047</v>
       </c>
       <c r="E9" s="170">
         <f>Statement!O148</f>
-        <v>65.360759493670884</v>
+        <v>-2189.3239999999996</v>
       </c>
       <c r="F9" s="170">
         <f>Statement!P148</f>
-        <v>20.892171344165437</v>
+        <v>21.167227586206895</v>
       </c>
       <c r="G9" s="170">
         <f>Statement!Q148</f>
-        <v>59.004316546762588</v>
+        <v>61.700604467805512</v>
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>36.789390756302524</v>
+        <v>34.000230439036699</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34501,7 +34496,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.688036633089355</v>
+        <v>10.755456554822814</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34530,7 +34525,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>46.048853171155521</v>
+        <v>42.934665508253694</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34559,7 +34554,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.10989129647076</v>
+        <v>11.009835495325749</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34588,7 +34583,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>30.582794655929725</v>
+        <v>27.804670571010249</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34670,23 +34665,23 @@
       </c>
       <c r="D18" s="171">
         <f>Statement!N101</f>
-        <v>-7.164138678223185E-2</v>
+        <v>-9.73726977248104E-2</v>
       </c>
       <c r="E18" s="171">
         <f>Statement!O101</f>
-        <v>5.1137230957105782E-2</v>
+        <v>-1.5264845061822622E-3</v>
       </c>
       <c r="F18" s="171">
         <f>Statement!P101</f>
-        <v>0.16148180718918326</v>
+        <v>0.15939320655161043</v>
       </c>
       <c r="G18" s="171">
         <f>Statement!Q101</f>
-        <v>0.26109061090610908</v>
+        <v>0.24961049610496105</v>
       </c>
       <c r="I18" s="171">
         <f>Statement!AC101</f>
-        <v>0.31857380969635479</v>
+        <v>0.31719689832596565</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34710,23 +34705,23 @@
       </c>
       <c r="D21" s="173">
         <f>Statement!N17</f>
-        <v>-529</v>
+        <v>-719</v>
       </c>
       <c r="E21" s="173">
         <f>Statement!O17</f>
-        <v>335</v>
+        <v>-10</v>
       </c>
       <c r="F21" s="173">
         <f>Statement!P17</f>
-        <v>1469</v>
+        <v>1450</v>
       </c>
       <c r="G21" s="173">
         <f>Statement!Q17</f>
-        <v>3184</v>
+        <v>3044</v>
       </c>
       <c r="I21" s="173">
         <f>Statement!AC17</f>
-        <v>4396</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -34770,21 +34765,21 @@
         <f t="shared" ref="D23:I23" si="0">IF(OR(D21&lt;=0, D22&lt;=0),"N/A",D21-D22)</f>
         <v>N/A</v>
       </c>
-      <c r="E23" s="191">
+      <c r="E23" s="191" t="str">
         <f t="shared" si="0"/>
-        <v>-583</v>
+        <v>N/A</v>
       </c>
       <c r="F23" s="191">
         <f t="shared" si="0"/>
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="G23" s="191">
         <f t="shared" si="0"/>
-        <v>-490</v>
+        <v>-630</v>
       </c>
       <c r="I23" s="191">
         <f t="shared" si="0"/>
-        <v>-436</v>
+        <v>-455</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34808,23 +34803,23 @@
       </c>
       <c r="D26" s="171">
         <f>Statement!N119</f>
-        <v>-7.164138678223185E-2</v>
+        <v>-9.73726977248104E-2</v>
       </c>
       <c r="E26" s="171">
         <f>Statement!O119</f>
-        <v>5.1137230957105782E-2</v>
+        <v>-1.5264845061822622E-3</v>
       </c>
       <c r="F26" s="171">
         <f>Statement!P119</f>
-        <v>0.16148180718918326</v>
+        <v>0.15939320655161043</v>
       </c>
       <c r="G26" s="171">
         <f>Statement!Q119</f>
-        <v>0.26109061090610908</v>
+        <v>0.24961049610496105</v>
       </c>
       <c r="I26" s="171">
         <f>Statement!AC119</f>
-        <v>0.31857380969635479</v>
+        <v>0.31719689832596565</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -34866,23 +34861,23 @@
       </c>
       <c r="D28" s="172">
         <f>Statement!N121</f>
-        <v>-7.0010587612493388E-2</v>
+        <v>-9.5156167284277393E-2</v>
       </c>
       <c r="E28" s="172">
         <f>Statement!O121</f>
-        <v>4.3287246414265401E-2</v>
+        <v>-1.2921566093810569E-3</v>
       </c>
       <c r="F28" s="172">
         <f>Statement!P121</f>
-        <v>0.18309859154929578</v>
+        <v>0.18073040009971333</v>
       </c>
       <c r="G28" s="172">
         <f>Statement!Q121</f>
-        <v>0.31929402326514245</v>
+        <v>0.30525471319695147</v>
       </c>
       <c r="I28" s="172">
         <f>Statement!AC121</f>
-        <v>0.42572147975982955</v>
+        <v>0.42388146426496226</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -34924,23 +34919,23 @@
       </c>
       <c r="D30" s="172">
         <f>Statement!N123</f>
-        <v>0.44120100083402836</v>
+        <v>0.59966638865721433</v>
       </c>
       <c r="E30" s="172">
         <f>Statement!O123</f>
-        <v>-0.22468142186452042</v>
+        <v>6.7069081153588199E-3</v>
       </c>
       <c r="F30" s="172">
         <f>Statement!P123</f>
-        <v>-3.2428256070640176</v>
+        <v>-3.2008830022075054</v>
       </c>
       <c r="G30" s="172">
         <f>Statement!Q123</f>
-        <v>1.4693124134748501</v>
+        <v>1.4047069681587447</v>
       </c>
       <c r="I30" s="172">
         <f>Statement!AC123</f>
-        <v>1.2730958586736172</v>
+        <v>1.2675933970460469</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34964,23 +34959,23 @@
       </c>
       <c r="D33" s="171">
         <f t="shared" ref="D33:G33" si="1">D28</f>
-        <v>-7.0010587612493388E-2</v>
+        <v>-9.5156167284277393E-2</v>
       </c>
       <c r="E33" s="171">
         <f t="shared" si="1"/>
-        <v>4.3287246414265401E-2</v>
+        <v>-1.2921566093810569E-3</v>
       </c>
       <c r="F33" s="171">
         <f t="shared" si="1"/>
-        <v>0.18309859154929578</v>
+        <v>0.18073040009971333</v>
       </c>
       <c r="G33" s="171">
         <f t="shared" si="1"/>
-        <v>0.31929402326514245</v>
+        <v>0.30525471319695147</v>
       </c>
       <c r="I33" s="171">
         <f>I28</f>
-        <v>0.42572147975982955</v>
+        <v>0.42388146426496226</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
@@ -34993,23 +34988,23 @@
       </c>
       <c r="D34" s="171">
         <f t="shared" ref="D34:G34" si="2">D30</f>
-        <v>0.44120100083402836</v>
+        <v>0.59966638865721433</v>
       </c>
       <c r="E34" s="171">
         <f t="shared" si="2"/>
-        <v>-0.22468142186452042</v>
+        <v>6.7069081153588199E-3</v>
       </c>
       <c r="F34" s="171">
         <f t="shared" si="2"/>
-        <v>-3.2428256070640176</v>
+        <v>-3.2008830022075054</v>
       </c>
       <c r="G34" s="171">
         <f t="shared" si="2"/>
-        <v>1.4693124134748501</v>
+        <v>1.4047069681587447</v>
       </c>
       <c r="I34" s="171">
         <f>I30</f>
-        <v>1.2730958586736172</v>
+        <v>1.2675933970460469</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
@@ -35026,19 +35021,19 @@
       </c>
       <c r="E35" s="171">
         <f>Statement!O138</f>
-        <v>0.12044943820224721</v>
+        <v>-2.8070175438596509E-2</v>
       </c>
       <c r="F35" s="171">
         <f>Statement!P138</f>
-        <v>0.5026119834618733</v>
+        <v>0.49415159283423393</v>
       </c>
       <c r="G35" s="171">
         <f>Statement!Q138</f>
-        <v>0.87701105809469215</v>
+        <v>0.83799481635055162</v>
       </c>
       <c r="I35" s="171">
         <f>Statement!AC138</f>
-        <v>1.0446242852597505</v>
+        <v>1.0026439594544252</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35345,23 +35340,23 @@
       </c>
       <c r="D51" s="171">
         <f>Statement!N160</f>
-        <v>-4.1377080976240509E-2</v>
+        <v>-5.6140778272035258E-2</v>
       </c>
       <c r="E51" s="171">
         <f>Statement!O160</f>
-        <v>1.529969981601627E-2</v>
+        <v>-4.5676199594029944E-4</v>
       </c>
       <c r="F51" s="171">
         <f>Statement!P160</f>
-        <v>4.7864819004524883E-2</v>
+        <v>4.7242842546447859E-2</v>
       </c>
       <c r="G51" s="171">
         <f>Statement!Q160</f>
-        <v>1.6947912602419041E-2</v>
+        <v>1.6207296648475877E-2</v>
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.7181749396833554E-2</v>
+        <v>2.9411565365506154E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35390,7 +35385,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.3691145529231458E-2</v>
+        <v>2.6075417027665002E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35419,7 +35414,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>4.1971818921581229E-3</v>
+        <v>4.5611095597133016E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35448,7 +35443,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>3.29495464136527E-3</v>
+        <v>3.6265581271631721E-3</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35477,7 +35472,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>7.2043249562575191E-3</v>
+        <v>7.929366581512165E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35615,7 +35610,7 @@
       </c>
       <c r="I63" s="171">
         <f>Statement!AC169</f>
-        <v>8.4388185654008432E-3</v>
+        <v>8.5470085470085479E-3</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35655,7 +35650,7 @@
       </c>
       <c r="I66" s="170">
         <f>Statement!AC170</f>
-        <v>5.5418502202643172</v>
+        <v>5.4695652173913043</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
@@ -35684,7 +35679,7 @@
       </c>
       <c r="I67" s="170">
         <f>Statement!AC173</f>
-        <v>-4.8149779735682818</v>
+        <v>-4.7521739130434781</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
@@ -35713,7 +35708,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>-6.5838855996567455E-3</v>
+        <v>-7.2464863491578562E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36034,19 +36029,19 @@
       </c>
       <c r="D85" s="171">
         <f>Statement!N96</f>
-        <v>-1.3208004851425106</v>
+        <v>-1.4360218314129776</v>
       </c>
       <c r="E85" s="171">
         <f>Statement!O96</f>
-        <v>1.6332703213610587</v>
+        <v>0.98609179415855353</v>
       </c>
       <c r="F85" s="171">
         <f>Statement!P96</f>
-        <v>3.3850746268656717</v>
+        <v>146</v>
       </c>
       <c r="G85" s="171">
         <f>Statement!Q96</f>
-        <v>1.1674608577263446</v>
+        <v>1.0993103448275863</v>
       </c>
       <c r="I85" s="193"/>
     </row>
@@ -36087,7 +36082,7 @@
       </c>
       <c r="I88" s="170">
         <f ca="1">Statement!AC157</f>
-        <v>42.20986270022884</v>
+        <v>38.350297482837526</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
@@ -36104,19 +36099,19 @@
       </c>
       <c r="E89" s="170">
         <f>Statement!O158</f>
-        <v>35.737599041631057</v>
+        <v>83.082930977177043</v>
       </c>
       <c r="F89" s="170">
         <f>Statement!P158</f>
-        <v>40.813593878239608</v>
+        <v>42.341425579564046</v>
       </c>
       <c r="G89" s="170">
         <f>Statement!Q158</f>
-        <v>63.70151446907547</v>
+        <v>67.125957963753976</v>
       </c>
       <c r="I89" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>40.501691517547179</v>
+        <v>38.608378517276584</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
@@ -36133,19 +36128,19 @@
       </c>
       <c r="E90" s="171">
         <f>Statement!O164</f>
-        <v>0.1123904232821475</v>
+        <v>4.834403211509157E-2</v>
       </c>
       <c r="F90" s="171">
         <f>Statement!P164</f>
-        <v>9.4100951040925501E-2</v>
+        <v>9.0705448547629769E-2</v>
       </c>
       <c r="G90" s="171">
         <f>Statement!Q164</f>
-        <v>0.25261177056215006</v>
+        <v>0.23972473310865286</v>
       </c>
       <c r="I90" s="171">
         <f>Statement!AC164</f>
-        <v>0.29899717376555007</v>
+        <v>0.28516700048407978</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
@@ -36303,14 +36298,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="253" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="F3" s="259" t="s">
+      <c r="D3" s="254"/>
+      <c r="F3" s="255" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="258"/>
+      <c r="G3" s="254"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36377,19 +36372,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="255">
+      <c r="C7" s="256">
         <f>Statement!AA88</f>
         <v>0.16643703499586662</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="F7" s="255">
+      <c r="D7" s="257"/>
+      <c r="F7" s="256">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.61011791555724615</v>
       </c>
-      <c r="G7" s="256"/>
+      <c r="G7" s="257"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36416,19 +36411,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="256">
         <f>Statement!AA89</f>
         <v>4.3327556325823226E-2</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="F9" s="255">
+      <c r="D9" s="257"/>
+      <c r="F9" s="256">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13442211055276382</v>
       </c>
-      <c r="G9" s="256"/>
+      <c r="G9" s="257"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36455,19 +36450,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="255">
+      <c r="C11" s="256">
         <f>Statement!AA90</f>
         <v>0.27871443624868281</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="F11" s="255">
+      <c r="D11" s="257"/>
+      <c r="F11" s="256">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.3404050144648023</v>
       </c>
-      <c r="G11" s="256"/>
+      <c r="G11" s="257"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36494,19 +36489,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="256">
         <f>Statement!AA93</f>
         <v>7.0796460176991149E-2</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="F13" s="255">
+      <c r="D13" s="257"/>
+      <c r="F13" s="256">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>5.8309037900874633E-2</v>
       </c>
-      <c r="G13" s="256"/>
+      <c r="G13" s="257"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36533,19 +36528,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="255">
+      <c r="C15" s="256">
         <f>Statement!AA94</f>
         <v>0.32392559332905707</v>
       </c>
-      <c r="D15" s="256"/>
-      <c r="F15" s="255">
+      <c r="D15" s="257"/>
+      <c r="F15" s="256">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.9740634005763689</v>
       </c>
-      <c r="G15" s="256"/>
+      <c r="G15" s="257"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36553,11 +36548,11 @@
       </c>
       <c r="C16" s="196">
         <f>Statement!Z17</f>
-        <v>1294</v>
+        <v>1273</v>
       </c>
       <c r="D16" s="194">
         <f>Statement!AA17</f>
-        <v>1761</v>
+        <v>1698</v>
       </c>
       <c r="F16" s="196">
         <f>Statement!W17</f>
@@ -36565,26 +36560,26 @@
       </c>
       <c r="G16" s="194">
         <f>Statement!AA17</f>
-        <v>1761</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="255">
+      <c r="C17" s="256">
         <f>Statement!AA96</f>
-        <v>0.36089644513137559</v>
-      </c>
-      <c r="D17" s="256"/>
-      <c r="F17" s="255">
+        <v>0.33385703063629224</v>
+      </c>
+      <c r="D17" s="257"/>
+      <c r="F17" s="256">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
-        <v>2.2076502732240435</v>
-      </c>
-      <c r="G17" s="256"/>
+        <v>2.0928961748633879</v>
+      </c>
+      <c r="G17" s="257"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36611,22 +36606,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="255">
+      <c r="C19" s="256">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>0</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="F19" s="255">
+      <c r="D19" s="257"/>
+      <c r="F19" s="256">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.6548672566371681E-2</v>
       </c>
-      <c r="G19" s="256"/>
+      <c r="G19" s="257"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36634,11 +36629,11 @@
       </c>
       <c r="C20" s="197">
         <f>Statement!Z25</f>
-        <v>5.58</v>
+        <v>5.4870689655172411</v>
       </c>
       <c r="D20" s="198">
         <f>Statement!AA25</f>
-        <v>7.59</v>
+        <v>7.318965517241379</v>
       </c>
       <c r="F20" s="197">
         <f>Statement!W25</f>
@@ -36646,29 +36641,29 @@
       </c>
       <c r="G20" s="198">
         <f>Statement!AA25</f>
-        <v>7.59</v>
+        <v>7.318965517241379</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="255">
+      <c r="C21" s="256">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
-        <v>0.36021505376344082</v>
-      </c>
-      <c r="D21" s="256"/>
-      <c r="F21" s="255">
+        <v>0.33385703063629224</v>
+      </c>
+      <c r="D21" s="257"/>
+      <c r="F21" s="256">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
-        <v>2.1234567901234569</v>
-      </c>
-      <c r="G21" s="256"/>
+        <v>2.0119199659429543</v>
+      </c>
+      <c r="G21" s="257"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36717,22 +36712,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="255">
+      <c r="C25" s="256">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.17592908285032391</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="F25" s="255">
+      <c r="D25" s="257"/>
+      <c r="F25" s="256">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.63150425733207194</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="257"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36760,37 +36755,25 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="255">
+      <c r="C27" s="256">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.12482065997130559</v>
       </c>
-      <c r="D27" s="256"/>
-      <c r="F27" s="255">
+      <c r="D27" s="257"/>
+      <c r="F27" s="256">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.52233009708737865</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
@@ -36801,6 +36784,18 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -37026,19 +37021,19 @@
       </c>
       <c r="I59" s="64">
         <f>Statement!N17</f>
-        <v>-529</v>
+        <v>-719</v>
       </c>
       <c r="J59" s="64">
         <f>Statement!O17</f>
-        <v>335</v>
+        <v>-10</v>
       </c>
       <c r="K59" s="64">
         <f>Statement!P17</f>
-        <v>1469</v>
+        <v>1450</v>
       </c>
       <c r="L59" s="64">
         <f>Statement!Q17</f>
-        <v>3184</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
@@ -37120,15 +37115,15 @@
       </c>
       <c r="J61" s="64">
         <f>Statement!O156</f>
-        <v>736.2696629213483</v>
+        <v>316.70175438596488</v>
       </c>
       <c r="K61" s="64">
         <f>Statement!P156</f>
-        <v>856.03635161929924</v>
+        <v>825.14746543778801</v>
       </c>
       <c r="L61" s="64">
         <f>Statement!Q156</f>
-        <v>3080.6005420054198</v>
+        <v>2923.4431202600217</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.2">
@@ -37251,19 +37246,19 @@
       </c>
       <c r="I64" s="58">
         <f>Statement!N101</f>
-        <v>-7.164138678223185E-2</v>
+        <v>-9.73726977248104E-2</v>
       </c>
       <c r="J64" s="58">
         <f>Statement!O101</f>
-        <v>5.1137230957105782E-2</v>
+        <v>-1.5264845061822622E-3</v>
       </c>
       <c r="K64" s="58">
         <f>Statement!P101</f>
-        <v>0.16148180718918326</v>
+        <v>0.15939320655161043</v>
       </c>
       <c r="L64" s="58">
         <f>Statement!Q101</f>
-        <v>0.26109061090610908</v>
+        <v>0.24961049610496105</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
@@ -37388,19 +37383,19 @@
       </c>
       <c r="I67" s="214">
         <f>Statement!N121</f>
-        <v>-7.0010587612493388E-2</v>
+        <v>-9.5156167284277393E-2</v>
       </c>
       <c r="J67" s="214">
         <f>Statement!O121</f>
-        <v>4.3287246414265401E-2</v>
+        <v>-1.2921566093810569E-3</v>
       </c>
       <c r="K67" s="214">
         <f>Statement!P121</f>
-        <v>0.18309859154929578</v>
+        <v>0.18073040009971333</v>
       </c>
       <c r="L67" s="214">
         <f>Statement!Q121</f>
-        <v>0.31929402326514245</v>
+        <v>0.30525471319695147</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.2">
@@ -37433,19 +37428,19 @@
       </c>
       <c r="I68" s="214">
         <f>Statement!N123</f>
-        <v>0.44120100083402836</v>
+        <v>0.59966638865721433</v>
       </c>
       <c r="J68" s="214">
         <f>Statement!O123</f>
-        <v>-0.22468142186452042</v>
+        <v>6.7069081153588199E-3</v>
       </c>
       <c r="K68" s="214">
         <f>Statement!P123</f>
-        <v>-3.2428256070640176</v>
+        <v>-3.2008830022075054</v>
       </c>
       <c r="L68" s="214">
         <f>Statement!Q123</f>
-        <v>1.4693124134748501</v>
+        <v>1.4047069681587447</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
@@ -37482,15 +37477,15 @@
       </c>
       <c r="J69" s="214">
         <f>Statement!O138</f>
-        <v>0.12044943820224721</v>
+        <v>-2.8070175438596509E-2</v>
       </c>
       <c r="K69" s="214">
         <f>Statement!P138</f>
-        <v>0.5026119834618733</v>
+        <v>0.49415159283423393</v>
       </c>
       <c r="L69" s="214">
         <f>Statement!Q138</f>
-        <v>0.87701105809469215</v>
+        <v>0.83799481635055162</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
@@ -37613,19 +37608,19 @@
       </c>
       <c r="I72" s="223">
         <f>Statement!N201</f>
-        <v>-34.782608695652172</v>
+        <v>-47.193341734929618</v>
       </c>
       <c r="J72" s="223">
         <f>Statement!O201</f>
-        <v>21.467391304347828</v>
+        <v>-0.64089417555373007</v>
       </c>
       <c r="K72" s="223">
         <f>Statement!P201</f>
-        <v>91.983695652173907</v>
+        <v>90.788419154478063</v>
       </c>
       <c r="L72" s="223">
         <f>Statement!Q201</f>
-        <v>188.85869565217394</v>
+        <v>180.60565786975508</v>
       </c>
     </row>
   </sheetData>
@@ -37799,11 +37794,11 @@
       </c>
       <c r="D59" s="64">
         <f>Statement!U17</f>
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E59" s="64">
         <f>Statement!V17</f>
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F59" s="64">
         <f>Statement!W17</f>
@@ -37811,19 +37806,19 @@
       </c>
       <c r="G59" s="64">
         <f>Statement!X17</f>
-        <v>593</v>
+        <v>644</v>
       </c>
       <c r="H59" s="64">
         <f>Statement!Y17</f>
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="I59" s="64">
         <f>Statement!Z17</f>
-        <v>1294</v>
+        <v>1273</v>
       </c>
       <c r="J59" s="64">
         <f>Statement!AA17</f>
-        <v>1761</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.2">
@@ -37910,11 +37905,11 @@
       </c>
       <c r="D62" s="58">
         <f>Statement!U101</f>
-        <v>0.15740740740740741</v>
+        <v>0.15694444444444444</v>
       </c>
       <c r="E62" s="58">
         <f>Statement!V101</f>
-        <v>0.19967266775777415</v>
+        <v>0.19803600654664485</v>
       </c>
       <c r="F62" s="58">
         <f>Statement!W101</f>
@@ -37922,19 +37917,19 @@
       </c>
       <c r="G62" s="58">
         <f>Statement!X101</f>
-        <v>0.20991150442477877</v>
+        <v>0.22796460176991151</v>
       </c>
       <c r="H62" s="58">
         <f>Statement!Y101</f>
-        <v>0.24035989717223649</v>
+        <v>0.24485861182519281</v>
       </c>
       <c r="I62" s="58">
         <f>Statement!Z101</f>
-        <v>0.35657205841829703</v>
+        <v>0.35078534031413611</v>
       </c>
       <c r="J62" s="58">
         <f>Statement!AA101</f>
-        <v>0.41601700921332391</v>
+        <v>0.4011339475549256</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
